--- a/resources/templates/ImportTemplate.xlsx
+++ b/resources/templates/ImportTemplate.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workdir\DeerHide\sources\jira-toolkit\rsc\templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jules/Workdir/sources/jira-toolkit/resources/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9471506-A60E-4104-83CF-1148AC344A3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8715B6CB-C258-0246-816F-293FA3525AAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13152" yWindow="6060" windowWidth="17568" windowHeight="12420" xr2:uid="{1FA076D1-0294-4A97-AB8C-3ADE2BC9CEA1}"/>
+    <workbookView xWindow="16820" yWindow="10420" windowWidth="17560" windowHeight="12420" xr2:uid="{1FA076D1-0294-4A97-AB8C-3ADE2BC9CEA1}"/>
   </bookViews>
   <sheets>
     <sheet name="Dataset" sheetId="1" r:id="rId1"/>
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="111">
   <si>
     <t>IssueType</t>
   </si>
@@ -245,9 +245,6 @@
     <t>Creation Marker</t>
   </si>
   <si>
-    <t>JV</t>
-  </si>
-  <si>
     <t>Issue Type</t>
   </si>
   <si>
@@ -399,6 +396,12 @@
   </si>
   <si>
     <t>pod_test</t>
+  </si>
+  <si>
+    <t>tst</t>
+  </si>
+  <si>
+    <t>a</t>
   </si>
 </sst>
 </file>
@@ -922,7 +925,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -953,6 +956,15 @@
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="16" applyAlignment="1">
       <alignment horizontal="left" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -999,7 +1011,291 @@
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="56">
+  <dxfs count="88">
+    <dxf>
+      <fill>
+        <patternFill patternType="darkUp"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor auto="1"/>
+          <bgColor rgb="FFFF5050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDAF2D0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF2CEEF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor auto="1"/>
+          <bgColor rgb="FFFF5050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.89996032593768116"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.34998626667073579"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor auto="1"/>
+          <bgColor rgb="FFF9B1AB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFCC99"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF99CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF6699"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="darkUp"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor auto="1"/>
+          <bgColor rgb="FFFF5050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDAF2D0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF2CEEF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor auto="1"/>
+          <bgColor rgb="FFFF5050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.89996032593768116"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.34998626667073579"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor auto="1"/>
+          <bgColor rgb="FFF9B1AB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFCC99"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF99CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF6699"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="darkUp"/>
@@ -1320,63 +1616,63 @@
 <file path=xl/namedSheetViews/namedSheetView1.xml><?xml version="1.0" encoding="utf-8"?>
 <namedSheetViews xmlns="http://schemas.microsoft.com/office/spreadsheetml/2019/namedsheetviews" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <namedSheetView name="View1" id="{77233F75-225A-4D7F-8A86-543E0A8C6E58}">
-    <nsvFilter filterId="{933FCFD5-1AB1-4076-B5DD-E2B69F5EB3F2}" ref="A1:AJ3" tableId="1"/>
+    <nsvFilter filterId="{933FCFD5-1AB1-4076-B5DD-E2B69F5EB3F2}" ref="A1:AJ5" tableId="1"/>
   </namedSheetView>
 </namedSheetViews>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{933FCFD5-1AB1-4076-B5DD-E2B69F5EB3F2}" name="JiraDataset" displayName="JiraDataset" ref="A1:AJ3" totalsRowShown="0" headerRowDxfId="55" dataDxfId="54">
-  <autoFilter ref="A1:AJ3" xr:uid="{933FCFD5-1AB1-4076-B5DD-E2B69F5EB3F2}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{933FCFD5-1AB1-4076-B5DD-E2B69F5EB3F2}" name="JiraDataset" displayName="JiraDataset" ref="A1:AJ5" totalsRowShown="0" headerRowDxfId="87" dataDxfId="86">
+  <autoFilter ref="A1:AJ5" xr:uid="{933FCFD5-1AB1-4076-B5DD-E2B69F5EB3F2}"/>
   <tableColumns count="36">
-    <tableColumn id="3" xr3:uid="{AF2EC907-349C-4651-852D-6E39C61E17FF}" name="Priority" dataDxfId="53"/>
-    <tableColumn id="2" xr3:uid="{E90C51F2-4386-421F-A3E4-E2CA9D43D396}" name="IssueType" dataDxfId="52"/>
-    <tableColumn id="1" xr3:uid="{BBAD373B-BA13-47E4-9F74-565F4D9E9680}" name="Summary" dataDxfId="51"/>
-    <tableColumn id="4" xr3:uid="{026E5B97-FAFC-4E46-860E-0B0C976B1148}" name="Issue Key" dataDxfId="50"/>
-    <tableColumn id="5" xr3:uid="{A2C262E8-D544-4669-99F1-151EDE081654}" name="Description" dataDxfId="49"/>
-    <tableColumn id="7" xr3:uid="{0FAD1ACC-432E-462C-8B89-71540710BCB5}" name="FixVersion" dataDxfId="48">
+    <tableColumn id="3" xr3:uid="{AF2EC907-349C-4651-852D-6E39C61E17FF}" name="Priority" dataDxfId="85"/>
+    <tableColumn id="2" xr3:uid="{E90C51F2-4386-421F-A3E4-E2CA9D43D396}" name="IssueType" dataDxfId="84"/>
+    <tableColumn id="1" xr3:uid="{BBAD373B-BA13-47E4-9F74-565F4D9E9680}" name="Summary" dataDxfId="83"/>
+    <tableColumn id="4" xr3:uid="{026E5B97-FAFC-4E46-860E-0B0C976B1148}" name="Issue Key" dataDxfId="82"/>
+    <tableColumn id="5" xr3:uid="{A2C262E8-D544-4669-99F1-151EDE081654}" name="Description" dataDxfId="81"/>
+    <tableColumn id="7" xr3:uid="{0FAD1ACC-432E-462C-8B89-71540710BCB5}" name="FixVersion" dataDxfId="80">
       <calculatedColumnFormula>Config!$G$4</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="28" xr3:uid="{07F3030C-7187-4B16-BBDB-798304851975}" name="Assignee.Name" dataDxfId="47"/>
-    <tableColumn id="8" xr3:uid="{8C7FB8DB-A85B-4189-93D8-0F0D4EEEF81B}" name="Component" dataDxfId="46"/>
-    <tableColumn id="9" xr3:uid="{DC5101A8-1204-44D2-BC2C-FEE1A4EFE7C1}" name="Sprint Name" dataDxfId="45"/>
-    <tableColumn id="40" xr3:uid="{1F406792-7ED2-4476-8FF4-4C6ABA231C97}" name="Estimate" dataDxfId="44"/>
-    <tableColumn id="10" xr3:uid="{70B7C471-B624-430B-8992-4711F27BB17E}" name="Issue ID" dataDxfId="43"/>
-    <tableColumn id="30" xr3:uid="{938D6CA2-8309-4146-9B62-E8CDFAB7B1C9}" name="Parent" dataDxfId="42"/>
-    <tableColumn id="11" xr3:uid="{594BD56F-7D1D-408F-BEDC-6BB9854C71A1}" name="Epic Link" dataDxfId="41"/>
-    <tableColumn id="33" xr3:uid="{3A94D4B2-1A5B-4BBF-B398-E56D2BB7F948}" name="Epic Name" dataDxfId="40">
+    <tableColumn id="28" xr3:uid="{07F3030C-7187-4B16-BBDB-798304851975}" name="Assignee.Name" dataDxfId="79"/>
+    <tableColumn id="8" xr3:uid="{8C7FB8DB-A85B-4189-93D8-0F0D4EEEF81B}" name="Component" dataDxfId="78"/>
+    <tableColumn id="9" xr3:uid="{DC5101A8-1204-44D2-BC2C-FEE1A4EFE7C1}" name="Sprint Name" dataDxfId="77"/>
+    <tableColumn id="40" xr3:uid="{1F406792-7ED2-4476-8FF4-4C6ABA231C97}" name="Estimate" dataDxfId="76"/>
+    <tableColumn id="10" xr3:uid="{70B7C471-B624-430B-8992-4711F27BB17E}" name="Issue ID" dataDxfId="75"/>
+    <tableColumn id="30" xr3:uid="{938D6CA2-8309-4146-9B62-E8CDFAB7B1C9}" name="Parent" dataDxfId="74"/>
+    <tableColumn id="11" xr3:uid="{594BD56F-7D1D-408F-BEDC-6BB9854C71A1}" name="Epic Link" dataDxfId="73"/>
+    <tableColumn id="33" xr3:uid="{3A94D4B2-1A5B-4BBF-B398-E56D2BB7F948}" name="Epic Name" dataDxfId="72">
       <calculatedColumnFormula>IF(JiraDataset[[#This Row],[IssueType]]="Epic",JiraDataset[[#This Row],[Summary]],"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="27" xr3:uid="{911C8FDC-5528-43FC-BDF4-D4761F03C0E5}" name="Child-Issue" dataDxfId="39"/>
-    <tableColumn id="41" xr3:uid="{AB248E07-9BFA-42CC-BC41-B4234F677BFB}" name="Child-Issue1" dataDxfId="38"/>
-    <tableColumn id="29" xr3:uid="{89D12135-F3E3-4253-844F-1B9A54169953}" name="Child-Issue2" dataDxfId="37"/>
-    <tableColumn id="12" xr3:uid="{0699B70E-673B-4238-8A66-12FC943A4812}" name="Labels" dataDxfId="36"/>
-    <tableColumn id="13" xr3:uid="{9840B81F-2CA6-4708-8C93-3E7C8F72A676}" name="Labels1" dataDxfId="35"/>
-    <tableColumn id="14" xr3:uid="{D4A99C0B-46B7-484A-842E-D62E9D5D9341}" name="Labels2" dataDxfId="34"/>
-    <tableColumn id="15" xr3:uid="{1D1C275E-5C65-4393-9663-6C5F617591E1}" name="Labels3" dataDxfId="33"/>
-    <tableColumn id="16" xr3:uid="{D823FA91-7106-42D3-9DBC-B337C509EB09}" name="Labels4" dataDxfId="32"/>
-    <tableColumn id="17" xr3:uid="{05A07F85-1763-4A66-9CBB-4A760BD03D27}" name="Labels5" dataDxfId="31"/>
-    <tableColumn id="18" xr3:uid="{16B98070-7F8A-4FC7-AD99-EA81D0BD26AB}" name="Labels6" dataDxfId="30"/>
-    <tableColumn id="19" xr3:uid="{016EAEF4-8EA9-408B-9F1A-ECFB17E81C77}" name="Labels7" dataDxfId="29"/>
-    <tableColumn id="26" xr3:uid="{8263F9EC-BF0A-46F7-BA83-6083A4262B91}" name="Labels8" dataDxfId="28"/>
-    <tableColumn id="20" xr3:uid="{389B11C5-1B22-48C0-BCA2-72F050425FA1}" name="Labels9" dataDxfId="27"/>
-    <tableColumn id="25" xr3:uid="{AE95F8A2-F7F0-4985-9AE6-4201B9792775}" name="Labels10" dataDxfId="26"/>
-    <tableColumn id="21" xr3:uid="{105F2D0F-70C1-4517-A55F-4C1DDFE85301}" name="Sprint" dataDxfId="25">
+    <tableColumn id="27" xr3:uid="{911C8FDC-5528-43FC-BDF4-D4761F03C0E5}" name="Child-Issue" dataDxfId="71"/>
+    <tableColumn id="41" xr3:uid="{AB248E07-9BFA-42CC-BC41-B4234F677BFB}" name="Child-Issue1" dataDxfId="70"/>
+    <tableColumn id="29" xr3:uid="{89D12135-F3E3-4253-844F-1B9A54169953}" name="Child-Issue2" dataDxfId="69"/>
+    <tableColumn id="12" xr3:uid="{0699B70E-673B-4238-8A66-12FC943A4812}" name="Labels" dataDxfId="68"/>
+    <tableColumn id="13" xr3:uid="{9840B81F-2CA6-4708-8C93-3E7C8F72A676}" name="Labels1" dataDxfId="67"/>
+    <tableColumn id="14" xr3:uid="{D4A99C0B-46B7-484A-842E-D62E9D5D9341}" name="Labels2" dataDxfId="66"/>
+    <tableColumn id="15" xr3:uid="{1D1C275E-5C65-4393-9663-6C5F617591E1}" name="Labels3" dataDxfId="65"/>
+    <tableColumn id="16" xr3:uid="{D823FA91-7106-42D3-9DBC-B337C509EB09}" name="Labels4" dataDxfId="64"/>
+    <tableColumn id="17" xr3:uid="{05A07F85-1763-4A66-9CBB-4A760BD03D27}" name="Labels5" dataDxfId="63"/>
+    <tableColumn id="18" xr3:uid="{16B98070-7F8A-4FC7-AD99-EA81D0BD26AB}" name="Labels6" dataDxfId="62"/>
+    <tableColumn id="19" xr3:uid="{016EAEF4-8EA9-408B-9F1A-ECFB17E81C77}" name="Labels7" dataDxfId="61"/>
+    <tableColumn id="26" xr3:uid="{8263F9EC-BF0A-46F7-BA83-6083A4262B91}" name="Labels8" dataDxfId="60"/>
+    <tableColumn id="20" xr3:uid="{389B11C5-1B22-48C0-BCA2-72F050425FA1}" name="Labels9" dataDxfId="59"/>
+    <tableColumn id="25" xr3:uid="{AE95F8A2-F7F0-4985-9AE6-4201B9792775}" name="Labels10" dataDxfId="58"/>
+    <tableColumn id="21" xr3:uid="{105F2D0F-70C1-4517-A55F-4C1DDFE85301}" name="Sprint" dataDxfId="57">
       <calculatedColumnFormula>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",IFERROR(VLOOKUP(JiraDataset[[#This Row],[Sprint Name]], Config!$D$4:$E$9, 2, FALSE), ""))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{D5984986-D838-4F87-A554-5DC4CA005452}" name="Labels0001" dataDxfId="24">
+    <tableColumn id="22" xr3:uid="{D5984986-D838-4F87-A554-5DC4CA005452}" name="Labels0001" dataDxfId="56">
       <calculatedColumnFormula>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",_xlfn.XLOOKUP("Creation Marker", CfgAutofieldValues[Name], CfgAutofieldValues[Value]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="39" xr3:uid="{C24E9ADD-96A8-4DBB-86A0-08D41975D750}" name="Labels0002" dataDxfId="23">
+    <tableColumn id="39" xr3:uid="{C24E9ADD-96A8-4DBB-86A0-08D41975D750}" name="Labels0002" dataDxfId="55">
       <calculatedColumnFormula>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",_xlfn.XLOOKUP("Feature Pod Label", CfgAutofieldValues[Name], CfgAutofieldValues[Value]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{A6D8D5A6-43EE-415C-80C1-30372C7FE5BF}" name="Assignee" dataDxfId="22">
+    <tableColumn id="6" xr3:uid="{A6D8D5A6-43EE-415C-80C1-30372C7FE5BF}" name="Assignee" dataDxfId="54">
       <calculatedColumnFormula>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",IFERROR(VLOOKUP(JiraDataset[[#This Row],[Assignee.Name]], Config!$A$4:$B$24, 2, FALSE), ""))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="23" xr3:uid="{51D4B5F4-C6D3-4EEC-8B1B-7BEC6E526A64}" name="Project Key" dataDxfId="21">
+    <tableColumn id="23" xr3:uid="{51D4B5F4-C6D3-4EEC-8B1B-7BEC6E526A64}" name="Project Key" dataDxfId="53">
       <calculatedColumnFormula>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",_xlfn.XLOOKUP("Project Key", CfgAutofieldValues[Name], CfgAutofieldValues[Value]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="42" xr3:uid="{82B78F0D-CAEF-4615-B12A-B15ACF33913C}" name="OrigEst" dataDxfId="20">
+    <tableColumn id="42" xr3:uid="{82B78F0D-CAEF-4615-B12A-B15ACF33913C}" name="OrigEst" dataDxfId="52">
       <calculatedColumnFormula array="1">IF(
   JiraDataset[[#This Row],[RowType]]=cfg_type_skip,
   "",
@@ -1392,7 +1688,7 @@
   )
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="44" xr3:uid="{C92FD7EC-0EAB-4967-A0E5-D2427E3A55B4}" name="RowType" dataDxfId="19">
+    <tableColumn id="44" xr3:uid="{C92FD7EC-0EAB-4967-A0E5-D2427E3A55B4}" name="RowType" dataDxfId="51">
       <calculatedColumnFormula array="1">IFERROR(
     _xlfn.IFS(
         JiraDataset[[#This Row],[IssueType]] = cfg_type_comment,"SKIP",
@@ -1402,7 +1698,7 @@
     cfg_type_workitem
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="24" xr3:uid="{B63E8FC4-20B3-4755-92F2-EA1F700CA72E}" name="Note" dataDxfId="18"/>
+    <tableColumn id="24" xr3:uid="{B63E8FC4-20B3-4755-92F2-EA1F700CA72E}" name="Note" dataDxfId="50"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1442,7 +1738,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{A6C0EE44-3F60-4588-BF11-75C3DD021846}" name="CfgPriorities" displayName="CfgPriorities" ref="O3:O9" totalsRowShown="0">
   <autoFilter ref="O3:O9" xr:uid="{A6C0EE44-3F60-4588-BF11-75C3DD021846}"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{3B3BE2ED-38C4-410B-B0BF-4A9BD9B4B974}" name="Priority.Name" dataDxfId="17"/>
+    <tableColumn id="1" xr3:uid="{3B3BE2ED-38C4-410B-B0BF-4A9BD9B4B974}" name="Priority.Name" dataDxfId="49"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium5" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1476,7 +1772,7 @@
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{D4E1611F-A2CF-465D-A219-1759EA66687D}" name="Name"/>
     <tableColumn id="2" xr3:uid="{174D0D86-B1AA-4BF7-AC91-FCACFC898851}" name="Value"/>
-    <tableColumn id="3" xr3:uid="{4D0493E3-2ED0-412B-9468-835FC91C2910}" name="Remark" dataDxfId="16"/>
+    <tableColumn id="3" xr3:uid="{4D0493E3-2ED0-412B-9468-835FC91C2910}" name="Remark" dataDxfId="48"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium5" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1809,43 +2105,43 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F73058B-F76D-4AAE-8108-6C4469E9D8B5}">
-  <dimension ref="A1:AK3"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelCol="1" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AK5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" outlineLevelCol="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="31.7109375" customWidth="1"/>
-    <col min="4" max="4" width="11.85546875" hidden="1" customWidth="1"/>
+    <col min="1" max="2" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="31.6640625" customWidth="1"/>
+    <col min="4" max="4" width="11.83203125" hidden="1" customWidth="1"/>
     <col min="5" max="5" width="33" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="46.28515625" customWidth="1"/>
-    <col min="7" max="7" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="22.5703125" customWidth="1"/>
+    <col min="6" max="6" width="46.33203125" customWidth="1"/>
+    <col min="7" max="7" width="17.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="22.5" customWidth="1"/>
     <col min="9" max="9" width="14" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.28515625" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" customWidth="1"/>
-    <col min="14" max="14" width="14.28515625" customWidth="1"/>
+    <col min="10" max="11" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.33203125" customWidth="1"/>
+    <col min="13" max="13" width="14.5" customWidth="1"/>
+    <col min="14" max="14" width="14.33203125" customWidth="1"/>
     <col min="15" max="15" width="0" hidden="1" customWidth="1"/>
-    <col min="16" max="16" width="22.28515625" hidden="1" customWidth="1"/>
-    <col min="17" max="17" width="12.85546875" hidden="1" customWidth="1"/>
-    <col min="18" max="18" width="12.42578125" customWidth="1"/>
-    <col min="19" max="19" width="15.5703125" customWidth="1"/>
-    <col min="20" max="20" width="12.85546875" customWidth="1"/>
+    <col min="16" max="16" width="22.33203125" hidden="1" customWidth="1"/>
+    <col min="17" max="17" width="12.83203125" hidden="1" customWidth="1"/>
+    <col min="18" max="18" width="12.5" customWidth="1"/>
+    <col min="19" max="19" width="15.5" customWidth="1"/>
+    <col min="20" max="20" width="12.83203125" customWidth="1"/>
     <col min="21" max="21" width="10" customWidth="1"/>
     <col min="22" max="22" width="10" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="10" customWidth="1"/>
-    <col min="24" max="24" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="10.1640625" bestFit="1" customWidth="1"/>
     <col min="25" max="30" width="10" customWidth="1" outlineLevel="1"/>
     <col min="31" max="31" width="10" customWidth="1"/>
-    <col min="32" max="32" width="8.7109375" customWidth="1" outlineLevel="1"/>
-    <col min="33" max="34" width="13.140625" customWidth="1" outlineLevel="1"/>
-    <col min="35" max="35" width="11.42578125" customWidth="1" outlineLevel="1"/>
-    <col min="36" max="37" width="13.7109375" customWidth="1" outlineLevel="1"/>
-    <col min="38" max="38" width="36.5703125" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="18.7109375" customWidth="1"/>
-    <col min="41" max="41" width="87.28515625" customWidth="1"/>
+    <col min="32" max="32" width="8.6640625" customWidth="1" outlineLevel="1"/>
+    <col min="33" max="34" width="13.1640625" customWidth="1" outlineLevel="1"/>
+    <col min="35" max="35" width="11.5" customWidth="1" outlineLevel="1"/>
+    <col min="36" max="37" width="13.6640625" customWidth="1" outlineLevel="1"/>
+    <col min="38" max="38" width="36.5" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="18.6640625" customWidth="1"/>
+    <col min="41" max="41" width="87.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:36" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>1</v>
       </c>
@@ -1880,7 +2176,7 @@
         <v>10</v>
       </c>
       <c r="L1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="M1" s="3" t="s">
         <v>11</v>
@@ -1955,7 +2251,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A2" s="3"/>
       <c r="B2" s="3" t="s">
         <v>33</v>
@@ -1972,7 +2268,7 @@
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K2" s="3">
         <v>1</v>
@@ -2047,7 +2343,7 @@
       </c>
       <c r="AJ2" s="3"/>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>53</v>
       </c>
@@ -2055,26 +2351,26 @@
         <v>42</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>58</v>
+        <v>105</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I3" s="3" t="s">
         <v>47</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="K3" s="3">
         <v>2</v>
@@ -2113,7 +2409,7 @@
       </c>
       <c r="AF3" s="3" t="str">
         <f>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",IFERROR(VLOOKUP(JiraDataset[[#This Row],[Assignee.Name]], Config!$A$4:$B$24, 2, FALSE), ""))</f>
-        <v/>
+        <v>712020:e4e815aa-df03-418a-9760-3e70901b6ec5</v>
       </c>
       <c r="AG3" s="3" t="str">
         <f>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",_xlfn.XLOOKUP("Project Key", CfgAutofieldValues[Name], CfgAutofieldValues[Value]))</f>
@@ -2149,71 +2445,245 @@
       </c>
       <c r="AJ3" s="3"/>
     </row>
+    <row r="4" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A4" s="13"/>
+      <c r="B4" s="13"/>
+      <c r="C4" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="14" t="str">
+        <f>Config!$G$4</f>
+        <v>JITTP Version 1</v>
+      </c>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+      <c r="K4" s="3"/>
+      <c r="L4" s="15"/>
+      <c r="M4" s="3"/>
+      <c r="N4" s="15" t="str">
+        <f>IF(JiraDataset[[#This Row],[IssueType]]="Epic",JiraDataset[[#This Row],[Summary]],"")</f>
+        <v/>
+      </c>
+      <c r="O4" s="3"/>
+      <c r="P4" s="3"/>
+      <c r="Q4" s="3"/>
+      <c r="R4" s="3"/>
+      <c r="S4" s="3"/>
+      <c r="T4" s="3"/>
+      <c r="U4" s="3"/>
+      <c r="V4" s="3"/>
+      <c r="W4" s="3"/>
+      <c r="X4" s="3"/>
+      <c r="Y4" s="3"/>
+      <c r="Z4" s="3"/>
+      <c r="AA4" s="3"/>
+      <c r="AB4" s="3"/>
+      <c r="AC4" s="15" t="str">
+        <f>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",IFERROR(VLOOKUP(JiraDataset[[#This Row],[Sprint Name]], Config!$D$4:$E$9, 2, FALSE), ""))</f>
+        <v/>
+      </c>
+      <c r="AD4" s="15" t="str">
+        <f>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",_xlfn.XLOOKUP("Creation Marker", CfgAutofieldValues[Name], CfgAutofieldValues[Value]))</f>
+        <v>imported</v>
+      </c>
+      <c r="AE4" s="8" t="str">
+        <f>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",_xlfn.XLOOKUP("Feature Pod Label", CfgAutofieldValues[Name], CfgAutofieldValues[Value]))</f>
+        <v>pod_test</v>
+      </c>
+      <c r="AF4" s="15" t="str">
+        <f>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",IFERROR(VLOOKUP(JiraDataset[[#This Row],[Assignee.Name]], Config!$A$4:$B$24, 2, FALSE), ""))</f>
+        <v/>
+      </c>
+      <c r="AG4" s="15" t="str">
+        <f>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",_xlfn.XLOOKUP("Project Key", CfgAutofieldValues[Name], CfgAutofieldValues[Value]))</f>
+        <v>JITTP2</v>
+      </c>
+      <c r="AH4" s="15" t="str" cm="1">
+        <f t="array" ref="AH4">IF(
+  JiraDataset[[#This Row],[RowType]]=cfg_type_skip,
+  "",
+  _xlfn.LET(
+    _xlpm.p, _xlfn.TEXTSPLIT(JiraDataset[[#This Row],[Estimate]], " "),
+    _xlpm.getVal, _xlfn.LAMBDA(_xlpm.u, IFERROR(VALUE(LEFT(_xlfn._xlws.FILTER(_xlpm.p, RIGHT(_xlpm.p,1)=_xlpm.u), LEN(_xlfn._xlws.FILTER(_xlpm.p, RIGHT(_xlpm.p,1)=_xlpm.u))-1)), 0)),
+    _xlpm.w, _xlpm.getVal("w"),
+    _xlpm.d, _xlpm.getVal("d"),
+    _xlpm.h, _xlpm.getVal("h"),
+    _xlpm.m, _xlpm.getVal("m"),
+    _xlpm.seconds, _xlpm.w*144000 + _xlpm.d*28800 + _xlpm.h*3600 + _xlpm.m*60,
+    IF(_xlpm.seconds=0, "", _xlpm.seconds*60)
+  )
+)</f>
+        <v/>
+      </c>
+      <c r="AI4" s="15" t="str" cm="1">
+        <f t="array" ref="AI4">IFERROR(
+    _xlfn.IFS(
+        JiraDataset[[#This Row],[IssueType]] = cfg_type_comment,"SKIP",
+        JiraDataset[[#This Row],[IssueType]] = cfg_type_skip,"SKIP",
+        JiraDataset[[#This Row],[IssueType]] = cfg_type_note,"SKIP"
+    ),
+    cfg_type_workitem
+)</f>
+        <v>WorkItem</v>
+      </c>
+      <c r="AJ4" s="3"/>
+    </row>
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A5" s="13"/>
+      <c r="B5" s="13"/>
+      <c r="C5" s="13"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="13"/>
+      <c r="F5" s="14" t="str">
+        <f>Config!$G$4</f>
+        <v>JITTP Version 1</v>
+      </c>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
+      <c r="J5" s="3"/>
+      <c r="K5" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="L5" s="15"/>
+      <c r="M5" s="3"/>
+      <c r="N5" s="15" t="str">
+        <f>IF(JiraDataset[[#This Row],[IssueType]]="Epic",JiraDataset[[#This Row],[Summary]],"")</f>
+        <v/>
+      </c>
+      <c r="O5" s="3"/>
+      <c r="P5" s="3"/>
+      <c r="Q5" s="3"/>
+      <c r="R5" s="3"/>
+      <c r="S5" s="3"/>
+      <c r="T5" s="3"/>
+      <c r="U5" s="3"/>
+      <c r="V5" s="3"/>
+      <c r="W5" s="3"/>
+      <c r="X5" s="3"/>
+      <c r="Y5" s="3"/>
+      <c r="Z5" s="3"/>
+      <c r="AA5" s="3"/>
+      <c r="AB5" s="3"/>
+      <c r="AC5" s="15" t="str">
+        <f>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",IFERROR(VLOOKUP(JiraDataset[[#This Row],[Sprint Name]], Config!$D$4:$E$9, 2, FALSE), ""))</f>
+        <v/>
+      </c>
+      <c r="AD5" s="15" t="str">
+        <f>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",_xlfn.XLOOKUP("Creation Marker", CfgAutofieldValues[Name], CfgAutofieldValues[Value]))</f>
+        <v>imported</v>
+      </c>
+      <c r="AE5" s="8" t="str">
+        <f>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",_xlfn.XLOOKUP("Feature Pod Label", CfgAutofieldValues[Name], CfgAutofieldValues[Value]))</f>
+        <v>pod_test</v>
+      </c>
+      <c r="AF5" s="15" t="str">
+        <f>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",IFERROR(VLOOKUP(JiraDataset[[#This Row],[Assignee.Name]], Config!$A$4:$B$24, 2, FALSE), ""))</f>
+        <v/>
+      </c>
+      <c r="AG5" s="15" t="str">
+        <f>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",_xlfn.XLOOKUP("Project Key", CfgAutofieldValues[Name], CfgAutofieldValues[Value]))</f>
+        <v>JITTP2</v>
+      </c>
+      <c r="AH5" s="15" t="str" cm="1">
+        <f t="array" ref="AH5">IF(
+  JiraDataset[[#This Row],[RowType]]=cfg_type_skip,
+  "",
+  _xlfn.LET(
+    _xlpm.p, _xlfn.TEXTSPLIT(JiraDataset[[#This Row],[Estimate]], " "),
+    _xlpm.getVal, _xlfn.LAMBDA(_xlpm.u, IFERROR(VALUE(LEFT(_xlfn._xlws.FILTER(_xlpm.p, RIGHT(_xlpm.p,1)=_xlpm.u), LEN(_xlfn._xlws.FILTER(_xlpm.p, RIGHT(_xlpm.p,1)=_xlpm.u))-1)), 0)),
+    _xlpm.w, _xlpm.getVal("w"),
+    _xlpm.d, _xlpm.getVal("d"),
+    _xlpm.h, _xlpm.getVal("h"),
+    _xlpm.m, _xlpm.getVal("m"),
+    _xlpm.seconds, _xlpm.w*144000 + _xlpm.d*28800 + _xlpm.h*3600 + _xlpm.m*60,
+    IF(_xlpm.seconds=0, "", _xlpm.seconds*60)
+  )
+)</f>
+        <v/>
+      </c>
+      <c r="AI5" s="15" t="str" cm="1">
+        <f t="array" ref="AI5">IFERROR(
+    _xlfn.IFS(
+        JiraDataset[[#This Row],[IssueType]] = cfg_type_comment,"SKIP",
+        JiraDataset[[#This Row],[IssueType]] = cfg_type_skip,"SKIP",
+        JiraDataset[[#This Row],[IssueType]] = cfg_type_note,"SKIP"
+    ),
+    cfg_type_workitem
+)</f>
+        <v>WorkItem</v>
+      </c>
+      <c r="AJ5" s="3"/>
+    </row>
   </sheetData>
   <protectedRanges>
     <protectedRange sqref="A1:A1048576 D4:N1048576 P4:AD1048576 C1:AB3" name="User Input"/>
     <protectedRange algorithmName="SHA-512" hashValue="tpheD+JLADkhiyalt6vInlMwkILPZx4PVQN/k2vmwjOBdYUuHaXCrwtObHeFz5dJh9f853O84pZ1Rn9Ujz33+A==" saltValue="9ir5NB4CJc/69S/Eh84/mA==" spinCount="100000" sqref="AC1:AI3 AE4:AK1048576" name="Computed values"/>
   </protectedRanges>
   <phoneticPr fontId="18" type="noConversion"/>
-  <conditionalFormatting sqref="A2:A3 C2:C3">
-    <cfRule type="containsText" dxfId="15" priority="429" operator="containsText" text="blocker">
+  <conditionalFormatting sqref="A2:A5 C2:C5">
+    <cfRule type="containsText" dxfId="47" priority="429" operator="containsText" text="blocker">
       <formula>NOT(ISERROR(SEARCH("blocker",A2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="14" priority="430" operator="containsText" text="critical">
+    <cfRule type="containsText" dxfId="46" priority="430" operator="containsText" text="critical">
       <formula>NOT(ISERROR(SEARCH("critical",A2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="13" priority="431" operator="containsText" text="High">
+    <cfRule type="containsText" dxfId="45" priority="431" operator="containsText" text="High">
       <formula>NOT(ISERROR(SEARCH("High",A2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="12" priority="432" operator="containsText" text="Medium">
+    <cfRule type="containsText" dxfId="44" priority="432" operator="containsText" text="Medium">
       <formula>NOT(ISERROR(SEARCH("Medium",A2)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:A3">
-    <cfRule type="containsBlanks" dxfId="11" priority="493">
+  <conditionalFormatting sqref="A2:A5">
+    <cfRule type="containsBlanks" dxfId="43" priority="493">
       <formula>LEN(TRIM(A2))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:AJ3">
-    <cfRule type="expression" dxfId="10" priority="409" stopIfTrue="1">
+  <conditionalFormatting sqref="A2:AJ5">
+    <cfRule type="expression" dxfId="42" priority="409" stopIfTrue="1">
       <formula>$B2=cfg_type_comment</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="9" priority="410">
+    <cfRule type="expression" dxfId="41" priority="410">
       <formula>$B2=cfg_type_skip</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="411">
+    <cfRule type="expression" dxfId="40" priority="411">
       <formula>$B2=cfg_type_note</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B3">
-    <cfRule type="containsText" dxfId="7" priority="413" operator="containsText" text="epic">
+  <conditionalFormatting sqref="B2:B5">
+    <cfRule type="containsText" dxfId="39" priority="413" operator="containsText" text="epic">
       <formula>NOT(ISERROR(SEARCH("epic",B2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="6" priority="427" operator="containsText" text="story">
+    <cfRule type="containsText" dxfId="38" priority="427" operator="containsText" text="story">
       <formula>NOT(ISERROR(SEARCH("story",B2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="5" priority="433" operator="containsText" text="task">
+    <cfRule type="containsText" dxfId="37" priority="433" operator="containsText" text="task">
       <formula>NOT(ISERROR(SEARCH("task",B2)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="4" priority="492">
+    <cfRule type="containsBlanks" dxfId="36" priority="492">
       <formula>LEN(TRIM(B2))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:AJ3">
-    <cfRule type="expression" dxfId="3" priority="1">
+  <conditionalFormatting sqref="B2:AJ5">
+    <cfRule type="expression" dxfId="35" priority="1">
       <formula>$B2="Epic"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="2">
+    <cfRule type="expression" dxfId="34" priority="2">
       <formula>$B2="Story"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C3">
-    <cfRule type="containsBlanks" dxfId="1" priority="494">
+  <conditionalFormatting sqref="C2:C5">
+    <cfRule type="containsBlanks" dxfId="33" priority="494">
       <formula>LEN(TRIM(C2))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:L3">
-    <cfRule type="containsBlanks" dxfId="0" priority="412">
+  <conditionalFormatting sqref="K2:L5">
+    <cfRule type="containsBlanks" dxfId="32" priority="412">
       <formula>LEN(TRIM(K2))=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2222,37 +2692,37 @@
       <formula1>1</formula1>
       <formula2>1000</formula2>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" error="must be a valid component" sqref="J2:J3" xr:uid="{386E3B68-2486-4DDE-BEB1-45F897521149}"/>
-    <dataValidation type="whole" allowBlank="1" showErrorMessage="1" promptTitle="Warning" prompt="This field should be the Issue ID or Issue Key of the child tasks. (upstream linkage is not possible)._x000a__x000a__x000a_To link Epics and Stories, use the Epic Link from the Story Issue." sqref="O2:Q3" xr:uid="{D7BD960D-9CEA-4120-B2E3-2AE0D4661093}">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" error="must be a valid component" sqref="J2:J5" xr:uid="{386E3B68-2486-4DDE-BEB1-45F897521149}"/>
+    <dataValidation type="whole" allowBlank="1" showErrorMessage="1" promptTitle="Warning" prompt="This field should be the Issue ID or Issue Key of the child tasks. (upstream linkage is not possible)._x000a__x000a__x000a_To link Epics and Stories, use the Epic Link from the Story Issue." sqref="O2:Q5" xr:uid="{D7BD960D-9CEA-4120-B2E3-2AE0D4661093}">
       <formula1>1</formula1>
       <formula2>1000</formula2>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Note" prompt="The content of this column will be ignored during the Jira import." sqref="AJ2:AJ3" xr:uid="{2DA3EDB6-7635-4349-8860-B614B5B71275}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Permissions" prompt="Updating Existing Issues requires global admin permissions" sqref="D2:D3" xr:uid="{D5E4A4BB-53C8-42DF-9B52-F5E00AC6407B}"/>
-    <dataValidation type="whole" allowBlank="1" showErrorMessage="1" promptTitle="Warning" prompt="Use the Issue ID value to link this work item to an Epic_x000a__x000a_Story Issues are not Child-Issues and should have Epic Link instead. " sqref="M2:M3" xr:uid="{16C14239-D6AA-4935-8809-57760481D8F1}">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Note" prompt="The content of this column will be ignored during the Jira import." sqref="AJ2:AJ5" xr:uid="{2DA3EDB6-7635-4349-8860-B614B5B71275}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Permissions" prompt="Updating Existing Issues requires global admin permissions" sqref="D2:D5" xr:uid="{D5E4A4BB-53C8-42DF-9B52-F5E00AC6407B}"/>
+    <dataValidation type="whole" allowBlank="1" showErrorMessage="1" promptTitle="Warning" prompt="Use the Issue ID value to link this work item to an Epic_x000a__x000a_Story Issues are not Child-Issues and should have Epic Link instead. " sqref="M2:M5" xr:uid="{16C14239-D6AA-4935-8809-57760481D8F1}">
       <formula1>1</formula1>
       <formula2>1000</formula2>
     </dataValidation>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="It must be a number (integer). This reference is only used during the import process." sqref="K1" xr:uid="{9C637146-F2E3-4D08-87A8-F70FD358E47E}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Use the Issue ID value to link this work item to an Epic_x000a__x000a_Story Issues are not Child-Issues and should have Epic Link instead. " sqref="M1" xr:uid="{A61138FD-C2B2-49D2-810B-69EAE2230B73}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="This field should be the Issue ID or Issue Key of the child tasks. (upstream linkage is not possible)._x000a__x000a__x000a_To link Epics and Stories, use the Epic Link from the Story Issue." sqref="O1:Q1" xr:uid="{BE6B7503-A11A-4130-9D63-988F0CFED80E}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" error="must be a valid fixversion" promptTitle="AUTOMATIC FIELD" prompt="Do not manually edit these!" sqref="AF2:AH3 AC2:AC3 AF1:AH1" xr:uid="{893DA5FE-9FD0-4D28-BBD0-3D7AEDECEACB}"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="must be a valid component" sqref="H2:H3" xr:uid="{65EDED96-6789-400B-B504-6BC3F5A79E70}">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" error="must be a valid fixversion" promptTitle="AUTOMATIC FIELD" prompt="Do not manually edit these!" sqref="AC2:AC5 AF1:AH5" xr:uid="{893DA5FE-9FD0-4D28-BBD0-3D7AEDECEACB}"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="must be a valid component" sqref="H2:H5" xr:uid="{65EDED96-6789-400B-B504-6BC3F5A79E70}">
       <formula1>INDIRECT("CfgComponents[Component.Name]")</formula1>
     </dataValidation>
-    <dataValidation type="list" errorStyle="warning" showErrorMessage="1" error="must be a valid fixversion" sqref="G2:G3" xr:uid="{44FDC20A-8BF5-49B5-9D2C-3A1FE5A7D835}">
+    <dataValidation type="list" errorStyle="warning" showErrorMessage="1" error="must be a valid fixversion" sqref="G2:G5" xr:uid="{44FDC20A-8BF5-49B5-9D2C-3A1FE5A7D835}">
       <formula1>INDIRECT("CfgAssignees[Asssignee.Name]")</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="must be a valid component" sqref="I2:I3" xr:uid="{A898E2E7-BC45-4B88-BA1E-4AAA377361D4}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="must be a valid component" sqref="I2:I5" xr:uid="{A898E2E7-BC45-4B88-BA1E-4AAA377361D4}">
       <formula1>INDIRECT("CfgSprints[Sprint.Name]")</formula1>
     </dataValidation>
     <dataValidation allowBlank="1" showErrorMessage="1" promptTitle="Warning" prompt="Field only used for Epic Issues, so they can be referenced in Story Issues via the Epic Link field.," sqref="N2:N3 L2:L3" xr:uid="{541AD292-0123-4B65-9663-081991FDF0C1}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Field only used for Epic Issues, so they can be referenced in Story Issues via the Epic Link field.," sqref="L1" xr:uid="{64C73155-DEE7-497D-8A98-01E54655ACA8}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="It must be a number (integer) or the Work Item key. This reference is only used during the import process to set the parent." sqref="L1" xr:uid="{8A2BE248-5762-43AD-9C47-C5A92A2E2357}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Field only used for Epic work item, so they can be referenced in Story work items via the Epic Link field. _x000a_DC Only" sqref="N1" xr:uid="{E8F6E005-1F9B-40F3-B24C-E2A3D286C532}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" error="must be a valid fixversion" promptTitle="Creation Marker (Config Sheet)" prompt="Do not manually edit these!" sqref="AD1:AD3" xr:uid="{412C516D-E091-4DDD-9C14-C33AC653C143}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" error="must be a valid fixversion" promptTitle="Feature Pod Label (Config Sheet)" prompt="Do not manually edit these!" sqref="AE1:AE3" xr:uid="{D2234141-379F-4413-AB08-6835BD9FF967}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" error="must be a valid fixversion" promptTitle="AUTOMATIC FIELD" prompt="Do not manually edit these! SKIP types won't be imported into Jira" sqref="AI1:AI3" xr:uid="{5A336857-7D14-4900-8734-BED680BE5154}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" error="must be a valid fixversion" promptTitle="Creation Marker (Config Sheet)" prompt="Do not manually edit these!" sqref="AD1:AD5" xr:uid="{412C516D-E091-4DDD-9C14-C33AC653C143}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" error="must be a valid fixversion" promptTitle="Feature Pod Label (Config Sheet)" prompt="Do not manually edit these!" sqref="AE1:AE5" xr:uid="{D2234141-379F-4413-AB08-6835BD9FF967}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" error="must be a valid fixversion" promptTitle="AUTOMATIC FIELD" prompt="Do not manually edit these! SKIP types won't be imported into Jira" sqref="AI1:AI5" xr:uid="{5A336857-7D14-4900-8734-BED680BE5154}"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -2266,19 +2736,19 @@
           <x14:formula1>
             <xm:f>Config!$O$4:$O$10</xm:f>
           </x14:formula1>
-          <xm:sqref>A2:A3</xm:sqref>
+          <xm:sqref>A2:A5</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Issue Type" xr:uid="{28BF52BF-C0B0-4D22-B02F-F1408D5A055B}">
           <x14:formula1>
             <xm:f>Config!$U$4:$U$33</xm:f>
           </x14:formula1>
-          <xm:sqref>B2:B3</xm:sqref>
+          <xm:sqref>B2:B5</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="must be a valid fixversion" xr:uid="{7708D6E2-1D6B-41D8-A9EE-0E87219BA8EA}">
           <x14:formula1>
             <xm:f>Config!$G$4:$G$8</xm:f>
           </x14:formula1>
-          <xm:sqref>F2:F3</xm:sqref>
+          <xm:sqref>F2:F5</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -2289,90 +2759,90 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2D54512-1380-4F02-BB23-352387C91232}">
   <dimension ref="A1:V21"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="29.7109375" customWidth="1"/>
+    <col min="1" max="1" width="29.6640625" customWidth="1"/>
     <col min="2" max="2" width="49" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.28515625" customWidth="1"/>
-    <col min="4" max="5" width="18.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.28515625" customWidth="1"/>
-    <col min="7" max="7" width="18.5703125" customWidth="1"/>
-    <col min="8" max="8" width="4.28515625" customWidth="1"/>
-    <col min="9" max="9" width="19.140625" customWidth="1"/>
-    <col min="10" max="10" width="4.28515625" customWidth="1"/>
-    <col min="11" max="11" width="18.5703125" customWidth="1"/>
-    <col min="12" max="12" width="4.28515625" customWidth="1"/>
-    <col min="13" max="13" width="17.5703125" customWidth="1"/>
-    <col min="14" max="14" width="4.28515625" customWidth="1"/>
-    <col min="15" max="15" width="18.7109375" customWidth="1"/>
-    <col min="16" max="16" width="4.28515625" customWidth="1"/>
-    <col min="17" max="18" width="18.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.33203125" customWidth="1"/>
+    <col min="4" max="5" width="18.6640625" customWidth="1"/>
+    <col min="6" max="6" width="4.33203125" customWidth="1"/>
+    <col min="7" max="7" width="18.5" customWidth="1"/>
+    <col min="8" max="8" width="4.33203125" customWidth="1"/>
+    <col min="9" max="9" width="19.1640625" customWidth="1"/>
+    <col min="10" max="10" width="4.33203125" customWidth="1"/>
+    <col min="11" max="11" width="18.5" customWidth="1"/>
+    <col min="12" max="12" width="4.33203125" customWidth="1"/>
+    <col min="13" max="13" width="17.5" customWidth="1"/>
+    <col min="14" max="14" width="4.33203125" customWidth="1"/>
+    <col min="15" max="15" width="18.6640625" customWidth="1"/>
+    <col min="16" max="16" width="4.33203125" customWidth="1"/>
+    <col min="17" max="18" width="18.6640625" customWidth="1"/>
     <col min="19" max="19" width="35" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="22.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="21" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:22" ht="22" x14ac:dyDescent="0.3">
       <c r="A1" s="11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B1" s="11"/>
       <c r="D1" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E1" s="11"/>
       <c r="G1" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I1" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="K1" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="M1" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="O1" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="M1" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="O1" s="6" t="s">
-        <v>60</v>
-      </c>
       <c r="Q1" s="11" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="R1" s="11"/>
       <c r="S1" s="11"/>
       <c r="U1" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A2" s="12" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B2" s="12"/>
       <c r="C2" s="7"/>
       <c r="D2" s="12" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E2" s="12"/>
       <c r="F2" s="7"/>
       <c r="G2" s="10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H2" s="10"/>
       <c r="I2" s="10" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="J2" s="10"/>
       <c r="K2" s="12" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="L2" s="12"/>
       <c r="M2" s="9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="N2" s="9"/>
       <c r="O2" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="P2" s="10"/>
       <c r="Q2" s="12"/>
@@ -2380,54 +2850,54 @@
       <c r="S2" s="9"/>
       <c r="T2" s="7"/>
       <c r="U2" s="9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="V2" s="9"/>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B3" t="s">
         <v>65</v>
       </c>
-      <c r="B3" t="s">
+      <c r="D3" t="s">
         <v>66</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>67</v>
       </c>
-      <c r="E3" t="s">
-        <v>68</v>
-      </c>
       <c r="G3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="K3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="M3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="O3" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>60</v>
+      </c>
+      <c r="R3" t="s">
+        <v>61</v>
+      </c>
+      <c r="S3" t="s">
+        <v>77</v>
+      </c>
+      <c r="U3" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="Q3" t="s">
-        <v>61</v>
-      </c>
-      <c r="R3" t="s">
-        <v>62</v>
-      </c>
-      <c r="S3" t="s">
-        <v>78</v>
-      </c>
-      <c r="U3" s="5" t="s">
-        <v>73</v>
-      </c>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B4" t="s">
         <v>50</v>
@@ -2439,10 +2909,10 @@
         <v>1</v>
       </c>
       <c r="G4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K4" t="s">
         <v>39</v>
@@ -2457,7 +2927,7 @@
         <v>31</v>
       </c>
       <c r="R4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="S4" s="7"/>
       <c r="U4" t="str" cm="1">
@@ -2465,9 +2935,9 @@
         <v>Story</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B5" t="s">
         <v>51</v>
@@ -2479,10 +2949,10 @@
         <v>2</v>
       </c>
       <c r="G5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K5" t="s">
         <v>37</v>
@@ -2500,25 +2970,25 @@
         <v>40</v>
       </c>
       <c r="S5" s="7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="U5" t="str">
         <f ca="1"/>
         <v>Task</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B6" t="s">
         <v>52</v>
       </c>
       <c r="G6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="K6" t="s">
         <v>41</v>
@@ -2533,21 +3003,21 @@
         <v>49</v>
       </c>
       <c r="R6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="S6" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="U6" t="str">
         <f ca="1"/>
         <v>Bug</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
       <c r="I7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="K7" t="s">
         <v>42</v>
@@ -2563,11 +3033,11 @@
         <v>Epic</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
       <c r="I8" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="O8" s="1" t="s">
         <v>55</v>
@@ -2577,11 +3047,11 @@
         <v>Comment</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
       <c r="I9" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="O9" s="1" t="s">
         <v>56</v>
@@ -2591,18 +3061,18 @@
         <v>Skip</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
       <c r="I10" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="U10" t="str">
         <f ca="1"/>
         <v>Note</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
       <c r="U11" t="str">
@@ -2610,43 +3080,43 @@
         <v>WorkItem</v>
       </c>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
     </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
     </row>
-    <row r="17" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="4:5" x14ac:dyDescent="0.2">
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
     </row>
-    <row r="18" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="4:5" x14ac:dyDescent="0.2">
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
     </row>
-    <row r="19" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="4:5" x14ac:dyDescent="0.2">
       <c r="D19" s="2"/>
       <c r="E19" s="2"/>
     </row>
-    <row r="20" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="4:5" x14ac:dyDescent="0.2">
       <c r="D20" s="2"/>
       <c r="E20" s="2"/>
     </row>
-    <row r="21" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="4:5" x14ac:dyDescent="0.2">
       <c r="D21" s="2"/>
       <c r="E21" s="2"/>
     </row>
@@ -2677,6 +3147,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c471fd26-9765-4fbe-b6fd-c17c1e55c974">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="9df69692-83aa-4c55-88c1-62abad05f4fe" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100FB038601AF41D04A88A4BD446922F1A8" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="e8d32171d27ae41230d53456f24efae5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c471fd26-9765-4fbe-b6fd-c17c1e55c974" xmlns:ns3="9df69692-83aa-4c55-88c1-62abad05f4fe" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1f2fb84de5621acf32f385a2ba90fb29" ns2:_="" ns3:_="">
     <xsd:import namespace="c471fd26-9765-4fbe-b6fd-c17c1e55c974"/>
@@ -2905,27 +3395,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9FFE630F-6530-4863-AB67-8477539A0000}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="c471fd26-9765-4fbe-b6fd-c17c1e55c974"/>
+    <ds:schemaRef ds:uri="9df69692-83aa-4c55-88c1-62abad05f4fe"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c471fd26-9765-4fbe-b6fd-c17c1e55c974">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="9df69692-83aa-4c55-88c1-62abad05f4fe" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{156C3F15-3876-4FBB-8F24-692088DE8D9F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2C983B91-58B3-4C2C-AC55-FFEC9F0DB5F6}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2942,23 +3431,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{156C3F15-3876-4FBB-8F24-692088DE8D9F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9FFE630F-6530-4863-AB67-8477539A0000}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="c471fd26-9765-4fbe-b6fd-c17c1e55c974"/>
-    <ds:schemaRef ds:uri="9df69692-83aa-4c55-88c1-62abad05f4fe"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/resources/templates/ImportTemplate.xlsx
+++ b/resources/templates/ImportTemplate.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jules/Workdir/sources/jira-toolkit/resources/templates/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tom_48_97\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8715B6CB-C258-0246-816F-293FA3525AAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CB533E1-F127-4B9B-ACDE-FE3A52926206}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16820" yWindow="10420" windowWidth="17560" windowHeight="12420" xr2:uid="{1FA076D1-0294-4A97-AB8C-3ADE2BC9CEA1}"/>
+    <workbookView xWindow="1116" yWindow="1116" windowWidth="23040" windowHeight="13560" activeTab="1" xr2:uid="{1FA076D1-0294-4A97-AB8C-3ADE2BC9CEA1}"/>
   </bookViews>
   <sheets>
-    <sheet name="Dataset" sheetId="1" r:id="rId1"/>
+    <sheet name="Dataset2" sheetId="1" r:id="rId1"/>
     <sheet name="Config" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="110">
   <si>
     <t>IssueType</t>
   </si>
@@ -245,6 +245,9 @@
     <t>Creation Marker</t>
   </si>
   <si>
+    <t>JV</t>
+  </si>
+  <si>
     <t>Issue Type</t>
   </si>
   <si>
@@ -396,12 +399,6 @@
   </si>
   <si>
     <t>pod_test</t>
-  </si>
-  <si>
-    <t>tst</t>
-  </si>
-  <si>
-    <t>a</t>
   </si>
 </sst>
 </file>
@@ -925,7 +922,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -956,15 +953,6 @@
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="16" applyAlignment="1">
       <alignment horizontal="left" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -1011,291 +999,7 @@
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="88">
-    <dxf>
-      <fill>
-        <patternFill patternType="darkUp"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor auto="1"/>
-          <bgColor rgb="FFFF5050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDAF2D0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF2CEEF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor auto="1"/>
-          <bgColor rgb="FFFF5050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.89996032593768116"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.34998626667073579"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="1" tint="4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor auto="1"/>
-          <bgColor rgb="FFF9B1AB"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFCC99"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF99CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF6699"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="darkUp"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor auto="1"/>
-          <bgColor rgb="FFFF5050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDAF2D0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF2CEEF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor auto="1"/>
-          <bgColor rgb="FFFF5050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.89996032593768116"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.34998626667073579"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="1" tint="4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor auto="1"/>
-          <bgColor rgb="FFF9B1AB"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFCC99"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF99CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF6699"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="56">
     <dxf>
       <fill>
         <patternFill patternType="darkUp"/>
@@ -1616,63 +1320,63 @@
 <file path=xl/namedSheetViews/namedSheetView1.xml><?xml version="1.0" encoding="utf-8"?>
 <namedSheetViews xmlns="http://schemas.microsoft.com/office/spreadsheetml/2019/namedsheetviews" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <namedSheetView name="View1" id="{77233F75-225A-4D7F-8A86-543E0A8C6E58}">
-    <nsvFilter filterId="{933FCFD5-1AB1-4076-B5DD-E2B69F5EB3F2}" ref="A1:AJ5" tableId="1"/>
+    <nsvFilter filterId="{933FCFD5-1AB1-4076-B5DD-E2B69F5EB3F2}" ref="A1:AJ3" tableId="1"/>
   </namedSheetView>
 </namedSheetViews>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{933FCFD5-1AB1-4076-B5DD-E2B69F5EB3F2}" name="JiraDataset" displayName="JiraDataset" ref="A1:AJ5" totalsRowShown="0" headerRowDxfId="87" dataDxfId="86">
-  <autoFilter ref="A1:AJ5" xr:uid="{933FCFD5-1AB1-4076-B5DD-E2B69F5EB3F2}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{933FCFD5-1AB1-4076-B5DD-E2B69F5EB3F2}" name="JiraDataset" displayName="JiraDataset" ref="A1:AJ3" totalsRowShown="0" headerRowDxfId="55" dataDxfId="54">
+  <autoFilter ref="A1:AJ3" xr:uid="{933FCFD5-1AB1-4076-B5DD-E2B69F5EB3F2}"/>
   <tableColumns count="36">
-    <tableColumn id="3" xr3:uid="{AF2EC907-349C-4651-852D-6E39C61E17FF}" name="Priority" dataDxfId="85"/>
-    <tableColumn id="2" xr3:uid="{E90C51F2-4386-421F-A3E4-E2CA9D43D396}" name="IssueType" dataDxfId="84"/>
-    <tableColumn id="1" xr3:uid="{BBAD373B-BA13-47E4-9F74-565F4D9E9680}" name="Summary" dataDxfId="83"/>
-    <tableColumn id="4" xr3:uid="{026E5B97-FAFC-4E46-860E-0B0C976B1148}" name="Issue Key" dataDxfId="82"/>
-    <tableColumn id="5" xr3:uid="{A2C262E8-D544-4669-99F1-151EDE081654}" name="Description" dataDxfId="81"/>
-    <tableColumn id="7" xr3:uid="{0FAD1ACC-432E-462C-8B89-71540710BCB5}" name="FixVersion" dataDxfId="80">
+    <tableColumn id="3" xr3:uid="{AF2EC907-349C-4651-852D-6E39C61E17FF}" name="Priority" dataDxfId="53"/>
+    <tableColumn id="2" xr3:uid="{E90C51F2-4386-421F-A3E4-E2CA9D43D396}" name="IssueType" dataDxfId="52"/>
+    <tableColumn id="1" xr3:uid="{BBAD373B-BA13-47E4-9F74-565F4D9E9680}" name="Summary" dataDxfId="51"/>
+    <tableColumn id="4" xr3:uid="{026E5B97-FAFC-4E46-860E-0B0C976B1148}" name="Issue Key" dataDxfId="50"/>
+    <tableColumn id="5" xr3:uid="{A2C262E8-D544-4669-99F1-151EDE081654}" name="Description" dataDxfId="49"/>
+    <tableColumn id="7" xr3:uid="{0FAD1ACC-432E-462C-8B89-71540710BCB5}" name="FixVersion" dataDxfId="48">
       <calculatedColumnFormula>Config!$G$4</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="28" xr3:uid="{07F3030C-7187-4B16-BBDB-798304851975}" name="Assignee.Name" dataDxfId="79"/>
-    <tableColumn id="8" xr3:uid="{8C7FB8DB-A85B-4189-93D8-0F0D4EEEF81B}" name="Component" dataDxfId="78"/>
-    <tableColumn id="9" xr3:uid="{DC5101A8-1204-44D2-BC2C-FEE1A4EFE7C1}" name="Sprint Name" dataDxfId="77"/>
-    <tableColumn id="40" xr3:uid="{1F406792-7ED2-4476-8FF4-4C6ABA231C97}" name="Estimate" dataDxfId="76"/>
-    <tableColumn id="10" xr3:uid="{70B7C471-B624-430B-8992-4711F27BB17E}" name="Issue ID" dataDxfId="75"/>
-    <tableColumn id="30" xr3:uid="{938D6CA2-8309-4146-9B62-E8CDFAB7B1C9}" name="Parent" dataDxfId="74"/>
-    <tableColumn id="11" xr3:uid="{594BD56F-7D1D-408F-BEDC-6BB9854C71A1}" name="Epic Link" dataDxfId="73"/>
-    <tableColumn id="33" xr3:uid="{3A94D4B2-1A5B-4BBF-B398-E56D2BB7F948}" name="Epic Name" dataDxfId="72">
+    <tableColumn id="28" xr3:uid="{07F3030C-7187-4B16-BBDB-798304851975}" name="Assignee.Name" dataDxfId="47"/>
+    <tableColumn id="8" xr3:uid="{8C7FB8DB-A85B-4189-93D8-0F0D4EEEF81B}" name="Component" dataDxfId="46"/>
+    <tableColumn id="9" xr3:uid="{DC5101A8-1204-44D2-BC2C-FEE1A4EFE7C1}" name="Sprint Name" dataDxfId="45"/>
+    <tableColumn id="40" xr3:uid="{1F406792-7ED2-4476-8FF4-4C6ABA231C97}" name="Estimate" dataDxfId="44"/>
+    <tableColumn id="10" xr3:uid="{70B7C471-B624-430B-8992-4711F27BB17E}" name="Issue ID" dataDxfId="43"/>
+    <tableColumn id="30" xr3:uid="{938D6CA2-8309-4146-9B62-E8CDFAB7B1C9}" name="Parent" dataDxfId="42"/>
+    <tableColumn id="11" xr3:uid="{594BD56F-7D1D-408F-BEDC-6BB9854C71A1}" name="Epic Link" dataDxfId="41"/>
+    <tableColumn id="33" xr3:uid="{3A94D4B2-1A5B-4BBF-B398-E56D2BB7F948}" name="Epic Name" dataDxfId="40">
       <calculatedColumnFormula>IF(JiraDataset[[#This Row],[IssueType]]="Epic",JiraDataset[[#This Row],[Summary]],"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="27" xr3:uid="{911C8FDC-5528-43FC-BDF4-D4761F03C0E5}" name="Child-Issue" dataDxfId="71"/>
-    <tableColumn id="41" xr3:uid="{AB248E07-9BFA-42CC-BC41-B4234F677BFB}" name="Child-Issue1" dataDxfId="70"/>
-    <tableColumn id="29" xr3:uid="{89D12135-F3E3-4253-844F-1B9A54169953}" name="Child-Issue2" dataDxfId="69"/>
-    <tableColumn id="12" xr3:uid="{0699B70E-673B-4238-8A66-12FC943A4812}" name="Labels" dataDxfId="68"/>
-    <tableColumn id="13" xr3:uid="{9840B81F-2CA6-4708-8C93-3E7C8F72A676}" name="Labels1" dataDxfId="67"/>
-    <tableColumn id="14" xr3:uid="{D4A99C0B-46B7-484A-842E-D62E9D5D9341}" name="Labels2" dataDxfId="66"/>
-    <tableColumn id="15" xr3:uid="{1D1C275E-5C65-4393-9663-6C5F617591E1}" name="Labels3" dataDxfId="65"/>
-    <tableColumn id="16" xr3:uid="{D823FA91-7106-42D3-9DBC-B337C509EB09}" name="Labels4" dataDxfId="64"/>
-    <tableColumn id="17" xr3:uid="{05A07F85-1763-4A66-9CBB-4A760BD03D27}" name="Labels5" dataDxfId="63"/>
-    <tableColumn id="18" xr3:uid="{16B98070-7F8A-4FC7-AD99-EA81D0BD26AB}" name="Labels6" dataDxfId="62"/>
-    <tableColumn id="19" xr3:uid="{016EAEF4-8EA9-408B-9F1A-ECFB17E81C77}" name="Labels7" dataDxfId="61"/>
-    <tableColumn id="26" xr3:uid="{8263F9EC-BF0A-46F7-BA83-6083A4262B91}" name="Labels8" dataDxfId="60"/>
-    <tableColumn id="20" xr3:uid="{389B11C5-1B22-48C0-BCA2-72F050425FA1}" name="Labels9" dataDxfId="59"/>
-    <tableColumn id="25" xr3:uid="{AE95F8A2-F7F0-4985-9AE6-4201B9792775}" name="Labels10" dataDxfId="58"/>
-    <tableColumn id="21" xr3:uid="{105F2D0F-70C1-4517-A55F-4C1DDFE85301}" name="Sprint" dataDxfId="57">
+    <tableColumn id="27" xr3:uid="{911C8FDC-5528-43FC-BDF4-D4761F03C0E5}" name="Child-Issue" dataDxfId="39"/>
+    <tableColumn id="41" xr3:uid="{AB248E07-9BFA-42CC-BC41-B4234F677BFB}" name="Child-Issue1" dataDxfId="38"/>
+    <tableColumn id="29" xr3:uid="{89D12135-F3E3-4253-844F-1B9A54169953}" name="Child-Issue2" dataDxfId="37"/>
+    <tableColumn id="12" xr3:uid="{0699B70E-673B-4238-8A66-12FC943A4812}" name="Labels" dataDxfId="36"/>
+    <tableColumn id="13" xr3:uid="{9840B81F-2CA6-4708-8C93-3E7C8F72A676}" name="Labels1" dataDxfId="35"/>
+    <tableColumn id="14" xr3:uid="{D4A99C0B-46B7-484A-842E-D62E9D5D9341}" name="Labels2" dataDxfId="34"/>
+    <tableColumn id="15" xr3:uid="{1D1C275E-5C65-4393-9663-6C5F617591E1}" name="Labels3" dataDxfId="33"/>
+    <tableColumn id="16" xr3:uid="{D823FA91-7106-42D3-9DBC-B337C509EB09}" name="Labels4" dataDxfId="32"/>
+    <tableColumn id="17" xr3:uid="{05A07F85-1763-4A66-9CBB-4A760BD03D27}" name="Labels5" dataDxfId="31"/>
+    <tableColumn id="18" xr3:uid="{16B98070-7F8A-4FC7-AD99-EA81D0BD26AB}" name="Labels6" dataDxfId="30"/>
+    <tableColumn id="19" xr3:uid="{016EAEF4-8EA9-408B-9F1A-ECFB17E81C77}" name="Labels7" dataDxfId="29"/>
+    <tableColumn id="26" xr3:uid="{8263F9EC-BF0A-46F7-BA83-6083A4262B91}" name="Labels8" dataDxfId="28"/>
+    <tableColumn id="20" xr3:uid="{389B11C5-1B22-48C0-BCA2-72F050425FA1}" name="Labels9" dataDxfId="27"/>
+    <tableColumn id="25" xr3:uid="{AE95F8A2-F7F0-4985-9AE6-4201B9792775}" name="Labels10" dataDxfId="26"/>
+    <tableColumn id="21" xr3:uid="{105F2D0F-70C1-4517-A55F-4C1DDFE85301}" name="Sprint" dataDxfId="25">
       <calculatedColumnFormula>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",IFERROR(VLOOKUP(JiraDataset[[#This Row],[Sprint Name]], Config!$D$4:$E$9, 2, FALSE), ""))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{D5984986-D838-4F87-A554-5DC4CA005452}" name="Labels0001" dataDxfId="56">
+    <tableColumn id="22" xr3:uid="{D5984986-D838-4F87-A554-5DC4CA005452}" name="Labels0001" dataDxfId="24">
       <calculatedColumnFormula>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",_xlfn.XLOOKUP("Creation Marker", CfgAutofieldValues[Name], CfgAutofieldValues[Value]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="39" xr3:uid="{C24E9ADD-96A8-4DBB-86A0-08D41975D750}" name="Labels0002" dataDxfId="55">
+    <tableColumn id="39" xr3:uid="{C24E9ADD-96A8-4DBB-86A0-08D41975D750}" name="Labels0002" dataDxfId="23">
       <calculatedColumnFormula>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",_xlfn.XLOOKUP("Feature Pod Label", CfgAutofieldValues[Name], CfgAutofieldValues[Value]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{A6D8D5A6-43EE-415C-80C1-30372C7FE5BF}" name="Assignee" dataDxfId="54">
+    <tableColumn id="6" xr3:uid="{A6D8D5A6-43EE-415C-80C1-30372C7FE5BF}" name="Assignee" dataDxfId="22">
       <calculatedColumnFormula>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",IFERROR(VLOOKUP(JiraDataset[[#This Row],[Assignee.Name]], Config!$A$4:$B$24, 2, FALSE), ""))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="23" xr3:uid="{51D4B5F4-C6D3-4EEC-8B1B-7BEC6E526A64}" name="Project Key" dataDxfId="53">
+    <tableColumn id="23" xr3:uid="{51D4B5F4-C6D3-4EEC-8B1B-7BEC6E526A64}" name="Project Key" dataDxfId="21">
       <calculatedColumnFormula>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",_xlfn.XLOOKUP("Project Key", CfgAutofieldValues[Name], CfgAutofieldValues[Value]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="42" xr3:uid="{82B78F0D-CAEF-4615-B12A-B15ACF33913C}" name="OrigEst" dataDxfId="52">
+    <tableColumn id="42" xr3:uid="{82B78F0D-CAEF-4615-B12A-B15ACF33913C}" name="OrigEst" dataDxfId="20">
       <calculatedColumnFormula array="1">IF(
   JiraDataset[[#This Row],[RowType]]=cfg_type_skip,
   "",
@@ -1688,7 +1392,7 @@
   )
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="44" xr3:uid="{C92FD7EC-0EAB-4967-A0E5-D2427E3A55B4}" name="RowType" dataDxfId="51">
+    <tableColumn id="44" xr3:uid="{C92FD7EC-0EAB-4967-A0E5-D2427E3A55B4}" name="RowType" dataDxfId="19">
       <calculatedColumnFormula array="1">IFERROR(
     _xlfn.IFS(
         JiraDataset[[#This Row],[IssueType]] = cfg_type_comment,"SKIP",
@@ -1698,7 +1402,7 @@
     cfg_type_workitem
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="24" xr3:uid="{B63E8FC4-20B3-4755-92F2-EA1F700CA72E}" name="Note" dataDxfId="50"/>
+    <tableColumn id="24" xr3:uid="{B63E8FC4-20B3-4755-92F2-EA1F700CA72E}" name="Note" dataDxfId="18"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1738,7 +1442,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{A6C0EE44-3F60-4588-BF11-75C3DD021846}" name="CfgPriorities" displayName="CfgPriorities" ref="O3:O9" totalsRowShown="0">
   <autoFilter ref="O3:O9" xr:uid="{A6C0EE44-3F60-4588-BF11-75C3DD021846}"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{3B3BE2ED-38C4-410B-B0BF-4A9BD9B4B974}" name="Priority.Name" dataDxfId="49"/>
+    <tableColumn id="1" xr3:uid="{3B3BE2ED-38C4-410B-B0BF-4A9BD9B4B974}" name="Priority.Name" dataDxfId="17"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium5" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1772,7 +1476,7 @@
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{D4E1611F-A2CF-465D-A219-1759EA66687D}" name="Name"/>
     <tableColumn id="2" xr3:uid="{174D0D86-B1AA-4BF7-AC91-FCACFC898851}" name="Value"/>
-    <tableColumn id="3" xr3:uid="{4D0493E3-2ED0-412B-9468-835FC91C2910}" name="Remark" dataDxfId="48"/>
+    <tableColumn id="3" xr3:uid="{4D0493E3-2ED0-412B-9468-835FC91C2910}" name="Remark" dataDxfId="16"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium5" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2105,43 +1809,43 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F73058B-F76D-4AAE-8108-6C4469E9D8B5}">
-  <dimension ref="A1:AK5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" outlineLevelCol="1" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:AK3"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelCol="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="12.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="31.6640625" customWidth="1"/>
-    <col min="4" max="4" width="11.83203125" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="11.88671875" hidden="1" customWidth="1"/>
     <col min="5" max="5" width="33" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="46.33203125" customWidth="1"/>
-    <col min="7" max="7" width="17.5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="22.5" customWidth="1"/>
+    <col min="7" max="7" width="17.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="22.5546875" customWidth="1"/>
     <col min="9" max="9" width="14" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.44140625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="14.33203125" customWidth="1"/>
-    <col min="13" max="13" width="14.5" customWidth="1"/>
+    <col min="13" max="13" width="14.44140625" customWidth="1"/>
     <col min="14" max="14" width="14.33203125" customWidth="1"/>
     <col min="15" max="15" width="0" hidden="1" customWidth="1"/>
     <col min="16" max="16" width="22.33203125" hidden="1" customWidth="1"/>
-    <col min="17" max="17" width="12.83203125" hidden="1" customWidth="1"/>
-    <col min="18" max="18" width="12.5" customWidth="1"/>
-    <col min="19" max="19" width="15.5" customWidth="1"/>
-    <col min="20" max="20" width="12.83203125" customWidth="1"/>
+    <col min="17" max="17" width="12.88671875" hidden="1" customWidth="1"/>
+    <col min="18" max="18" width="12.44140625" customWidth="1"/>
+    <col min="19" max="19" width="15.5546875" customWidth="1"/>
+    <col min="20" max="20" width="12.88671875" customWidth="1"/>
     <col min="21" max="21" width="10" customWidth="1"/>
     <col min="22" max="22" width="10" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="10" customWidth="1"/>
-    <col min="24" max="24" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="10.109375" bestFit="1" customWidth="1"/>
     <col min="25" max="30" width="10" customWidth="1" outlineLevel="1"/>
     <col min="31" max="31" width="10" customWidth="1"/>
     <col min="32" max="32" width="8.6640625" customWidth="1" outlineLevel="1"/>
-    <col min="33" max="34" width="13.1640625" customWidth="1" outlineLevel="1"/>
-    <col min="35" max="35" width="11.5" customWidth="1" outlineLevel="1"/>
+    <col min="33" max="34" width="13.109375" customWidth="1" outlineLevel="1"/>
+    <col min="35" max="35" width="11.44140625" customWidth="1" outlineLevel="1"/>
     <col min="36" max="37" width="13.6640625" customWidth="1" outlineLevel="1"/>
-    <col min="38" max="38" width="36.5" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="36.5546875" bestFit="1" customWidth="1"/>
     <col min="40" max="40" width="18.6640625" customWidth="1"/>
     <col min="41" max="41" width="87.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" ht="16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>1</v>
       </c>
@@ -2176,7 +1880,7 @@
         <v>10</v>
       </c>
       <c r="L1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="M1" s="3" t="s">
         <v>11</v>
@@ -2251,7 +1955,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A2" s="3"/>
       <c r="B2" s="3" t="s">
         <v>33</v>
@@ -2268,7 +1972,7 @@
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K2" s="3">
         <v>1</v>
@@ -2343,7 +2047,7 @@
       </c>
       <c r="AJ2" s="3"/>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>53</v>
       </c>
@@ -2351,26 +2055,26 @@
         <v>42</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>105</v>
+        <v>58</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I3" s="3" t="s">
         <v>47</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K3" s="3">
         <v>2</v>
@@ -2409,7 +2113,7 @@
       </c>
       <c r="AF3" s="3" t="str">
         <f>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",IFERROR(VLOOKUP(JiraDataset[[#This Row],[Assignee.Name]], Config!$A$4:$B$24, 2, FALSE), ""))</f>
-        <v>712020:e4e815aa-df03-418a-9760-3e70901b6ec5</v>
+        <v/>
       </c>
       <c r="AG3" s="3" t="str">
         <f>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",_xlfn.XLOOKUP("Project Key", CfgAutofieldValues[Name], CfgAutofieldValues[Value]))</f>
@@ -2445,245 +2149,71 @@
       </c>
       <c r="AJ3" s="3"/>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.2">
-      <c r="A4" s="13"/>
-      <c r="B4" s="13"/>
-      <c r="C4" s="13" t="s">
-        <v>109</v>
-      </c>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="14" t="str">
-        <f>Config!$G$4</f>
-        <v>JITTP Version 1</v>
-      </c>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
-      <c r="L4" s="15"/>
-      <c r="M4" s="3"/>
-      <c r="N4" s="15" t="str">
-        <f>IF(JiraDataset[[#This Row],[IssueType]]="Epic",JiraDataset[[#This Row],[Summary]],"")</f>
-        <v/>
-      </c>
-      <c r="O4" s="3"/>
-      <c r="P4" s="3"/>
-      <c r="Q4" s="3"/>
-      <c r="R4" s="3"/>
-      <c r="S4" s="3"/>
-      <c r="T4" s="3"/>
-      <c r="U4" s="3"/>
-      <c r="V4" s="3"/>
-      <c r="W4" s="3"/>
-      <c r="X4" s="3"/>
-      <c r="Y4" s="3"/>
-      <c r="Z4" s="3"/>
-      <c r="AA4" s="3"/>
-      <c r="AB4" s="3"/>
-      <c r="AC4" s="15" t="str">
-        <f>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",IFERROR(VLOOKUP(JiraDataset[[#This Row],[Sprint Name]], Config!$D$4:$E$9, 2, FALSE), ""))</f>
-        <v/>
-      </c>
-      <c r="AD4" s="15" t="str">
-        <f>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",_xlfn.XLOOKUP("Creation Marker", CfgAutofieldValues[Name], CfgAutofieldValues[Value]))</f>
-        <v>imported</v>
-      </c>
-      <c r="AE4" s="8" t="str">
-        <f>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",_xlfn.XLOOKUP("Feature Pod Label", CfgAutofieldValues[Name], CfgAutofieldValues[Value]))</f>
-        <v>pod_test</v>
-      </c>
-      <c r="AF4" s="15" t="str">
-        <f>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",IFERROR(VLOOKUP(JiraDataset[[#This Row],[Assignee.Name]], Config!$A$4:$B$24, 2, FALSE), ""))</f>
-        <v/>
-      </c>
-      <c r="AG4" s="15" t="str">
-        <f>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",_xlfn.XLOOKUP("Project Key", CfgAutofieldValues[Name], CfgAutofieldValues[Value]))</f>
-        <v>JITTP2</v>
-      </c>
-      <c r="AH4" s="15" t="str" cm="1">
-        <f t="array" ref="AH4">IF(
-  JiraDataset[[#This Row],[RowType]]=cfg_type_skip,
-  "",
-  _xlfn.LET(
-    _xlpm.p, _xlfn.TEXTSPLIT(JiraDataset[[#This Row],[Estimate]], " "),
-    _xlpm.getVal, _xlfn.LAMBDA(_xlpm.u, IFERROR(VALUE(LEFT(_xlfn._xlws.FILTER(_xlpm.p, RIGHT(_xlpm.p,1)=_xlpm.u), LEN(_xlfn._xlws.FILTER(_xlpm.p, RIGHT(_xlpm.p,1)=_xlpm.u))-1)), 0)),
-    _xlpm.w, _xlpm.getVal("w"),
-    _xlpm.d, _xlpm.getVal("d"),
-    _xlpm.h, _xlpm.getVal("h"),
-    _xlpm.m, _xlpm.getVal("m"),
-    _xlpm.seconds, _xlpm.w*144000 + _xlpm.d*28800 + _xlpm.h*3600 + _xlpm.m*60,
-    IF(_xlpm.seconds=0, "", _xlpm.seconds*60)
-  )
-)</f>
-        <v/>
-      </c>
-      <c r="AI4" s="15" t="str" cm="1">
-        <f t="array" ref="AI4">IFERROR(
-    _xlfn.IFS(
-        JiraDataset[[#This Row],[IssueType]] = cfg_type_comment,"SKIP",
-        JiraDataset[[#This Row],[IssueType]] = cfg_type_skip,"SKIP",
-        JiraDataset[[#This Row],[IssueType]] = cfg_type_note,"SKIP"
-    ),
-    cfg_type_workitem
-)</f>
-        <v>WorkItem</v>
-      </c>
-      <c r="AJ4" s="3"/>
-    </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
-      <c r="A5" s="13"/>
-      <c r="B5" s="13"/>
-      <c r="C5" s="13"/>
-      <c r="D5" s="13"/>
-      <c r="E5" s="13"/>
-      <c r="F5" s="14" t="str">
-        <f>Config!$G$4</f>
-        <v>JITTP Version 1</v>
-      </c>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
-      <c r="K5" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="L5" s="15"/>
-      <c r="M5" s="3"/>
-      <c r="N5" s="15" t="str">
-        <f>IF(JiraDataset[[#This Row],[IssueType]]="Epic",JiraDataset[[#This Row],[Summary]],"")</f>
-        <v/>
-      </c>
-      <c r="O5" s="3"/>
-      <c r="P5" s="3"/>
-      <c r="Q5" s="3"/>
-      <c r="R5" s="3"/>
-      <c r="S5" s="3"/>
-      <c r="T5" s="3"/>
-      <c r="U5" s="3"/>
-      <c r="V5" s="3"/>
-      <c r="W5" s="3"/>
-      <c r="X5" s="3"/>
-      <c r="Y5" s="3"/>
-      <c r="Z5" s="3"/>
-      <c r="AA5" s="3"/>
-      <c r="AB5" s="3"/>
-      <c r="AC5" s="15" t="str">
-        <f>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",IFERROR(VLOOKUP(JiraDataset[[#This Row],[Sprint Name]], Config!$D$4:$E$9, 2, FALSE), ""))</f>
-        <v/>
-      </c>
-      <c r="AD5" s="15" t="str">
-        <f>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",_xlfn.XLOOKUP("Creation Marker", CfgAutofieldValues[Name], CfgAutofieldValues[Value]))</f>
-        <v>imported</v>
-      </c>
-      <c r="AE5" s="8" t="str">
-        <f>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",_xlfn.XLOOKUP("Feature Pod Label", CfgAutofieldValues[Name], CfgAutofieldValues[Value]))</f>
-        <v>pod_test</v>
-      </c>
-      <c r="AF5" s="15" t="str">
-        <f>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",IFERROR(VLOOKUP(JiraDataset[[#This Row],[Assignee.Name]], Config!$A$4:$B$24, 2, FALSE), ""))</f>
-        <v/>
-      </c>
-      <c r="AG5" s="15" t="str">
-        <f>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",_xlfn.XLOOKUP("Project Key", CfgAutofieldValues[Name], CfgAutofieldValues[Value]))</f>
-        <v>JITTP2</v>
-      </c>
-      <c r="AH5" s="15" t="str" cm="1">
-        <f t="array" ref="AH5">IF(
-  JiraDataset[[#This Row],[RowType]]=cfg_type_skip,
-  "",
-  _xlfn.LET(
-    _xlpm.p, _xlfn.TEXTSPLIT(JiraDataset[[#This Row],[Estimate]], " "),
-    _xlpm.getVal, _xlfn.LAMBDA(_xlpm.u, IFERROR(VALUE(LEFT(_xlfn._xlws.FILTER(_xlpm.p, RIGHT(_xlpm.p,1)=_xlpm.u), LEN(_xlfn._xlws.FILTER(_xlpm.p, RIGHT(_xlpm.p,1)=_xlpm.u))-1)), 0)),
-    _xlpm.w, _xlpm.getVal("w"),
-    _xlpm.d, _xlpm.getVal("d"),
-    _xlpm.h, _xlpm.getVal("h"),
-    _xlpm.m, _xlpm.getVal("m"),
-    _xlpm.seconds, _xlpm.w*144000 + _xlpm.d*28800 + _xlpm.h*3600 + _xlpm.m*60,
-    IF(_xlpm.seconds=0, "", _xlpm.seconds*60)
-  )
-)</f>
-        <v/>
-      </c>
-      <c r="AI5" s="15" t="str" cm="1">
-        <f t="array" ref="AI5">IFERROR(
-    _xlfn.IFS(
-        JiraDataset[[#This Row],[IssueType]] = cfg_type_comment,"SKIP",
-        JiraDataset[[#This Row],[IssueType]] = cfg_type_skip,"SKIP",
-        JiraDataset[[#This Row],[IssueType]] = cfg_type_note,"SKIP"
-    ),
-    cfg_type_workitem
-)</f>
-        <v>WorkItem</v>
-      </c>
-      <c r="AJ5" s="3"/>
-    </row>
   </sheetData>
   <protectedRanges>
     <protectedRange sqref="A1:A1048576 D4:N1048576 P4:AD1048576 C1:AB3" name="User Input"/>
     <protectedRange algorithmName="SHA-512" hashValue="tpheD+JLADkhiyalt6vInlMwkILPZx4PVQN/k2vmwjOBdYUuHaXCrwtObHeFz5dJh9f853O84pZ1Rn9Ujz33+A==" saltValue="9ir5NB4CJc/69S/Eh84/mA==" spinCount="100000" sqref="AC1:AI3 AE4:AK1048576" name="Computed values"/>
   </protectedRanges>
   <phoneticPr fontId="18" type="noConversion"/>
-  <conditionalFormatting sqref="A2:A5 C2:C5">
-    <cfRule type="containsText" dxfId="47" priority="429" operator="containsText" text="blocker">
+  <conditionalFormatting sqref="A2:A3 C2:C3">
+    <cfRule type="containsText" dxfId="15" priority="429" operator="containsText" text="blocker">
       <formula>NOT(ISERROR(SEARCH("blocker",A2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="46" priority="430" operator="containsText" text="critical">
+    <cfRule type="containsText" dxfId="14" priority="430" operator="containsText" text="critical">
       <formula>NOT(ISERROR(SEARCH("critical",A2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="45" priority="431" operator="containsText" text="High">
+    <cfRule type="containsText" dxfId="13" priority="431" operator="containsText" text="High">
       <formula>NOT(ISERROR(SEARCH("High",A2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="44" priority="432" operator="containsText" text="Medium">
+    <cfRule type="containsText" dxfId="12" priority="432" operator="containsText" text="Medium">
       <formula>NOT(ISERROR(SEARCH("Medium",A2)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:A5">
-    <cfRule type="containsBlanks" dxfId="43" priority="493">
+  <conditionalFormatting sqref="A2:A3">
+    <cfRule type="containsBlanks" dxfId="11" priority="493">
       <formula>LEN(TRIM(A2))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:AJ5">
-    <cfRule type="expression" dxfId="42" priority="409" stopIfTrue="1">
+  <conditionalFormatting sqref="A2:AJ3">
+    <cfRule type="expression" dxfId="10" priority="409" stopIfTrue="1">
       <formula>$B2=cfg_type_comment</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="41" priority="410">
+    <cfRule type="expression" dxfId="9" priority="410">
       <formula>$B2=cfg_type_skip</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="40" priority="411">
+    <cfRule type="expression" dxfId="8" priority="411">
       <formula>$B2=cfg_type_note</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B5">
-    <cfRule type="containsText" dxfId="39" priority="413" operator="containsText" text="epic">
+  <conditionalFormatting sqref="B2:B3">
+    <cfRule type="containsText" dxfId="7" priority="413" operator="containsText" text="epic">
       <formula>NOT(ISERROR(SEARCH("epic",B2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="38" priority="427" operator="containsText" text="story">
+    <cfRule type="containsText" dxfId="6" priority="427" operator="containsText" text="story">
       <formula>NOT(ISERROR(SEARCH("story",B2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="37" priority="433" operator="containsText" text="task">
+    <cfRule type="containsText" dxfId="5" priority="433" operator="containsText" text="task">
       <formula>NOT(ISERROR(SEARCH("task",B2)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="36" priority="492">
+    <cfRule type="containsBlanks" dxfId="4" priority="492">
       <formula>LEN(TRIM(B2))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:AJ5">
-    <cfRule type="expression" dxfId="35" priority="1">
+  <conditionalFormatting sqref="B2:AJ3">
+    <cfRule type="expression" dxfId="3" priority="1">
       <formula>$B2="Epic"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="34" priority="2">
+    <cfRule type="expression" dxfId="2" priority="2">
       <formula>$B2="Story"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C5">
-    <cfRule type="containsBlanks" dxfId="33" priority="494">
+  <conditionalFormatting sqref="C2:C3">
+    <cfRule type="containsBlanks" dxfId="1" priority="494">
       <formula>LEN(TRIM(C2))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:L5">
-    <cfRule type="containsBlanks" dxfId="32" priority="412">
+  <conditionalFormatting sqref="K2:L3">
+    <cfRule type="containsBlanks" dxfId="0" priority="412">
       <formula>LEN(TRIM(K2))=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2692,37 +2222,37 @@
       <formula1>1</formula1>
       <formula2>1000</formula2>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" error="must be a valid component" sqref="J2:J5" xr:uid="{386E3B68-2486-4DDE-BEB1-45F897521149}"/>
-    <dataValidation type="whole" allowBlank="1" showErrorMessage="1" promptTitle="Warning" prompt="This field should be the Issue ID or Issue Key of the child tasks. (upstream linkage is not possible)._x000a__x000a__x000a_To link Epics and Stories, use the Epic Link from the Story Issue." sqref="O2:Q5" xr:uid="{D7BD960D-9CEA-4120-B2E3-2AE0D4661093}">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" error="must be a valid component" sqref="J2:J3" xr:uid="{386E3B68-2486-4DDE-BEB1-45F897521149}"/>
+    <dataValidation type="whole" allowBlank="1" showErrorMessage="1" promptTitle="Warning" prompt="This field should be the Issue ID or Issue Key of the child tasks. (upstream linkage is not possible)._x000a__x000a__x000a_To link Epics and Stories, use the Epic Link from the Story Issue." sqref="O2:Q3" xr:uid="{D7BD960D-9CEA-4120-B2E3-2AE0D4661093}">
       <formula1>1</formula1>
       <formula2>1000</formula2>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Note" prompt="The content of this column will be ignored during the Jira import." sqref="AJ2:AJ5" xr:uid="{2DA3EDB6-7635-4349-8860-B614B5B71275}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Permissions" prompt="Updating Existing Issues requires global admin permissions" sqref="D2:D5" xr:uid="{D5E4A4BB-53C8-42DF-9B52-F5E00AC6407B}"/>
-    <dataValidation type="whole" allowBlank="1" showErrorMessage="1" promptTitle="Warning" prompt="Use the Issue ID value to link this work item to an Epic_x000a__x000a_Story Issues are not Child-Issues and should have Epic Link instead. " sqref="M2:M5" xr:uid="{16C14239-D6AA-4935-8809-57760481D8F1}">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Note" prompt="The content of this column will be ignored during the Jira import." sqref="AJ2:AJ3" xr:uid="{2DA3EDB6-7635-4349-8860-B614B5B71275}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Permissions" prompt="Updating Existing Issues requires global admin permissions" sqref="D2:D3" xr:uid="{D5E4A4BB-53C8-42DF-9B52-F5E00AC6407B}"/>
+    <dataValidation type="whole" allowBlank="1" showErrorMessage="1" promptTitle="Warning" prompt="Use the Issue ID value to link this work item to an Epic_x000a__x000a_Story Issues are not Child-Issues and should have Epic Link instead. " sqref="M2:M3" xr:uid="{16C14239-D6AA-4935-8809-57760481D8F1}">
       <formula1>1</formula1>
       <formula2>1000</formula2>
     </dataValidation>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="It must be a number (integer). This reference is only used during the import process." sqref="K1" xr:uid="{9C637146-F2E3-4D08-87A8-F70FD358E47E}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Use the Issue ID value to link this work item to an Epic_x000a__x000a_Story Issues are not Child-Issues and should have Epic Link instead. " sqref="M1" xr:uid="{A61138FD-C2B2-49D2-810B-69EAE2230B73}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="This field should be the Issue ID or Issue Key of the child tasks. (upstream linkage is not possible)._x000a__x000a__x000a_To link Epics and Stories, use the Epic Link from the Story Issue." sqref="O1:Q1" xr:uid="{BE6B7503-A11A-4130-9D63-988F0CFED80E}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" error="must be a valid fixversion" promptTitle="AUTOMATIC FIELD" prompt="Do not manually edit these!" sqref="AC2:AC5 AF1:AH5" xr:uid="{893DA5FE-9FD0-4D28-BBD0-3D7AEDECEACB}"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="must be a valid component" sqref="H2:H5" xr:uid="{65EDED96-6789-400B-B504-6BC3F5A79E70}">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" error="must be a valid fixversion" promptTitle="AUTOMATIC FIELD" prompt="Do not manually edit these!" sqref="AF2:AH3 AC2:AC3 AF1:AH1" xr:uid="{893DA5FE-9FD0-4D28-BBD0-3D7AEDECEACB}"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="must be a valid component" sqref="H2:H3" xr:uid="{65EDED96-6789-400B-B504-6BC3F5A79E70}">
       <formula1>INDIRECT("CfgComponents[Component.Name]")</formula1>
     </dataValidation>
-    <dataValidation type="list" errorStyle="warning" showErrorMessage="1" error="must be a valid fixversion" sqref="G2:G5" xr:uid="{44FDC20A-8BF5-49B5-9D2C-3A1FE5A7D835}">
+    <dataValidation type="list" errorStyle="warning" showErrorMessage="1" error="must be a valid fixversion" sqref="G2:G3" xr:uid="{44FDC20A-8BF5-49B5-9D2C-3A1FE5A7D835}">
       <formula1>INDIRECT("CfgAssignees[Asssignee.Name]")</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="must be a valid component" sqref="I2:I5" xr:uid="{A898E2E7-BC45-4B88-BA1E-4AAA377361D4}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="must be a valid component" sqref="I2:I3" xr:uid="{A898E2E7-BC45-4B88-BA1E-4AAA377361D4}">
       <formula1>INDIRECT("CfgSprints[Sprint.Name]")</formula1>
     </dataValidation>
     <dataValidation allowBlank="1" showErrorMessage="1" promptTitle="Warning" prompt="Field only used for Epic Issues, so they can be referenced in Story Issues via the Epic Link field.," sqref="N2:N3 L2:L3" xr:uid="{541AD292-0123-4B65-9663-081991FDF0C1}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Field only used for Epic Issues, so they can be referenced in Story Issues via the Epic Link field.," sqref="L1" xr:uid="{64C73155-DEE7-497D-8A98-01E54655ACA8}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="It must be a number (integer) or the Work Item key. This reference is only used during the import process to set the parent." sqref="L1" xr:uid="{8A2BE248-5762-43AD-9C47-C5A92A2E2357}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Field only used for Epic work item, so they can be referenced in Story work items via the Epic Link field. _x000a_DC Only" sqref="N1" xr:uid="{E8F6E005-1F9B-40F3-B24C-E2A3D286C532}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" error="must be a valid fixversion" promptTitle="Creation Marker (Config Sheet)" prompt="Do not manually edit these!" sqref="AD1:AD5" xr:uid="{412C516D-E091-4DDD-9C14-C33AC653C143}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" error="must be a valid fixversion" promptTitle="Feature Pod Label (Config Sheet)" prompt="Do not manually edit these!" sqref="AE1:AE5" xr:uid="{D2234141-379F-4413-AB08-6835BD9FF967}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" error="must be a valid fixversion" promptTitle="AUTOMATIC FIELD" prompt="Do not manually edit these! SKIP types won't be imported into Jira" sqref="AI1:AI5" xr:uid="{5A336857-7D14-4900-8734-BED680BE5154}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" error="must be a valid fixversion" promptTitle="Creation Marker (Config Sheet)" prompt="Do not manually edit these!" sqref="AD1:AD3" xr:uid="{412C516D-E091-4DDD-9C14-C33AC653C143}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" error="must be a valid fixversion" promptTitle="Feature Pod Label (Config Sheet)" prompt="Do not manually edit these!" sqref="AE1:AE3" xr:uid="{D2234141-379F-4413-AB08-6835BD9FF967}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" error="must be a valid fixversion" promptTitle="AUTOMATIC FIELD" prompt="Do not manually edit these! SKIP types won't be imported into Jira" sqref="AI1:AI3" xr:uid="{5A336857-7D14-4900-8734-BED680BE5154}"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -2736,19 +2266,19 @@
           <x14:formula1>
             <xm:f>Config!$O$4:$O$10</xm:f>
           </x14:formula1>
-          <xm:sqref>A2:A5</xm:sqref>
+          <xm:sqref>A2:A3</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Issue Type" xr:uid="{28BF52BF-C0B0-4D22-B02F-F1408D5A055B}">
           <x14:formula1>
             <xm:f>Config!$U$4:$U$33</xm:f>
           </x14:formula1>
-          <xm:sqref>B2:B5</xm:sqref>
+          <xm:sqref>B2:B3</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="must be a valid fixversion" xr:uid="{7708D6E2-1D6B-41D8-A9EE-0E87219BA8EA}">
           <x14:formula1>
             <xm:f>Config!$G$4:$G$8</xm:f>
           </x14:formula1>
-          <xm:sqref>F2:F5</xm:sqref>
+          <xm:sqref>F2:F3</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -2759,20 +2289,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2D54512-1380-4F02-BB23-352387C91232}">
   <dimension ref="A1:V21"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="29.6640625" customWidth="1"/>
     <col min="2" max="2" width="49" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="4.33203125" customWidth="1"/>
     <col min="4" max="5" width="18.6640625" customWidth="1"/>
     <col min="6" max="6" width="4.33203125" customWidth="1"/>
-    <col min="7" max="7" width="18.5" customWidth="1"/>
+    <col min="7" max="7" width="18.5546875" customWidth="1"/>
     <col min="8" max="8" width="4.33203125" customWidth="1"/>
-    <col min="9" max="9" width="19.1640625" customWidth="1"/>
+    <col min="9" max="9" width="19.109375" customWidth="1"/>
     <col min="10" max="10" width="4.33203125" customWidth="1"/>
-    <col min="11" max="11" width="18.5" customWidth="1"/>
+    <col min="11" max="11" width="18.5546875" customWidth="1"/>
     <col min="12" max="12" width="4.33203125" customWidth="1"/>
-    <col min="13" max="13" width="17.5" customWidth="1"/>
+    <col min="13" max="13" width="17.5546875" customWidth="1"/>
     <col min="14" max="14" width="4.33203125" customWidth="1"/>
     <col min="15" max="15" width="18.6640625" customWidth="1"/>
     <col min="16" max="16" width="4.33203125" customWidth="1"/>
@@ -2781,68 +2311,68 @@
     <col min="21" max="21" width="22.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="22" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:22" ht="21" x14ac:dyDescent="0.4">
       <c r="A1" s="11" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B1" s="11"/>
       <c r="D1" s="11" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E1" s="11"/>
       <c r="G1" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="I1" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="I1" s="6" t="s">
-        <v>62</v>
-      </c>
       <c r="K1" s="6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="M1" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="O1" s="6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="Q1" s="11" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="R1" s="11"/>
       <c r="S1" s="11"/>
       <c r="U1" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B2" s="12"/>
       <c r="C2" s="7"/>
       <c r="D2" s="12" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E2" s="12"/>
       <c r="F2" s="7"/>
       <c r="G2" s="10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H2" s="10"/>
       <c r="I2" s="10" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J2" s="10"/>
       <c r="K2" s="12" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L2" s="12"/>
       <c r="M2" s="9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N2" s="9"/>
       <c r="O2" s="10" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="P2" s="10"/>
       <c r="Q2" s="12"/>
@@ -2850,54 +2380,54 @@
       <c r="S2" s="9"/>
       <c r="T2" s="7"/>
       <c r="U2" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="V2" s="9"/>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G3" t="s">
+        <v>75</v>
+      </c>
+      <c r="I3" t="s">
         <v>74</v>
       </c>
-      <c r="I3" t="s">
+      <c r="K3" t="s">
         <v>73</v>
       </c>
-      <c r="K3" t="s">
+      <c r="M3" t="s">
+        <v>80</v>
+      </c>
+      <c r="O3" t="s">
         <v>72</v>
       </c>
-      <c r="M3" t="s">
-        <v>79</v>
-      </c>
-      <c r="O3" t="s">
-        <v>71</v>
-      </c>
       <c r="Q3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="R3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="S3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="U3" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B4" t="s">
         <v>50</v>
@@ -2909,10 +2439,10 @@
         <v>1</v>
       </c>
       <c r="G4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K4" t="s">
         <v>39</v>
@@ -2927,7 +2457,7 @@
         <v>31</v>
       </c>
       <c r="R4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="S4" s="7"/>
       <c r="U4" t="str" cm="1">
@@ -2935,9 +2465,9 @@
         <v>Story</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B5" t="s">
         <v>51</v>
@@ -2949,10 +2479,10 @@
         <v>2</v>
       </c>
       <c r="G5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K5" t="s">
         <v>37</v>
@@ -2970,25 +2500,25 @@
         <v>40</v>
       </c>
       <c r="S5" s="7" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U5" t="str">
         <f ca="1"/>
         <v>Task</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B6" t="s">
         <v>52</v>
       </c>
       <c r="G6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K6" t="s">
         <v>41</v>
@@ -3003,21 +2533,21 @@
         <v>49</v>
       </c>
       <c r="R6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="S6" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="U6" t="str">
         <f ca="1"/>
         <v>Bug</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
       <c r="I7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K7" t="s">
         <v>42</v>
@@ -3033,11 +2563,11 @@
         <v>Epic</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.3">
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
       <c r="I8" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="O8" s="1" t="s">
         <v>55</v>
@@ -3047,11 +2577,11 @@
         <v>Comment</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.3">
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
       <c r="I9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="O9" s="1" t="s">
         <v>56</v>
@@ -3061,18 +2591,18 @@
         <v>Skip</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
       <c r="I10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="U10" t="str">
         <f ca="1"/>
         <v>Note</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
       <c r="U11" t="str">
@@ -3080,43 +2610,43 @@
         <v>WorkItem</v>
       </c>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
     </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.3">
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
     </row>
-    <row r="17" spans="4:5" x14ac:dyDescent="0.2">
+    <row r="17" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
     </row>
-    <row r="18" spans="4:5" x14ac:dyDescent="0.2">
+    <row r="18" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
     </row>
-    <row r="19" spans="4:5" x14ac:dyDescent="0.2">
+    <row r="19" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D19" s="2"/>
       <c r="E19" s="2"/>
     </row>
-    <row r="20" spans="4:5" x14ac:dyDescent="0.2">
+    <row r="20" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D20" s="2"/>
       <c r="E20" s="2"/>
     </row>
-    <row r="21" spans="4:5" x14ac:dyDescent="0.2">
+    <row r="21" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D21" s="2"/>
       <c r="E21" s="2"/>
     </row>
@@ -3147,17 +2677,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c471fd26-9765-4fbe-b6fd-c17c1e55c974">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="9df69692-83aa-4c55-88c1-62abad05f4fe" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -3166,7 +2685,7 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100FB038601AF41D04A88A4BD446922F1A8" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="e8d32171d27ae41230d53456f24efae5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c471fd26-9765-4fbe-b6fd-c17c1e55c974" xmlns:ns3="9df69692-83aa-4c55-88c1-62abad05f4fe" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1f2fb84de5621acf32f385a2ba90fb29" ns2:_="" ns3:_="">
     <xsd:import namespace="c471fd26-9765-4fbe-b6fd-c17c1e55c974"/>
@@ -3395,18 +2914,18 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9FFE630F-6530-4863-AB67-8477539A0000}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="c471fd26-9765-4fbe-b6fd-c17c1e55c974"/>
-    <ds:schemaRef ds:uri="9df69692-83aa-4c55-88c1-62abad05f4fe"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c471fd26-9765-4fbe-b6fd-c17c1e55c974">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="9df69692-83aa-4c55-88c1-62abad05f4fe" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{156C3F15-3876-4FBB-8F24-692088DE8D9F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
@@ -3414,7 +2933,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2C983B91-58B3-4C2C-AC55-FFEC9F0DB5F6}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3431,4 +2950,15 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9FFE630F-6530-4863-AB67-8477539A0000}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="c471fd26-9765-4fbe-b6fd-c17c1e55c974"/>
+    <ds:schemaRef ds:uri="9df69692-83aa-4c55-88c1-62abad05f4fe"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/resources/templates/ImportTemplate.xlsx
+++ b/resources/templates/ImportTemplate.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workdir\DeerHide\sources\jira-toolkit\resources\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6F4E5E5-CAF5-42B8-BDD6-A49043ED4875}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAB2016C-9C42-4109-8F33-1BC568D87C6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="5355" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dataset" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="111">
   <si>
     <t>Priority</t>
   </si>
@@ -399,9 +399,6 @@
   </si>
   <si>
     <t>Quality Control</t>
-  </si>
-  <si>
-    <t>g</t>
   </si>
 </sst>
 </file>
@@ -501,7 +498,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -534,16 +531,13 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Accent4" xfId="2" builtinId="41"/>
     <cellStyle name="Explanatory Text" xfId="1" builtinId="53"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="72">
+  <dxfs count="56">
     <dxf>
       <fill>
         <patternFill patternType="darkUp"/>
@@ -682,6 +676,12 @@
       </fill>
     </dxf>
     <dxf>
+      <alignment horizontal="general" vertical="bottom" shrinkToFit="1"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
       <alignment vertical="top"/>
     </dxf>
     <dxf>
@@ -804,149 +804,6 @@
     </dxf>
     <dxf>
       <alignment vertical="top"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="darkUp"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor auto="1"/>
-          <bgColor rgb="FFFF5050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDAF2D0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF2CEEF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor auto="1"/>
-          <bgColor rgb="FFFF5050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.89996032593768116"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.34998626667073579"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="1" tint="4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor auto="1"/>
-          <bgColor rgb="FFF9B1AB"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFCC99"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF99CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF6699"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" shrinkToFit="1"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -962,57 +819,57 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="JiraDataset" displayName="JiraDataset" ref="A1:AJ4" totalsRowShown="0" headerRowDxfId="53" dataDxfId="52">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="JiraDataset" displayName="JiraDataset" ref="A1:AJ4" totalsRowShown="0" headerRowDxfId="55" dataDxfId="54">
   <autoFilter ref="A1:AJ4" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="36">
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Priority" dataDxfId="51"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="IssueType" dataDxfId="50"/>
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Summary" dataDxfId="49"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Issue Key" dataDxfId="48"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Description" dataDxfId="47"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="FixVersion" dataDxfId="46">
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Priority" dataDxfId="53"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="IssueType" dataDxfId="52"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Summary" dataDxfId="51"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Issue Key" dataDxfId="50"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Description" dataDxfId="49"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="FixVersion" dataDxfId="48">
       <calculatedColumnFormula>Config!$G$4</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0000-00001C000000}" name="Assignee.Name" dataDxfId="45"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Component" dataDxfId="44"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Sprint Name" dataDxfId="43"/>
-    <tableColumn id="40" xr3:uid="{00000000-0010-0000-0000-000028000000}" name="Estimate" dataDxfId="42"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Issue ID" dataDxfId="41"/>
-    <tableColumn id="30" xr3:uid="{00000000-0010-0000-0000-00001E000000}" name="Parent" dataDxfId="40"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Epic Link" dataDxfId="39"/>
-    <tableColumn id="33" xr3:uid="{00000000-0010-0000-0000-000021000000}" name="Epic Name" dataDxfId="38">
+    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0000-00001C000000}" name="Assignee.Name" dataDxfId="47"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Component" dataDxfId="46"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Sprint Name" dataDxfId="45"/>
+    <tableColumn id="40" xr3:uid="{00000000-0010-0000-0000-000028000000}" name="Estimate" dataDxfId="44"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Issue ID" dataDxfId="43"/>
+    <tableColumn id="30" xr3:uid="{00000000-0010-0000-0000-00001E000000}" name="Parent" dataDxfId="42"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Epic Link" dataDxfId="41"/>
+    <tableColumn id="33" xr3:uid="{00000000-0010-0000-0000-000021000000}" name="Epic Name" dataDxfId="40">
       <calculatedColumnFormula>IF(JiraDataset[[#This Row],[IssueType]]="Epic",JiraDataset[[#This Row],[Summary]],"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="27" xr3:uid="{00000000-0010-0000-0000-00001B000000}" name="Child-Issue" dataDxfId="37"/>
-    <tableColumn id="41" xr3:uid="{00000000-0010-0000-0000-000029000000}" name="Child-Issue1" dataDxfId="36"/>
-    <tableColumn id="29" xr3:uid="{00000000-0010-0000-0000-00001D000000}" name="Child-Issue2" dataDxfId="35"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Labels" dataDxfId="34"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Labels1" dataDxfId="33"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Labels2" dataDxfId="32"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Labels3" dataDxfId="31"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Labels4" dataDxfId="30"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Labels5" dataDxfId="29"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Labels6" dataDxfId="28"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Labels7" dataDxfId="27"/>
-    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="Labels8" dataDxfId="26"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="Labels9" dataDxfId="25"/>
-    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="Labels10" dataDxfId="24"/>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="Sprint" dataDxfId="23">
+    <tableColumn id="27" xr3:uid="{00000000-0010-0000-0000-00001B000000}" name="Child-Issue" dataDxfId="39"/>
+    <tableColumn id="41" xr3:uid="{00000000-0010-0000-0000-000029000000}" name="Child-Issue1" dataDxfId="38"/>
+    <tableColumn id="29" xr3:uid="{00000000-0010-0000-0000-00001D000000}" name="Child-Issue2" dataDxfId="37"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Labels" dataDxfId="36"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Labels1" dataDxfId="35"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Labels2" dataDxfId="34"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Labels3" dataDxfId="33"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Labels4" dataDxfId="32"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Labels5" dataDxfId="31"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Labels6" dataDxfId="30"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Labels7" dataDxfId="29"/>
+    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="Labels8" dataDxfId="28"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="Labels9" dataDxfId="27"/>
+    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="Labels10" dataDxfId="26"/>
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="Sprint" dataDxfId="25">
       <calculatedColumnFormula>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",IFERROR(VLOOKUP(JiraDataset[[#This Row],[Sprint Name]], Config!$D$4:$E$9, 2, FALSE), ""))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="Labels0001" dataDxfId="22">
+    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="Labels0001" dataDxfId="24">
       <calculatedColumnFormula>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",_xlfn.XLOOKUP("Creation Marker", CfgAutofieldValues[Name], CfgAutofieldValues[Value]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="39" xr3:uid="{00000000-0010-0000-0000-000027000000}" name="Labels0002" dataDxfId="21">
+    <tableColumn id="39" xr3:uid="{00000000-0010-0000-0000-000027000000}" name="Labels0002" dataDxfId="23">
       <calculatedColumnFormula>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",_xlfn.XLOOKUP("Feature Pod Label", CfgAutofieldValues[Name], CfgAutofieldValues[Value]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Assignee" dataDxfId="20">
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Assignee" dataDxfId="22">
       <calculatedColumnFormula>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",IFERROR(VLOOKUP(JiraDataset[[#This Row],[Assignee.Name]], Config!$A$4:$B$24, 2, FALSE), ""))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="Project Key" dataDxfId="19">
+    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="Project Key" dataDxfId="21">
       <calculatedColumnFormula>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",_xlfn.XLOOKUP("Project Key", CfgAutofieldValues[Name], CfgAutofieldValues[Value]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="42" xr3:uid="{00000000-0010-0000-0000-00002A000000}" name="OrigEst" dataDxfId="18">
+    <tableColumn id="42" xr3:uid="{00000000-0010-0000-0000-00002A000000}" name="OrigEst" dataDxfId="20">
       <calculatedColumnFormula array="1">IF(
   JiraDataset[[#This Row],[RowType]]=cfg_type_skip,
   "",
@@ -1028,7 +885,7 @@
   )
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="44" xr3:uid="{00000000-0010-0000-0000-00002C000000}" name="RowType" dataDxfId="17">
+    <tableColumn id="44" xr3:uid="{00000000-0010-0000-0000-00002C000000}" name="RowType" dataDxfId="19">
       <calculatedColumnFormula array="1">IFERROR(
     _xlfn.IFS(
         JiraDataset[[#This Row],[IssueType]] = cfg_type_comment,"SKIP",
@@ -1038,7 +895,7 @@
     cfg_type_workitem
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="Note" dataDxfId="16"/>
+    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="Note" dataDxfId="18"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1078,7 +935,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="CfgPriorities" displayName="CfgPriorities" ref="O3:O9" totalsRowShown="0">
   <autoFilter ref="O3:O9" xr:uid="{00000000-0009-0000-0100-000005000000}"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="Priority.Name" dataDxfId="71"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="Priority.Name" dataDxfId="17"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium5" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1112,7 +969,7 @@
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0700-000001000000}" name="Name"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0700-000002000000}" name="Value"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0700-000003000000}" name="Remark" dataDxfId="70"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0700-000003000000}" name="Remark" dataDxfId="16"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium5" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1719,7 +1576,7 @@
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
-      <c r="F4" s="14" t="str">
+      <c r="F4" s="3" t="str">
         <f>Config!$G$4</f>
         <v>JITTP Version 1</v>
       </c>
@@ -1728,9 +1585,9 @@
       <c r="I4" s="3"/>
       <c r="J4" s="3"/>
       <c r="K4" s="3"/>
-      <c r="L4" s="14"/>
+      <c r="L4" s="3"/>
       <c r="M4" s="3"/>
-      <c r="N4" s="14" t="str">
+      <c r="N4" s="3" t="str">
         <f>IF(JiraDataset[[#This Row],[IssueType]]="Epic",JiraDataset[[#This Row],[Summary]],"")</f>
         <v/>
       </c>
@@ -1748,11 +1605,11 @@
       <c r="Z4" s="3"/>
       <c r="AA4" s="3"/>
       <c r="AB4" s="3"/>
-      <c r="AC4" s="14" t="str">
+      <c r="AC4" s="3" t="str">
         <f>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",IFERROR(VLOOKUP(JiraDataset[[#This Row],[Sprint Name]], Config!$D$4:$E$9, 2, FALSE), ""))</f>
         <v/>
       </c>
-      <c r="AD4" s="14" t="str">
+      <c r="AD4" s="3" t="str">
         <f>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",_xlfn.XLOOKUP("Creation Marker", CfgAutofieldValues[Name], CfgAutofieldValues[Value]))</f>
         <v>imported</v>
       </c>
@@ -1760,15 +1617,15 @@
         <f>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",_xlfn.XLOOKUP("Feature Pod Label", CfgAutofieldValues[Name], CfgAutofieldValues[Value]))</f>
         <v>pod_test</v>
       </c>
-      <c r="AF4" s="14" t="str">
+      <c r="AF4" s="3" t="str">
         <f>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",IFERROR(VLOOKUP(JiraDataset[[#This Row],[Assignee.Name]], Config!$A$4:$B$24, 2, FALSE), ""))</f>
         <v/>
       </c>
-      <c r="AG4" s="14" t="str">
+      <c r="AG4" s="3" t="str">
         <f>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",_xlfn.XLOOKUP("Project Key", CfgAutofieldValues[Name], CfgAutofieldValues[Value]))</f>
         <v>JITTP2</v>
       </c>
-      <c r="AH4" s="14" t="str" cm="1">
+      <c r="AH4" s="3" t="str" cm="1">
         <f t="array" ref="AH4">IF(
   JiraDataset[[#This Row],[RowType]]=cfg_type_skip,
   "",
@@ -1785,7 +1642,7 @@
 )</f>
         <v/>
       </c>
-      <c r="AI4" s="14" t="str" cm="1">
+      <c r="AI4" s="3" t="str" cm="1">
         <f t="array" ref="AI4">IFERROR(
     _xlfn.IFS(
         JiraDataset[[#This Row],[IssueType]] = cfg_type_comment,"SKIP",
@@ -1796,9 +1653,7 @@
 )</f>
         <v>WorkItem</v>
       </c>
-      <c r="AJ4" s="3" t="s">
-        <v>111</v>
-      </c>
+      <c r="AJ4" s="3"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:A4 C2:C4">

--- a/resources/templates/ImportTemplate.xlsx
+++ b/resources/templates/ImportTemplate.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workdir\DeerHide\sources\jira-toolkit\resources\templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workdir\temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAB2016C-9C42-4109-8F33-1BC568D87C6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77E3885F-31A5-4652-AED3-4A4A21786D96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="5355" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="252" yWindow="6408" windowWidth="30696" windowHeight="12420" xr2:uid="{1FA076D1-0294-4A97-AB8C-3ADE2BC9CEA1}"/>
   </bookViews>
   <sheets>
     <sheet name="Dataset" sheetId="1" r:id="rId1"/>
@@ -26,8 +26,11 @@
     <definedName name="cfg_type_skip">Config!$M$5</definedName>
     <definedName name="cfg_type_workitem">Config!$M$7</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -44,7 +47,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -66,14 +69,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="111">
+  <si>
+    <t>IssueType</t>
+  </si>
   <si>
     <t>Priority</t>
   </si>
   <si>
-    <t>IssueType</t>
-  </si>
-  <si>
     <t>Summary</t>
   </si>
   <si>
@@ -101,314 +104,403 @@
     <t>Issue ID</t>
   </si>
   <si>
+    <t>Epic Link</t>
+  </si>
+  <si>
+    <t>Epic Name</t>
+  </si>
+  <si>
+    <t>Child-Issue</t>
+  </si>
+  <si>
+    <t>Child-Issue1</t>
+  </si>
+  <si>
+    <t>Child-Issue2</t>
+  </si>
+  <si>
+    <t>Labels</t>
+  </si>
+  <si>
+    <t>Labels1</t>
+  </si>
+  <si>
+    <t>Labels2</t>
+  </si>
+  <si>
+    <t>Labels3</t>
+  </si>
+  <si>
+    <t>Labels4</t>
+  </si>
+  <si>
+    <t>Labels5</t>
+  </si>
+  <si>
+    <t>Labels6</t>
+  </si>
+  <si>
+    <t>Labels7</t>
+  </si>
+  <si>
+    <t>Labels8</t>
+  </si>
+  <si>
+    <t>Labels9</t>
+  </si>
+  <si>
+    <t>Labels10</t>
+  </si>
+  <si>
+    <t>Sprint</t>
+  </si>
+  <si>
+    <t>Labels0001</t>
+  </si>
+  <si>
+    <t>Labels0002</t>
+  </si>
+  <si>
+    <t>Assignee</t>
+  </si>
+  <si>
+    <t>Project Key</t>
+  </si>
+  <si>
+    <t>OrigEst</t>
+  </si>
+  <si>
+    <t>Note</t>
+  </si>
+  <si>
+    <t>Comment</t>
+  </si>
+  <si>
+    <t>FORMULA HOLDER</t>
+  </si>
+  <si>
+    <t>DO NOT DELETE OR CLEAR THIS ROW</t>
+  </si>
+  <si>
+    <t>Task</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>Story</t>
+  </si>
+  <si>
+    <t>imported</t>
+  </si>
+  <si>
+    <t>Bug</t>
+  </si>
+  <si>
+    <t>Epic</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>RowType</t>
+  </si>
+  <si>
+    <t>Skip</t>
+  </si>
+  <si>
+    <t>WorkItem</t>
+  </si>
+  <si>
+    <t>Sprint 1</t>
+  </si>
+  <si>
+    <t>Sprint 2</t>
+  </si>
+  <si>
+    <t>Feature Pod Label</t>
+  </si>
+  <si>
+    <t>712020:e4e815aa-df03-418a-9760-3e70901b6ec5</t>
+  </si>
+  <si>
+    <t>712020:69ead6b8-698d-48a8-8abb-b55246f6cb7c</t>
+  </si>
+  <si>
+    <t>712020:63630dfe-2a04-4021-9f7b-53445ba456e7</t>
+  </si>
+  <si>
+    <t>Highest</t>
+  </si>
+  <si>
+    <t>Hight</t>
+  </si>
+  <si>
+    <t>Lowest</t>
+  </si>
+  <si>
+    <t>Triage</t>
+  </si>
+  <si>
+    <t>Creation Marker</t>
+  </si>
+  <si>
+    <t>Issue Type</t>
+  </si>
+  <si>
+    <t>Priority Lists</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Components</t>
+  </si>
+  <si>
+    <t>Fix Version</t>
+  </si>
+  <si>
+    <t>Asssignee.Name</t>
+  </si>
+  <si>
+    <t>Assignee.ID</t>
+  </si>
+  <si>
+    <t>Sprint.Name</t>
+  </si>
+  <si>
+    <t>Sprint.ID</t>
+  </si>
+  <si>
+    <t>JITTP Version 1</t>
+  </si>
+  <si>
+    <t>JITTP Version 2</t>
+  </si>
+  <si>
+    <t>JITTP Version 3</t>
+  </si>
+  <si>
+    <t>Priority.Name</t>
+  </si>
+  <si>
+    <t>IssueType.Name</t>
+  </si>
+  <si>
+    <t>Component.Name</t>
+  </si>
+  <si>
+    <t>FixVersion.Name</t>
+  </si>
+  <si>
+    <t>SysOps</t>
+  </si>
+  <si>
+    <t>DevOps</t>
+  </si>
+  <si>
+    <t>Remark</t>
+  </si>
+  <si>
+    <t>Ignore List</t>
+  </si>
+  <si>
+    <t>IgnoreList.Name</t>
+  </si>
+  <si>
+    <t>Assignees</t>
+  </si>
+  <si>
+    <t>Sprints</t>
+  </si>
+  <si>
+    <t>1w 2d 3h</t>
+  </si>
+  <si>
+    <t>Combined Types</t>
+  </si>
+  <si>
+    <t>A label added to all imported task to flag them in Jira</t>
+  </si>
+  <si>
+    <t>Appropirate label for the feature pod when relevant</t>
+  </si>
+  <si>
+    <t>List of assignees with their ID (Cloud) or Usernames (DC)</t>
+  </si>
+  <si>
+    <t>Sprints Symbolic Names and their Jira IDs</t>
+  </si>
+  <si>
+    <t>Fix Version Namess</t>
+  </si>
+  <si>
+    <t>List of Components</t>
+  </si>
+  <si>
+    <t>Accepted User Types</t>
+  </si>
+  <si>
+    <t>Issue Types that won't be imported</t>
+  </si>
+  <si>
+    <t>List of Piorities</t>
+  </si>
+  <si>
+    <t>Combined list for the table</t>
+  </si>
+  <si>
+    <t>1w</t>
+  </si>
+  <si>
+    <t>JITTP2</t>
+  </si>
+  <si>
+    <t>Test, Epic</t>
+  </si>
+  <si>
+    <t>This is a test work item</t>
+  </si>
+  <si>
     <t>Parent</t>
   </si>
   <si>
-    <t>Epic Link</t>
-  </si>
-  <si>
-    <t>Epic Name</t>
-  </si>
-  <si>
-    <t>Child-Issue</t>
-  </si>
-  <si>
-    <t>Child-Issue1</t>
-  </si>
-  <si>
-    <t>Child-Issue2</t>
-  </si>
-  <si>
-    <t>Labels</t>
-  </si>
-  <si>
-    <t>Labels1</t>
-  </si>
-  <si>
-    <t>Labels2</t>
-  </si>
-  <si>
-    <t>Labels3</t>
-  </si>
-  <si>
-    <t>Labels4</t>
-  </si>
-  <si>
-    <t>Labels5</t>
-  </si>
-  <si>
-    <t>Labels6</t>
-  </si>
-  <si>
-    <t>Labels7</t>
-  </si>
-  <si>
-    <t>Labels8</t>
-  </si>
-  <si>
-    <t>Labels9</t>
-  </si>
-  <si>
-    <t>Labels10</t>
-  </si>
-  <si>
-    <t>Sprint</t>
-  </si>
-  <si>
-    <t>Labels0001</t>
-  </si>
-  <si>
-    <t>Labels0002</t>
-  </si>
-  <si>
-    <t>Assignee</t>
-  </si>
-  <si>
-    <t>Project Key</t>
-  </si>
-  <si>
-    <t>OrigEst</t>
-  </si>
-  <si>
-    <t>RowType</t>
-  </si>
-  <si>
-    <t>Note</t>
-  </si>
-  <si>
-    <t>FORMULA HOLDER</t>
-  </si>
-  <si>
-    <t>DO NOT DELETE OR CLEAR THIS ROW</t>
-  </si>
-  <si>
-    <t>1w 2d 3h</t>
-  </si>
-  <si>
-    <t>SKIP</t>
-  </si>
-  <si>
-    <t>Highest</t>
-  </si>
-  <si>
-    <t>Epic</t>
-  </si>
-  <si>
-    <t>Test, Epic</t>
-  </si>
-  <si>
-    <t>This is a test work item</t>
-  </si>
-  <si>
-    <t>JITTP Version 3</t>
-  </si>
-  <si>
-    <t>JV</t>
-  </si>
-  <si>
-    <t>DevOps</t>
-  </si>
-  <si>
-    <t>Sprint 1</t>
-  </si>
-  <si>
-    <t>1w</t>
-  </si>
-  <si>
-    <t>imported</t>
+    <t>Design</t>
+  </si>
+  <si>
+    <t>Development</t>
+  </si>
+  <si>
+    <t>Production</t>
+  </si>
+  <si>
+    <t>Quality Assurance</t>
+  </si>
+  <si>
+    <t>Quality Control</t>
+  </si>
+  <si>
+    <t>Misc Fields</t>
+  </si>
+  <si>
+    <t>tom4897</t>
+  </si>
+  <si>
+    <t>Nakool</t>
+  </si>
+  <si>
+    <t>MirageCentury</t>
   </si>
   <si>
     <t>pod_test</t>
   </si>
   <si>
-    <t>JITTP2</t>
-  </si>
-  <si>
-    <t>WorkItem</t>
-  </si>
-  <si>
-    <t>Assignees</t>
-  </si>
-  <si>
-    <t>Sprints</t>
-  </si>
-  <si>
-    <t>Fix Version</t>
-  </si>
-  <si>
-    <t>Components</t>
-  </si>
-  <si>
-    <t>Issue Type</t>
-  </si>
-  <si>
-    <t>Ignore List</t>
-  </si>
-  <si>
-    <t>Priority Lists</t>
-  </si>
-  <si>
-    <t>Misc Fields</t>
-  </si>
-  <si>
-    <t>Combined Types</t>
-  </si>
-  <si>
-    <t>List of assignees with their ID (Cloud) or Usernames (DC)</t>
-  </si>
-  <si>
-    <t>Sprints Symbolic Names and their Jira IDs</t>
-  </si>
-  <si>
-    <t>Fix Version Namess</t>
-  </si>
-  <si>
-    <t>List of Components</t>
-  </si>
-  <si>
-    <t>Accepted User Types</t>
-  </si>
-  <si>
-    <t>Issue Types that won't be imported</t>
-  </si>
-  <si>
-    <t>List of Piorities</t>
-  </si>
-  <si>
-    <t>Combined list for the table</t>
-  </si>
-  <si>
-    <t>Asssignee.Name</t>
-  </si>
-  <si>
-    <t>Assignee.ID</t>
-  </si>
-  <si>
-    <t>Sprint.Name</t>
-  </si>
-  <si>
-    <t>Sprint.ID</t>
-  </si>
-  <si>
-    <t>FixVersion.Name</t>
-  </si>
-  <si>
-    <t>Component.Name</t>
-  </si>
-  <si>
-    <t>IssueType.Name</t>
-  </si>
-  <si>
-    <t>IgnoreList.Name</t>
-  </si>
-  <si>
-    <t>Priority.Name</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Value</t>
-  </si>
-  <si>
-    <t>Remark</t>
-  </si>
-  <si>
-    <t>tom4897</t>
-  </si>
-  <si>
-    <t>712020:e4e815aa-df03-418a-9760-3e70901b6ec5</t>
-  </si>
-  <si>
-    <t>JITTP Version 1</t>
-  </si>
-  <si>
-    <t>SysOps</t>
-  </si>
-  <si>
-    <t>Story</t>
-  </si>
-  <si>
-    <t>Comment</t>
-  </si>
-  <si>
-    <t>Medium</t>
-  </si>
-  <si>
-    <t>Nakool</t>
-  </si>
-  <si>
-    <t>712020:69ead6b8-698d-48a8-8abb-b55246f6cb7c</t>
-  </si>
-  <si>
-    <t>Sprint 2</t>
-  </si>
-  <si>
-    <t>JITTP Version 2</t>
-  </si>
-  <si>
-    <t>Task</t>
-  </si>
-  <si>
-    <t>Skip</t>
-  </si>
-  <si>
-    <t>Creation Marker</t>
-  </si>
-  <si>
-    <t>A label added to all imported task to flag them in Jira</t>
-  </si>
-  <si>
-    <t>MirageCentury</t>
-  </si>
-  <si>
-    <t>712020:63630dfe-2a04-4021-9f7b-53445ba456e7</t>
-  </si>
-  <si>
-    <t>Design</t>
-  </si>
-  <si>
-    <t>Bug</t>
-  </si>
-  <si>
-    <t>Hight</t>
-  </si>
-  <si>
-    <t>Feature Pod Label</t>
-  </si>
-  <si>
-    <t>Appropirate label for the feature pod when relevant</t>
-  </si>
-  <si>
-    <t>Development</t>
-  </si>
-  <si>
-    <t>Low</t>
-  </si>
-  <si>
-    <t>Production</t>
-  </si>
-  <si>
-    <t>Lowest</t>
-  </si>
-  <si>
-    <t>Quality Assurance</t>
-  </si>
-  <si>
-    <t>Triage</t>
-  </si>
-  <si>
-    <t>Quality Control</t>
+    <t>High</t>
+  </si>
+  <si>
+    <t>Test, Task</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Aptos Display"/>
+      <family val="2"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C5700"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -422,6 +514,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
@@ -430,8 +529,22 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -452,16 +565,184 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
       </patternFill>
     </fill>
     <fill>
@@ -471,12 +752,119 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="11">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -493,23 +881,62 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" xfId="30" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -518,26 +945,73 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="16" applyAlignment="1">
       <alignment horizontal="left" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="16" applyAlignment="1">
       <alignment shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" xfId="30" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="16" applyAlignment="1">
       <alignment horizontal="left" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
-  <cellStyles count="3">
-    <cellStyle name="Accent4" xfId="2" builtinId="41"/>
-    <cellStyle name="Explanatory Text" xfId="1" builtinId="53"/>
+  <cellStyles count="42">
+    <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
+    <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
+    <cellStyle name="20% - Accent4" xfId="31" builtinId="42" customBuiltin="1"/>
+    <cellStyle name="20% - Accent5" xfId="35" builtinId="46" customBuiltin="1"/>
+    <cellStyle name="20% - Accent6" xfId="39" builtinId="50" customBuiltin="1"/>
+    <cellStyle name="40% - Accent1" xfId="20" builtinId="31" customBuiltin="1"/>
+    <cellStyle name="40% - Accent2" xfId="24" builtinId="35" customBuiltin="1"/>
+    <cellStyle name="40% - Accent3" xfId="28" builtinId="39" customBuiltin="1"/>
+    <cellStyle name="40% - Accent4" xfId="32" builtinId="43" customBuiltin="1"/>
+    <cellStyle name="40% - Accent5" xfId="36" builtinId="47" customBuiltin="1"/>
+    <cellStyle name="40% - Accent6" xfId="40" builtinId="51" customBuiltin="1"/>
+    <cellStyle name="60% - Accent1" xfId="21" builtinId="32" customBuiltin="1"/>
+    <cellStyle name="60% - Accent2" xfId="25" builtinId="36" customBuiltin="1"/>
+    <cellStyle name="60% - Accent3" xfId="29" builtinId="40" customBuiltin="1"/>
+    <cellStyle name="60% - Accent4" xfId="33" builtinId="44" customBuiltin="1"/>
+    <cellStyle name="60% - Accent5" xfId="37" builtinId="48" customBuiltin="1"/>
+    <cellStyle name="60% - Accent6" xfId="41" builtinId="52" customBuiltin="1"/>
+    <cellStyle name="Accent1" xfId="18" builtinId="29" customBuiltin="1"/>
+    <cellStyle name="Accent2" xfId="22" builtinId="33" customBuiltin="1"/>
+    <cellStyle name="Accent3" xfId="26" builtinId="37" customBuiltin="1"/>
+    <cellStyle name="Accent4" xfId="30" builtinId="41" customBuiltin="1"/>
+    <cellStyle name="Accent5" xfId="34" builtinId="45" customBuiltin="1"/>
+    <cellStyle name="Accent6" xfId="38" builtinId="49" customBuiltin="1"/>
+    <cellStyle name="Bad" xfId="7" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="Calculation" xfId="11" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="Check Cell" xfId="13" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="Explanatory Text" xfId="16" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="Good" xfId="6" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="Heading 1" xfId="2" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Note" xfId="15" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
+    <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="56">
+  <dxfs count="72">
     <dxf>
       <fill>
         <patternFill patternType="darkUp"/>
@@ -596,6 +1070,7 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
         <i/>
         <strike val="0"/>
         <color theme="0" tint="-0.34998626667073579"/>
@@ -612,7 +1087,7 @@
         <color auto="1"/>
       </font>
       <fill>
-        <patternFill>
+        <patternFill patternType="none">
           <bgColor auto="1"/>
         </patternFill>
       </fill>
@@ -638,6 +1113,7 @@
     <dxf>
       <font>
         <b/>
+        <i val="0"/>
       </font>
       <fill>
         <patternFill>
@@ -648,6 +1124,7 @@
     <dxf>
       <font>
         <b/>
+        <i val="0"/>
       </font>
       <fill>
         <patternFill>
@@ -658,6 +1135,7 @@
     <dxf>
       <font>
         <b/>
+        <i val="0"/>
       </font>
       <fill>
         <patternFill>
@@ -668,6 +1146,7 @@
     <dxf>
       <font>
         <b/>
+        <i val="0"/>
       </font>
       <fill>
         <patternFill>
@@ -676,137 +1155,311 @@
       </fill>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" shrinkToFit="1"/>
+      <fill>
+        <patternFill patternType="darkUp"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor auto="1"/>
+          <bgColor rgb="FFFF5050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDAF2D0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF2CEEF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor auto="1"/>
+          <bgColor rgb="FFFF5050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.89996032593768116"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.34998626667073579"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor auto="1"/>
+          <bgColor rgb="FFF9B1AB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFCC99"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF99CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF6699"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <alignment vertical="top"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment vertical="top"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment vertical="top"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
       <alignment vertical="top"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="general" vertical="top"/>
+      <alignment vertical="top"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="general" vertical="top"/>
+      <alignment vertical="top"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
       <alignment vertical="top"/>
     </dxf>
     <dxf>
+      <alignment vertical="top"/>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
-      <alignment vertical="top"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment vertical="top"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+      </font>
+      <alignment vertical="top"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+      </font>
+      <alignment vertical="top"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+      </font>
+      <alignment vertical="top"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+      </font>
+      <alignment vertical="top"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="1" readingOrder="0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="30" formatCode="@"/>
-      <alignment vertical="top"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment vertical="top"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment vertical="top"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment vertical="top"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="general" vertical="top"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment vertical="top"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFDAF2D0"/>
+      <color rgb="FFF2CEEF"/>
+      <color rgb="FFAFE49C"/>
+      <color rgb="FFE18FD9"/>
+      <color rgb="FFFF5050"/>
+      <color rgb="FFF9B1AB"/>
+      <color rgb="FFCCECFF"/>
+      <color rgb="FF99CCFF"/>
+      <color rgb="FFFF6699"/>
+      <color rgb="FFFF99CC"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -818,58 +1471,64 @@
 </styleSheet>
 </file>
 
+<file path=xl/namedSheetViews/namedSheetView1.xml><?xml version="1.0" encoding="utf-8"?>
+<namedSheetViews xmlns="http://schemas.microsoft.com/office/spreadsheetml/2019/namedsheetviews" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <namedSheetView name="View1" id="{77233F75-225A-4D7F-8A86-543E0A8C6E58}">
+    <nsvFilter filterId="{933FCFD5-1AB1-4076-B5DD-E2B69F5EB3F2}" ref="A1:AJ4" tableId="1"/>
+  </namedSheetView>
+</namedSheetViews>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="JiraDataset" displayName="JiraDataset" ref="A1:AJ4" totalsRowShown="0" headerRowDxfId="55" dataDxfId="54">
-  <autoFilter ref="A1:AJ4" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{933FCFD5-1AB1-4076-B5DD-E2B69F5EB3F2}" name="JiraDataset" displayName="JiraDataset" ref="A1:AJ4" totalsRowShown="0" headerRowDxfId="69" dataDxfId="68">
+  <autoFilter ref="A1:AJ4" xr:uid="{933FCFD5-1AB1-4076-B5DD-E2B69F5EB3F2}"/>
   <tableColumns count="36">
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Priority" dataDxfId="53"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="IssueType" dataDxfId="52"/>
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Summary" dataDxfId="51"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Issue Key" dataDxfId="50"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Description" dataDxfId="49"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="FixVersion" dataDxfId="48">
-      <calculatedColumnFormula>Config!$G$4</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0000-00001C000000}" name="Assignee.Name" dataDxfId="47"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Component" dataDxfId="46"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Sprint Name" dataDxfId="45"/>
-    <tableColumn id="40" xr3:uid="{00000000-0010-0000-0000-000028000000}" name="Estimate" dataDxfId="44"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Issue ID" dataDxfId="43"/>
-    <tableColumn id="30" xr3:uid="{00000000-0010-0000-0000-00001E000000}" name="Parent" dataDxfId="42"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Epic Link" dataDxfId="41"/>
-    <tableColumn id="33" xr3:uid="{00000000-0010-0000-0000-000021000000}" name="Epic Name" dataDxfId="40">
+    <tableColumn id="3" xr3:uid="{AF2EC907-349C-4651-852D-6E39C61E17FF}" name="Priority" dataDxfId="67"/>
+    <tableColumn id="2" xr3:uid="{E90C51F2-4386-421F-A3E4-E2CA9D43D396}" name="IssueType" dataDxfId="66"/>
+    <tableColumn id="1" xr3:uid="{BBAD373B-BA13-47E4-9F74-565F4D9E9680}" name="Summary" dataDxfId="65"/>
+    <tableColumn id="4" xr3:uid="{026E5B97-FAFC-4E46-860E-0B0C976B1148}" name="Issue Key" dataDxfId="64"/>
+    <tableColumn id="5" xr3:uid="{A2C262E8-D544-4669-99F1-151EDE081654}" name="Description" dataDxfId="63"/>
+    <tableColumn id="7" xr3:uid="{0FAD1ACC-432E-462C-8B89-71540710BCB5}" name="FixVersion" dataDxfId="62"/>
+    <tableColumn id="28" xr3:uid="{07F3030C-7187-4B16-BBDB-798304851975}" name="Assignee.Name" dataDxfId="61"/>
+    <tableColumn id="8" xr3:uid="{8C7FB8DB-A85B-4189-93D8-0F0D4EEEF81B}" name="Component" dataDxfId="60"/>
+    <tableColumn id="9" xr3:uid="{DC5101A8-1204-44D2-BC2C-FEE1A4EFE7C1}" name="Sprint Name" dataDxfId="59"/>
+    <tableColumn id="40" xr3:uid="{1F406792-7ED2-4476-8FF4-4C6ABA231C97}" name="Estimate" dataDxfId="58"/>
+    <tableColumn id="10" xr3:uid="{70B7C471-B624-430B-8992-4711F27BB17E}" name="Issue ID" dataDxfId="57"/>
+    <tableColumn id="30" xr3:uid="{938D6CA2-8309-4146-9B62-E8CDFAB7B1C9}" name="Parent" dataDxfId="56"/>
+    <tableColumn id="11" xr3:uid="{594BD56F-7D1D-408F-BEDC-6BB9854C71A1}" name="Epic Link" dataDxfId="55"/>
+    <tableColumn id="33" xr3:uid="{3A94D4B2-1A5B-4BBF-B398-E56D2BB7F948}" name="Epic Name" dataDxfId="54">
       <calculatedColumnFormula>IF(JiraDataset[[#This Row],[IssueType]]="Epic",JiraDataset[[#This Row],[Summary]],"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="27" xr3:uid="{00000000-0010-0000-0000-00001B000000}" name="Child-Issue" dataDxfId="39"/>
-    <tableColumn id="41" xr3:uid="{00000000-0010-0000-0000-000029000000}" name="Child-Issue1" dataDxfId="38"/>
-    <tableColumn id="29" xr3:uid="{00000000-0010-0000-0000-00001D000000}" name="Child-Issue2" dataDxfId="37"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Labels" dataDxfId="36"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Labels1" dataDxfId="35"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Labels2" dataDxfId="34"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Labels3" dataDxfId="33"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Labels4" dataDxfId="32"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Labels5" dataDxfId="31"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Labels6" dataDxfId="30"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Labels7" dataDxfId="29"/>
-    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="Labels8" dataDxfId="28"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="Labels9" dataDxfId="27"/>
-    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="Labels10" dataDxfId="26"/>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="Sprint" dataDxfId="25">
+    <tableColumn id="27" xr3:uid="{911C8FDC-5528-43FC-BDF4-D4761F03C0E5}" name="Child-Issue" dataDxfId="53"/>
+    <tableColumn id="41" xr3:uid="{AB248E07-9BFA-42CC-BC41-B4234F677BFB}" name="Child-Issue1" dataDxfId="52"/>
+    <tableColumn id="29" xr3:uid="{89D12135-F3E3-4253-844F-1B9A54169953}" name="Child-Issue2" dataDxfId="51"/>
+    <tableColumn id="12" xr3:uid="{0699B70E-673B-4238-8A66-12FC943A4812}" name="Labels" dataDxfId="50"/>
+    <tableColumn id="13" xr3:uid="{9840B81F-2CA6-4708-8C93-3E7C8F72A676}" name="Labels1" dataDxfId="49"/>
+    <tableColumn id="14" xr3:uid="{D4A99C0B-46B7-484A-842E-D62E9D5D9341}" name="Labels2" dataDxfId="48"/>
+    <tableColumn id="15" xr3:uid="{1D1C275E-5C65-4393-9663-6C5F617591E1}" name="Labels3" dataDxfId="47"/>
+    <tableColumn id="16" xr3:uid="{D823FA91-7106-42D3-9DBC-B337C509EB09}" name="Labels4" dataDxfId="46"/>
+    <tableColumn id="17" xr3:uid="{05A07F85-1763-4A66-9CBB-4A760BD03D27}" name="Labels5" dataDxfId="45"/>
+    <tableColumn id="18" xr3:uid="{16B98070-7F8A-4FC7-AD99-EA81D0BD26AB}" name="Labels6" dataDxfId="44"/>
+    <tableColumn id="19" xr3:uid="{016EAEF4-8EA9-408B-9F1A-ECFB17E81C77}" name="Labels7" dataDxfId="43"/>
+    <tableColumn id="26" xr3:uid="{8263F9EC-BF0A-46F7-BA83-6083A4262B91}" name="Labels8" dataDxfId="42"/>
+    <tableColumn id="20" xr3:uid="{389B11C5-1B22-48C0-BCA2-72F050425FA1}" name="Labels9" dataDxfId="41"/>
+    <tableColumn id="25" xr3:uid="{AE95F8A2-F7F0-4985-9AE6-4201B9792775}" name="Labels10" dataDxfId="40"/>
+    <tableColumn id="21" xr3:uid="{105F2D0F-70C1-4517-A55F-4C1DDFE85301}" name="Sprint" dataDxfId="39">
       <calculatedColumnFormula>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",IFERROR(VLOOKUP(JiraDataset[[#This Row],[Sprint Name]], Config!$D$4:$E$9, 2, FALSE), ""))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="Labels0001" dataDxfId="24">
+    <tableColumn id="22" xr3:uid="{D5984986-D838-4F87-A554-5DC4CA005452}" name="Labels0001" dataDxfId="38">
       <calculatedColumnFormula>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",_xlfn.XLOOKUP("Creation Marker", CfgAutofieldValues[Name], CfgAutofieldValues[Value]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="39" xr3:uid="{00000000-0010-0000-0000-000027000000}" name="Labels0002" dataDxfId="23">
+    <tableColumn id="39" xr3:uid="{C24E9ADD-96A8-4DBB-86A0-08D41975D750}" name="Labels0002" dataDxfId="37">
       <calculatedColumnFormula>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",_xlfn.XLOOKUP("Feature Pod Label", CfgAutofieldValues[Name], CfgAutofieldValues[Value]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Assignee" dataDxfId="22">
+    <tableColumn id="6" xr3:uid="{A6D8D5A6-43EE-415C-80C1-30372C7FE5BF}" name="Assignee" dataDxfId="36">
       <calculatedColumnFormula>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",IFERROR(VLOOKUP(JiraDataset[[#This Row],[Assignee.Name]], Config!$A$4:$B$24, 2, FALSE), ""))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="Project Key" dataDxfId="21">
+    <tableColumn id="23" xr3:uid="{51D4B5F4-C6D3-4EEC-8B1B-7BEC6E526A64}" name="Project Key" dataDxfId="35">
       <calculatedColumnFormula>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",_xlfn.XLOOKUP("Project Key", CfgAutofieldValues[Name], CfgAutofieldValues[Value]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="42" xr3:uid="{00000000-0010-0000-0000-00002A000000}" name="OrigEst" dataDxfId="20">
+    <tableColumn id="42" xr3:uid="{82B78F0D-CAEF-4615-B12A-B15ACF33913C}" name="OrigEst" dataDxfId="34">
       <calculatedColumnFormula array="1">IF(
   JiraDataset[[#This Row],[RowType]]=cfg_type_skip,
   "",
@@ -885,7 +1544,7 @@
   )
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="44" xr3:uid="{00000000-0010-0000-0000-00002C000000}" name="RowType" dataDxfId="19">
+    <tableColumn id="44" xr3:uid="{C92FD7EC-0EAB-4967-A0E5-D2427E3A55B4}" name="RowType" dataDxfId="33">
       <calculatedColumnFormula array="1">IFERROR(
     _xlfn.IFS(
         JiraDataset[[#This Row],[IssueType]] = cfg_type_comment,"SKIP",
@@ -895,91 +1554,91 @@
     cfg_type_workitem
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="Note" dataDxfId="18"/>
+    <tableColumn id="24" xr3:uid="{B63E8FC4-20B3-4755-92F2-EA1F700CA72E}" name="Note" dataDxfId="32"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="CfgComponents" displayName="CfgComponents" ref="I3:I10" totalsRowShown="0">
-  <autoFilter ref="I3:I10" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{93F2D14D-2ABD-4171-895D-1041B0893491}" name="CfgComponents" displayName="CfgComponents" ref="I3:I11" totalsRowShown="0">
+  <autoFilter ref="I3:I11" xr:uid="{93F2D14D-2ABD-4171-895D-1041B0893491}"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Component.Name"/>
+    <tableColumn id="1" xr3:uid="{10F6CCA4-1068-4FC8-AB82-E48B87DB0F71}" name="Component.Name"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium5" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="CfgFixVersions" displayName="CfgFixVersions" ref="G3:G6" totalsRowShown="0">
-  <autoFilter ref="G3:G6" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{7007FF9D-9384-422B-8DB3-300D782E5FE6}" name="CfgFixVersions" displayName="CfgFixVersions" ref="G3:G7" totalsRowShown="0">
+  <autoFilter ref="G3:G7" xr:uid="{7007FF9D-9384-422B-8DB3-300D782E5FE6}"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="FixVersion.Name"/>
+    <tableColumn id="1" xr3:uid="{E20FAA91-E54E-42EA-9BFF-2FDA27CD5D33}" name="FixVersion.Name"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium5" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="CfgIssueTypes" displayName="CfgIssueTypes" ref="K3:K7" totalsRowShown="0">
-  <autoFilter ref="K3:K7" xr:uid="{00000000-0009-0000-0100-000004000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{6F085B8C-1322-4F43-A516-588923936259}" name="CfgIssueTypes" displayName="CfgIssueTypes" ref="K3:K7" totalsRowShown="0">
+  <autoFilter ref="K3:K7" xr:uid="{6F085B8C-1322-4F43-A516-588923936259}"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="IssueType.Name"/>
+    <tableColumn id="1" xr3:uid="{A92436BC-3156-493F-B5C6-0BB6B51F89EB}" name="IssueType.Name"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium5" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="CfgPriorities" displayName="CfgPriorities" ref="O3:O9" totalsRowShown="0">
-  <autoFilter ref="O3:O9" xr:uid="{00000000-0009-0000-0100-000005000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{A6C0EE44-3F60-4588-BF11-75C3DD021846}" name="CfgPriorities" displayName="CfgPriorities" ref="O3:O9" totalsRowShown="0">
+  <autoFilter ref="O3:O9" xr:uid="{A6C0EE44-3F60-4588-BF11-75C3DD021846}"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="Priority.Name" dataDxfId="17"/>
+    <tableColumn id="1" xr3:uid="{3B3BE2ED-38C4-410B-B0BF-4A9BD9B4B974}" name="Priority.Name" dataDxfId="71"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium5" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="CfgAssignees" displayName="CfgAssignees" ref="A3:B6" totalsRowShown="0">
-  <autoFilter ref="A3:B6" xr:uid="{00000000-0009-0000-0100-000006000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{1EF5833D-4918-4C71-A990-1B275126361D}" name="CfgAssignees" displayName="CfgAssignees" ref="A3:B7" totalsRowShown="0">
+  <autoFilter ref="A3:B7" xr:uid="{1EF5833D-4918-4C71-A990-1B275126361D}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" name="Asssignee.Name"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0500-000002000000}" name="Assignee.ID"/>
+    <tableColumn id="1" xr3:uid="{7F7B4E10-E51C-443F-875D-3E6A9FD9994C}" name="Asssignee.Name"/>
+    <tableColumn id="2" xr3:uid="{3A4C6F03-89A9-4E38-8288-00D055D51CD3}" name="Assignee.ID"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium5" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{00000000-000C-0000-FFFF-FFFF06000000}" name="CfgSprints" displayName="CfgSprints" ref="D3:E5" totalsRowShown="0">
-  <autoFilter ref="D3:E5" xr:uid="{00000000-0009-0000-0100-000007000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{72674B63-54C8-47AC-9FF0-4034C2D499BA}" name="CfgSprints" displayName="CfgSprints" ref="D3:E6" totalsRowShown="0">
+  <autoFilter ref="D3:E6" xr:uid="{72674B63-54C8-47AC-9FF0-4034C2D499BA}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0600-000001000000}" name="Sprint.Name"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0600-000002000000}" name="Sprint.ID"/>
+    <tableColumn id="1" xr3:uid="{397B719B-4CC6-4F47-8F3C-168F13ED56DA}" name="Sprint.Name"/>
+    <tableColumn id="2" xr3:uid="{2FD208E7-540E-4D07-9144-6E9F3065D9DE}" name="Sprint.ID"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium5" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{00000000-000C-0000-FFFF-FFFF07000000}" name="CfgAutofieldValues" displayName="CfgAutofieldValues" ref="Q3:S6" totalsRowShown="0">
-  <autoFilter ref="Q3:S6" xr:uid="{00000000-0009-0000-0100-000008000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{383560BC-B1F2-44B6-B877-188131EFA163}" name="CfgAutofieldValues" displayName="CfgAutofieldValues" ref="Q3:S6" totalsRowShown="0">
+  <autoFilter ref="Q3:S6" xr:uid="{383560BC-B1F2-44B6-B877-188131EFA163}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0700-000001000000}" name="Name"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0700-000002000000}" name="Value"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0700-000003000000}" name="Remark" dataDxfId="16"/>
+    <tableColumn id="1" xr3:uid="{D4E1611F-A2CF-465D-A219-1759EA66687D}" name="Name"/>
+    <tableColumn id="2" xr3:uid="{174D0D86-B1AA-4BF7-AC91-FCACFC898851}" name="Value"/>
+    <tableColumn id="3" xr3:uid="{4D0493E3-2ED0-412B-9468-835FC91C2910}" name="Remark" dataDxfId="70"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium5" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{00000000-000C-0000-FFFF-FFFF08000000}" name="CfgIgnoreList" displayName="CfgIgnoreList" ref="M3:M7" totalsRowShown="0">
-  <autoFilter ref="M3:M7" xr:uid="{00000000-0009-0000-0100-000009000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{0ABE2B38-573A-4A51-8D54-C217B9D7D54F}" name="CfgIgnoreList" displayName="CfgIgnoreList" ref="M3:M7" totalsRowShown="0">
+  <autoFilter ref="M3:M7" xr:uid="{0ABE2B38-573A-4A51-8D54-C217B9D7D54F}"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0800-000001000000}" name="IgnoreList.Name"/>
+    <tableColumn id="1" xr3:uid="{1396737E-05D6-4D62-AF56-4B039C3A3607}" name="IgnoreList.Name"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium5" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1301,49 +1960,49 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F73058B-F76D-4AAE-8108-6C4469E9D8B5}">
   <dimension ref="A1:AK4"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelCol="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelCol="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="31.7109375" customWidth="1"/>
-    <col min="4" max="4" width="11.85546875" hidden="1" customWidth="1"/>
+    <col min="1" max="2" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="31.6640625" customWidth="1"/>
+    <col min="4" max="4" width="11.88671875" hidden="1" customWidth="1"/>
     <col min="5" max="5" width="33" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="46.28515625" customWidth="1"/>
-    <col min="7" max="7" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="22.5703125" customWidth="1"/>
+    <col min="6" max="6" width="15.5546875" customWidth="1"/>
+    <col min="7" max="7" width="17.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="22.5546875" customWidth="1"/>
     <col min="9" max="9" width="14" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.28515625" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" customWidth="1"/>
-    <col min="14" max="14" width="14.28515625" customWidth="1"/>
-    <col min="15" max="15" width="13" hidden="1" customWidth="1"/>
-    <col min="16" max="16" width="22.28515625" hidden="1" customWidth="1"/>
-    <col min="17" max="17" width="12.85546875" hidden="1" customWidth="1"/>
-    <col min="18" max="18" width="12.42578125" customWidth="1"/>
-    <col min="19" max="19" width="15.5703125" customWidth="1"/>
-    <col min="20" max="20" width="12.85546875" customWidth="1"/>
+    <col min="10" max="11" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.33203125" customWidth="1"/>
+    <col min="13" max="13" width="14.44140625" customWidth="1"/>
+    <col min="14" max="14" width="14.33203125" customWidth="1"/>
+    <col min="15" max="15" width="0" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="22.33203125" hidden="1" customWidth="1"/>
+    <col min="17" max="17" width="12.88671875" hidden="1" customWidth="1"/>
+    <col min="18" max="18" width="12.44140625" customWidth="1"/>
+    <col min="19" max="19" width="15.5546875" customWidth="1"/>
+    <col min="20" max="20" width="12.88671875" customWidth="1"/>
     <col min="21" max="21" width="10" customWidth="1"/>
     <col min="22" max="22" width="10" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="10" customWidth="1"/>
-    <col min="24" max="24" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="10.109375" bestFit="1" customWidth="1"/>
     <col min="25" max="30" width="10" customWidth="1" outlineLevel="1"/>
     <col min="31" max="31" width="10" customWidth="1"/>
-    <col min="32" max="32" width="8.7109375" customWidth="1" outlineLevel="1"/>
-    <col min="33" max="34" width="13.140625" customWidth="1" outlineLevel="1"/>
-    <col min="35" max="35" width="11.42578125" customWidth="1" outlineLevel="1"/>
-    <col min="36" max="37" width="13.7109375" customWidth="1" outlineLevel="1"/>
-    <col min="38" max="38" width="36.5703125" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="18.7109375" customWidth="1"/>
-    <col min="41" max="41" width="87.28515625" customWidth="1"/>
+    <col min="32" max="32" width="8.6640625" customWidth="1" outlineLevel="1"/>
+    <col min="33" max="34" width="13.109375" customWidth="1" outlineLevel="1"/>
+    <col min="35" max="35" width="11.44140625" customWidth="1" outlineLevel="1"/>
+    <col min="36" max="37" width="13.6640625" customWidth="1" outlineLevel="1"/>
+    <col min="38" max="38" width="36.5546875" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="18.6640625" customWidth="1"/>
+    <col min="41" max="41" width="87.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>2</v>
@@ -1373,106 +2032,107 @@
         <v>10</v>
       </c>
       <c r="L1" t="s">
+        <v>98</v>
+      </c>
+      <c r="M1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="N1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="P1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="Q1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="R1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="S1" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="3" t="s">
+      <c r="T1" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="3" t="s">
+      <c r="U1" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="3" t="s">
+      <c r="V1" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="3" t="s">
+      <c r="W1" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="3" t="s">
+      <c r="X1" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="3" t="s">
+      <c r="Y1" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="3" t="s">
+      <c r="Z1" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="3" t="s">
+      <c r="AA1" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="3" t="s">
+      <c r="AB1" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="3" t="s">
+      <c r="AC1" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="3" t="s">
+      <c r="AD1" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="3" t="s">
+      <c r="AE1" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="3" t="s">
+      <c r="AF1" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="3" t="s">
+      <c r="AG1" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" s="3" t="s">
+      <c r="AH1" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" s="4" t="s">
+      <c r="AI1" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="AJ1" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="AJ1" s="3" t="s">
-        <v>35</v>
-      </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A2" s="3"/>
       <c r="B2" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>35</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>36</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F2" s="3"/>
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="K2" s="3">
-        <v>1</v>
-      </c>
+        <v>82</v>
+      </c>
+      <c r="K2" s="3"/>
       <c r="L2" s="3"/>
       <c r="M2" s="3"/>
-      <c r="N2" s="3"/>
+      <c r="N2" s="3" t="str">
+        <f>IF(JiraDataset[[#This Row],[IssueType]]="Epic",JiraDataset[[#This Row],[Summary]],"")</f>
+        <v/>
+      </c>
       <c r="O2" s="3"/>
       <c r="P2" s="3"/>
       <c r="Q2" s="3"/>
@@ -1487,53 +2147,85 @@
       <c r="Z2" s="3"/>
       <c r="AA2" s="3"/>
       <c r="AB2" s="3"/>
-      <c r="AC2" s="3"/>
-      <c r="AD2" s="3"/>
-      <c r="AE2" s="8"/>
-      <c r="AF2" s="3"/>
-      <c r="AG2" s="3"/>
-      <c r="AH2" s="3"/>
-      <c r="AI2" s="3" t="s">
-        <v>39</v>
+      <c r="AC2" s="3" t="str">
+        <f>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",IFERROR(VLOOKUP(JiraDataset[[#This Row],[Sprint Name]], Config!$D$4:$E$9, 2, FALSE), ""))</f>
+        <v/>
+      </c>
+      <c r="AD2" s="3" t="str">
+        <f>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",_xlfn.XLOOKUP("Creation Marker", CfgAutofieldValues[Name], CfgAutofieldValues[Value]))</f>
+        <v/>
+      </c>
+      <c r="AE2" s="8" t="str">
+        <f>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",_xlfn.XLOOKUP("Feature Pod Label", CfgAutofieldValues[Name], CfgAutofieldValues[Value]))</f>
+        <v/>
+      </c>
+      <c r="AF2" s="3" t="str">
+        <f>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",IFERROR(VLOOKUP(JiraDataset[[#This Row],[Assignee.Name]], Config!$A$4:$B$24, 2, FALSE), ""))</f>
+        <v/>
+      </c>
+      <c r="AG2" s="3" t="str">
+        <f>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",_xlfn.XLOOKUP("Project Key", CfgAutofieldValues[Name], CfgAutofieldValues[Value]))</f>
+        <v/>
+      </c>
+      <c r="AH2" s="3" t="str" cm="1">
+        <f t="array" ref="AH2">IF(
+  JiraDataset[[#This Row],[RowType]]=cfg_type_skip,
+  "",
+  _xlfn.LET(
+    _xlpm.p, _xlfn.TEXTSPLIT(JiraDataset[[#This Row],[Estimate]], " "),
+    _xlpm.getVal, _xlfn.LAMBDA(_xlpm.u, IFERROR(VALUE(LEFT(_xlfn._xlws.FILTER(_xlpm.p, RIGHT(_xlpm.p,1)=_xlpm.u), LEN(_xlfn._xlws.FILTER(_xlpm.p, RIGHT(_xlpm.p,1)=_xlpm.u))-1)), 0)),
+    _xlpm.w, _xlpm.getVal("w"),
+    _xlpm.d, _xlpm.getVal("d"),
+    _xlpm.h, _xlpm.getVal("h"),
+    _xlpm.m, _xlpm.getVal("m"),
+    _xlpm.seconds, _xlpm.w*144000 + _xlpm.d*28800 + _xlpm.h*3600 + _xlpm.m*60,
+    IF(_xlpm.seconds=0, "", _xlpm.seconds*60)
+  )
+)</f>
+        <v/>
+      </c>
+      <c r="AI2" s="3" t="str" cm="1">
+        <f t="array" ref="AI2">IFERROR(
+    _xlfn.IFS(
+        JiraDataset[[#This Row],[IssueType]] = cfg_type_comment,"SKIP",
+        JiraDataset[[#This Row],[IssueType]] = cfg_type_skip,"SKIP",
+        JiraDataset[[#This Row],[IssueType]] = cfg_type_note,"SKIP"
+    ),
+    cfg_type_workitem
+)</f>
+        <v>SKIP</v>
       </c>
       <c r="AJ2" s="3"/>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>42</v>
+        <v>96</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>47</v>
-      </c>
+        <v>97</v>
+      </c>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
       <c r="J3" s="3" t="s">
-        <v>48</v>
+        <v>94</v>
       </c>
       <c r="K3" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L3" s="3"/>
       <c r="M3" s="3"/>
-      <c r="N3" s="3" t="s">
-        <v>42</v>
+      <c r="N3" s="3" t="str">
+        <f>IF(JiraDataset[[#This Row],[IssueType]]="Epic",JiraDataset[[#This Row],[Summary]],"")</f>
+        <v>Test, Epic</v>
       </c>
       <c r="O3" s="3"/>
       <c r="P3" s="3"/>
@@ -1549,45 +2241,79 @@
       <c r="Z3" s="3"/>
       <c r="AA3" s="3"/>
       <c r="AB3" s="3"/>
-      <c r="AC3" s="3">
-        <v>1</v>
-      </c>
-      <c r="AD3" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="AE3" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="AF3" s="3"/>
-      <c r="AG3" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="AH3" s="3">
+      <c r="AC3" s="3" t="str">
+        <f>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",IFERROR(VLOOKUP(JiraDataset[[#This Row],[Sprint Name]], Config!$D$4:$E$9, 2, FALSE), ""))</f>
+        <v/>
+      </c>
+      <c r="AD3" s="3" t="str">
+        <f>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",_xlfn.XLOOKUP("Creation Marker", CfgAutofieldValues[Name], CfgAutofieldValues[Value]))</f>
+        <v>imported</v>
+      </c>
+      <c r="AE3" s="8" t="str">
+        <f>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",_xlfn.XLOOKUP("Feature Pod Label", CfgAutofieldValues[Name], CfgAutofieldValues[Value]))</f>
+        <v>pod_test</v>
+      </c>
+      <c r="AF3" s="3" t="str">
+        <f>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",IFERROR(VLOOKUP(JiraDataset[[#This Row],[Assignee.Name]], Config!$A$4:$B$24, 2, FALSE), ""))</f>
+        <v/>
+      </c>
+      <c r="AG3" s="3" t="str">
+        <f>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",_xlfn.XLOOKUP("Project Key", CfgAutofieldValues[Name], CfgAutofieldValues[Value]))</f>
+        <v>JITTP2</v>
+      </c>
+      <c r="AH3" s="3" cm="1">
+        <f t="array" ref="AH3">IF(
+  JiraDataset[[#This Row],[RowType]]=cfg_type_skip,
+  "",
+  _xlfn.LET(
+    _xlpm.p, _xlfn.TEXTSPLIT(JiraDataset[[#This Row],[Estimate]], " "),
+    _xlpm.getVal, _xlfn.LAMBDA(_xlpm.u, IFERROR(VALUE(LEFT(_xlfn._xlws.FILTER(_xlpm.p, RIGHT(_xlpm.p,1)=_xlpm.u), LEN(_xlfn._xlws.FILTER(_xlpm.p, RIGHT(_xlpm.p,1)=_xlpm.u))-1)), 0)),
+    _xlpm.w, _xlpm.getVal("w"),
+    _xlpm.d, _xlpm.getVal("d"),
+    _xlpm.h, _xlpm.getVal("h"),
+    _xlpm.m, _xlpm.getVal("m"),
+    _xlpm.seconds, _xlpm.w*144000 + _xlpm.d*28800 + _xlpm.h*3600 + _xlpm.m*60,
+    IF(_xlpm.seconds=0, "", _xlpm.seconds*60)
+  )
+)</f>
         <v>8640000</v>
       </c>
-      <c r="AI3" s="3" t="s">
-        <v>52</v>
+      <c r="AI3" s="3" t="str" cm="1">
+        <f t="array" ref="AI3">IFERROR(
+    _xlfn.IFS(
+        JiraDataset[[#This Row],[IssueType]] = cfg_type_comment,"SKIP",
+        JiraDataset[[#This Row],[IssueType]] = cfg_type_skip,"SKIP",
+        JiraDataset[[#This Row],[IssueType]] = cfg_type_note,"SKIP"
+    ),
+    cfg_type_workitem
+)</f>
+        <v>WorkItem</v>
       </c>
       <c r="AJ3" s="3"/>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3" t="str">
-        <f>Config!$G$4</f>
-        <v>JITTP Version 1</v>
-      </c>
+    <row r="4" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A4" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="14"/>
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
       <c r="J4" s="3"/>
       <c r="K4" s="3"/>
-      <c r="L4" s="3"/>
+      <c r="L4" s="15">
+        <v>1</v>
+      </c>
       <c r="M4" s="3"/>
-      <c r="N4" s="3" t="str">
+      <c r="N4" s="15" t="str">
         <f>IF(JiraDataset[[#This Row],[IssueType]]="Epic",JiraDataset[[#This Row],[Summary]],"")</f>
         <v/>
       </c>
@@ -1605,11 +2331,11 @@
       <c r="Z4" s="3"/>
       <c r="AA4" s="3"/>
       <c r="AB4" s="3"/>
-      <c r="AC4" s="3" t="str">
+      <c r="AC4" s="15" t="str">
         <f>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",IFERROR(VLOOKUP(JiraDataset[[#This Row],[Sprint Name]], Config!$D$4:$E$9, 2, FALSE), ""))</f>
         <v/>
       </c>
-      <c r="AD4" s="3" t="str">
+      <c r="AD4" s="15" t="str">
         <f>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",_xlfn.XLOOKUP("Creation Marker", CfgAutofieldValues[Name], CfgAutofieldValues[Value]))</f>
         <v>imported</v>
       </c>
@@ -1617,15 +2343,15 @@
         <f>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",_xlfn.XLOOKUP("Feature Pod Label", CfgAutofieldValues[Name], CfgAutofieldValues[Value]))</f>
         <v>pod_test</v>
       </c>
-      <c r="AF4" s="3" t="str">
+      <c r="AF4" s="15" t="str">
         <f>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",IFERROR(VLOOKUP(JiraDataset[[#This Row],[Assignee.Name]], Config!$A$4:$B$24, 2, FALSE), ""))</f>
         <v/>
       </c>
-      <c r="AG4" s="3" t="str">
+      <c r="AG4" s="15" t="str">
         <f>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",_xlfn.XLOOKUP("Project Key", CfgAutofieldValues[Name], CfgAutofieldValues[Value]))</f>
         <v>JITTP2</v>
       </c>
-      <c r="AH4" s="3" t="str" cm="1">
+      <c r="AH4" s="15" t="str" cm="1">
         <f t="array" ref="AH4">IF(
   JiraDataset[[#This Row],[RowType]]=cfg_type_skip,
   "",
@@ -1642,7 +2368,7 @@
 )</f>
         <v/>
       </c>
-      <c r="AI4" s="3" t="str" cm="1">
+      <c r="AI4" s="15" t="str" cm="1">
         <f t="array" ref="AI4">IFERROR(
     _xlfn.IFS(
         JiraDataset[[#This Row],[IssueType]] = cfg_type_comment,"SKIP",
@@ -1656,258 +2382,287 @@
       <c r="AJ4" s="3"/>
     </row>
   </sheetData>
+  <protectedRanges>
+    <protectedRange sqref="A1:A1048576 D4:N1048576 P4:AD1048576 C1:AB3" name="User Input"/>
+    <protectedRange algorithmName="SHA-512" hashValue="tpheD+JLADkhiyalt6vInlMwkILPZx4PVQN/k2vmwjOBdYUuHaXCrwtObHeFz5dJh9f853O84pZ1Rn9Ujz33+A==" saltValue="9ir5NB4CJc/69S/Eh84/mA==" spinCount="100000" sqref="AC1:AI3 AE4:AK1048576" name="Computed values"/>
+  </protectedRanges>
+  <phoneticPr fontId="18" type="noConversion"/>
   <conditionalFormatting sqref="A2:A4 C2:C4">
-    <cfRule type="containsText" dxfId="15" priority="429" operator="containsText" text="blocker">
+    <cfRule type="containsText" dxfId="31" priority="429" operator="containsText" text="blocker">
       <formula>NOT(ISERROR(SEARCH("blocker",A2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="14" priority="430" operator="containsText" text="critical">
+    <cfRule type="containsText" dxfId="30" priority="430" operator="containsText" text="critical">
       <formula>NOT(ISERROR(SEARCH("critical",A2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="13" priority="431" operator="containsText" text="High">
+    <cfRule type="containsText" dxfId="29" priority="431" operator="containsText" text="High">
       <formula>NOT(ISERROR(SEARCH("High",A2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="12" priority="432" operator="containsText" text="Medium">
+    <cfRule type="containsText" dxfId="28" priority="432" operator="containsText" text="Medium">
       <formula>NOT(ISERROR(SEARCH("Medium",A2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:A4">
-    <cfRule type="containsBlanks" dxfId="11" priority="493">
+    <cfRule type="containsBlanks" dxfId="27" priority="493">
       <formula>LEN(TRIM(A2))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:AJ4">
-    <cfRule type="expression" dxfId="10" priority="409" stopIfTrue="1">
+    <cfRule type="expression" dxfId="26" priority="409" stopIfTrue="1">
       <formula>$B2=cfg_type_comment</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="9" priority="410">
+    <cfRule type="expression" dxfId="25" priority="410">
       <formula>$B2=cfg_type_skip</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="411">
+    <cfRule type="expression" dxfId="24" priority="411">
       <formula>$B2=cfg_type_note</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:B4">
-    <cfRule type="containsText" dxfId="7" priority="413" operator="containsText" text="epic">
+    <cfRule type="containsText" dxfId="23" priority="413" operator="containsText" text="epic">
       <formula>NOT(ISERROR(SEARCH("epic",B2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="6" priority="427" operator="containsText" text="story">
+    <cfRule type="containsText" dxfId="22" priority="427" operator="containsText" text="story">
       <formula>NOT(ISERROR(SEARCH("story",B2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="5" priority="433" operator="containsText" text="task">
+    <cfRule type="containsText" dxfId="21" priority="433" operator="containsText" text="task">
       <formula>NOT(ISERROR(SEARCH("task",B2)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="4" priority="492">
+    <cfRule type="containsBlanks" dxfId="20" priority="492">
       <formula>LEN(TRIM(B2))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:AJ4">
-    <cfRule type="expression" dxfId="3" priority="1">
+    <cfRule type="expression" dxfId="19" priority="1">
       <formula>$B2="Epic"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="2">
+    <cfRule type="expression" dxfId="18" priority="2">
       <formula>$B2="Story"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:C4">
-    <cfRule type="containsBlanks" dxfId="1" priority="494">
+    <cfRule type="containsBlanks" dxfId="17" priority="494">
       <formula>LEN(TRIM(C2))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:L4">
-    <cfRule type="containsBlanks" dxfId="0" priority="412">
+    <cfRule type="containsBlanks" dxfId="16" priority="412">
       <formula>LEN(TRIM(K2))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations xWindow="1573" yWindow="665" count="20">
-    <dataValidation type="whole" allowBlank="1" showErrorMessage="1" prompt="It must be a number (integer). This reference is only used during the import process." sqref="K2:L3" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="whole" allowBlank="1" showErrorMessage="1" prompt="It must be a number (integer). This reference is only used during the import process." sqref="K2:L3" xr:uid="{005E18F2-4447-4781-8F18-5A58920A4F75}">
       <formula1>1</formula1>
       <formula2>1000</formula2>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" error="must be a valid component" sqref="J2:J4" xr:uid="{00000000-0002-0000-0000-000001000000}"/>
-    <dataValidation type="whole" allowBlank="1" showErrorMessage="1" promptTitle="Warning" prompt="This field should be the Issue ID or Issue Key of the child tasks. (upstream linkage is not possible)._x000a__x000a__x000a_To link Epics and Stories, use the Epic Link from the Story Issue." sqref="O2:Q4" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" error="must be a valid component" sqref="J2:J4" xr:uid="{386E3B68-2486-4DDE-BEB1-45F897521149}"/>
+    <dataValidation type="whole" allowBlank="1" showErrorMessage="1" promptTitle="Warning" prompt="This field should be the Issue ID or Issue Key of the child tasks. (upstream linkage is not possible)._x000a__x000a__x000a_To link Epics and Stories, use the Epic Link from the Story Issue." sqref="O2:Q4" xr:uid="{D7BD960D-9CEA-4120-B2E3-2AE0D4661093}">
       <formula1>1</formula1>
       <formula2>1000</formula2>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Note" prompt="The content of this column will be ignored during the Jira import." sqref="AJ2:AJ4" xr:uid="{00000000-0002-0000-0000-000003000000}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Permissions" prompt="Updating Existing Issues requires global admin permissions" sqref="D2:D4" xr:uid="{00000000-0002-0000-0000-000004000000}"/>
-    <dataValidation type="whole" allowBlank="1" showErrorMessage="1" promptTitle="Warning" prompt="Use the Issue ID value to link this work item to an Epic_x000a__x000a_Story Issues are not Child-Issues and should have Epic Link instead. " sqref="M2:M4" xr:uid="{00000000-0002-0000-0000-000005000000}">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Note" prompt="The content of this column will be ignored during the Jira import." sqref="AJ2:AJ4" xr:uid="{2DA3EDB6-7635-4349-8860-B614B5B71275}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Permissions" prompt="Updating Existing Issues requires global admin permissions" sqref="D2:D4" xr:uid="{D5E4A4BB-53C8-42DF-9B52-F5E00AC6407B}"/>
+    <dataValidation type="whole" allowBlank="1" showErrorMessage="1" promptTitle="Warning" prompt="Use the Issue ID value to link this work item to an Epic_x000a__x000a_Story Issues are not Child-Issues and should have Epic Link instead. " sqref="M2:M4" xr:uid="{16C14239-D6AA-4935-8809-57760481D8F1}">
       <formula1>1</formula1>
       <formula2>1000</formula2>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="It must be a number (integer). This reference is only used during the import process." sqref="K1" xr:uid="{00000000-0002-0000-0000-000006000000}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Use the Issue ID value to link this work item to an Epic_x000a__x000a_Story Issues are not Child-Issues and should have Epic Link instead. " sqref="M1" xr:uid="{00000000-0002-0000-0000-000007000000}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="This field should be the Issue ID or Issue Key of the child tasks. (upstream linkage is not possible)._x000a__x000a__x000a_To link Epics and Stories, use the Epic Link from the Story Issue." sqref="O1:Q1" xr:uid="{00000000-0002-0000-0000-000008000000}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" error="must be a valid fixversion" promptTitle="AUTOMATIC FIELD" prompt="Do not manually edit these!" sqref="AC2:AC4 AF1:AH4" xr:uid="{00000000-0002-0000-0000-000009000000}"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="must be a valid component" sqref="H2:H4" xr:uid="{00000000-0002-0000-0000-00000A000000}">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="It must be a number (integer). This reference is only used during the import process." sqref="K1" xr:uid="{9C637146-F2E3-4D08-87A8-F70FD358E47E}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Use the Issue ID value to link this work item to an Epic_x000a__x000a_Story Issues are not Child-Issues and should have Epic Link instead. " sqref="M1" xr:uid="{A61138FD-C2B2-49D2-810B-69EAE2230B73}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="This field should be the Issue ID or Issue Key of the child tasks. (upstream linkage is not possible)._x000a__x000a__x000a_To link Epics and Stories, use the Epic Link from the Story Issue." sqref="O1:Q1" xr:uid="{BE6B7503-A11A-4130-9D63-988F0CFED80E}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" error="must be a valid fixversion" promptTitle="AUTOMATIC FIELD" prompt="Do not manually edit these!" sqref="AC2:AC4 AF1:AH4" xr:uid="{893DA5FE-9FD0-4D28-BBD0-3D7AEDECEACB}"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="must be a valid component" sqref="H2:H4" xr:uid="{65EDED96-6789-400B-B504-6BC3F5A79E70}">
       <formula1>INDIRECT("CfgComponents[Component.Name]")</formula1>
     </dataValidation>
-    <dataValidation type="list" errorStyle="warning" showErrorMessage="1" error="must be a valid fixversion" sqref="G2:G4" xr:uid="{00000000-0002-0000-0000-00000B000000}">
+    <dataValidation type="list" errorStyle="warning" showErrorMessage="1" error="must be a valid fixversion" sqref="G2:G4" xr:uid="{44FDC20A-8BF5-49B5-9D2C-3A1FE5A7D835}">
       <formula1>INDIRECT("CfgAssignees[Asssignee.Name]")</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="must be a valid component" sqref="I2:I4" xr:uid="{00000000-0002-0000-0000-00000C000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="must be a valid component" sqref="I2:I4" xr:uid="{A898E2E7-BC45-4B88-BA1E-4AAA377361D4}">
       <formula1>INDIRECT("CfgSprints[Sprint.Name]")</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showErrorMessage="1" promptTitle="Warning" prompt="Field only used for Epic Issues, so they can be referenced in Story Issues via the Epic Link field.," sqref="L2:L3 N2:N3" xr:uid="{00000000-0002-0000-0000-00000D000000}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Field only used for Epic Issues, so they can be referenced in Story Issues via the Epic Link field.," sqref="L1" xr:uid="{00000000-0002-0000-0000-00000E000000}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="It must be a number (integer) or the Work Item key. This reference is only used during the import process to set the parent." sqref="L1" xr:uid="{00000000-0002-0000-0000-00000F000000}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Field only used for Epic work item, so they can be referenced in Story work items via the Epic Link field. _x000a_DC Only" sqref="N1" xr:uid="{00000000-0002-0000-0000-000010000000}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" error="must be a valid fixversion" promptTitle="Creation Marker (Config Sheet)" prompt="Do not manually edit these!" sqref="AD1:AD4" xr:uid="{00000000-0002-0000-0000-000011000000}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" error="must be a valid fixversion" promptTitle="Feature Pod Label (Config Sheet)" prompt="Do not manually edit these!" sqref="AE1:AE4" xr:uid="{00000000-0002-0000-0000-000012000000}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" error="must be a valid fixversion" promptTitle="AUTOMATIC FIELD" prompt="Do not manually edit these! SKIP types won't be imported into Jira" sqref="AI1:AI4" xr:uid="{00000000-0002-0000-0000-000013000000}"/>
+    <dataValidation allowBlank="1" showErrorMessage="1" promptTitle="Warning" prompt="Field only used for Epic Issues, so they can be referenced in Story Issues via the Epic Link field.," sqref="N2:N3 L2:L3" xr:uid="{541AD292-0123-4B65-9663-081991FDF0C1}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Field only used for Epic Issues, so they can be referenced in Story Issues via the Epic Link field.," sqref="L1" xr:uid="{64C73155-DEE7-497D-8A98-01E54655ACA8}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="It must be a number (integer) or the Work Item key. This reference is only used during the import process to set the parent." sqref="L1" xr:uid="{8A2BE248-5762-43AD-9C47-C5A92A2E2357}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Field only used for Epic work item, so they can be referenced in Story work items via the Epic Link field. _x000a_DC Only" sqref="N1" xr:uid="{E8F6E005-1F9B-40F3-B24C-E2A3D286C532}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" error="must be a valid fixversion" promptTitle="Creation Marker (Config Sheet)" prompt="Do not manually edit these!" sqref="AD1:AD4" xr:uid="{412C516D-E091-4DDD-9C14-C33AC653C143}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" error="must be a valid fixversion" promptTitle="Feature Pod Label (Config Sheet)" prompt="Do not manually edit these!" sqref="AE1:AE4" xr:uid="{D2234141-379F-4413-AB08-6835BD9FF967}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" error="must be a valid fixversion" promptTitle="AUTOMATIC FIELD" prompt="Do not manually edit these! SKIP types won't be imported into Jira" sqref="AI1:AI4" xr:uid="{5A336857-7D14-4900-8734-BED680BE5154}"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xWindow="1573" yWindow="665" count="3">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{5EEBB8D5-878D-4D0E-9267-0919B5A1B925}">
+          <x14:formula1>
+            <xm:f>Config!$O$4:$O$10</xm:f>
+          </x14:formula1>
+          <xm:sqref>A2:A4</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Issue Type" xr:uid="{28BF52BF-C0B0-4D22-B02F-F1408D5A055B}">
+          <x14:formula1>
+            <xm:f>Config!$U$4:$U$33</xm:f>
+          </x14:formula1>
+          <xm:sqref>B2:B4</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="must be a valid fixversion" xr:uid="{7708D6E2-1D6B-41D8-A9EE-0E87219BA8EA}">
+          <x14:formula1>
+            <xm:f>Config!$G$4:$G$8</xm:f>
+          </x14:formula1>
+          <xm:sqref>F2:F4</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2D54512-1380-4F02-BB23-352387C91232}">
   <dimension ref="A1:V21"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="29.7109375" customWidth="1"/>
+    <col min="1" max="1" width="29.6640625" customWidth="1"/>
     <col min="2" max="2" width="49" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.28515625" customWidth="1"/>
-    <col min="4" max="5" width="18.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.28515625" customWidth="1"/>
-    <col min="7" max="7" width="18.5703125" customWidth="1"/>
-    <col min="8" max="8" width="4.28515625" customWidth="1"/>
-    <col min="9" max="9" width="19.140625" customWidth="1"/>
-    <col min="10" max="10" width="4.28515625" customWidth="1"/>
-    <col min="11" max="11" width="18.5703125" customWidth="1"/>
-    <col min="12" max="12" width="4.28515625" customWidth="1"/>
-    <col min="13" max="13" width="17.5703125" customWidth="1"/>
-    <col min="14" max="14" width="4.28515625" customWidth="1"/>
-    <col min="15" max="15" width="18.7109375" customWidth="1"/>
-    <col min="16" max="16" width="4.28515625" customWidth="1"/>
-    <col min="17" max="18" width="18.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.33203125" customWidth="1"/>
+    <col min="4" max="5" width="18.6640625" customWidth="1"/>
+    <col min="6" max="6" width="4.33203125" customWidth="1"/>
+    <col min="7" max="7" width="18.5546875" customWidth="1"/>
+    <col min="8" max="8" width="4.33203125" customWidth="1"/>
+    <col min="9" max="9" width="19.109375" customWidth="1"/>
+    <col min="10" max="10" width="4.33203125" customWidth="1"/>
+    <col min="11" max="11" width="18.5546875" customWidth="1"/>
+    <col min="12" max="12" width="4.33203125" customWidth="1"/>
+    <col min="13" max="13" width="17.5546875" customWidth="1"/>
+    <col min="14" max="14" width="4.33203125" customWidth="1"/>
+    <col min="15" max="15" width="18.6640625" customWidth="1"/>
+    <col min="16" max="16" width="4.33203125" customWidth="1"/>
+    <col min="17" max="18" width="18.6640625" customWidth="1"/>
     <col min="19" max="19" width="35" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="22.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="B1" s="12"/>
-      <c r="D1" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="E1" s="12"/>
+    <row r="1" spans="1:22" ht="21" x14ac:dyDescent="0.4">
+      <c r="A1" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="B1" s="11"/>
+      <c r="D1" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="E1" s="11"/>
       <c r="G1" s="6" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="I1" s="6" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="K1" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M1" s="6" t="s">
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="O1" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="Q1" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="R1" s="12"/>
-      <c r="S1" s="12"/>
+      <c r="Q1" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="R1" s="11"/>
+      <c r="S1" s="11"/>
       <c r="U1" s="6" t="s">
-        <v>61</v>
+        <v>83</v>
       </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A2" s="11" t="s">
-        <v>62</v>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A2" s="12" t="s">
+        <v>86</v>
       </c>
       <c r="B2" s="12"/>
       <c r="C2" s="7"/>
-      <c r="D2" s="11" t="s">
-        <v>63</v>
+      <c r="D2" s="12" t="s">
+        <v>87</v>
       </c>
       <c r="E2" s="12"/>
       <c r="F2" s="7"/>
       <c r="G2" s="10" t="s">
-        <v>64</v>
+        <v>88</v>
       </c>
       <c r="H2" s="10"/>
       <c r="I2" s="10" t="s">
-        <v>65</v>
+        <v>89</v>
       </c>
       <c r="J2" s="10"/>
-      <c r="K2" s="11" t="s">
-        <v>66</v>
+      <c r="K2" s="12" t="s">
+        <v>90</v>
       </c>
       <c r="L2" s="12"/>
       <c r="M2" s="9" t="s">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="N2" s="9"/>
       <c r="O2" s="10" t="s">
-        <v>68</v>
+        <v>92</v>
       </c>
       <c r="P2" s="10"/>
-      <c r="Q2" s="11"/>
+      <c r="Q2" s="12"/>
       <c r="R2" s="12"/>
       <c r="S2" s="9"/>
       <c r="T2" s="7"/>
       <c r="U2" s="9" t="s">
-        <v>69</v>
+        <v>93</v>
       </c>
       <c r="V2" s="9"/>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="B3" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="D3" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="E3" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="G3" t="s">
         <v>74</v>
       </c>
       <c r="I3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="K3" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="M3" t="s">
+        <v>79</v>
+      </c>
+      <c r="O3" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>60</v>
+      </c>
+      <c r="R3" t="s">
+        <v>61</v>
+      </c>
+      <c r="S3" t="s">
         <v>77</v>
       </c>
-      <c r="O3" t="s">
-        <v>78</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>79</v>
-      </c>
-      <c r="R3" t="s">
-        <v>80</v>
-      </c>
-      <c r="S3" t="s">
-        <v>81</v>
-      </c>
       <c r="U3" s="5" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="B4" t="s">
-        <v>83</v>
+        <v>50</v>
       </c>
       <c r="D4" t="s">
         <v>47</v>
@@ -1916,223 +2671,231 @@
         <v>1</v>
       </c>
       <c r="G4" t="s">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="I4" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K4" t="s">
-        <v>86</v>
+        <v>39</v>
       </c>
       <c r="M4" t="s">
-        <v>87</v>
+        <v>34</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>88</v>
+        <v>38</v>
       </c>
       <c r="Q4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="R4" t="s">
+        <v>95</v>
+      </c>
+      <c r="S4" s="7"/>
+      <c r="U4" t="str" cm="1">
+        <f t="array" aca="1" ref="U4:U11" ca="1">_xlfn.UNIQUE((_xlfn.VSTACK(INDIRECT("CfgIssueTypes[IssueType.Name]"),INDIRECT("CfgIgnoreList[IgnoreList.Name]"))))</f>
+        <v>Story</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>106</v>
+      </c>
+      <c r="B5" t="s">
         <v>51</v>
       </c>
-      <c r="S4" s="7"/>
-      <c r="U4" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>89</v>
-      </c>
-      <c r="B5" t="s">
-        <v>90</v>
-      </c>
       <c r="D5" t="s">
-        <v>91</v>
+        <v>48</v>
       </c>
       <c r="E5">
         <v>2</v>
       </c>
       <c r="G5" t="s">
-        <v>92</v>
+        <v>69</v>
       </c>
       <c r="I5" t="s">
-        <v>46</v>
+        <v>76</v>
       </c>
       <c r="K5" t="s">
-        <v>93</v>
+        <v>37</v>
       </c>
       <c r="M5" t="s">
-        <v>94</v>
+        <v>45</v>
       </c>
       <c r="O5" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>57</v>
+      </c>
+      <c r="R5" t="s">
         <v>40</v>
       </c>
-      <c r="Q5" t="s">
-        <v>95</v>
-      </c>
-      <c r="R5" t="s">
-        <v>49</v>
-      </c>
       <c r="S5" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="U5" t="s">
-        <v>93</v>
+        <v>84</v>
+      </c>
+      <c r="U5" t="str">
+        <f ca="1"/>
+        <v>Task</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="B6" t="s">
-        <v>98</v>
+        <v>52</v>
       </c>
       <c r="G6" t="s">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="I6" t="s">
         <v>99</v>
       </c>
       <c r="K6" t="s">
-        <v>100</v>
+        <v>41</v>
       </c>
       <c r="M6" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="Q6" t="s">
-        <v>102</v>
+        <v>49</v>
       </c>
       <c r="R6" t="s">
-        <v>50</v>
+        <v>108</v>
       </c>
       <c r="S6" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="U6" t="s">
-        <v>100</v>
+        <v>85</v>
+      </c>
+      <c r="U6" t="str">
+        <f ca="1"/>
+        <v>Bug</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
       <c r="I7" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="K7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M7" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="U7" t="s">
-        <v>41</v>
+        <v>43</v>
+      </c>
+      <c r="U7" t="str">
+        <f ca="1"/>
+        <v>Epic</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.3">
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
       <c r="I8" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="U8" t="s">
-        <v>87</v>
+        <v>55</v>
+      </c>
+      <c r="U8" t="str">
+        <f ca="1"/>
+        <v>Comment</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.3">
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
       <c r="I9" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="U9" t="s">
-        <v>94</v>
+        <v>56</v>
+      </c>
+      <c r="U9" t="str">
+        <f ca="1"/>
+        <v>Skip</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
       <c r="I10" t="s">
-        <v>110</v>
-      </c>
-      <c r="U10" t="s">
-        <v>35</v>
+        <v>103</v>
+      </c>
+      <c r="U10" t="str">
+        <f ca="1"/>
+        <v>Note</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
-      <c r="U11" t="s">
-        <v>52</v>
+      <c r="U11" t="str">
+        <f ca="1"/>
+        <v>WorkItem</v>
       </c>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
     </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.3">
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
     </row>
-    <row r="17" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
     </row>
-    <row r="18" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
     </row>
-    <row r="19" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D19" s="2"/>
       <c r="E19" s="2"/>
     </row>
-    <row r="20" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D20" s="2"/>
       <c r="E20" s="2"/>
     </row>
-    <row r="21" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D21" s="2"/>
       <c r="E21" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="Q1:S1"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="A1:B1"/>
     <mergeCell ref="A2:B2"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="K2:L2"/>
     <mergeCell ref="Q2:R2"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="Q1:S1"/>
   </mergeCells>
+  <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
   <tableParts count="8">
-    <tablePart r:id="rId1"/>
     <tablePart r:id="rId2"/>
     <tablePart r:id="rId3"/>
     <tablePart r:id="rId4"/>
@@ -2140,6 +2903,294 @@
     <tablePart r:id="rId6"/>
     <tablePart r:id="rId7"/>
     <tablePart r:id="rId8"/>
+    <tablePart r:id="rId9"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100FB038601AF41D04A88A4BD446922F1A8" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="e8d32171d27ae41230d53456f24efae5">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c471fd26-9765-4fbe-b6fd-c17c1e55c974" xmlns:ns3="9df69692-83aa-4c55-88c1-62abad05f4fe" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1f2fb84de5621acf32f385a2ba90fb29" ns2:_="" ns3:_="">
+    <xsd:import namespace="c471fd26-9765-4fbe-b6fd-c17c1e55c974"/>
+    <xsd:import namespace="9df69692-83aa-4c55-88c1-62abad05f4fe"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="c471fd26-9765-4fbe-b6fd-c17c1e55c974" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="10" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="12" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="19cd79a3-f605-49ec-b3bf-026e10135845" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="14" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="17" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="18" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="19" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="9df69692-83aa-4c55-88c1-62abad05f4fe" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="TaxCatchAll" ma:index="13" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{8a6cf1a7-3894-43e8-8094-3feccbd66ed9}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="9df69692-83aa-4c55-88c1-62abad05f4fe">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithUsers" ma:index="20" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="21" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c471fd26-9765-4fbe-b6fd-c17c1e55c974">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="9df69692-83aa-4c55-88c1-62abad05f4fe" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2C983B91-58B3-4C2C-AC55-FFEC9F0DB5F6}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="c471fd26-9765-4fbe-b6fd-c17c1e55c974"/>
+    <ds:schemaRef ds:uri="9df69692-83aa-4c55-88c1-62abad05f4fe"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{156C3F15-3876-4FBB-8F24-692088DE8D9F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9FFE630F-6530-4863-AB67-8477539A0000}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="c471fd26-9765-4fbe-b6fd-c17c1e55c974"/>
+    <ds:schemaRef ds:uri="9df69692-83aa-4c55-88c1-62abad05f4fe"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/resources/templates/ImportTemplate.xlsx
+++ b/resources/templates/ImportTemplate.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workdir\temp\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workdir\DeerHide\sources\jira-toolkit\resources\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77E3885F-31A5-4652-AED3-4A4A21786D96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC33135F-B90A-4C24-BAC9-7A123C771B85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="252" yWindow="6408" windowWidth="30696" windowHeight="12420" xr2:uid="{1FA076D1-0294-4A97-AB8C-3ADE2BC9CEA1}"/>
+    <workbookView xWindow="5376" yWindow="5376" windowWidth="34560" windowHeight="18600" activeTab="1" xr2:uid="{1FA076D1-0294-4A97-AB8C-3ADE2BC9CEA1}"/>
   </bookViews>
   <sheets>
     <sheet name="Dataset" sheetId="1" r:id="rId1"/>
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="110">
   <si>
     <t>IssueType</t>
   </si>
@@ -245,6 +245,9 @@
     <t>Creation Marker</t>
   </si>
   <si>
+    <t>JV</t>
+  </si>
+  <si>
     <t>Issue Type</t>
   </si>
   <si>
@@ -396,12 +399,6 @@
   </si>
   <si>
     <t>pod_test</t>
-  </si>
-  <si>
-    <t>High</t>
-  </si>
-  <si>
-    <t>Test, Task</t>
   </si>
 </sst>
 </file>
@@ -925,7 +922,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -956,15 +953,6 @@
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="16" applyAlignment="1">
       <alignment horizontal="left" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -1011,7 +999,7 @@
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="72">
+  <dxfs count="56">
     <dxf>
       <fill>
         <patternFill patternType="darkUp"/>
@@ -1155,146 +1143,10 @@
       </fill>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill patternType="darkUp"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor auto="1"/>
-          <bgColor rgb="FFFF5050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDAF2D0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF2CEEF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor auto="1"/>
-          <bgColor rgb="FFFF5050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.89996032593768116"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.34998626667073579"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="1" tint="4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor auto="1"/>
-          <bgColor rgb="FFF9B1AB"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFCC99"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF99CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF6699"/>
-        </patternFill>
-      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="1" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
     </dxf>
     <dxf>
       <alignment vertical="top"/>
@@ -1437,12 +1289,6 @@
     </dxf>
     <dxf>
       <alignment vertical="top"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="1" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1474,61 +1320,63 @@
 <file path=xl/namedSheetViews/namedSheetView1.xml><?xml version="1.0" encoding="utf-8"?>
 <namedSheetViews xmlns="http://schemas.microsoft.com/office/spreadsheetml/2019/namedsheetviews" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <namedSheetView name="View1" id="{77233F75-225A-4D7F-8A86-543E0A8C6E58}">
-    <nsvFilter filterId="{933FCFD5-1AB1-4076-B5DD-E2B69F5EB3F2}" ref="A1:AJ4" tableId="1"/>
+    <nsvFilter filterId="{933FCFD5-1AB1-4076-B5DD-E2B69F5EB3F2}" ref="A1:AJ3" tableId="1"/>
   </namedSheetView>
 </namedSheetViews>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{933FCFD5-1AB1-4076-B5DD-E2B69F5EB3F2}" name="JiraDataset" displayName="JiraDataset" ref="A1:AJ4" totalsRowShown="0" headerRowDxfId="69" dataDxfId="68">
-  <autoFilter ref="A1:AJ4" xr:uid="{933FCFD5-1AB1-4076-B5DD-E2B69F5EB3F2}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{933FCFD5-1AB1-4076-B5DD-E2B69F5EB3F2}" name="JiraDataset" displayName="JiraDataset" ref="A1:AJ3" totalsRowShown="0" headerRowDxfId="55" dataDxfId="54">
+  <autoFilter ref="A1:AJ3" xr:uid="{933FCFD5-1AB1-4076-B5DD-E2B69F5EB3F2}"/>
   <tableColumns count="36">
-    <tableColumn id="3" xr3:uid="{AF2EC907-349C-4651-852D-6E39C61E17FF}" name="Priority" dataDxfId="67"/>
-    <tableColumn id="2" xr3:uid="{E90C51F2-4386-421F-A3E4-E2CA9D43D396}" name="IssueType" dataDxfId="66"/>
-    <tableColumn id="1" xr3:uid="{BBAD373B-BA13-47E4-9F74-565F4D9E9680}" name="Summary" dataDxfId="65"/>
-    <tableColumn id="4" xr3:uid="{026E5B97-FAFC-4E46-860E-0B0C976B1148}" name="Issue Key" dataDxfId="64"/>
-    <tableColumn id="5" xr3:uid="{A2C262E8-D544-4669-99F1-151EDE081654}" name="Description" dataDxfId="63"/>
-    <tableColumn id="7" xr3:uid="{0FAD1ACC-432E-462C-8B89-71540710BCB5}" name="FixVersion" dataDxfId="62"/>
-    <tableColumn id="28" xr3:uid="{07F3030C-7187-4B16-BBDB-798304851975}" name="Assignee.Name" dataDxfId="61"/>
-    <tableColumn id="8" xr3:uid="{8C7FB8DB-A85B-4189-93D8-0F0D4EEEF81B}" name="Component" dataDxfId="60"/>
-    <tableColumn id="9" xr3:uid="{DC5101A8-1204-44D2-BC2C-FEE1A4EFE7C1}" name="Sprint Name" dataDxfId="59"/>
-    <tableColumn id="40" xr3:uid="{1F406792-7ED2-4476-8FF4-4C6ABA231C97}" name="Estimate" dataDxfId="58"/>
-    <tableColumn id="10" xr3:uid="{70B7C471-B624-430B-8992-4711F27BB17E}" name="Issue ID" dataDxfId="57"/>
-    <tableColumn id="30" xr3:uid="{938D6CA2-8309-4146-9B62-E8CDFAB7B1C9}" name="Parent" dataDxfId="56"/>
-    <tableColumn id="11" xr3:uid="{594BD56F-7D1D-408F-BEDC-6BB9854C71A1}" name="Epic Link" dataDxfId="55"/>
-    <tableColumn id="33" xr3:uid="{3A94D4B2-1A5B-4BBF-B398-E56D2BB7F948}" name="Epic Name" dataDxfId="54">
+    <tableColumn id="3" xr3:uid="{AF2EC907-349C-4651-852D-6E39C61E17FF}" name="Priority" dataDxfId="53"/>
+    <tableColumn id="2" xr3:uid="{E90C51F2-4386-421F-A3E4-E2CA9D43D396}" name="IssueType" dataDxfId="52"/>
+    <tableColumn id="1" xr3:uid="{BBAD373B-BA13-47E4-9F74-565F4D9E9680}" name="Summary" dataDxfId="51"/>
+    <tableColumn id="4" xr3:uid="{026E5B97-FAFC-4E46-860E-0B0C976B1148}" name="Issue Key" dataDxfId="50"/>
+    <tableColumn id="5" xr3:uid="{A2C262E8-D544-4669-99F1-151EDE081654}" name="Description" dataDxfId="49"/>
+    <tableColumn id="7" xr3:uid="{0FAD1ACC-432E-462C-8B89-71540710BCB5}" name="FixVersion" dataDxfId="48">
+      <calculatedColumnFormula>Config!$G$4</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="28" xr3:uid="{07F3030C-7187-4B16-BBDB-798304851975}" name="Assignee.Name" dataDxfId="47"/>
+    <tableColumn id="8" xr3:uid="{8C7FB8DB-A85B-4189-93D8-0F0D4EEEF81B}" name="Component" dataDxfId="46"/>
+    <tableColumn id="9" xr3:uid="{DC5101A8-1204-44D2-BC2C-FEE1A4EFE7C1}" name="Sprint Name" dataDxfId="45"/>
+    <tableColumn id="40" xr3:uid="{1F406792-7ED2-4476-8FF4-4C6ABA231C97}" name="Estimate" dataDxfId="44"/>
+    <tableColumn id="10" xr3:uid="{70B7C471-B624-430B-8992-4711F27BB17E}" name="Issue ID" dataDxfId="43"/>
+    <tableColumn id="30" xr3:uid="{938D6CA2-8309-4146-9B62-E8CDFAB7B1C9}" name="Parent" dataDxfId="42"/>
+    <tableColumn id="11" xr3:uid="{594BD56F-7D1D-408F-BEDC-6BB9854C71A1}" name="Epic Link" dataDxfId="41"/>
+    <tableColumn id="33" xr3:uid="{3A94D4B2-1A5B-4BBF-B398-E56D2BB7F948}" name="Epic Name" dataDxfId="40">
       <calculatedColumnFormula>IF(JiraDataset[[#This Row],[IssueType]]="Epic",JiraDataset[[#This Row],[Summary]],"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="27" xr3:uid="{911C8FDC-5528-43FC-BDF4-D4761F03C0E5}" name="Child-Issue" dataDxfId="53"/>
-    <tableColumn id="41" xr3:uid="{AB248E07-9BFA-42CC-BC41-B4234F677BFB}" name="Child-Issue1" dataDxfId="52"/>
-    <tableColumn id="29" xr3:uid="{89D12135-F3E3-4253-844F-1B9A54169953}" name="Child-Issue2" dataDxfId="51"/>
-    <tableColumn id="12" xr3:uid="{0699B70E-673B-4238-8A66-12FC943A4812}" name="Labels" dataDxfId="50"/>
-    <tableColumn id="13" xr3:uid="{9840B81F-2CA6-4708-8C93-3E7C8F72A676}" name="Labels1" dataDxfId="49"/>
-    <tableColumn id="14" xr3:uid="{D4A99C0B-46B7-484A-842E-D62E9D5D9341}" name="Labels2" dataDxfId="48"/>
-    <tableColumn id="15" xr3:uid="{1D1C275E-5C65-4393-9663-6C5F617591E1}" name="Labels3" dataDxfId="47"/>
-    <tableColumn id="16" xr3:uid="{D823FA91-7106-42D3-9DBC-B337C509EB09}" name="Labels4" dataDxfId="46"/>
-    <tableColumn id="17" xr3:uid="{05A07F85-1763-4A66-9CBB-4A760BD03D27}" name="Labels5" dataDxfId="45"/>
-    <tableColumn id="18" xr3:uid="{16B98070-7F8A-4FC7-AD99-EA81D0BD26AB}" name="Labels6" dataDxfId="44"/>
-    <tableColumn id="19" xr3:uid="{016EAEF4-8EA9-408B-9F1A-ECFB17E81C77}" name="Labels7" dataDxfId="43"/>
-    <tableColumn id="26" xr3:uid="{8263F9EC-BF0A-46F7-BA83-6083A4262B91}" name="Labels8" dataDxfId="42"/>
-    <tableColumn id="20" xr3:uid="{389B11C5-1B22-48C0-BCA2-72F050425FA1}" name="Labels9" dataDxfId="41"/>
-    <tableColumn id="25" xr3:uid="{AE95F8A2-F7F0-4985-9AE6-4201B9792775}" name="Labels10" dataDxfId="40"/>
-    <tableColumn id="21" xr3:uid="{105F2D0F-70C1-4517-A55F-4C1DDFE85301}" name="Sprint" dataDxfId="39">
+    <tableColumn id="27" xr3:uid="{911C8FDC-5528-43FC-BDF4-D4761F03C0E5}" name="Child-Issue" dataDxfId="39"/>
+    <tableColumn id="41" xr3:uid="{AB248E07-9BFA-42CC-BC41-B4234F677BFB}" name="Child-Issue1" dataDxfId="38"/>
+    <tableColumn id="29" xr3:uid="{89D12135-F3E3-4253-844F-1B9A54169953}" name="Child-Issue2" dataDxfId="37"/>
+    <tableColumn id="12" xr3:uid="{0699B70E-673B-4238-8A66-12FC943A4812}" name="Labels" dataDxfId="36"/>
+    <tableColumn id="13" xr3:uid="{9840B81F-2CA6-4708-8C93-3E7C8F72A676}" name="Labels1" dataDxfId="35"/>
+    <tableColumn id="14" xr3:uid="{D4A99C0B-46B7-484A-842E-D62E9D5D9341}" name="Labels2" dataDxfId="34"/>
+    <tableColumn id="15" xr3:uid="{1D1C275E-5C65-4393-9663-6C5F617591E1}" name="Labels3" dataDxfId="33"/>
+    <tableColumn id="16" xr3:uid="{D823FA91-7106-42D3-9DBC-B337C509EB09}" name="Labels4" dataDxfId="32"/>
+    <tableColumn id="17" xr3:uid="{05A07F85-1763-4A66-9CBB-4A760BD03D27}" name="Labels5" dataDxfId="31"/>
+    <tableColumn id="18" xr3:uid="{16B98070-7F8A-4FC7-AD99-EA81D0BD26AB}" name="Labels6" dataDxfId="30"/>
+    <tableColumn id="19" xr3:uid="{016EAEF4-8EA9-408B-9F1A-ECFB17E81C77}" name="Labels7" dataDxfId="29"/>
+    <tableColumn id="26" xr3:uid="{8263F9EC-BF0A-46F7-BA83-6083A4262B91}" name="Labels8" dataDxfId="28"/>
+    <tableColumn id="20" xr3:uid="{389B11C5-1B22-48C0-BCA2-72F050425FA1}" name="Labels9" dataDxfId="27"/>
+    <tableColumn id="25" xr3:uid="{AE95F8A2-F7F0-4985-9AE6-4201B9792775}" name="Labels10" dataDxfId="26"/>
+    <tableColumn id="21" xr3:uid="{105F2D0F-70C1-4517-A55F-4C1DDFE85301}" name="Sprint" dataDxfId="25">
       <calculatedColumnFormula>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",IFERROR(VLOOKUP(JiraDataset[[#This Row],[Sprint Name]], Config!$D$4:$E$9, 2, FALSE), ""))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{D5984986-D838-4F87-A554-5DC4CA005452}" name="Labels0001" dataDxfId="38">
+    <tableColumn id="22" xr3:uid="{D5984986-D838-4F87-A554-5DC4CA005452}" name="Labels0001" dataDxfId="24">
       <calculatedColumnFormula>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",_xlfn.XLOOKUP("Creation Marker", CfgAutofieldValues[Name], CfgAutofieldValues[Value]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="39" xr3:uid="{C24E9ADD-96A8-4DBB-86A0-08D41975D750}" name="Labels0002" dataDxfId="37">
+    <tableColumn id="39" xr3:uid="{C24E9ADD-96A8-4DBB-86A0-08D41975D750}" name="Labels0002" dataDxfId="23">
       <calculatedColumnFormula>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",_xlfn.XLOOKUP("Feature Pod Label", CfgAutofieldValues[Name], CfgAutofieldValues[Value]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{A6D8D5A6-43EE-415C-80C1-30372C7FE5BF}" name="Assignee" dataDxfId="36">
+    <tableColumn id="6" xr3:uid="{A6D8D5A6-43EE-415C-80C1-30372C7FE5BF}" name="Assignee" dataDxfId="22">
       <calculatedColumnFormula>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",IFERROR(VLOOKUP(JiraDataset[[#This Row],[Assignee.Name]], Config!$A$4:$B$24, 2, FALSE), ""))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="23" xr3:uid="{51D4B5F4-C6D3-4EEC-8B1B-7BEC6E526A64}" name="Project Key" dataDxfId="35">
+    <tableColumn id="23" xr3:uid="{51D4B5F4-C6D3-4EEC-8B1B-7BEC6E526A64}" name="Project Key" dataDxfId="21">
       <calculatedColumnFormula>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",_xlfn.XLOOKUP("Project Key", CfgAutofieldValues[Name], CfgAutofieldValues[Value]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="42" xr3:uid="{82B78F0D-CAEF-4615-B12A-B15ACF33913C}" name="OrigEst" dataDxfId="34">
+    <tableColumn id="42" xr3:uid="{82B78F0D-CAEF-4615-B12A-B15ACF33913C}" name="OrigEst" dataDxfId="20">
       <calculatedColumnFormula array="1">IF(
   JiraDataset[[#This Row],[RowType]]=cfg_type_skip,
   "",
@@ -1544,7 +1392,7 @@
   )
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="44" xr3:uid="{C92FD7EC-0EAB-4967-A0E5-D2427E3A55B4}" name="RowType" dataDxfId="33">
+    <tableColumn id="44" xr3:uid="{C92FD7EC-0EAB-4967-A0E5-D2427E3A55B4}" name="RowType" dataDxfId="19">
       <calculatedColumnFormula array="1">IFERROR(
     _xlfn.IFS(
         JiraDataset[[#This Row],[IssueType]] = cfg_type_comment,"SKIP",
@@ -1554,15 +1402,15 @@
     cfg_type_workitem
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="24" xr3:uid="{B63E8FC4-20B3-4755-92F2-EA1F700CA72E}" name="Note" dataDxfId="32"/>
+    <tableColumn id="24" xr3:uid="{B63E8FC4-20B3-4755-92F2-EA1F700CA72E}" name="Note" dataDxfId="18"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{93F2D14D-2ABD-4171-895D-1041B0893491}" name="CfgComponents" displayName="CfgComponents" ref="I3:I11" totalsRowShown="0">
-  <autoFilter ref="I3:I11" xr:uid="{93F2D14D-2ABD-4171-895D-1041B0893491}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{93F2D14D-2ABD-4171-895D-1041B0893491}" name="CfgComponents" displayName="CfgComponents" ref="I3:I10" totalsRowShown="0">
+  <autoFilter ref="I3:I10" xr:uid="{93F2D14D-2ABD-4171-895D-1041B0893491}"/>
   <tableColumns count="1">
     <tableColumn id="1" xr3:uid="{10F6CCA4-1068-4FC8-AB82-E48B87DB0F71}" name="Component.Name"/>
   </tableColumns>
@@ -1571,8 +1419,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{7007FF9D-9384-422B-8DB3-300D782E5FE6}" name="CfgFixVersions" displayName="CfgFixVersions" ref="G3:G7" totalsRowShown="0">
-  <autoFilter ref="G3:G7" xr:uid="{7007FF9D-9384-422B-8DB3-300D782E5FE6}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{7007FF9D-9384-422B-8DB3-300D782E5FE6}" name="CfgFixVersions" displayName="CfgFixVersions" ref="G3:G6" totalsRowShown="0">
+  <autoFilter ref="G3:G6" xr:uid="{7007FF9D-9384-422B-8DB3-300D782E5FE6}"/>
   <tableColumns count="1">
     <tableColumn id="1" xr3:uid="{E20FAA91-E54E-42EA-9BFF-2FDA27CD5D33}" name="FixVersion.Name"/>
   </tableColumns>
@@ -1594,15 +1442,15 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{A6C0EE44-3F60-4588-BF11-75C3DD021846}" name="CfgPriorities" displayName="CfgPriorities" ref="O3:O9" totalsRowShown="0">
   <autoFilter ref="O3:O9" xr:uid="{A6C0EE44-3F60-4588-BF11-75C3DD021846}"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{3B3BE2ED-38C4-410B-B0BF-4A9BD9B4B974}" name="Priority.Name" dataDxfId="71"/>
+    <tableColumn id="1" xr3:uid="{3B3BE2ED-38C4-410B-B0BF-4A9BD9B4B974}" name="Priority.Name" dataDxfId="17"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium5" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{1EF5833D-4918-4C71-A990-1B275126361D}" name="CfgAssignees" displayName="CfgAssignees" ref="A3:B7" totalsRowShown="0">
-  <autoFilter ref="A3:B7" xr:uid="{1EF5833D-4918-4C71-A990-1B275126361D}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{1EF5833D-4918-4C71-A990-1B275126361D}" name="CfgAssignees" displayName="CfgAssignees" ref="A3:B6" totalsRowShown="0">
+  <autoFilter ref="A3:B6" xr:uid="{1EF5833D-4918-4C71-A990-1B275126361D}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{7F7B4E10-E51C-443F-875D-3E6A9FD9994C}" name="Asssignee.Name"/>
     <tableColumn id="2" xr3:uid="{3A4C6F03-89A9-4E38-8288-00D055D51CD3}" name="Assignee.ID"/>
@@ -1612,8 +1460,8 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{72674B63-54C8-47AC-9FF0-4034C2D499BA}" name="CfgSprints" displayName="CfgSprints" ref="D3:E6" totalsRowShown="0">
-  <autoFilter ref="D3:E6" xr:uid="{72674B63-54C8-47AC-9FF0-4034C2D499BA}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{72674B63-54C8-47AC-9FF0-4034C2D499BA}" name="CfgSprints" displayName="CfgSprints" ref="D3:E5" totalsRowShown="0">
+  <autoFilter ref="D3:E5" xr:uid="{72674B63-54C8-47AC-9FF0-4034C2D499BA}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{397B719B-4CC6-4F47-8F3C-168F13ED56DA}" name="Sprint.Name"/>
     <tableColumn id="2" xr3:uid="{2FD208E7-540E-4D07-9144-6E9F3065D9DE}" name="Sprint.ID"/>
@@ -1628,7 +1476,7 @@
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{D4E1611F-A2CF-465D-A219-1759EA66687D}" name="Name"/>
     <tableColumn id="2" xr3:uid="{174D0D86-B1AA-4BF7-AC91-FCACFC898851}" name="Value"/>
-    <tableColumn id="3" xr3:uid="{4D0493E3-2ED0-412B-9468-835FC91C2910}" name="Remark" dataDxfId="70"/>
+    <tableColumn id="3" xr3:uid="{4D0493E3-2ED0-412B-9468-835FC91C2910}" name="Remark" dataDxfId="16"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium5" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1961,14 +1809,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F73058B-F76D-4AAE-8108-6C4469E9D8B5}">
-  <dimension ref="A1:AK4"/>
+  <dimension ref="A1:AK3"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelCol="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="12.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="31.6640625" customWidth="1"/>
     <col min="4" max="4" width="11.88671875" hidden="1" customWidth="1"/>
     <col min="5" max="5" width="33" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.5546875" customWidth="1"/>
+    <col min="6" max="6" width="46.33203125" customWidth="1"/>
     <col min="7" max="7" width="17.44140625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="22.5546875" customWidth="1"/>
     <col min="9" max="9" width="14" bestFit="1" customWidth="1"/>
@@ -2032,7 +1880,7 @@
         <v>10</v>
       </c>
       <c r="L1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="M1" s="3" t="s">
         <v>11</v>
@@ -2124,9 +1972,11 @@
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="K2" s="3"/>
+        <v>83</v>
+      </c>
+      <c r="K2" s="3">
+        <v>1</v>
+      </c>
       <c r="L2" s="3"/>
       <c r="M2" s="3"/>
       <c r="N2" s="3" t="str">
@@ -2205,21 +2055,29 @@
         <v>42</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
+        <v>98</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>47</v>
+      </c>
       <c r="J3" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K3" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L3" s="3"/>
       <c r="M3" s="3"/>
@@ -2241,9 +2099,9 @@
       <c r="Z3" s="3"/>
       <c r="AA3" s="3"/>
       <c r="AB3" s="3"/>
-      <c r="AC3" s="3" t="str">
+      <c r="AC3" s="3">
         <f>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",IFERROR(VLOOKUP(JiraDataset[[#This Row],[Sprint Name]], Config!$D$4:$E$9, 2, FALSE), ""))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AD3" s="3" t="str">
         <f>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",_xlfn.XLOOKUP("Creation Marker", CfgAutofieldValues[Name], CfgAutofieldValues[Value]))</f>
@@ -2291,161 +2149,71 @@
       </c>
       <c r="AJ3" s="3"/>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.3">
-      <c r="A4" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="B4" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="C4" s="13" t="s">
-        <v>110</v>
-      </c>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="14"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
-      <c r="L4" s="15">
-        <v>1</v>
-      </c>
-      <c r="M4" s="3"/>
-      <c r="N4" s="15" t="str">
-        <f>IF(JiraDataset[[#This Row],[IssueType]]="Epic",JiraDataset[[#This Row],[Summary]],"")</f>
-        <v/>
-      </c>
-      <c r="O4" s="3"/>
-      <c r="P4" s="3"/>
-      <c r="Q4" s="3"/>
-      <c r="R4" s="3"/>
-      <c r="S4" s="3"/>
-      <c r="T4" s="3"/>
-      <c r="U4" s="3"/>
-      <c r="V4" s="3"/>
-      <c r="W4" s="3"/>
-      <c r="X4" s="3"/>
-      <c r="Y4" s="3"/>
-      <c r="Z4" s="3"/>
-      <c r="AA4" s="3"/>
-      <c r="AB4" s="3"/>
-      <c r="AC4" s="15" t="str">
-        <f>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",IFERROR(VLOOKUP(JiraDataset[[#This Row],[Sprint Name]], Config!$D$4:$E$9, 2, FALSE), ""))</f>
-        <v/>
-      </c>
-      <c r="AD4" s="15" t="str">
-        <f>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",_xlfn.XLOOKUP("Creation Marker", CfgAutofieldValues[Name], CfgAutofieldValues[Value]))</f>
-        <v>imported</v>
-      </c>
-      <c r="AE4" s="8" t="str">
-        <f>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",_xlfn.XLOOKUP("Feature Pod Label", CfgAutofieldValues[Name], CfgAutofieldValues[Value]))</f>
-        <v>pod_test</v>
-      </c>
-      <c r="AF4" s="15" t="str">
-        <f>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",IFERROR(VLOOKUP(JiraDataset[[#This Row],[Assignee.Name]], Config!$A$4:$B$24, 2, FALSE), ""))</f>
-        <v/>
-      </c>
-      <c r="AG4" s="15" t="str">
-        <f>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",_xlfn.XLOOKUP("Project Key", CfgAutofieldValues[Name], CfgAutofieldValues[Value]))</f>
-        <v>JITTP2</v>
-      </c>
-      <c r="AH4" s="15" t="str" cm="1">
-        <f t="array" ref="AH4">IF(
-  JiraDataset[[#This Row],[RowType]]=cfg_type_skip,
-  "",
-  _xlfn.LET(
-    _xlpm.p, _xlfn.TEXTSPLIT(JiraDataset[[#This Row],[Estimate]], " "),
-    _xlpm.getVal, _xlfn.LAMBDA(_xlpm.u, IFERROR(VALUE(LEFT(_xlfn._xlws.FILTER(_xlpm.p, RIGHT(_xlpm.p,1)=_xlpm.u), LEN(_xlfn._xlws.FILTER(_xlpm.p, RIGHT(_xlpm.p,1)=_xlpm.u))-1)), 0)),
-    _xlpm.w, _xlpm.getVal("w"),
-    _xlpm.d, _xlpm.getVal("d"),
-    _xlpm.h, _xlpm.getVal("h"),
-    _xlpm.m, _xlpm.getVal("m"),
-    _xlpm.seconds, _xlpm.w*144000 + _xlpm.d*28800 + _xlpm.h*3600 + _xlpm.m*60,
-    IF(_xlpm.seconds=0, "", _xlpm.seconds*60)
-  )
-)</f>
-        <v/>
-      </c>
-      <c r="AI4" s="15" t="str" cm="1">
-        <f t="array" ref="AI4">IFERROR(
-    _xlfn.IFS(
-        JiraDataset[[#This Row],[IssueType]] = cfg_type_comment,"SKIP",
-        JiraDataset[[#This Row],[IssueType]] = cfg_type_skip,"SKIP",
-        JiraDataset[[#This Row],[IssueType]] = cfg_type_note,"SKIP"
-    ),
-    cfg_type_workitem
-)</f>
-        <v>WorkItem</v>
-      </c>
-      <c r="AJ4" s="3"/>
-    </row>
   </sheetData>
   <protectedRanges>
     <protectedRange sqref="A1:A1048576 D4:N1048576 P4:AD1048576 C1:AB3" name="User Input"/>
     <protectedRange algorithmName="SHA-512" hashValue="tpheD+JLADkhiyalt6vInlMwkILPZx4PVQN/k2vmwjOBdYUuHaXCrwtObHeFz5dJh9f853O84pZ1Rn9Ujz33+A==" saltValue="9ir5NB4CJc/69S/Eh84/mA==" spinCount="100000" sqref="AC1:AI3 AE4:AK1048576" name="Computed values"/>
   </protectedRanges>
   <phoneticPr fontId="18" type="noConversion"/>
-  <conditionalFormatting sqref="A2:A4 C2:C4">
-    <cfRule type="containsText" dxfId="31" priority="429" operator="containsText" text="blocker">
+  <conditionalFormatting sqref="A2:A3 C2:C3">
+    <cfRule type="containsText" dxfId="15" priority="429" operator="containsText" text="blocker">
       <formula>NOT(ISERROR(SEARCH("blocker",A2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="30" priority="430" operator="containsText" text="critical">
+    <cfRule type="containsText" dxfId="14" priority="430" operator="containsText" text="critical">
       <formula>NOT(ISERROR(SEARCH("critical",A2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="29" priority="431" operator="containsText" text="High">
+    <cfRule type="containsText" dxfId="13" priority="431" operator="containsText" text="High">
       <formula>NOT(ISERROR(SEARCH("High",A2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="28" priority="432" operator="containsText" text="Medium">
+    <cfRule type="containsText" dxfId="12" priority="432" operator="containsText" text="Medium">
       <formula>NOT(ISERROR(SEARCH("Medium",A2)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:A4">
-    <cfRule type="containsBlanks" dxfId="27" priority="493">
+  <conditionalFormatting sqref="A2:A3">
+    <cfRule type="containsBlanks" dxfId="11" priority="493">
       <formula>LEN(TRIM(A2))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:AJ4">
-    <cfRule type="expression" dxfId="26" priority="409" stopIfTrue="1">
+  <conditionalFormatting sqref="A2:AJ3">
+    <cfRule type="expression" dxfId="10" priority="409" stopIfTrue="1">
       <formula>$B2=cfg_type_comment</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="25" priority="410">
+    <cfRule type="expression" dxfId="9" priority="410">
       <formula>$B2=cfg_type_skip</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="24" priority="411">
+    <cfRule type="expression" dxfId="8" priority="411">
       <formula>$B2=cfg_type_note</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B4">
-    <cfRule type="containsText" dxfId="23" priority="413" operator="containsText" text="epic">
+  <conditionalFormatting sqref="B2:B3">
+    <cfRule type="containsText" dxfId="7" priority="413" operator="containsText" text="epic">
       <formula>NOT(ISERROR(SEARCH("epic",B2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="22" priority="427" operator="containsText" text="story">
+    <cfRule type="containsText" dxfId="6" priority="427" operator="containsText" text="story">
       <formula>NOT(ISERROR(SEARCH("story",B2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="21" priority="433" operator="containsText" text="task">
+    <cfRule type="containsText" dxfId="5" priority="433" operator="containsText" text="task">
       <formula>NOT(ISERROR(SEARCH("task",B2)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="20" priority="492">
+    <cfRule type="containsBlanks" dxfId="4" priority="492">
       <formula>LEN(TRIM(B2))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:AJ4">
-    <cfRule type="expression" dxfId="19" priority="1">
+  <conditionalFormatting sqref="B2:AJ3">
+    <cfRule type="expression" dxfId="3" priority="1">
       <formula>$B2="Epic"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="18" priority="2">
+    <cfRule type="expression" dxfId="2" priority="2">
       <formula>$B2="Story"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C4">
-    <cfRule type="containsBlanks" dxfId="17" priority="494">
+  <conditionalFormatting sqref="C2:C3">
+    <cfRule type="containsBlanks" dxfId="1" priority="494">
       <formula>LEN(TRIM(C2))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:L4">
-    <cfRule type="containsBlanks" dxfId="16" priority="412">
+  <conditionalFormatting sqref="K2:L3">
+    <cfRule type="containsBlanks" dxfId="0" priority="412">
       <formula>LEN(TRIM(K2))=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2454,37 +2222,37 @@
       <formula1>1</formula1>
       <formula2>1000</formula2>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" error="must be a valid component" sqref="J2:J4" xr:uid="{386E3B68-2486-4DDE-BEB1-45F897521149}"/>
-    <dataValidation type="whole" allowBlank="1" showErrorMessage="1" promptTitle="Warning" prompt="This field should be the Issue ID or Issue Key of the child tasks. (upstream linkage is not possible)._x000a__x000a__x000a_To link Epics and Stories, use the Epic Link from the Story Issue." sqref="O2:Q4" xr:uid="{D7BD960D-9CEA-4120-B2E3-2AE0D4661093}">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" error="must be a valid component" sqref="J2:J3" xr:uid="{386E3B68-2486-4DDE-BEB1-45F897521149}"/>
+    <dataValidation type="whole" allowBlank="1" showErrorMessage="1" promptTitle="Warning" prompt="This field should be the Issue ID or Issue Key of the child tasks. (upstream linkage is not possible)._x000a__x000a__x000a_To link Epics and Stories, use the Epic Link from the Story Issue." sqref="O2:Q3" xr:uid="{D7BD960D-9CEA-4120-B2E3-2AE0D4661093}">
       <formula1>1</formula1>
       <formula2>1000</formula2>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Note" prompt="The content of this column will be ignored during the Jira import." sqref="AJ2:AJ4" xr:uid="{2DA3EDB6-7635-4349-8860-B614B5B71275}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Permissions" prompt="Updating Existing Issues requires global admin permissions" sqref="D2:D4" xr:uid="{D5E4A4BB-53C8-42DF-9B52-F5E00AC6407B}"/>
-    <dataValidation type="whole" allowBlank="1" showErrorMessage="1" promptTitle="Warning" prompt="Use the Issue ID value to link this work item to an Epic_x000a__x000a_Story Issues are not Child-Issues and should have Epic Link instead. " sqref="M2:M4" xr:uid="{16C14239-D6AA-4935-8809-57760481D8F1}">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Note" prompt="The content of this column will be ignored during the Jira import." sqref="AJ2:AJ3" xr:uid="{2DA3EDB6-7635-4349-8860-B614B5B71275}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Permissions" prompt="Updating Existing Issues requires global admin permissions" sqref="D2:D3" xr:uid="{D5E4A4BB-53C8-42DF-9B52-F5E00AC6407B}"/>
+    <dataValidation type="whole" allowBlank="1" showErrorMessage="1" promptTitle="Warning" prompt="Use the Issue ID value to link this work item to an Epic_x000a__x000a_Story Issues are not Child-Issues and should have Epic Link instead. " sqref="M2:M3" xr:uid="{16C14239-D6AA-4935-8809-57760481D8F1}">
       <formula1>1</formula1>
       <formula2>1000</formula2>
     </dataValidation>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="It must be a number (integer). This reference is only used during the import process." sqref="K1" xr:uid="{9C637146-F2E3-4D08-87A8-F70FD358E47E}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Use the Issue ID value to link this work item to an Epic_x000a__x000a_Story Issues are not Child-Issues and should have Epic Link instead. " sqref="M1" xr:uid="{A61138FD-C2B2-49D2-810B-69EAE2230B73}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="This field should be the Issue ID or Issue Key of the child tasks. (upstream linkage is not possible)._x000a__x000a__x000a_To link Epics and Stories, use the Epic Link from the Story Issue." sqref="O1:Q1" xr:uid="{BE6B7503-A11A-4130-9D63-988F0CFED80E}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" error="must be a valid fixversion" promptTitle="AUTOMATIC FIELD" prompt="Do not manually edit these!" sqref="AC2:AC4 AF1:AH4" xr:uid="{893DA5FE-9FD0-4D28-BBD0-3D7AEDECEACB}"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="must be a valid component" sqref="H2:H4" xr:uid="{65EDED96-6789-400B-B504-6BC3F5A79E70}">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" error="must be a valid fixversion" promptTitle="AUTOMATIC FIELD" prompt="Do not manually edit these!" sqref="AF2:AH3 AC2:AC3 AF1:AH1" xr:uid="{893DA5FE-9FD0-4D28-BBD0-3D7AEDECEACB}"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="must be a valid component" sqref="H2:H3" xr:uid="{65EDED96-6789-400B-B504-6BC3F5A79E70}">
       <formula1>INDIRECT("CfgComponents[Component.Name]")</formula1>
     </dataValidation>
-    <dataValidation type="list" errorStyle="warning" showErrorMessage="1" error="must be a valid fixversion" sqref="G2:G4" xr:uid="{44FDC20A-8BF5-49B5-9D2C-3A1FE5A7D835}">
+    <dataValidation type="list" errorStyle="warning" showErrorMessage="1" error="must be a valid fixversion" sqref="G2:G3" xr:uid="{44FDC20A-8BF5-49B5-9D2C-3A1FE5A7D835}">
       <formula1>INDIRECT("CfgAssignees[Asssignee.Name]")</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="must be a valid component" sqref="I2:I4" xr:uid="{A898E2E7-BC45-4B88-BA1E-4AAA377361D4}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="must be a valid component" sqref="I2:I3" xr:uid="{A898E2E7-BC45-4B88-BA1E-4AAA377361D4}">
       <formula1>INDIRECT("CfgSprints[Sprint.Name]")</formula1>
     </dataValidation>
     <dataValidation allowBlank="1" showErrorMessage="1" promptTitle="Warning" prompt="Field only used for Epic Issues, so they can be referenced in Story Issues via the Epic Link field.," sqref="N2:N3 L2:L3" xr:uid="{541AD292-0123-4B65-9663-081991FDF0C1}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Field only used for Epic Issues, so they can be referenced in Story Issues via the Epic Link field.," sqref="L1" xr:uid="{64C73155-DEE7-497D-8A98-01E54655ACA8}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="It must be a number (integer) or the Work Item key. This reference is only used during the import process to set the parent." sqref="L1" xr:uid="{8A2BE248-5762-43AD-9C47-C5A92A2E2357}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Field only used for Epic work item, so they can be referenced in Story work items via the Epic Link field. _x000a_DC Only" sqref="N1" xr:uid="{E8F6E005-1F9B-40F3-B24C-E2A3D286C532}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" error="must be a valid fixversion" promptTitle="Creation Marker (Config Sheet)" prompt="Do not manually edit these!" sqref="AD1:AD4" xr:uid="{412C516D-E091-4DDD-9C14-C33AC653C143}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" error="must be a valid fixversion" promptTitle="Feature Pod Label (Config Sheet)" prompt="Do not manually edit these!" sqref="AE1:AE4" xr:uid="{D2234141-379F-4413-AB08-6835BD9FF967}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" error="must be a valid fixversion" promptTitle="AUTOMATIC FIELD" prompt="Do not manually edit these! SKIP types won't be imported into Jira" sqref="AI1:AI4" xr:uid="{5A336857-7D14-4900-8734-BED680BE5154}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" error="must be a valid fixversion" promptTitle="Creation Marker (Config Sheet)" prompt="Do not manually edit these!" sqref="AD1:AD3" xr:uid="{412C516D-E091-4DDD-9C14-C33AC653C143}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" error="must be a valid fixversion" promptTitle="Feature Pod Label (Config Sheet)" prompt="Do not manually edit these!" sqref="AE1:AE3" xr:uid="{D2234141-379F-4413-AB08-6835BD9FF967}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" error="must be a valid fixversion" promptTitle="AUTOMATIC FIELD" prompt="Do not manually edit these! SKIP types won't be imported into Jira" sqref="AI1:AI3" xr:uid="{5A336857-7D14-4900-8734-BED680BE5154}"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -2498,19 +2266,19 @@
           <x14:formula1>
             <xm:f>Config!$O$4:$O$10</xm:f>
           </x14:formula1>
-          <xm:sqref>A2:A4</xm:sqref>
+          <xm:sqref>A2:A3</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Issue Type" xr:uid="{28BF52BF-C0B0-4D22-B02F-F1408D5A055B}">
           <x14:formula1>
             <xm:f>Config!$U$4:$U$33</xm:f>
           </x14:formula1>
-          <xm:sqref>B2:B4</xm:sqref>
+          <xm:sqref>B2:B3</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="must be a valid fixversion" xr:uid="{7708D6E2-1D6B-41D8-A9EE-0E87219BA8EA}">
           <x14:formula1>
             <xm:f>Config!$G$4:$G$8</xm:f>
           </x14:formula1>
-          <xm:sqref>F2:F4</xm:sqref>
+          <xm:sqref>F2:F3</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -2545,66 +2313,66 @@
   <sheetData>
     <row r="1" spans="1:22" ht="21" x14ac:dyDescent="0.4">
       <c r="A1" s="11" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B1" s="11"/>
       <c r="D1" s="11" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E1" s="11"/>
       <c r="G1" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="I1" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="I1" s="6" t="s">
-        <v>62</v>
-      </c>
       <c r="K1" s="6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="M1" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="O1" s="6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="Q1" s="11" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="R1" s="11"/>
       <c r="S1" s="11"/>
       <c r="U1" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B2" s="12"/>
       <c r="C2" s="7"/>
       <c r="D2" s="12" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E2" s="12"/>
       <c r="F2" s="7"/>
       <c r="G2" s="10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H2" s="10"/>
       <c r="I2" s="10" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J2" s="10"/>
       <c r="K2" s="12" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L2" s="12"/>
       <c r="M2" s="9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N2" s="9"/>
       <c r="O2" s="10" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="P2" s="10"/>
       <c r="Q2" s="12"/>
@@ -2612,54 +2380,54 @@
       <c r="S2" s="9"/>
       <c r="T2" s="7"/>
       <c r="U2" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="V2" s="9"/>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G3" t="s">
+        <v>75</v>
+      </c>
+      <c r="I3" t="s">
         <v>74</v>
       </c>
-      <c r="I3" t="s">
+      <c r="K3" t="s">
         <v>73</v>
       </c>
-      <c r="K3" t="s">
+      <c r="M3" t="s">
+        <v>80</v>
+      </c>
+      <c r="O3" t="s">
         <v>72</v>
       </c>
-      <c r="M3" t="s">
-        <v>79</v>
-      </c>
-      <c r="O3" t="s">
-        <v>71</v>
-      </c>
       <c r="Q3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="R3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="S3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="U3" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B4" t="s">
         <v>50</v>
@@ -2671,10 +2439,10 @@
         <v>1</v>
       </c>
       <c r="G4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K4" t="s">
         <v>39</v>
@@ -2689,7 +2457,7 @@
         <v>31</v>
       </c>
       <c r="R4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="S4" s="7"/>
       <c r="U4" t="str" cm="1">
@@ -2699,7 +2467,7 @@
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B5" t="s">
         <v>51</v>
@@ -2711,10 +2479,10 @@
         <v>2</v>
       </c>
       <c r="G5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K5" t="s">
         <v>37</v>
@@ -2732,7 +2500,7 @@
         <v>40</v>
       </c>
       <c r="S5" s="7" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U5" t="str">
         <f ca="1"/>
@@ -2741,16 +2509,16 @@
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B6" t="s">
         <v>52</v>
       </c>
       <c r="G6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K6" t="s">
         <v>41</v>
@@ -2759,16 +2527,16 @@
         <v>33</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>109</v>
+        <v>54</v>
       </c>
       <c r="Q6" t="s">
         <v>49</v>
       </c>
       <c r="R6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="S6" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="U6" t="str">
         <f ca="1"/>
@@ -2779,7 +2547,7 @@
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
       <c r="I7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K7" t="s">
         <v>42</v>
@@ -2799,7 +2567,7 @@
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
       <c r="I8" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="O8" s="1" t="s">
         <v>55</v>
@@ -2813,7 +2581,7 @@
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
       <c r="I9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="O9" s="1" t="s">
         <v>56</v>
@@ -2827,7 +2595,7 @@
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
       <c r="I10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="U10" t="str">
         <f ca="1"/>

--- a/resources/templates/ImportTemplate.xlsx
+++ b/resources/templates/ImportTemplate.xlsx
@@ -8,19 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workdir\DeerHide\sources\jira-toolkit\resources\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC33135F-B90A-4C24-BAC9-7A123C771B85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01FCCE72-DF9E-484F-AFA5-1709264A86F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5376" yWindow="5376" windowWidth="34560" windowHeight="18600" activeTab="1" xr2:uid="{1FA076D1-0294-4A97-AB8C-3ADE2BC9CEA1}"/>
+    <workbookView xWindow="1152" yWindow="1152" windowWidth="34560" windowHeight="18600" xr2:uid="{1FA076D1-0294-4A97-AB8C-3ADE2BC9CEA1}"/>
   </bookViews>
   <sheets>
     <sheet name="Dataset" sheetId="1" r:id="rId1"/>
     <sheet name="Config" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="cfg_labels_ft_label">Config!$R$6</definedName>
-    <definedName name="cfg_labels_ft_name">Config!$R$6</definedName>
-    <definedName name="cfg_labels_imported">Config!$R$5</definedName>
-    <definedName name="cfg_projectKey">Config!$R$4</definedName>
+    <definedName name="cfg_labels_ft_label">Config!$R$5</definedName>
+    <definedName name="cfg_labels_ft_name">Config!$R$5</definedName>
+    <definedName name="cfg_labels_imported">Config!$R$4</definedName>
+    <definedName name="cfg_projectKey">Config!#REF!</definedName>
     <definedName name="cfg_type_comment">Config!$M$4</definedName>
     <definedName name="cfg_type_note">Config!$M$6</definedName>
     <definedName name="cfg_type_skip">Config!$M$5</definedName>
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="106">
   <si>
     <t>IssueType</t>
   </si>
@@ -191,9 +191,6 @@
     <t>Story</t>
   </si>
   <si>
-    <t>imported</t>
-  </si>
-  <si>
     <t>Bug</t>
   </si>
   <si>
@@ -233,9 +230,6 @@
     <t>Highest</t>
   </si>
   <si>
-    <t>Hight</t>
-  </si>
-  <si>
     <t>Lowest</t>
   </si>
   <si>
@@ -245,9 +239,6 @@
     <t>Creation Marker</t>
   </si>
   <si>
-    <t>JV</t>
-  </si>
-  <si>
     <t>Issue Type</t>
   </si>
   <si>
@@ -278,15 +269,6 @@
     <t>Sprint.ID</t>
   </si>
   <si>
-    <t>JITTP Version 1</t>
-  </si>
-  <si>
-    <t>JITTP Version 2</t>
-  </si>
-  <si>
-    <t>JITTP Version 3</t>
-  </si>
-  <si>
     <t>Priority.Name</t>
   </si>
   <si>
@@ -299,12 +281,6 @@
     <t>FixVersion.Name</t>
   </si>
   <si>
-    <t>SysOps</t>
-  </si>
-  <si>
-    <t>DevOps</t>
-  </si>
-  <si>
     <t>Remark</t>
   </si>
   <si>
@@ -356,12 +332,6 @@
     <t>Combined list for the table</t>
   </si>
   <si>
-    <t>1w</t>
-  </si>
-  <si>
-    <t>JITTP2</t>
-  </si>
-  <si>
     <t>Test, Epic</t>
   </si>
   <si>
@@ -371,21 +341,9 @@
     <t>Parent</t>
   </si>
   <si>
-    <t>Design</t>
-  </si>
-  <si>
     <t>Development</t>
   </si>
   <si>
-    <t>Production</t>
-  </si>
-  <si>
-    <t>Quality Assurance</t>
-  </si>
-  <si>
-    <t>Quality Control</t>
-  </si>
-  <si>
     <t>Misc Fields</t>
   </si>
   <si>
@@ -399,6 +357,36 @@
   </si>
   <si>
     <t>pod_test</t>
+  </si>
+  <si>
+    <t>jira.connection.site_address</t>
+  </si>
+  <si>
+    <t>jira.project.key</t>
+  </si>
+  <si>
+    <t>validation.skip_rowtype</t>
+  </si>
+  <si>
+    <t>validation.skip_issuetypes</t>
+  </si>
+  <si>
+    <t>["comment", "note", "skip"]</t>
+  </si>
+  <si>
+    <t>Version_Tag</t>
+  </si>
+  <si>
+    <t>PROJECT KEY</t>
+  </si>
+  <si>
+    <t>jt-imported</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>Sub-Task</t>
   </si>
 </sst>
 </file>
@@ -999,7 +987,7 @@
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="56">
+  <dxfs count="200">
     <dxf>
       <fill>
         <patternFill patternType="darkUp"/>
@@ -1143,10 +1131,430 @@
       </fill>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="1" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill patternType="darkUp"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor auto="1"/>
+          <bgColor rgb="FFFF5050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDAF2D0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF2CEEF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor auto="1"/>
+          <bgColor rgb="FFFF5050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.89996032593768116"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.34998626667073579"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor auto="1"/>
+          <bgColor rgb="FFF9B1AB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFCC99"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF99CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF6699"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="darkUp"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor auto="1"/>
+          <bgColor rgb="FFFF5050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDAF2D0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF2CEEF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor auto="1"/>
+          <bgColor rgb="FFFF5050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.89996032593768116"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.34998626667073579"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor auto="1"/>
+          <bgColor rgb="FFF9B1AB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFCC99"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF99CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF6699"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="darkUp"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor auto="1"/>
+          <bgColor rgb="FFFF5050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDAF2D0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF2CEEF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor auto="1"/>
+          <bgColor rgb="FFFF5050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.89996032593768116"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.34998626667073579"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor auto="1"/>
+          <bgColor rgb="FFF9B1AB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFCC99"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF99CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF6699"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <alignment vertical="top"/>
@@ -1289,6 +1697,864 @@
     </dxf>
     <dxf>
       <alignment vertical="top"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="darkUp"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor auto="1"/>
+          <bgColor rgb="FFFF5050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDAF2D0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF2CEEF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor auto="1"/>
+          <bgColor rgb="FFFF5050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.89996032593768116"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.34998626667073579"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor auto="1"/>
+          <bgColor rgb="FFF9B1AB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFCC99"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF99CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF6699"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="darkUp"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor auto="1"/>
+          <bgColor rgb="FFFF5050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDAF2D0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF2CEEF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor auto="1"/>
+          <bgColor rgb="FFFF5050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.89996032593768116"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.34998626667073579"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor auto="1"/>
+          <bgColor rgb="FFF9B1AB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFCC99"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF99CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF6699"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="darkUp"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor auto="1"/>
+          <bgColor rgb="FFFF5050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDAF2D0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF2CEEF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor auto="1"/>
+          <bgColor rgb="FFFF5050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.89996032593768116"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.34998626667073579"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor auto="1"/>
+          <bgColor rgb="FFF9B1AB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFCC99"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF99CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF6699"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="darkUp"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor auto="1"/>
+          <bgColor rgb="FFFF5050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDAF2D0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF2CEEF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor auto="1"/>
+          <bgColor rgb="FFFF5050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.89996032593768116"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.34998626667073579"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor auto="1"/>
+          <bgColor rgb="FFF9B1AB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFCC99"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF99CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF6699"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="darkUp"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor auto="1"/>
+          <bgColor rgb="FFFF5050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDAF2D0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF2CEEF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor auto="1"/>
+          <bgColor rgb="FFFF5050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.89996032593768116"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.34998626667073579"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor auto="1"/>
+          <bgColor rgb="FFF9B1AB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFCC99"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF99CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF6699"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="darkUp"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor auto="1"/>
+          <bgColor rgb="FFFF5050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDAF2D0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF2CEEF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor auto="1"/>
+          <bgColor rgb="FFFF5050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.89996032593768116"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.34998626667073579"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor auto="1"/>
+          <bgColor rgb="FFF9B1AB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFCC99"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF99CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF6699"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="1" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1326,57 +2592,57 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{933FCFD5-1AB1-4076-B5DD-E2B69F5EB3F2}" name="JiraDataset" displayName="JiraDataset" ref="A1:AJ3" totalsRowShown="0" headerRowDxfId="55" dataDxfId="54">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{933FCFD5-1AB1-4076-B5DD-E2B69F5EB3F2}" name="JiraDataset" displayName="JiraDataset" ref="A1:AJ3" totalsRowShown="0" headerRowDxfId="101" dataDxfId="100">
   <autoFilter ref="A1:AJ3" xr:uid="{933FCFD5-1AB1-4076-B5DD-E2B69F5EB3F2}"/>
   <tableColumns count="36">
-    <tableColumn id="3" xr3:uid="{AF2EC907-349C-4651-852D-6E39C61E17FF}" name="Priority" dataDxfId="53"/>
-    <tableColumn id="2" xr3:uid="{E90C51F2-4386-421F-A3E4-E2CA9D43D396}" name="IssueType" dataDxfId="52"/>
-    <tableColumn id="1" xr3:uid="{BBAD373B-BA13-47E4-9F74-565F4D9E9680}" name="Summary" dataDxfId="51"/>
-    <tableColumn id="4" xr3:uid="{026E5B97-FAFC-4E46-860E-0B0C976B1148}" name="Issue Key" dataDxfId="50"/>
-    <tableColumn id="5" xr3:uid="{A2C262E8-D544-4669-99F1-151EDE081654}" name="Description" dataDxfId="49"/>
-    <tableColumn id="7" xr3:uid="{0FAD1ACC-432E-462C-8B89-71540710BCB5}" name="FixVersion" dataDxfId="48">
+    <tableColumn id="3" xr3:uid="{AF2EC907-349C-4651-852D-6E39C61E17FF}" name="Priority" dataDxfId="99"/>
+    <tableColumn id="2" xr3:uid="{E90C51F2-4386-421F-A3E4-E2CA9D43D396}" name="IssueType" dataDxfId="98"/>
+    <tableColumn id="1" xr3:uid="{BBAD373B-BA13-47E4-9F74-565F4D9E9680}" name="Summary" dataDxfId="97"/>
+    <tableColumn id="4" xr3:uid="{026E5B97-FAFC-4E46-860E-0B0C976B1148}" name="Issue Key" dataDxfId="96"/>
+    <tableColumn id="5" xr3:uid="{A2C262E8-D544-4669-99F1-151EDE081654}" name="Description" dataDxfId="95"/>
+    <tableColumn id="7" xr3:uid="{0FAD1ACC-432E-462C-8B89-71540710BCB5}" name="FixVersion" dataDxfId="94">
       <calculatedColumnFormula>Config!$G$4</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="28" xr3:uid="{07F3030C-7187-4B16-BBDB-798304851975}" name="Assignee.Name" dataDxfId="47"/>
-    <tableColumn id="8" xr3:uid="{8C7FB8DB-A85B-4189-93D8-0F0D4EEEF81B}" name="Component" dataDxfId="46"/>
-    <tableColumn id="9" xr3:uid="{DC5101A8-1204-44D2-BC2C-FEE1A4EFE7C1}" name="Sprint Name" dataDxfId="45"/>
-    <tableColumn id="40" xr3:uid="{1F406792-7ED2-4476-8FF4-4C6ABA231C97}" name="Estimate" dataDxfId="44"/>
-    <tableColumn id="10" xr3:uid="{70B7C471-B624-430B-8992-4711F27BB17E}" name="Issue ID" dataDxfId="43"/>
-    <tableColumn id="30" xr3:uid="{938D6CA2-8309-4146-9B62-E8CDFAB7B1C9}" name="Parent" dataDxfId="42"/>
-    <tableColumn id="11" xr3:uid="{594BD56F-7D1D-408F-BEDC-6BB9854C71A1}" name="Epic Link" dataDxfId="41"/>
-    <tableColumn id="33" xr3:uid="{3A94D4B2-1A5B-4BBF-B398-E56D2BB7F948}" name="Epic Name" dataDxfId="40">
+    <tableColumn id="28" xr3:uid="{07F3030C-7187-4B16-BBDB-798304851975}" name="Assignee.Name" dataDxfId="93"/>
+    <tableColumn id="8" xr3:uid="{8C7FB8DB-A85B-4189-93D8-0F0D4EEEF81B}" name="Component" dataDxfId="92"/>
+    <tableColumn id="9" xr3:uid="{DC5101A8-1204-44D2-BC2C-FEE1A4EFE7C1}" name="Sprint Name" dataDxfId="91"/>
+    <tableColumn id="40" xr3:uid="{1F406792-7ED2-4476-8FF4-4C6ABA231C97}" name="Estimate" dataDxfId="90"/>
+    <tableColumn id="10" xr3:uid="{70B7C471-B624-430B-8992-4711F27BB17E}" name="Issue ID" dataDxfId="89"/>
+    <tableColumn id="30" xr3:uid="{938D6CA2-8309-4146-9B62-E8CDFAB7B1C9}" name="Parent" dataDxfId="88"/>
+    <tableColumn id="11" xr3:uid="{594BD56F-7D1D-408F-BEDC-6BB9854C71A1}" name="Epic Link" dataDxfId="87"/>
+    <tableColumn id="33" xr3:uid="{3A94D4B2-1A5B-4BBF-B398-E56D2BB7F948}" name="Epic Name" dataDxfId="86">
       <calculatedColumnFormula>IF(JiraDataset[[#This Row],[IssueType]]="Epic",JiraDataset[[#This Row],[Summary]],"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="27" xr3:uid="{911C8FDC-5528-43FC-BDF4-D4761F03C0E5}" name="Child-Issue" dataDxfId="39"/>
-    <tableColumn id="41" xr3:uid="{AB248E07-9BFA-42CC-BC41-B4234F677BFB}" name="Child-Issue1" dataDxfId="38"/>
-    <tableColumn id="29" xr3:uid="{89D12135-F3E3-4253-844F-1B9A54169953}" name="Child-Issue2" dataDxfId="37"/>
-    <tableColumn id="12" xr3:uid="{0699B70E-673B-4238-8A66-12FC943A4812}" name="Labels" dataDxfId="36"/>
-    <tableColumn id="13" xr3:uid="{9840B81F-2CA6-4708-8C93-3E7C8F72A676}" name="Labels1" dataDxfId="35"/>
-    <tableColumn id="14" xr3:uid="{D4A99C0B-46B7-484A-842E-D62E9D5D9341}" name="Labels2" dataDxfId="34"/>
-    <tableColumn id="15" xr3:uid="{1D1C275E-5C65-4393-9663-6C5F617591E1}" name="Labels3" dataDxfId="33"/>
-    <tableColumn id="16" xr3:uid="{D823FA91-7106-42D3-9DBC-B337C509EB09}" name="Labels4" dataDxfId="32"/>
-    <tableColumn id="17" xr3:uid="{05A07F85-1763-4A66-9CBB-4A760BD03D27}" name="Labels5" dataDxfId="31"/>
-    <tableColumn id="18" xr3:uid="{16B98070-7F8A-4FC7-AD99-EA81D0BD26AB}" name="Labels6" dataDxfId="30"/>
-    <tableColumn id="19" xr3:uid="{016EAEF4-8EA9-408B-9F1A-ECFB17E81C77}" name="Labels7" dataDxfId="29"/>
-    <tableColumn id="26" xr3:uid="{8263F9EC-BF0A-46F7-BA83-6083A4262B91}" name="Labels8" dataDxfId="28"/>
-    <tableColumn id="20" xr3:uid="{389B11C5-1B22-48C0-BCA2-72F050425FA1}" name="Labels9" dataDxfId="27"/>
-    <tableColumn id="25" xr3:uid="{AE95F8A2-F7F0-4985-9AE6-4201B9792775}" name="Labels10" dataDxfId="26"/>
-    <tableColumn id="21" xr3:uid="{105F2D0F-70C1-4517-A55F-4C1DDFE85301}" name="Sprint" dataDxfId="25">
+    <tableColumn id="27" xr3:uid="{911C8FDC-5528-43FC-BDF4-D4761F03C0E5}" name="Child-Issue" dataDxfId="85"/>
+    <tableColumn id="41" xr3:uid="{AB248E07-9BFA-42CC-BC41-B4234F677BFB}" name="Child-Issue1" dataDxfId="84"/>
+    <tableColumn id="29" xr3:uid="{89D12135-F3E3-4253-844F-1B9A54169953}" name="Child-Issue2" dataDxfId="83"/>
+    <tableColumn id="12" xr3:uid="{0699B70E-673B-4238-8A66-12FC943A4812}" name="Labels" dataDxfId="82"/>
+    <tableColumn id="13" xr3:uid="{9840B81F-2CA6-4708-8C93-3E7C8F72A676}" name="Labels1" dataDxfId="81"/>
+    <tableColumn id="14" xr3:uid="{D4A99C0B-46B7-484A-842E-D62E9D5D9341}" name="Labels2" dataDxfId="80"/>
+    <tableColumn id="15" xr3:uid="{1D1C275E-5C65-4393-9663-6C5F617591E1}" name="Labels3" dataDxfId="79"/>
+    <tableColumn id="16" xr3:uid="{D823FA91-7106-42D3-9DBC-B337C509EB09}" name="Labels4" dataDxfId="78"/>
+    <tableColumn id="17" xr3:uid="{05A07F85-1763-4A66-9CBB-4A760BD03D27}" name="Labels5" dataDxfId="77"/>
+    <tableColumn id="18" xr3:uid="{16B98070-7F8A-4FC7-AD99-EA81D0BD26AB}" name="Labels6" dataDxfId="76"/>
+    <tableColumn id="19" xr3:uid="{016EAEF4-8EA9-408B-9F1A-ECFB17E81C77}" name="Labels7" dataDxfId="75"/>
+    <tableColumn id="26" xr3:uid="{8263F9EC-BF0A-46F7-BA83-6083A4262B91}" name="Labels8" dataDxfId="74"/>
+    <tableColumn id="20" xr3:uid="{389B11C5-1B22-48C0-BCA2-72F050425FA1}" name="Labels9" dataDxfId="73"/>
+    <tableColumn id="25" xr3:uid="{AE95F8A2-F7F0-4985-9AE6-4201B9792775}" name="Labels10" dataDxfId="72"/>
+    <tableColumn id="21" xr3:uid="{105F2D0F-70C1-4517-A55F-4C1DDFE85301}" name="Sprint" dataDxfId="71">
       <calculatedColumnFormula>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",IFERROR(VLOOKUP(JiraDataset[[#This Row],[Sprint Name]], Config!$D$4:$E$9, 2, FALSE), ""))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{D5984986-D838-4F87-A554-5DC4CA005452}" name="Labels0001" dataDxfId="24">
+    <tableColumn id="22" xr3:uid="{D5984986-D838-4F87-A554-5DC4CA005452}" name="Labels0001" dataDxfId="70">
       <calculatedColumnFormula>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",_xlfn.XLOOKUP("Creation Marker", CfgAutofieldValues[Name], CfgAutofieldValues[Value]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="39" xr3:uid="{C24E9ADD-96A8-4DBB-86A0-08D41975D750}" name="Labels0002" dataDxfId="23">
+    <tableColumn id="39" xr3:uid="{C24E9ADD-96A8-4DBB-86A0-08D41975D750}" name="Labels0002" dataDxfId="69">
       <calculatedColumnFormula>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",_xlfn.XLOOKUP("Feature Pod Label", CfgAutofieldValues[Name], CfgAutofieldValues[Value]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{A6D8D5A6-43EE-415C-80C1-30372C7FE5BF}" name="Assignee" dataDxfId="22">
+    <tableColumn id="6" xr3:uid="{A6D8D5A6-43EE-415C-80C1-30372C7FE5BF}" name="Assignee" dataDxfId="68">
       <calculatedColumnFormula>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",IFERROR(VLOOKUP(JiraDataset[[#This Row],[Assignee.Name]], Config!$A$4:$B$24, 2, FALSE), ""))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="23" xr3:uid="{51D4B5F4-C6D3-4EEC-8B1B-7BEC6E526A64}" name="Project Key" dataDxfId="21">
-      <calculatedColumnFormula>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",_xlfn.XLOOKUP("Project Key", CfgAutofieldValues[Name], CfgAutofieldValues[Value]))</calculatedColumnFormula>
+    <tableColumn id="23" xr3:uid="{51D4B5F4-C6D3-4EEC-8B1B-7BEC6E526A64}" name="Project Key" dataDxfId="67">
+      <calculatedColumnFormula>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",_xlfn.XLOOKUP("jira.project.key", CfgAutofieldValues[Name], CfgAutofieldValues[Value]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="42" xr3:uid="{82B78F0D-CAEF-4615-B12A-B15ACF33913C}" name="OrigEst" dataDxfId="20">
+    <tableColumn id="42" xr3:uid="{82B78F0D-CAEF-4615-B12A-B15ACF33913C}" name="OrigEst" dataDxfId="66">
       <calculatedColumnFormula array="1">IF(
   JiraDataset[[#This Row],[RowType]]=cfg_type_skip,
   "",
@@ -1392,7 +2658,7 @@
   )
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="44" xr3:uid="{C92FD7EC-0EAB-4967-A0E5-D2427E3A55B4}" name="RowType" dataDxfId="19">
+    <tableColumn id="44" xr3:uid="{C92FD7EC-0EAB-4967-A0E5-D2427E3A55B4}" name="RowType" dataDxfId="65">
       <calculatedColumnFormula array="1">IFERROR(
     _xlfn.IFS(
         JiraDataset[[#This Row],[IssueType]] = cfg_type_comment,"SKIP",
@@ -1402,15 +2668,15 @@
     cfg_type_workitem
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="24" xr3:uid="{B63E8FC4-20B3-4755-92F2-EA1F700CA72E}" name="Note" dataDxfId="18"/>
+    <tableColumn id="24" xr3:uid="{B63E8FC4-20B3-4755-92F2-EA1F700CA72E}" name="Note" dataDxfId="64"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{93F2D14D-2ABD-4171-895D-1041B0893491}" name="CfgComponents" displayName="CfgComponents" ref="I3:I10" totalsRowShown="0">
-  <autoFilter ref="I3:I10" xr:uid="{93F2D14D-2ABD-4171-895D-1041B0893491}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{93F2D14D-2ABD-4171-895D-1041B0893491}" name="CfgComponents" displayName="CfgComponents" ref="I3:I5" totalsRowShown="0">
+  <autoFilter ref="I3:I5" xr:uid="{93F2D14D-2ABD-4171-895D-1041B0893491}"/>
   <tableColumns count="1">
     <tableColumn id="1" xr3:uid="{10F6CCA4-1068-4FC8-AB82-E48B87DB0F71}" name="Component.Name"/>
   </tableColumns>
@@ -1419,8 +2685,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{7007FF9D-9384-422B-8DB3-300D782E5FE6}" name="CfgFixVersions" displayName="CfgFixVersions" ref="G3:G6" totalsRowShown="0">
-  <autoFilter ref="G3:G6" xr:uid="{7007FF9D-9384-422B-8DB3-300D782E5FE6}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{7007FF9D-9384-422B-8DB3-300D782E5FE6}" name="CfgFixVersions" displayName="CfgFixVersions" ref="G3:G5" totalsRowShown="0">
+  <autoFilter ref="G3:G5" xr:uid="{7007FF9D-9384-422B-8DB3-300D782E5FE6}"/>
   <tableColumns count="1">
     <tableColumn id="1" xr3:uid="{E20FAA91-E54E-42EA-9BFF-2FDA27CD5D33}" name="FixVersion.Name"/>
   </tableColumns>
@@ -1429,8 +2695,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{6F085B8C-1322-4F43-A516-588923936259}" name="CfgIssueTypes" displayName="CfgIssueTypes" ref="K3:K7" totalsRowShown="0">
-  <autoFilter ref="K3:K7" xr:uid="{6F085B8C-1322-4F43-A516-588923936259}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{6F085B8C-1322-4F43-A516-588923936259}" name="CfgIssueTypes" displayName="CfgIssueTypes" ref="K3:K8" totalsRowShown="0">
+  <autoFilter ref="K3:K8" xr:uid="{6F085B8C-1322-4F43-A516-588923936259}"/>
   <tableColumns count="1">
     <tableColumn id="1" xr3:uid="{A92436BC-3156-493F-B5C6-0BB6B51F89EB}" name="IssueType.Name"/>
   </tableColumns>
@@ -1442,7 +2708,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{A6C0EE44-3F60-4588-BF11-75C3DD021846}" name="CfgPriorities" displayName="CfgPriorities" ref="O3:O9" totalsRowShown="0">
   <autoFilter ref="O3:O9" xr:uid="{A6C0EE44-3F60-4588-BF11-75C3DD021846}"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{3B3BE2ED-38C4-410B-B0BF-4A9BD9B4B974}" name="Priority.Name" dataDxfId="17"/>
+    <tableColumn id="1" xr3:uid="{3B3BE2ED-38C4-410B-B0BF-4A9BD9B4B974}" name="Priority.Name" dataDxfId="199"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium5" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1471,12 +2737,12 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{383560BC-B1F2-44B6-B877-188131EFA163}" name="CfgAutofieldValues" displayName="CfgAutofieldValues" ref="Q3:S6" totalsRowShown="0">
-  <autoFilter ref="Q3:S6" xr:uid="{383560BC-B1F2-44B6-B877-188131EFA163}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{383560BC-B1F2-44B6-B877-188131EFA163}" name="CfgAutofieldValues" displayName="CfgAutofieldValues" ref="Q3:S9" totalsRowShown="0">
+  <autoFilter ref="Q3:S9" xr:uid="{383560BC-B1F2-44B6-B877-188131EFA163}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{D4E1611F-A2CF-465D-A219-1759EA66687D}" name="Name"/>
     <tableColumn id="2" xr3:uid="{174D0D86-B1AA-4BF7-AC91-FCACFC898851}" name="Value"/>
-    <tableColumn id="3" xr3:uid="{4D0493E3-2ED0-412B-9468-835FC91C2910}" name="Remark" dataDxfId="16"/>
+    <tableColumn id="3" xr3:uid="{4D0493E3-2ED0-412B-9468-835FC91C2910}" name="Remark" dataDxfId="198"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium5" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1880,7 +3146,7 @@
         <v>10</v>
       </c>
       <c r="L1" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="M1" s="3" t="s">
         <v>11</v>
@@ -1949,7 +3215,7 @@
         <v>32</v>
       </c>
       <c r="AI1" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AJ1" s="3" t="s">
         <v>33</v>
@@ -1972,7 +3238,7 @@
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="K2" s="3">
         <v>1</v>
@@ -2014,7 +3280,7 @@
         <v/>
       </c>
       <c r="AG2" s="3" t="str">
-        <f>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",_xlfn.XLOOKUP("Project Key", CfgAutofieldValues[Name], CfgAutofieldValues[Value]))</f>
+        <f>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",_xlfn.XLOOKUP("jira.project.key", CfgAutofieldValues[Name], CfgAutofieldValues[Value]))</f>
         <v/>
       </c>
       <c r="AH2" s="3" t="str" cm="1">
@@ -2049,33 +3315,31 @@
     </row>
     <row r="3" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>71</v>
+        <v>101</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>95</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="J3" s="3"/>
       <c r="K3" s="3">
         <v>2</v>
       </c>
@@ -2105,7 +3369,7 @@
       </c>
       <c r="AD3" s="3" t="str">
         <f>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",_xlfn.XLOOKUP("Creation Marker", CfgAutofieldValues[Name], CfgAutofieldValues[Value]))</f>
-        <v>imported</v>
+        <v>jt-imported</v>
       </c>
       <c r="AE3" s="8" t="str">
         <f>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",_xlfn.XLOOKUP("Feature Pod Label", CfgAutofieldValues[Name], CfgAutofieldValues[Value]))</f>
@@ -2113,13 +3377,13 @@
       </c>
       <c r="AF3" s="3" t="str">
         <f>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",IFERROR(VLOOKUP(JiraDataset[[#This Row],[Assignee.Name]], Config!$A$4:$B$24, 2, FALSE), ""))</f>
-        <v/>
+        <v>712020:e4e815aa-df03-418a-9760-3e70901b6ec5</v>
       </c>
       <c r="AG3" s="3" t="str">
-        <f>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",_xlfn.XLOOKUP("Project Key", CfgAutofieldValues[Name], CfgAutofieldValues[Value]))</f>
-        <v>JITTP2</v>
-      </c>
-      <c r="AH3" s="3" cm="1">
+        <f>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",_xlfn.XLOOKUP("jira.project.key", CfgAutofieldValues[Name], CfgAutofieldValues[Value]))</f>
+        <v>PROJECT KEY</v>
+      </c>
+      <c r="AH3" s="3" t="str" cm="1">
         <f t="array" ref="AH3">IF(
   JiraDataset[[#This Row],[RowType]]=cfg_type_skip,
   "",
@@ -2134,7 +3398,7 @@
     IF(_xlpm.seconds=0, "", _xlpm.seconds*60)
   )
 )</f>
-        <v>8640000</v>
+        <v/>
       </c>
       <c r="AI3" s="3" t="str" cm="1">
         <f t="array" ref="AI3">IFERROR(
@@ -2151,7 +3415,7 @@
     </row>
   </sheetData>
   <protectedRanges>
-    <protectedRange sqref="A1:A1048576 D4:N1048576 P4:AD1048576 C1:AB3" name="User Input"/>
+    <protectedRange sqref="D4:N1048576 P4:AD1048576 C1:AB3 A1:A1048576" name="User Input"/>
     <protectedRange algorithmName="SHA-512" hashValue="tpheD+JLADkhiyalt6vInlMwkILPZx4PVQN/k2vmwjOBdYUuHaXCrwtObHeFz5dJh9f853O84pZ1Rn9Ujz33+A==" saltValue="9ir5NB4CJc/69S/Eh84/mA==" spinCount="100000" sqref="AC1:AI3 AE4:AK1048576" name="Computed values"/>
   </protectedRanges>
   <phoneticPr fontId="18" type="noConversion"/>
@@ -2236,7 +3500,7 @@
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="It must be a number (integer). This reference is only used during the import process." sqref="K1" xr:uid="{9C637146-F2E3-4D08-87A8-F70FD358E47E}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Use the Issue ID value to link this work item to an Epic_x000a__x000a_Story Issues are not Child-Issues and should have Epic Link instead. " sqref="M1" xr:uid="{A61138FD-C2B2-49D2-810B-69EAE2230B73}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="This field should be the Issue ID or Issue Key of the child tasks. (upstream linkage is not possible)._x000a__x000a__x000a_To link Epics and Stories, use the Epic Link from the Story Issue." sqref="O1:Q1" xr:uid="{BE6B7503-A11A-4130-9D63-988F0CFED80E}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" error="must be a valid fixversion" promptTitle="AUTOMATIC FIELD" prompt="Do not manually edit these!" sqref="AF2:AH3 AC2:AC3 AF1:AH1" xr:uid="{893DA5FE-9FD0-4D28-BBD0-3D7AEDECEACB}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" error="must be a valid fixversion" promptTitle="AUTOMATIC FIELD" prompt="Do not manually edit these!" sqref="AC2:AC3 AF1:AH3" xr:uid="{893DA5FE-9FD0-4D28-BBD0-3D7AEDECEACB}"/>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="must be a valid component" sqref="H2:H3" xr:uid="{65EDED96-6789-400B-B504-6BC3F5A79E70}">
       <formula1>INDIRECT("CfgComponents[Component.Name]")</formula1>
     </dataValidation>
@@ -2313,66 +3577,66 @@
   <sheetData>
     <row r="1" spans="1:22" ht="21" x14ac:dyDescent="0.4">
       <c r="A1" s="11" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="B1" s="11"/>
       <c r="D1" s="11" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="E1" s="11"/>
       <c r="G1" s="6" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="I1" s="6" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="K1" s="6" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="M1" s="6" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="O1" s="6" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="Q1" s="11" t="s">
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="R1" s="11"/>
       <c r="S1" s="11"/>
       <c r="U1" s="6" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="B2" s="12"/>
       <c r="C2" s="7"/>
       <c r="D2" s="12" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="E2" s="12"/>
       <c r="F2" s="7"/>
       <c r="G2" s="10" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H2" s="10"/>
       <c r="I2" s="10" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="J2" s="10"/>
       <c r="K2" s="12" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="L2" s="12"/>
       <c r="M2" s="9" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="N2" s="9"/>
       <c r="O2" s="10" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="P2" s="10"/>
       <c r="Q2" s="12"/>
@@ -2380,69 +3644,69 @@
       <c r="S2" s="9"/>
       <c r="T2" s="7"/>
       <c r="U2" s="9" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="V2" s="9"/>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D3" t="s">
+        <v>64</v>
+      </c>
+      <c r="E3" t="s">
         <v>65</v>
       </c>
-      <c r="B3" t="s">
+      <c r="G3" t="s">
+        <v>69</v>
+      </c>
+      <c r="I3" t="s">
+        <v>68</v>
+      </c>
+      <c r="K3" t="s">
+        <v>67</v>
+      </c>
+      <c r="M3" t="s">
+        <v>72</v>
+      </c>
+      <c r="O3" t="s">
         <v>66</v>
       </c>
-      <c r="D3" t="s">
+      <c r="Q3" t="s">
+        <v>58</v>
+      </c>
+      <c r="R3" t="s">
+        <v>59</v>
+      </c>
+      <c r="S3" t="s">
+        <v>70</v>
+      </c>
+      <c r="U3" s="5" t="s">
         <v>67</v>
-      </c>
-      <c r="E3" t="s">
-        <v>68</v>
-      </c>
-      <c r="G3" t="s">
-        <v>75</v>
-      </c>
-      <c r="I3" t="s">
-        <v>74</v>
-      </c>
-      <c r="K3" t="s">
-        <v>73</v>
-      </c>
-      <c r="M3" t="s">
-        <v>80</v>
-      </c>
-      <c r="O3" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>61</v>
-      </c>
-      <c r="R3" t="s">
-        <v>62</v>
-      </c>
-      <c r="S3" t="s">
-        <v>78</v>
-      </c>
-      <c r="U3" s="5" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="B4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E4">
         <v>1</v>
       </c>
       <c r="G4" t="s">
-        <v>69</v>
+        <v>101</v>
       </c>
       <c r="I4" t="s">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="K4" t="s">
         <v>39</v>
@@ -2454,53 +3718,49 @@
         <v>38</v>
       </c>
       <c r="Q4" t="s">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="R4" t="s">
-        <v>96</v>
-      </c>
-      <c r="S4" s="7"/>
+        <v>103</v>
+      </c>
+      <c r="S4" s="7" t="s">
+        <v>77</v>
+      </c>
       <c r="U4" t="str" cm="1">
-        <f t="array" aca="1" ref="U4:U11" ca="1">_xlfn.UNIQUE((_xlfn.VSTACK(INDIRECT("CfgIssueTypes[IssueType.Name]"),INDIRECT("CfgIgnoreList[IgnoreList.Name]"))))</f>
+        <f t="array" aca="1" ref="U4:U12" ca="1">_xlfn.UNIQUE((_xlfn.VSTACK(INDIRECT("CfgIssueTypes[IssueType.Name]"),INDIRECT("CfgIgnoreList[IgnoreList.Name]"))))</f>
         <v>Story</v>
       </c>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="B5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E5">
         <v>2</v>
       </c>
-      <c r="G5" t="s">
-        <v>70</v>
-      </c>
-      <c r="I5" t="s">
-        <v>77</v>
-      </c>
       <c r="K5" t="s">
         <v>37</v>
       </c>
       <c r="M5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O5" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Q5" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="R5" t="s">
-        <v>40</v>
+        <v>95</v>
       </c>
       <c r="S5" s="7" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="U5" t="str">
         <f ca="1"/>
@@ -2509,35 +3769,24 @@
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>108</v>
+        <v>94</v>
       </c>
       <c r="B6" t="s">
-        <v>52</v>
-      </c>
-      <c r="G6" t="s">
-        <v>71</v>
-      </c>
-      <c r="I6" t="s">
-        <v>100</v>
+        <v>51</v>
       </c>
       <c r="K6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="M6" t="s">
         <v>33</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>54</v>
+        <v>104</v>
       </c>
       <c r="Q6" t="s">
-        <v>49</v>
-      </c>
-      <c r="R6" t="s">
-        <v>109</v>
-      </c>
-      <c r="S6" s="7" t="s">
-        <v>86</v>
-      </c>
+        <v>96</v>
+      </c>
+      <c r="S6" s="7"/>
       <c r="U6" t="str">
         <f ca="1"/>
         <v>Bug</v>
@@ -2546,18 +3795,22 @@
     <row r="7" spans="1:22" x14ac:dyDescent="0.3">
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
-      <c r="I7" t="s">
-        <v>101</v>
-      </c>
       <c r="K7" t="s">
+        <v>41</v>
+      </c>
+      <c r="M7" t="s">
+        <v>45</v>
+      </c>
+      <c r="O7" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="M7" t="s">
-        <v>46</v>
-      </c>
-      <c r="O7" s="1" t="s">
-        <v>43</v>
-      </c>
+      <c r="Q7" t="s">
+        <v>97</v>
+      </c>
+      <c r="R7" t="s">
+        <v>102</v>
+      </c>
+      <c r="S7" s="7"/>
       <c r="U7" t="str">
         <f ca="1"/>
         <v>Epic</v>
@@ -2566,40 +3819,48 @@
     <row r="8" spans="1:22" x14ac:dyDescent="0.3">
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
-      <c r="I8" t="s">
-        <v>102</v>
+      <c r="K8" t="s">
+        <v>105</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>55</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>98</v>
+      </c>
+      <c r="R8" t="b">
+        <v>1</v>
+      </c>
+      <c r="S8" s="7"/>
       <c r="U8" t="str">
         <f ca="1"/>
-        <v>Comment</v>
+        <v>Sub-Task</v>
       </c>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.3">
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
-      <c r="I9" t="s">
-        <v>103</v>
-      </c>
       <c r="O9" s="1" t="s">
-        <v>56</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>99</v>
+      </c>
+      <c r="R9" t="s">
+        <v>100</v>
+      </c>
+      <c r="S9" s="7"/>
       <c r="U9" t="str">
         <f ca="1"/>
-        <v>Skip</v>
+        <v>Comment</v>
       </c>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.3">
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
-      <c r="I10" t="s">
-        <v>104</v>
-      </c>
       <c r="U10" t="str">
         <f ca="1"/>
-        <v>Note</v>
+        <v>Skip</v>
       </c>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.3">
@@ -2607,12 +3868,16 @@
       <c r="E11" s="2"/>
       <c r="U11" t="str">
         <f ca="1"/>
-        <v>WorkItem</v>
+        <v>Note</v>
       </c>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.3">
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
+      <c r="U12" t="str">
+        <f ca="1"/>
+        <v>WorkItem</v>
+      </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.3">
       <c r="D13" s="2"/>

--- a/resources/templates/ImportTemplate.xlsx
+++ b/resources/templates/ImportTemplate.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workdir\DeerHide\sources\jira-toolkit\resources\templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workdir\DeerHide\sources\jira-toolkit\resources\Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01FCCE72-DF9E-484F-AFA5-1709264A86F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC11B61B-52F2-4383-A081-3EA527C8CFCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1152" yWindow="1152" windowWidth="34560" windowHeight="18600" xr2:uid="{1FA076D1-0294-4A97-AB8C-3ADE2BC9CEA1}"/>
+    <workbookView xWindow="3156" yWindow="6612" windowWidth="34560" windowHeight="18600" xr2:uid="{1FA076D1-0294-4A97-AB8C-3ADE2BC9CEA1}"/>
   </bookViews>
   <sheets>
     <sheet name="Dataset" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
     <definedName name="cfg_labels_ft_label">Config!$R$5</definedName>
     <definedName name="cfg_labels_ft_name">Config!$R$5</definedName>
     <definedName name="cfg_labels_imported">Config!$R$4</definedName>
-    <definedName name="cfg_projectKey">Config!#REF!</definedName>
+    <definedName name="cfg_projectKey">Config!$R$7</definedName>
     <definedName name="cfg_type_comment">Config!$M$4</definedName>
     <definedName name="cfg_type_note">Config!$M$6</definedName>
     <definedName name="cfg_type_skip">Config!$M$5</definedName>
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="101">
   <si>
     <t>IssueType</t>
   </si>
@@ -212,21 +212,9 @@
     <t>Sprint 1</t>
   </si>
   <si>
-    <t>Sprint 2</t>
-  </si>
-  <si>
     <t>Feature Pod Label</t>
   </si>
   <si>
-    <t>712020:e4e815aa-df03-418a-9760-3e70901b6ec5</t>
-  </si>
-  <si>
-    <t>712020:69ead6b8-698d-48a8-8abb-b55246f6cb7c</t>
-  </si>
-  <si>
-    <t>712020:63630dfe-2a04-4021-9f7b-53445ba456e7</t>
-  </si>
-  <si>
     <t>Highest</t>
   </si>
   <si>
@@ -347,15 +335,6 @@
     <t>Misc Fields</t>
   </si>
   <si>
-    <t>tom4897</t>
-  </si>
-  <si>
-    <t>Nakool</t>
-  </si>
-  <si>
-    <t>MirageCentury</t>
-  </si>
-  <si>
     <t>pod_test</t>
   </si>
   <si>
@@ -387,6 +366,12 @@
   </si>
   <si>
     <t>Sub-Task</t>
+  </si>
+  <si>
+    <t>AtlassianID (cloud) or Email (DC)</t>
+  </si>
+  <si>
+    <t>4w</t>
   </si>
 </sst>
 </file>
@@ -987,7 +972,7 @@
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="200">
+  <dxfs count="72">
     <dxf>
       <fill>
         <patternFill patternType="darkUp"/>
@@ -1079,6 +1064,17 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF6699"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor auto="1"/>
@@ -1116,17 +1112,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFF99CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF6699"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1221,6 +1206,17 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF6699"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor auto="1"/>
@@ -1262,301 +1258,6 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF6699"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="darkUp"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor auto="1"/>
-          <bgColor rgb="FFFF5050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDAF2D0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF2CEEF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor auto="1"/>
-          <bgColor rgb="FFFF5050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.89996032593768116"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.34998626667073579"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="1" tint="4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor auto="1"/>
-          <bgColor rgb="FFF9B1AB"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFCC99"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF99CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF6699"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="darkUp"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor auto="1"/>
-          <bgColor rgb="FFFF5050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDAF2D0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF2CEEF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor auto="1"/>
-          <bgColor rgb="FFFF5050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.89996032593768116"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.34998626667073579"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="1" tint="4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor auto="1"/>
-          <bgColor rgb="FFF9B1AB"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFCC99"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF99CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF6699"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <alignment vertical="top"/>
     </dxf>
     <dxf>
@@ -1697,858 +1398,6 @@
     </dxf>
     <dxf>
       <alignment vertical="top"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="darkUp"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor auto="1"/>
-          <bgColor rgb="FFFF5050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDAF2D0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF2CEEF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor auto="1"/>
-          <bgColor rgb="FFFF5050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.89996032593768116"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.34998626667073579"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="1" tint="4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor auto="1"/>
-          <bgColor rgb="FFF9B1AB"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFCC99"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF99CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF6699"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="darkUp"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor auto="1"/>
-          <bgColor rgb="FFFF5050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDAF2D0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF2CEEF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor auto="1"/>
-          <bgColor rgb="FFFF5050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.89996032593768116"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.34998626667073579"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="1" tint="4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor auto="1"/>
-          <bgColor rgb="FFF9B1AB"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFCC99"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF99CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF6699"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="darkUp"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor auto="1"/>
-          <bgColor rgb="FFFF5050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDAF2D0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF2CEEF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor auto="1"/>
-          <bgColor rgb="FFFF5050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.89996032593768116"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.34998626667073579"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="1" tint="4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor auto="1"/>
-          <bgColor rgb="FFF9B1AB"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFCC99"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF99CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF6699"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="darkUp"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor auto="1"/>
-          <bgColor rgb="FFFF5050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDAF2D0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF2CEEF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor auto="1"/>
-          <bgColor rgb="FFFF5050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.89996032593768116"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.34998626667073579"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="1" tint="4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor auto="1"/>
-          <bgColor rgb="FFF9B1AB"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFCC99"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF99CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF6699"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="darkUp"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor auto="1"/>
-          <bgColor rgb="FFFF5050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDAF2D0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF2CEEF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor auto="1"/>
-          <bgColor rgb="FFFF5050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.89996032593768116"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.34998626667073579"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="1" tint="4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor auto="1"/>
-          <bgColor rgb="FFF9B1AB"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFCC99"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF99CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF6699"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="darkUp"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor auto="1"/>
-          <bgColor rgb="FFFF5050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDAF2D0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF2CEEF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor auto="1"/>
-          <bgColor rgb="FFFF5050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.89996032593768116"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.34998626667073579"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="1" tint="4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor auto="1"/>
-          <bgColor rgb="FFF9B1AB"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFCC99"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF99CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF6699"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="1" readingOrder="0"/>
@@ -2592,57 +1441,57 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{933FCFD5-1AB1-4076-B5DD-E2B69F5EB3F2}" name="JiraDataset" displayName="JiraDataset" ref="A1:AJ3" totalsRowShown="0" headerRowDxfId="101" dataDxfId="100">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{933FCFD5-1AB1-4076-B5DD-E2B69F5EB3F2}" name="JiraDataset" displayName="JiraDataset" ref="A1:AJ3" totalsRowShown="0" headerRowDxfId="69" dataDxfId="68">
   <autoFilter ref="A1:AJ3" xr:uid="{933FCFD5-1AB1-4076-B5DD-E2B69F5EB3F2}"/>
   <tableColumns count="36">
-    <tableColumn id="3" xr3:uid="{AF2EC907-349C-4651-852D-6E39C61E17FF}" name="Priority" dataDxfId="99"/>
-    <tableColumn id="2" xr3:uid="{E90C51F2-4386-421F-A3E4-E2CA9D43D396}" name="IssueType" dataDxfId="98"/>
-    <tableColumn id="1" xr3:uid="{BBAD373B-BA13-47E4-9F74-565F4D9E9680}" name="Summary" dataDxfId="97"/>
-    <tableColumn id="4" xr3:uid="{026E5B97-FAFC-4E46-860E-0B0C976B1148}" name="Issue Key" dataDxfId="96"/>
-    <tableColumn id="5" xr3:uid="{A2C262E8-D544-4669-99F1-151EDE081654}" name="Description" dataDxfId="95"/>
-    <tableColumn id="7" xr3:uid="{0FAD1ACC-432E-462C-8B89-71540710BCB5}" name="FixVersion" dataDxfId="94">
+    <tableColumn id="3" xr3:uid="{AF2EC907-349C-4651-852D-6E39C61E17FF}" name="Priority" dataDxfId="67"/>
+    <tableColumn id="2" xr3:uid="{E90C51F2-4386-421F-A3E4-E2CA9D43D396}" name="IssueType" dataDxfId="66"/>
+    <tableColumn id="1" xr3:uid="{BBAD373B-BA13-47E4-9F74-565F4D9E9680}" name="Summary" dataDxfId="65"/>
+    <tableColumn id="4" xr3:uid="{026E5B97-FAFC-4E46-860E-0B0C976B1148}" name="Issue Key" dataDxfId="64"/>
+    <tableColumn id="5" xr3:uid="{A2C262E8-D544-4669-99F1-151EDE081654}" name="Description" dataDxfId="63"/>
+    <tableColumn id="7" xr3:uid="{0FAD1ACC-432E-462C-8B89-71540710BCB5}" name="FixVersion" dataDxfId="62">
       <calculatedColumnFormula>Config!$G$4</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="28" xr3:uid="{07F3030C-7187-4B16-BBDB-798304851975}" name="Assignee.Name" dataDxfId="93"/>
-    <tableColumn id="8" xr3:uid="{8C7FB8DB-A85B-4189-93D8-0F0D4EEEF81B}" name="Component" dataDxfId="92"/>
-    <tableColumn id="9" xr3:uid="{DC5101A8-1204-44D2-BC2C-FEE1A4EFE7C1}" name="Sprint Name" dataDxfId="91"/>
-    <tableColumn id="40" xr3:uid="{1F406792-7ED2-4476-8FF4-4C6ABA231C97}" name="Estimate" dataDxfId="90"/>
-    <tableColumn id="10" xr3:uid="{70B7C471-B624-430B-8992-4711F27BB17E}" name="Issue ID" dataDxfId="89"/>
-    <tableColumn id="30" xr3:uid="{938D6CA2-8309-4146-9B62-E8CDFAB7B1C9}" name="Parent" dataDxfId="88"/>
-    <tableColumn id="11" xr3:uid="{594BD56F-7D1D-408F-BEDC-6BB9854C71A1}" name="Epic Link" dataDxfId="87"/>
-    <tableColumn id="33" xr3:uid="{3A94D4B2-1A5B-4BBF-B398-E56D2BB7F948}" name="Epic Name" dataDxfId="86">
+    <tableColumn id="28" xr3:uid="{07F3030C-7187-4B16-BBDB-798304851975}" name="Assignee.Name" dataDxfId="61"/>
+    <tableColumn id="8" xr3:uid="{8C7FB8DB-A85B-4189-93D8-0F0D4EEEF81B}" name="Component" dataDxfId="60"/>
+    <tableColumn id="9" xr3:uid="{DC5101A8-1204-44D2-BC2C-FEE1A4EFE7C1}" name="Sprint Name" dataDxfId="59"/>
+    <tableColumn id="40" xr3:uid="{1F406792-7ED2-4476-8FF4-4C6ABA231C97}" name="Estimate" dataDxfId="58"/>
+    <tableColumn id="10" xr3:uid="{70B7C471-B624-430B-8992-4711F27BB17E}" name="Issue ID" dataDxfId="57"/>
+    <tableColumn id="30" xr3:uid="{938D6CA2-8309-4146-9B62-E8CDFAB7B1C9}" name="Parent" dataDxfId="56"/>
+    <tableColumn id="11" xr3:uid="{594BD56F-7D1D-408F-BEDC-6BB9854C71A1}" name="Epic Link" dataDxfId="55"/>
+    <tableColumn id="33" xr3:uid="{3A94D4B2-1A5B-4BBF-B398-E56D2BB7F948}" name="Epic Name" dataDxfId="54">
       <calculatedColumnFormula>IF(JiraDataset[[#This Row],[IssueType]]="Epic",JiraDataset[[#This Row],[Summary]],"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="27" xr3:uid="{911C8FDC-5528-43FC-BDF4-D4761F03C0E5}" name="Child-Issue" dataDxfId="85"/>
-    <tableColumn id="41" xr3:uid="{AB248E07-9BFA-42CC-BC41-B4234F677BFB}" name="Child-Issue1" dataDxfId="84"/>
-    <tableColumn id="29" xr3:uid="{89D12135-F3E3-4253-844F-1B9A54169953}" name="Child-Issue2" dataDxfId="83"/>
-    <tableColumn id="12" xr3:uid="{0699B70E-673B-4238-8A66-12FC943A4812}" name="Labels" dataDxfId="82"/>
-    <tableColumn id="13" xr3:uid="{9840B81F-2CA6-4708-8C93-3E7C8F72A676}" name="Labels1" dataDxfId="81"/>
-    <tableColumn id="14" xr3:uid="{D4A99C0B-46B7-484A-842E-D62E9D5D9341}" name="Labels2" dataDxfId="80"/>
-    <tableColumn id="15" xr3:uid="{1D1C275E-5C65-4393-9663-6C5F617591E1}" name="Labels3" dataDxfId="79"/>
-    <tableColumn id="16" xr3:uid="{D823FA91-7106-42D3-9DBC-B337C509EB09}" name="Labels4" dataDxfId="78"/>
-    <tableColumn id="17" xr3:uid="{05A07F85-1763-4A66-9CBB-4A760BD03D27}" name="Labels5" dataDxfId="77"/>
-    <tableColumn id="18" xr3:uid="{16B98070-7F8A-4FC7-AD99-EA81D0BD26AB}" name="Labels6" dataDxfId="76"/>
-    <tableColumn id="19" xr3:uid="{016EAEF4-8EA9-408B-9F1A-ECFB17E81C77}" name="Labels7" dataDxfId="75"/>
-    <tableColumn id="26" xr3:uid="{8263F9EC-BF0A-46F7-BA83-6083A4262B91}" name="Labels8" dataDxfId="74"/>
-    <tableColumn id="20" xr3:uid="{389B11C5-1B22-48C0-BCA2-72F050425FA1}" name="Labels9" dataDxfId="73"/>
-    <tableColumn id="25" xr3:uid="{AE95F8A2-F7F0-4985-9AE6-4201B9792775}" name="Labels10" dataDxfId="72"/>
-    <tableColumn id="21" xr3:uid="{105F2D0F-70C1-4517-A55F-4C1DDFE85301}" name="Sprint" dataDxfId="71">
+    <tableColumn id="27" xr3:uid="{911C8FDC-5528-43FC-BDF4-D4761F03C0E5}" name="Child-Issue" dataDxfId="53"/>
+    <tableColumn id="41" xr3:uid="{AB248E07-9BFA-42CC-BC41-B4234F677BFB}" name="Child-Issue1" dataDxfId="52"/>
+    <tableColumn id="29" xr3:uid="{89D12135-F3E3-4253-844F-1B9A54169953}" name="Child-Issue2" dataDxfId="51"/>
+    <tableColumn id="12" xr3:uid="{0699B70E-673B-4238-8A66-12FC943A4812}" name="Labels" dataDxfId="50"/>
+    <tableColumn id="13" xr3:uid="{9840B81F-2CA6-4708-8C93-3E7C8F72A676}" name="Labels1" dataDxfId="49"/>
+    <tableColumn id="14" xr3:uid="{D4A99C0B-46B7-484A-842E-D62E9D5D9341}" name="Labels2" dataDxfId="48"/>
+    <tableColumn id="15" xr3:uid="{1D1C275E-5C65-4393-9663-6C5F617591E1}" name="Labels3" dataDxfId="47"/>
+    <tableColumn id="16" xr3:uid="{D823FA91-7106-42D3-9DBC-B337C509EB09}" name="Labels4" dataDxfId="46"/>
+    <tableColumn id="17" xr3:uid="{05A07F85-1763-4A66-9CBB-4A760BD03D27}" name="Labels5" dataDxfId="45"/>
+    <tableColumn id="18" xr3:uid="{16B98070-7F8A-4FC7-AD99-EA81D0BD26AB}" name="Labels6" dataDxfId="44"/>
+    <tableColumn id="19" xr3:uid="{016EAEF4-8EA9-408B-9F1A-ECFB17E81C77}" name="Labels7" dataDxfId="43"/>
+    <tableColumn id="26" xr3:uid="{8263F9EC-BF0A-46F7-BA83-6083A4262B91}" name="Labels8" dataDxfId="42"/>
+    <tableColumn id="20" xr3:uid="{389B11C5-1B22-48C0-BCA2-72F050425FA1}" name="Labels9" dataDxfId="41"/>
+    <tableColumn id="25" xr3:uid="{AE95F8A2-F7F0-4985-9AE6-4201B9792775}" name="Labels10" dataDxfId="40"/>
+    <tableColumn id="21" xr3:uid="{105F2D0F-70C1-4517-A55F-4C1DDFE85301}" name="Sprint" dataDxfId="39">
       <calculatedColumnFormula>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",IFERROR(VLOOKUP(JiraDataset[[#This Row],[Sprint Name]], Config!$D$4:$E$9, 2, FALSE), ""))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{D5984986-D838-4F87-A554-5DC4CA005452}" name="Labels0001" dataDxfId="70">
+    <tableColumn id="22" xr3:uid="{D5984986-D838-4F87-A554-5DC4CA005452}" name="Labels0001" dataDxfId="38">
       <calculatedColumnFormula>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",_xlfn.XLOOKUP("Creation Marker", CfgAutofieldValues[Name], CfgAutofieldValues[Value]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="39" xr3:uid="{C24E9ADD-96A8-4DBB-86A0-08D41975D750}" name="Labels0002" dataDxfId="69">
+    <tableColumn id="39" xr3:uid="{C24E9ADD-96A8-4DBB-86A0-08D41975D750}" name="Labels0002" dataDxfId="37">
       <calculatedColumnFormula>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",_xlfn.XLOOKUP("Feature Pod Label", CfgAutofieldValues[Name], CfgAutofieldValues[Value]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{A6D8D5A6-43EE-415C-80C1-30372C7FE5BF}" name="Assignee" dataDxfId="68">
+    <tableColumn id="6" xr3:uid="{A6D8D5A6-43EE-415C-80C1-30372C7FE5BF}" name="Assignee" dataDxfId="36">
       <calculatedColumnFormula>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",IFERROR(VLOOKUP(JiraDataset[[#This Row],[Assignee.Name]], Config!$A$4:$B$24, 2, FALSE), ""))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="23" xr3:uid="{51D4B5F4-C6D3-4EEC-8B1B-7BEC6E526A64}" name="Project Key" dataDxfId="67">
+    <tableColumn id="23" xr3:uid="{51D4B5F4-C6D3-4EEC-8B1B-7BEC6E526A64}" name="Project Key" dataDxfId="35">
       <calculatedColumnFormula>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",_xlfn.XLOOKUP("jira.project.key", CfgAutofieldValues[Name], CfgAutofieldValues[Value]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="42" xr3:uid="{82B78F0D-CAEF-4615-B12A-B15ACF33913C}" name="OrigEst" dataDxfId="66">
+    <tableColumn id="42" xr3:uid="{82B78F0D-CAEF-4615-B12A-B15ACF33913C}" name="OrigEst" dataDxfId="34">
       <calculatedColumnFormula array="1">IF(
   JiraDataset[[#This Row],[RowType]]=cfg_type_skip,
   "",
@@ -2658,7 +1507,7 @@
   )
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="44" xr3:uid="{C92FD7EC-0EAB-4967-A0E5-D2427E3A55B4}" name="RowType" dataDxfId="65">
+    <tableColumn id="44" xr3:uid="{C92FD7EC-0EAB-4967-A0E5-D2427E3A55B4}" name="RowType" dataDxfId="33">
       <calculatedColumnFormula array="1">IFERROR(
     _xlfn.IFS(
         JiraDataset[[#This Row],[IssueType]] = cfg_type_comment,"SKIP",
@@ -2668,7 +1517,7 @@
     cfg_type_workitem
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="24" xr3:uid="{B63E8FC4-20B3-4755-92F2-EA1F700CA72E}" name="Note" dataDxfId="64"/>
+    <tableColumn id="24" xr3:uid="{B63E8FC4-20B3-4755-92F2-EA1F700CA72E}" name="Note" dataDxfId="32"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2708,15 +1557,15 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{A6C0EE44-3F60-4588-BF11-75C3DD021846}" name="CfgPriorities" displayName="CfgPriorities" ref="O3:O9" totalsRowShown="0">
   <autoFilter ref="O3:O9" xr:uid="{A6C0EE44-3F60-4588-BF11-75C3DD021846}"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{3B3BE2ED-38C4-410B-B0BF-4A9BD9B4B974}" name="Priority.Name" dataDxfId="199"/>
+    <tableColumn id="1" xr3:uid="{3B3BE2ED-38C4-410B-B0BF-4A9BD9B4B974}" name="Priority.Name" dataDxfId="71"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium5" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{1EF5833D-4918-4C71-A990-1B275126361D}" name="CfgAssignees" displayName="CfgAssignees" ref="A3:B6" totalsRowShown="0">
-  <autoFilter ref="A3:B6" xr:uid="{1EF5833D-4918-4C71-A990-1B275126361D}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{1EF5833D-4918-4C71-A990-1B275126361D}" name="CfgAssignees" displayName="CfgAssignees" ref="A3:B5" totalsRowShown="0">
+  <autoFilter ref="A3:B5" xr:uid="{1EF5833D-4918-4C71-A990-1B275126361D}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{7F7B4E10-E51C-443F-875D-3E6A9FD9994C}" name="Asssignee.Name"/>
     <tableColumn id="2" xr3:uid="{3A4C6F03-89A9-4E38-8288-00D055D51CD3}" name="Assignee.ID"/>
@@ -2742,7 +1591,7 @@
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{D4E1611F-A2CF-465D-A219-1759EA66687D}" name="Name"/>
     <tableColumn id="2" xr3:uid="{174D0D86-B1AA-4BF7-AC91-FCACFC898851}" name="Value"/>
-    <tableColumn id="3" xr3:uid="{4D0493E3-2ED0-412B-9468-835FC91C2910}" name="Remark" dataDxfId="198"/>
+    <tableColumn id="3" xr3:uid="{4D0493E3-2ED0-412B-9468-835FC91C2910}" name="Remark" dataDxfId="70"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium5" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3146,7 +1995,7 @@
         <v>10</v>
       </c>
       <c r="L1" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="M1" s="3" t="s">
         <v>11</v>
@@ -3238,7 +2087,7 @@
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="K2" s="3">
         <v>1</v>
@@ -3315,31 +2164,33 @@
     </row>
     <row r="3" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>41</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>92</v>
+        <v>54</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="I3" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="J3" s="3"/>
+      <c r="J3" s="3" t="s">
+        <v>100</v>
+      </c>
       <c r="K3" s="3">
         <v>2</v>
       </c>
@@ -3377,13 +2228,13 @@
       </c>
       <c r="AF3" s="3" t="str">
         <f>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",IFERROR(VLOOKUP(JiraDataset[[#This Row],[Assignee.Name]], Config!$A$4:$B$24, 2, FALSE), ""))</f>
-        <v>712020:e4e815aa-df03-418a-9760-3e70901b6ec5</v>
+        <v>AtlassianID (cloud) or Email (DC)</v>
       </c>
       <c r="AG3" s="3" t="str">
         <f>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",_xlfn.XLOOKUP("jira.project.key", CfgAutofieldValues[Name], CfgAutofieldValues[Value]))</f>
         <v>PROJECT KEY</v>
       </c>
-      <c r="AH3" s="3" t="str" cm="1">
+      <c r="AH3" s="3" cm="1">
         <f t="array" ref="AH3">IF(
   JiraDataset[[#This Row],[RowType]]=cfg_type_skip,
   "",
@@ -3398,7 +2249,7 @@
     IF(_xlpm.seconds=0, "", _xlpm.seconds*60)
   )
 )</f>
-        <v/>
+        <v>34560000</v>
       </c>
       <c r="AI3" s="3" t="str" cm="1">
         <f t="array" ref="AI3">IFERROR(
@@ -3420,22 +2271,24 @@
   </protectedRanges>
   <phoneticPr fontId="18" type="noConversion"/>
   <conditionalFormatting sqref="A2:A3 C2:C3">
-    <cfRule type="containsText" dxfId="15" priority="429" operator="containsText" text="blocker">
-      <formula>NOT(ISERROR(SEARCH("blocker",A2)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="14" priority="430" operator="containsText" text="critical">
+    <cfRule type="containsText" dxfId="15" priority="430" operator="containsText" text="critical">
       <formula>NOT(ISERROR(SEARCH("critical",A2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="13" priority="431" operator="containsText" text="High">
+    <cfRule type="containsText" dxfId="14" priority="431" operator="containsText" text="High">
       <formula>NOT(ISERROR(SEARCH("High",A2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="12" priority="432" operator="containsText" text="Medium">
+    <cfRule type="containsText" dxfId="13" priority="432" operator="containsText" text="Medium">
       <formula>NOT(ISERROR(SEARCH("Medium",A2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:A3">
-    <cfRule type="containsBlanks" dxfId="11" priority="493">
+    <cfRule type="containsBlanks" dxfId="12" priority="493">
       <formula>LEN(TRIM(A2))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2:C3">
+    <cfRule type="containsText" dxfId="11" priority="429" operator="containsText" text="blocker">
+      <formula>NOT(ISERROR(SEARCH("blocker",A2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:AJ3">
@@ -3481,7 +2334,7 @@
       <formula>LEN(TRIM(K2))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations xWindow="1573" yWindow="665" count="20">
+  <dataValidations xWindow="1573" yWindow="665" count="21">
     <dataValidation type="whole" allowBlank="1" showErrorMessage="1" prompt="It must be a number (integer). This reference is only used during the import process." sqref="K2:L3" xr:uid="{005E18F2-4447-4781-8F18-5A58920A4F75}">
       <formula1>1</formula1>
       <formula2>1000</formula2>
@@ -3504,7 +2357,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="must be a valid component" sqref="H2:H3" xr:uid="{65EDED96-6789-400B-B504-6BC3F5A79E70}">
       <formula1>INDIRECT("CfgComponents[Component.Name]")</formula1>
     </dataValidation>
-    <dataValidation type="list" errorStyle="warning" showErrorMessage="1" error="must be a valid fixversion" sqref="G2:G3" xr:uid="{44FDC20A-8BF5-49B5-9D2C-3A1FE5A7D835}">
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" error="must be a valid fixversion" sqref="G2:G3" xr:uid="{44FDC20A-8BF5-49B5-9D2C-3A1FE5A7D835}">
       <formula1>INDIRECT("CfgAssignees[Asssignee.Name]")</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="must be a valid component" sqref="I2:I3" xr:uid="{A898E2E7-BC45-4B88-BA1E-4AAA377361D4}">
@@ -3517,6 +2370,9 @@
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" error="must be a valid fixversion" promptTitle="Creation Marker (Config Sheet)" prompt="Do not manually edit these!" sqref="AD1:AD3" xr:uid="{412C516D-E091-4DDD-9C14-C33AC653C143}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" error="must be a valid fixversion" promptTitle="Feature Pod Label (Config Sheet)" prompt="Do not manually edit these!" sqref="AE1:AE3" xr:uid="{D2234141-379F-4413-AB08-6835BD9FF967}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" error="must be a valid fixversion" promptTitle="AUTOMATIC FIELD" prompt="Do not manually edit these! SKIP types won't be imported into Jira" sqref="AI1:AI3" xr:uid="{5A336857-7D14-4900-8734-BED680BE5154}"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="must be a valid fixversion" sqref="F2:F3" xr:uid="{7708D6E2-1D6B-41D8-A9EE-0E87219BA8EA}">
+      <formula1>INDIRECT("CfgFixVersions[FixVersion.Name]")</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -3525,7 +2381,7 @@
   </tableParts>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xWindow="1573" yWindow="665" count="3">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xWindow="1573" yWindow="665" count="2">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{5EEBB8D5-878D-4D0E-9267-0919B5A1B925}">
           <x14:formula1>
             <xm:f>Config!$O$4:$O$10</xm:f>
@@ -3537,12 +2393,6 @@
             <xm:f>Config!$U$4:$U$33</xm:f>
           </x14:formula1>
           <xm:sqref>B2:B3</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="must be a valid fixversion" xr:uid="{7708D6E2-1D6B-41D8-A9EE-0E87219BA8EA}">
-          <x14:formula1>
-            <xm:f>Config!$G$4:$G$8</xm:f>
-          </x14:formula1>
-          <xm:sqref>F2:F3</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -3577,66 +2427,66 @@
   <sheetData>
     <row r="1" spans="1:22" ht="21" x14ac:dyDescent="0.4">
       <c r="A1" s="11" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B1" s="11"/>
       <c r="D1" s="11" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="E1" s="11"/>
       <c r="G1" s="6" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="I1" s="6" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="K1" s="6" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="M1" s="6" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="O1" s="6" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="Q1" s="11" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="R1" s="11"/>
       <c r="S1" s="11"/>
       <c r="U1" s="6" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B2" s="12"/>
       <c r="C2" s="7"/>
       <c r="D2" s="12" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="E2" s="12"/>
       <c r="F2" s="7"/>
       <c r="G2" s="10" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="H2" s="10"/>
       <c r="I2" s="10" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="J2" s="10"/>
       <c r="K2" s="12" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="L2" s="12"/>
       <c r="M2" s="9" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="N2" s="9"/>
       <c r="O2" s="10" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="P2" s="10"/>
       <c r="Q2" s="12"/>
@@ -3644,57 +2494,57 @@
       <c r="S2" s="9"/>
       <c r="T2" s="7"/>
       <c r="U2" s="9" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="V2" s="9"/>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D3" t="s">
+        <v>60</v>
+      </c>
+      <c r="E3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G3" t="s">
+        <v>65</v>
+      </c>
+      <c r="I3" t="s">
+        <v>64</v>
+      </c>
+      <c r="K3" t="s">
+        <v>63</v>
+      </c>
+      <c r="M3" t="s">
+        <v>68</v>
+      </c>
+      <c r="O3" t="s">
         <v>62</v>
       </c>
-      <c r="B3" t="s">
+      <c r="Q3" t="s">
+        <v>54</v>
+      </c>
+      <c r="R3" t="s">
+        <v>55</v>
+      </c>
+      <c r="S3" t="s">
+        <v>66</v>
+      </c>
+      <c r="U3" s="5" t="s">
         <v>63</v>
-      </c>
-      <c r="D3" t="s">
-        <v>64</v>
-      </c>
-      <c r="E3" t="s">
-        <v>65</v>
-      </c>
-      <c r="G3" t="s">
-        <v>69</v>
-      </c>
-      <c r="I3" t="s">
-        <v>68</v>
-      </c>
-      <c r="K3" t="s">
-        <v>67</v>
-      </c>
-      <c r="M3" t="s">
-        <v>72</v>
-      </c>
-      <c r="O3" t="s">
-        <v>66</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>58</v>
-      </c>
-      <c r="R3" t="s">
-        <v>59</v>
-      </c>
-      <c r="S3" t="s">
-        <v>70</v>
-      </c>
-      <c r="U3" s="5" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>92</v>
+        <v>54</v>
       </c>
       <c r="B4" t="s">
-        <v>49</v>
+        <v>99</v>
       </c>
       <c r="D4" t="s">
         <v>46</v>
@@ -3703,10 +2553,10 @@
         <v>1</v>
       </c>
       <c r="G4" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="I4" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="K4" t="s">
         <v>39</v>
@@ -3718,13 +2568,13 @@
         <v>38</v>
       </c>
       <c r="Q4" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="R4" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="S4" s="7" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="U4" t="str" cm="1">
         <f t="array" aca="1" ref="U4:U12" ca="1">_xlfn.UNIQUE((_xlfn.VSTACK(INDIRECT("CfgIssueTypes[IssueType.Name]"),INDIRECT("CfgIgnoreList[IgnoreList.Name]"))))</f>
@@ -3732,18 +2582,6 @@
       </c>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>93</v>
-      </c>
-      <c r="B5" t="s">
-        <v>50</v>
-      </c>
-      <c r="D5" t="s">
-        <v>47</v>
-      </c>
-      <c r="E5">
-        <v>2</v>
-      </c>
       <c r="K5" t="s">
         <v>37</v>
       </c>
@@ -3751,16 +2589,16 @@
         <v>44</v>
       </c>
       <c r="O5" s="1" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="Q5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="R5" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="S5" s="7" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="U5" t="str">
         <f ca="1"/>
@@ -3768,12 +2606,6 @@
       </c>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>94</v>
-      </c>
-      <c r="B6" t="s">
-        <v>51</v>
-      </c>
       <c r="K6" t="s">
         <v>40</v>
       </c>
@@ -3781,10 +2613,10 @@
         <v>33</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="Q6" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="S6" s="7"/>
       <c r="U6" t="str">
@@ -3805,10 +2637,10 @@
         <v>42</v>
       </c>
       <c r="Q7" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="R7" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="S7" s="7"/>
       <c r="U7" t="str">
@@ -3820,13 +2652,13 @@
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
       <c r="K8" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="Q8" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="R8" t="b">
         <v>1</v>
@@ -3841,13 +2673,13 @@
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
       <c r="O9" s="1" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="Q9" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="R9" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="S9" s="7"/>
       <c r="U9" t="str">

--- a/resources/templates/ImportTemplate.xlsx
+++ b/resources/templates/ImportTemplate.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workdir\DeerHide\sources\jira-toolkit\resources\Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC11B61B-52F2-4383-A081-3EA527C8CFCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6BCD59E-577E-4328-B7B7-C716757B942C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3156" yWindow="6612" windowWidth="34560" windowHeight="18600" xr2:uid="{1FA076D1-0294-4A97-AB8C-3ADE2BC9CEA1}"/>
+    <workbookView xWindow="14685" yWindow="5445" windowWidth="33090" windowHeight="19545" activeTab="1" xr2:uid="{1FA076D1-0294-4A97-AB8C-3ADE2BC9CEA1}"/>
   </bookViews>
   <sheets>
     <sheet name="Dataset" sheetId="1" r:id="rId1"/>
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="117">
   <si>
     <t>IssueType</t>
   </si>
@@ -332,9 +332,6 @@
     <t>Development</t>
   </si>
   <si>
-    <t>Misc Fields</t>
-  </si>
-  <si>
     <t>pod_test</t>
   </si>
   <si>
@@ -372,6 +369,57 @@
   </si>
   <si>
     <t>4w</t>
+  </si>
+  <si>
+    <t>Configuration</t>
+  </si>
+  <si>
+    <t>Custom Fields</t>
+  </si>
+  <si>
+    <t>Id</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Format</t>
+  </si>
+  <si>
+    <t>CF Number</t>
+  </si>
+  <si>
+    <t>customfield_10125</t>
+  </si>
+  <si>
+    <t>number</t>
+  </si>
+  <si>
+    <t>CF Plain Text</t>
+  </si>
+  <si>
+    <t>customfield_10124</t>
+  </si>
+  <si>
+    <t>text</t>
+  </si>
+  <si>
+    <t>CF Select</t>
+  </si>
+  <si>
+    <t>customfield_10126</t>
+  </si>
+  <si>
+    <t>select</t>
+  </si>
+  <si>
+    <t>CF Date</t>
+  </si>
+  <si>
+    <t>customfield_10123</t>
+  </si>
+  <si>
+    <t>date</t>
   </si>
 </sst>
 </file>
@@ -972,7 +1020,7 @@
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="72">
+  <dxfs count="56">
     <dxf>
       <fill>
         <patternFill patternType="darkUp"/>
@@ -1116,146 +1164,10 @@
       </fill>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill patternType="darkUp"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor auto="1"/>
-          <bgColor rgb="FFFF5050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDAF2D0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF2CEEF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor auto="1"/>
-          <bgColor rgb="FFFF5050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.89996032593768116"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.34998626667073579"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="1" tint="4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF6699"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor auto="1"/>
-          <bgColor rgb="FFF9B1AB"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFCC99"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF99CC"/>
-        </patternFill>
-      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="1" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
     </dxf>
     <dxf>
       <alignment vertical="top"/>
@@ -1398,12 +1310,6 @@
     </dxf>
     <dxf>
       <alignment vertical="top"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="1" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1441,57 +1347,55 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{933FCFD5-1AB1-4076-B5DD-E2B69F5EB3F2}" name="JiraDataset" displayName="JiraDataset" ref="A1:AJ3" totalsRowShown="0" headerRowDxfId="69" dataDxfId="68">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{933FCFD5-1AB1-4076-B5DD-E2B69F5EB3F2}" name="JiraDataset" displayName="JiraDataset" ref="A1:AJ3" totalsRowShown="0" headerRowDxfId="55" dataDxfId="54">
   <autoFilter ref="A1:AJ3" xr:uid="{933FCFD5-1AB1-4076-B5DD-E2B69F5EB3F2}"/>
   <tableColumns count="36">
-    <tableColumn id="3" xr3:uid="{AF2EC907-349C-4651-852D-6E39C61E17FF}" name="Priority" dataDxfId="67"/>
-    <tableColumn id="2" xr3:uid="{E90C51F2-4386-421F-A3E4-E2CA9D43D396}" name="IssueType" dataDxfId="66"/>
-    <tableColumn id="1" xr3:uid="{BBAD373B-BA13-47E4-9F74-565F4D9E9680}" name="Summary" dataDxfId="65"/>
-    <tableColumn id="4" xr3:uid="{026E5B97-FAFC-4E46-860E-0B0C976B1148}" name="Issue Key" dataDxfId="64"/>
-    <tableColumn id="5" xr3:uid="{A2C262E8-D544-4669-99F1-151EDE081654}" name="Description" dataDxfId="63"/>
-    <tableColumn id="7" xr3:uid="{0FAD1ACC-432E-462C-8B89-71540710BCB5}" name="FixVersion" dataDxfId="62">
-      <calculatedColumnFormula>Config!$G$4</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="28" xr3:uid="{07F3030C-7187-4B16-BBDB-798304851975}" name="Assignee.Name" dataDxfId="61"/>
-    <tableColumn id="8" xr3:uid="{8C7FB8DB-A85B-4189-93D8-0F0D4EEEF81B}" name="Component" dataDxfId="60"/>
-    <tableColumn id="9" xr3:uid="{DC5101A8-1204-44D2-BC2C-FEE1A4EFE7C1}" name="Sprint Name" dataDxfId="59"/>
-    <tableColumn id="40" xr3:uid="{1F406792-7ED2-4476-8FF4-4C6ABA231C97}" name="Estimate" dataDxfId="58"/>
-    <tableColumn id="10" xr3:uid="{70B7C471-B624-430B-8992-4711F27BB17E}" name="Issue ID" dataDxfId="57"/>
-    <tableColumn id="30" xr3:uid="{938D6CA2-8309-4146-9B62-E8CDFAB7B1C9}" name="Parent" dataDxfId="56"/>
-    <tableColumn id="11" xr3:uid="{594BD56F-7D1D-408F-BEDC-6BB9854C71A1}" name="Epic Link" dataDxfId="55"/>
-    <tableColumn id="33" xr3:uid="{3A94D4B2-1A5B-4BBF-B398-E56D2BB7F948}" name="Epic Name" dataDxfId="54">
+    <tableColumn id="3" xr3:uid="{AF2EC907-349C-4651-852D-6E39C61E17FF}" name="Priority" dataDxfId="53"/>
+    <tableColumn id="2" xr3:uid="{E90C51F2-4386-421F-A3E4-E2CA9D43D396}" name="IssueType" dataDxfId="52"/>
+    <tableColumn id="1" xr3:uid="{BBAD373B-BA13-47E4-9F74-565F4D9E9680}" name="Summary" dataDxfId="51"/>
+    <tableColumn id="4" xr3:uid="{026E5B97-FAFC-4E46-860E-0B0C976B1148}" name="Issue Key" dataDxfId="50"/>
+    <tableColumn id="5" xr3:uid="{A2C262E8-D544-4669-99F1-151EDE081654}" name="Description" dataDxfId="49"/>
+    <tableColumn id="7" xr3:uid="{0FAD1ACC-432E-462C-8B89-71540710BCB5}" name="FixVersion" dataDxfId="48"/>
+    <tableColumn id="28" xr3:uid="{07F3030C-7187-4B16-BBDB-798304851975}" name="Assignee.Name" dataDxfId="47"/>
+    <tableColumn id="8" xr3:uid="{8C7FB8DB-A85B-4189-93D8-0F0D4EEEF81B}" name="Component" dataDxfId="46"/>
+    <tableColumn id="9" xr3:uid="{DC5101A8-1204-44D2-BC2C-FEE1A4EFE7C1}" name="Sprint Name" dataDxfId="45"/>
+    <tableColumn id="40" xr3:uid="{1F406792-7ED2-4476-8FF4-4C6ABA231C97}" name="Estimate" dataDxfId="44"/>
+    <tableColumn id="10" xr3:uid="{70B7C471-B624-430B-8992-4711F27BB17E}" name="Issue ID" dataDxfId="43"/>
+    <tableColumn id="30" xr3:uid="{938D6CA2-8309-4146-9B62-E8CDFAB7B1C9}" name="Parent" dataDxfId="42"/>
+    <tableColumn id="11" xr3:uid="{594BD56F-7D1D-408F-BEDC-6BB9854C71A1}" name="Epic Link" dataDxfId="41"/>
+    <tableColumn id="33" xr3:uid="{3A94D4B2-1A5B-4BBF-B398-E56D2BB7F948}" name="Epic Name" dataDxfId="40">
       <calculatedColumnFormula>IF(JiraDataset[[#This Row],[IssueType]]="Epic",JiraDataset[[#This Row],[Summary]],"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="27" xr3:uid="{911C8FDC-5528-43FC-BDF4-D4761F03C0E5}" name="Child-Issue" dataDxfId="53"/>
-    <tableColumn id="41" xr3:uid="{AB248E07-9BFA-42CC-BC41-B4234F677BFB}" name="Child-Issue1" dataDxfId="52"/>
-    <tableColumn id="29" xr3:uid="{89D12135-F3E3-4253-844F-1B9A54169953}" name="Child-Issue2" dataDxfId="51"/>
-    <tableColumn id="12" xr3:uid="{0699B70E-673B-4238-8A66-12FC943A4812}" name="Labels" dataDxfId="50"/>
-    <tableColumn id="13" xr3:uid="{9840B81F-2CA6-4708-8C93-3E7C8F72A676}" name="Labels1" dataDxfId="49"/>
-    <tableColumn id="14" xr3:uid="{D4A99C0B-46B7-484A-842E-D62E9D5D9341}" name="Labels2" dataDxfId="48"/>
-    <tableColumn id="15" xr3:uid="{1D1C275E-5C65-4393-9663-6C5F617591E1}" name="Labels3" dataDxfId="47"/>
-    <tableColumn id="16" xr3:uid="{D823FA91-7106-42D3-9DBC-B337C509EB09}" name="Labels4" dataDxfId="46"/>
-    <tableColumn id="17" xr3:uid="{05A07F85-1763-4A66-9CBB-4A760BD03D27}" name="Labels5" dataDxfId="45"/>
-    <tableColumn id="18" xr3:uid="{16B98070-7F8A-4FC7-AD99-EA81D0BD26AB}" name="Labels6" dataDxfId="44"/>
-    <tableColumn id="19" xr3:uid="{016EAEF4-8EA9-408B-9F1A-ECFB17E81C77}" name="Labels7" dataDxfId="43"/>
-    <tableColumn id="26" xr3:uid="{8263F9EC-BF0A-46F7-BA83-6083A4262B91}" name="Labels8" dataDxfId="42"/>
-    <tableColumn id="20" xr3:uid="{389B11C5-1B22-48C0-BCA2-72F050425FA1}" name="Labels9" dataDxfId="41"/>
-    <tableColumn id="25" xr3:uid="{AE95F8A2-F7F0-4985-9AE6-4201B9792775}" name="Labels10" dataDxfId="40"/>
-    <tableColumn id="21" xr3:uid="{105F2D0F-70C1-4517-A55F-4C1DDFE85301}" name="Sprint" dataDxfId="39">
+    <tableColumn id="27" xr3:uid="{911C8FDC-5528-43FC-BDF4-D4761F03C0E5}" name="Child-Issue" dataDxfId="39"/>
+    <tableColumn id="41" xr3:uid="{AB248E07-9BFA-42CC-BC41-B4234F677BFB}" name="Child-Issue1" dataDxfId="38"/>
+    <tableColumn id="29" xr3:uid="{89D12135-F3E3-4253-844F-1B9A54169953}" name="Child-Issue2" dataDxfId="37"/>
+    <tableColumn id="12" xr3:uid="{0699B70E-673B-4238-8A66-12FC943A4812}" name="Labels" dataDxfId="36"/>
+    <tableColumn id="13" xr3:uid="{9840B81F-2CA6-4708-8C93-3E7C8F72A676}" name="Labels1" dataDxfId="35"/>
+    <tableColumn id="14" xr3:uid="{D4A99C0B-46B7-484A-842E-D62E9D5D9341}" name="Labels2" dataDxfId="34"/>
+    <tableColumn id="15" xr3:uid="{1D1C275E-5C65-4393-9663-6C5F617591E1}" name="Labels3" dataDxfId="33"/>
+    <tableColumn id="16" xr3:uid="{D823FA91-7106-42D3-9DBC-B337C509EB09}" name="Labels4" dataDxfId="32"/>
+    <tableColumn id="17" xr3:uid="{05A07F85-1763-4A66-9CBB-4A760BD03D27}" name="Labels5" dataDxfId="31"/>
+    <tableColumn id="18" xr3:uid="{16B98070-7F8A-4FC7-AD99-EA81D0BD26AB}" name="Labels6" dataDxfId="30"/>
+    <tableColumn id="19" xr3:uid="{016EAEF4-8EA9-408B-9F1A-ECFB17E81C77}" name="Labels7" dataDxfId="29"/>
+    <tableColumn id="26" xr3:uid="{8263F9EC-BF0A-46F7-BA83-6083A4262B91}" name="Labels8" dataDxfId="28"/>
+    <tableColumn id="20" xr3:uid="{389B11C5-1B22-48C0-BCA2-72F050425FA1}" name="Labels9" dataDxfId="27"/>
+    <tableColumn id="25" xr3:uid="{AE95F8A2-F7F0-4985-9AE6-4201B9792775}" name="Labels10" dataDxfId="26"/>
+    <tableColumn id="21" xr3:uid="{105F2D0F-70C1-4517-A55F-4C1DDFE85301}" name="Sprint" dataDxfId="25">
       <calculatedColumnFormula>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",IFERROR(VLOOKUP(JiraDataset[[#This Row],[Sprint Name]], Config!$D$4:$E$9, 2, FALSE), ""))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{D5984986-D838-4F87-A554-5DC4CA005452}" name="Labels0001" dataDxfId="38">
+    <tableColumn id="22" xr3:uid="{D5984986-D838-4F87-A554-5DC4CA005452}" name="Labels0001" dataDxfId="24">
       <calculatedColumnFormula>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",_xlfn.XLOOKUP("Creation Marker", CfgAutofieldValues[Name], CfgAutofieldValues[Value]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="39" xr3:uid="{C24E9ADD-96A8-4DBB-86A0-08D41975D750}" name="Labels0002" dataDxfId="37">
+    <tableColumn id="39" xr3:uid="{C24E9ADD-96A8-4DBB-86A0-08D41975D750}" name="Labels0002" dataDxfId="23">
       <calculatedColumnFormula>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",_xlfn.XLOOKUP("Feature Pod Label", CfgAutofieldValues[Name], CfgAutofieldValues[Value]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{A6D8D5A6-43EE-415C-80C1-30372C7FE5BF}" name="Assignee" dataDxfId="36">
+    <tableColumn id="6" xr3:uid="{A6D8D5A6-43EE-415C-80C1-30372C7FE5BF}" name="Assignee" dataDxfId="22">
       <calculatedColumnFormula>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",IFERROR(VLOOKUP(JiraDataset[[#This Row],[Assignee.Name]], Config!$A$4:$B$24, 2, FALSE), ""))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="23" xr3:uid="{51D4B5F4-C6D3-4EEC-8B1B-7BEC6E526A64}" name="Project Key" dataDxfId="35">
+    <tableColumn id="23" xr3:uid="{51D4B5F4-C6D3-4EEC-8B1B-7BEC6E526A64}" name="Project Key" dataDxfId="21">
       <calculatedColumnFormula>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",_xlfn.XLOOKUP("jira.project.key", CfgAutofieldValues[Name], CfgAutofieldValues[Value]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="42" xr3:uid="{82B78F0D-CAEF-4615-B12A-B15ACF33913C}" name="OrigEst" dataDxfId="34">
+    <tableColumn id="42" xr3:uid="{82B78F0D-CAEF-4615-B12A-B15ACF33913C}" name="OrigEst" dataDxfId="20">
       <calculatedColumnFormula array="1">IF(
   JiraDataset[[#This Row],[RowType]]=cfg_type_skip,
   "",
@@ -1507,7 +1411,7 @@
   )
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="44" xr3:uid="{C92FD7EC-0EAB-4967-A0E5-D2427E3A55B4}" name="RowType" dataDxfId="33">
+    <tableColumn id="44" xr3:uid="{C92FD7EC-0EAB-4967-A0E5-D2427E3A55B4}" name="RowType" dataDxfId="19">
       <calculatedColumnFormula array="1">IFERROR(
     _xlfn.IFS(
         JiraDataset[[#This Row],[IssueType]] = cfg_type_comment,"SKIP",
@@ -1517,9 +1421,22 @@
     cfg_type_workitem
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="24" xr3:uid="{B63E8FC4-20B3-4755-92F2-EA1F700CA72E}" name="Note" dataDxfId="32"/>
+    <tableColumn id="24" xr3:uid="{B63E8FC4-20B3-4755-92F2-EA1F700CA72E}" name="Note" dataDxfId="18"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{3EF499BE-ED9A-4C28-BC5A-BCDEF51C613F}" name="CfgCustomFields" displayName="CfgCustomFields" ref="U3:X7" totalsRowShown="0">
+  <autoFilter ref="U3:X7" xr:uid="{3EF499BE-ED9A-4C28-BC5A-BCDEF51C613F}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{44010E5A-E449-477A-BFB0-2ECA215E3FEB}" name="Name"/>
+    <tableColumn id="2" xr3:uid="{0E558995-744D-4813-9A4E-F64FFF5047AE}" name="Id"/>
+    <tableColumn id="3" xr3:uid="{8D81F1E3-8799-4AE9-BACA-610A64846357}" name="Type"/>
+    <tableColumn id="4" xr3:uid="{BEA106CA-BE66-4629-B856-FE53C841A6BA}" name="Format"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium5" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -1557,7 +1474,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{A6C0EE44-3F60-4588-BF11-75C3DD021846}" name="CfgPriorities" displayName="CfgPriorities" ref="O3:O9" totalsRowShown="0">
   <autoFilter ref="O3:O9" xr:uid="{A6C0EE44-3F60-4588-BF11-75C3DD021846}"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{3B3BE2ED-38C4-410B-B0BF-4A9BD9B4B974}" name="Priority.Name" dataDxfId="71"/>
+    <tableColumn id="1" xr3:uid="{3B3BE2ED-38C4-410B-B0BF-4A9BD9B4B974}" name="Priority.Name" dataDxfId="17"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium5" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1591,7 +1508,7 @@
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{D4E1611F-A2CF-465D-A219-1759EA66687D}" name="Name"/>
     <tableColumn id="2" xr3:uid="{174D0D86-B1AA-4BF7-AC91-FCACFC898851}" name="Value"/>
-    <tableColumn id="3" xr3:uid="{4D0493E3-2ED0-412B-9468-835FC91C2910}" name="Remark" dataDxfId="70"/>
+    <tableColumn id="3" xr3:uid="{4D0493E3-2ED0-412B-9468-835FC91C2910}" name="Remark" dataDxfId="16"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium5" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1925,42 +1842,42 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F73058B-F76D-4AAE-8108-6C4469E9D8B5}">
   <dimension ref="A1:AK3"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelCol="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelCol="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="31.6640625" customWidth="1"/>
-    <col min="4" max="4" width="11.88671875" hidden="1" customWidth="1"/>
+    <col min="1" max="2" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="31.7109375" customWidth="1"/>
+    <col min="4" max="4" width="11.85546875" hidden="1" customWidth="1"/>
     <col min="5" max="5" width="33" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="46.33203125" customWidth="1"/>
-    <col min="7" max="7" width="17.44140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="22.5546875" customWidth="1"/>
+    <col min="6" max="6" width="46.28515625" customWidth="1"/>
+    <col min="7" max="7" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="22.5703125" customWidth="1"/>
     <col min="9" max="9" width="14" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.44140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.33203125" customWidth="1"/>
-    <col min="13" max="13" width="14.44140625" customWidth="1"/>
-    <col min="14" max="14" width="14.33203125" customWidth="1"/>
+    <col min="10" max="11" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.28515625" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" customWidth="1"/>
+    <col min="14" max="14" width="14.28515625" customWidth="1"/>
     <col min="15" max="15" width="0" hidden="1" customWidth="1"/>
-    <col min="16" max="16" width="22.33203125" hidden="1" customWidth="1"/>
-    <col min="17" max="17" width="12.88671875" hidden="1" customWidth="1"/>
-    <col min="18" max="18" width="12.44140625" customWidth="1"/>
-    <col min="19" max="19" width="15.5546875" customWidth="1"/>
-    <col min="20" max="20" width="12.88671875" customWidth="1"/>
+    <col min="16" max="16" width="22.28515625" hidden="1" customWidth="1"/>
+    <col min="17" max="17" width="12.85546875" hidden="1" customWidth="1"/>
+    <col min="18" max="18" width="12.42578125" customWidth="1"/>
+    <col min="19" max="19" width="15.5703125" customWidth="1"/>
+    <col min="20" max="20" width="12.85546875" customWidth="1"/>
     <col min="21" max="21" width="10" customWidth="1"/>
     <col min="22" max="22" width="10" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="10" customWidth="1"/>
-    <col min="24" max="24" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="10.140625" bestFit="1" customWidth="1"/>
     <col min="25" max="30" width="10" customWidth="1" outlineLevel="1"/>
     <col min="31" max="31" width="10" customWidth="1"/>
-    <col min="32" max="32" width="8.6640625" customWidth="1" outlineLevel="1"/>
-    <col min="33" max="34" width="13.109375" customWidth="1" outlineLevel="1"/>
-    <col min="35" max="35" width="11.44140625" customWidth="1" outlineLevel="1"/>
-    <col min="36" max="37" width="13.6640625" customWidth="1" outlineLevel="1"/>
-    <col min="38" max="38" width="36.5546875" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="18.6640625" customWidth="1"/>
-    <col min="41" max="41" width="87.33203125" customWidth="1"/>
+    <col min="32" max="32" width="8.7109375" customWidth="1" outlineLevel="1"/>
+    <col min="33" max="34" width="13.140625" customWidth="1" outlineLevel="1"/>
+    <col min="35" max="35" width="11.42578125" customWidth="1" outlineLevel="1"/>
+    <col min="36" max="37" width="13.7109375" customWidth="1" outlineLevel="1"/>
+    <col min="38" max="38" width="36.5703125" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="18.7109375" customWidth="1"/>
+    <col min="41" max="41" width="87.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>1</v>
       </c>
@@ -2070,7 +1987,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="3" t="s">
         <v>33</v>
@@ -2162,7 +2079,7 @@
       </c>
       <c r="AJ2" s="3"/>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>48</v>
       </c>
@@ -2177,7 +2094,7 @@
         <v>84</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>54</v>
@@ -2189,7 +2106,7 @@
         <v>46</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="K3" s="3">
         <v>2</v>
@@ -2390,7 +2307,7 @@
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Issue Type" xr:uid="{28BF52BF-C0B0-4D22-B02F-F1408D5A055B}">
           <x14:formula1>
-            <xm:f>Config!$U$4:$U$33</xm:f>
+            <xm:f>Config!$Z$4:$Z$33</xm:f>
           </x14:formula1>
           <xm:sqref>B2:B3</xm:sqref>
         </x14:dataValidation>
@@ -2402,30 +2319,30 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2D54512-1380-4F02-BB23-352387C91232}">
-  <dimension ref="A1:V21"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:AA21"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="29.6640625" customWidth="1"/>
+    <col min="1" max="1" width="29.7109375" customWidth="1"/>
     <col min="2" max="2" width="49" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.33203125" customWidth="1"/>
-    <col min="4" max="5" width="18.6640625" customWidth="1"/>
-    <col min="6" max="6" width="4.33203125" customWidth="1"/>
-    <col min="7" max="7" width="18.5546875" customWidth="1"/>
-    <col min="8" max="8" width="4.33203125" customWidth="1"/>
-    <col min="9" max="9" width="19.109375" customWidth="1"/>
-    <col min="10" max="10" width="4.33203125" customWidth="1"/>
-    <col min="11" max="11" width="18.5546875" customWidth="1"/>
-    <col min="12" max="12" width="4.33203125" customWidth="1"/>
-    <col min="13" max="13" width="17.5546875" customWidth="1"/>
-    <col min="14" max="14" width="4.33203125" customWidth="1"/>
-    <col min="15" max="15" width="18.6640625" customWidth="1"/>
-    <col min="16" max="16" width="4.33203125" customWidth="1"/>
-    <col min="17" max="18" width="18.6640625" customWidth="1"/>
+    <col min="3" max="3" width="4.28515625" customWidth="1"/>
+    <col min="4" max="5" width="18.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.28515625" customWidth="1"/>
+    <col min="7" max="7" width="18.5703125" customWidth="1"/>
+    <col min="8" max="8" width="4.28515625" customWidth="1"/>
+    <col min="9" max="9" width="19.140625" customWidth="1"/>
+    <col min="10" max="10" width="4.28515625" customWidth="1"/>
+    <col min="11" max="11" width="18.5703125" customWidth="1"/>
+    <col min="12" max="12" width="4.28515625" customWidth="1"/>
+    <col min="13" max="13" width="17.5703125" customWidth="1"/>
+    <col min="14" max="14" width="4.28515625" customWidth="1"/>
+    <col min="15" max="15" width="18.7109375" customWidth="1"/>
+    <col min="16" max="16" width="4.28515625" customWidth="1"/>
+    <col min="17" max="18" width="18.7109375" customWidth="1"/>
     <col min="19" max="19" width="35" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="22.33203125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="22.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="21" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:27" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="11" t="s">
         <v>69</v>
       </c>
@@ -2450,15 +2367,21 @@
         <v>53</v>
       </c>
       <c r="Q1" s="11" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="R1" s="11"/>
       <c r="S1" s="11"/>
-      <c r="U1" s="6" t="s">
+      <c r="U1" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="V1" s="11"/>
+      <c r="W1" s="11"/>
+      <c r="X1" s="11"/>
+      <c r="Z1" s="6" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
         <v>75</v>
       </c>
@@ -2493,12 +2416,17 @@
       <c r="R2" s="12"/>
       <c r="S2" s="9"/>
       <c r="T2" s="7"/>
-      <c r="U2" s="9" t="s">
+      <c r="U2" s="7"/>
+      <c r="V2" s="7"/>
+      <c r="W2" s="7"/>
+      <c r="X2" s="7"/>
+      <c r="Y2" s="7"/>
+      <c r="Z2" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="V2" s="9"/>
+      <c r="AA2" s="9"/>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>58</v>
       </c>
@@ -2535,16 +2463,28 @@
       <c r="S3" t="s">
         <v>66</v>
       </c>
-      <c r="U3" s="5" t="s">
+      <c r="U3" t="s">
+        <v>54</v>
+      </c>
+      <c r="V3" t="s">
+        <v>102</v>
+      </c>
+      <c r="W3" t="s">
+        <v>103</v>
+      </c>
+      <c r="X3" t="s">
+        <v>104</v>
+      </c>
+      <c r="Z3" s="5" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>54</v>
       </c>
       <c r="B4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D4" t="s">
         <v>46</v>
@@ -2553,7 +2493,7 @@
         <v>1</v>
       </c>
       <c r="G4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I4" t="s">
         <v>86</v>
@@ -2571,17 +2511,26 @@
         <v>51</v>
       </c>
       <c r="R4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="S4" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="U4" t="str" cm="1">
-        <f t="array" aca="1" ref="U4:U12" ca="1">_xlfn.UNIQUE((_xlfn.VSTACK(INDIRECT("CfgIssueTypes[IssueType.Name]"),INDIRECT("CfgIgnoreList[IgnoreList.Name]"))))</f>
+      <c r="U4" t="s">
+        <v>105</v>
+      </c>
+      <c r="V4" t="s">
+        <v>106</v>
+      </c>
+      <c r="W4" t="s">
+        <v>107</v>
+      </c>
+      <c r="Z4" t="str" cm="1">
+        <f t="array" aca="1" ref="Z4:Z12" ca="1">_xlfn.UNIQUE((_xlfn.VSTACK(INDIRECT("CfgIssueTypes[IssueType.Name]"),INDIRECT("CfgIgnoreList[IgnoreList.Name]"))))</f>
         <v>Story</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
       <c r="K5" t="s">
         <v>37</v>
       </c>
@@ -2595,17 +2544,26 @@
         <v>47</v>
       </c>
       <c r="R5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="S5" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="U5" t="str">
+      <c r="U5" t="s">
+        <v>108</v>
+      </c>
+      <c r="V5" t="s">
+        <v>109</v>
+      </c>
+      <c r="W5" t="s">
+        <v>110</v>
+      </c>
+      <c r="Z5" t="str">
         <f ca="1"/>
         <v>Task</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
       <c r="K6" t="s">
         <v>40</v>
       </c>
@@ -2613,18 +2571,27 @@
         <v>33</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="Q6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="S6" s="7"/>
-      <c r="U6" t="str">
+      <c r="U6" t="s">
+        <v>111</v>
+      </c>
+      <c r="V6" t="s">
+        <v>112</v>
+      </c>
+      <c r="W6" t="s">
+        <v>113</v>
+      </c>
+      <c r="Z6" t="str">
         <f ca="1"/>
         <v>Bug</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
       <c r="K7" t="s">
@@ -2637,118 +2604,128 @@
         <v>42</v>
       </c>
       <c r="Q7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="R7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="S7" s="7"/>
-      <c r="U7" t="str">
+      <c r="U7" t="s">
+        <v>114</v>
+      </c>
+      <c r="V7" t="s">
+        <v>115</v>
+      </c>
+      <c r="W7" t="s">
+        <v>116</v>
+      </c>
+      <c r="Z7" t="str">
         <f ca="1"/>
         <v>Epic</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
       <c r="K8" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="O8" s="1" t="s">
         <v>49</v>
       </c>
       <c r="Q8" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="R8" t="b">
         <v>1</v>
       </c>
       <c r="S8" s="7"/>
-      <c r="U8" t="str">
+      <c r="Z8" t="str">
         <f ca="1"/>
         <v>Sub-Task</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
       <c r="O9" s="1" t="s">
         <v>50</v>
       </c>
       <c r="Q9" t="s">
+        <v>91</v>
+      </c>
+      <c r="R9" t="s">
         <v>92</v>
       </c>
-      <c r="R9" t="s">
-        <v>93</v>
-      </c>
       <c r="S9" s="7"/>
-      <c r="U9" t="str">
+      <c r="Z9" t="str">
         <f ca="1"/>
         <v>Comment</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
-      <c r="U10" t="str">
+      <c r="Z10" t="str">
         <f ca="1"/>
         <v>Skip</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
-      <c r="U11" t="str">
+      <c r="Z11" t="str">
         <f ca="1"/>
         <v>Note</v>
       </c>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
-      <c r="U12" t="str">
+      <c r="Z12" t="str">
         <f ca="1"/>
         <v>WorkItem</v>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
     </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
     </row>
-    <row r="17" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
     </row>
-    <row r="18" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
     </row>
-    <row r="19" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D19" s="2"/>
       <c r="E19" s="2"/>
     </row>
-    <row r="20" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D20" s="2"/>
       <c r="E20" s="2"/>
     </row>
-    <row r="21" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D21" s="2"/>
       <c r="E21" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
+    <mergeCell ref="U1:X1"/>
     <mergeCell ref="Q1:S1"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="A1:B1"/>
@@ -2760,7 +2737,7 @@
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
-  <tableParts count="8">
+  <tableParts count="9">
     <tablePart r:id="rId2"/>
     <tablePart r:id="rId3"/>
     <tablePart r:id="rId4"/>
@@ -2769,11 +2746,32 @@
     <tablePart r:id="rId7"/>
     <tablePart r:id="rId8"/>
     <tablePart r:id="rId9"/>
+    <tablePart r:id="rId10"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c471fd26-9765-4fbe-b6fd-c17c1e55c974">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="9df69692-83aa-4c55-88c1-62abad05f4fe" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100FB038601AF41D04A88A4BD446922F1A8" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="e8d32171d27ae41230d53456f24efae5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c471fd26-9765-4fbe-b6fd-c17c1e55c974" xmlns:ns3="9df69692-83aa-4c55-88c1-62abad05f4fe" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1f2fb84de5621acf32f385a2ba90fb29" ns2:_="" ns3:_="">
     <xsd:import namespace="c471fd26-9765-4fbe-b6fd-c17c1e55c974"/>
@@ -3002,27 +3000,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9FFE630F-6530-4863-AB67-8477539A0000}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="c471fd26-9765-4fbe-b6fd-c17c1e55c974"/>
+    <ds:schemaRef ds:uri="9df69692-83aa-4c55-88c1-62abad05f4fe"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c471fd26-9765-4fbe-b6fd-c17c1e55c974">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="9df69692-83aa-4c55-88c1-62abad05f4fe" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{156C3F15-3876-4FBB-8F24-692088DE8D9F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2C983B91-58B3-4C2C-AC55-FFEC9F0DB5F6}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3039,23 +3036,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{156C3F15-3876-4FBB-8F24-692088DE8D9F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9FFE630F-6530-4863-AB67-8477539A0000}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="c471fd26-9765-4fbe-b6fd-c17c1e55c974"/>
-    <ds:schemaRef ds:uri="9df69692-83aa-4c55-88c1-62abad05f4fe"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/resources/templates/ImportTemplate.xlsx
+++ b/resources/templates/ImportTemplate.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workdir\DeerHide\sources\jira-toolkit\resources\Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6BCD59E-577E-4328-B7B7-C716757B942C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F55D66A0-1E6F-4D7B-9000-CD63805D1508}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14685" yWindow="5445" windowWidth="33090" windowHeight="19545" activeTab="1" xr2:uid="{1FA076D1-0294-4A97-AB8C-3ADE2BC9CEA1}"/>
+    <workbookView xWindow="9060" yWindow="7155" windowWidth="33090" windowHeight="19545" xr2:uid="{1FA076D1-0294-4A97-AB8C-3ADE2BC9CEA1}"/>
   </bookViews>
   <sheets>
     <sheet name="Dataset" sheetId="1" r:id="rId1"/>
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="120">
   <si>
     <t>IssueType</t>
   </si>
@@ -420,6 +420,15 @@
   </si>
   <si>
     <t>date</t>
+  </si>
+  <si>
+    <t>CF Field</t>
+  </si>
+  <si>
+    <t>any</t>
+  </si>
+  <si>
+    <t>customfield_10128</t>
   </si>
 </sst>
 </file>
@@ -1428,8 +1437,8 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{3EF499BE-ED9A-4C28-BC5A-BCDEF51C613F}" name="CfgCustomFields" displayName="CfgCustomFields" ref="U3:X7" totalsRowShown="0">
-  <autoFilter ref="U3:X7" xr:uid="{3EF499BE-ED9A-4C28-BC5A-BCDEF51C613F}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{3EF499BE-ED9A-4C28-BC5A-BCDEF51C613F}" name="CfgCustomFields" displayName="CfgCustomFields" ref="U3:X8" totalsRowShown="0">
+  <autoFilter ref="U3:X8" xr:uid="{3EF499BE-ED9A-4C28-BC5A-BCDEF51C613F}"/>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{44010E5A-E449-477A-BFB0-2ECA215E3FEB}" name="Name"/>
     <tableColumn id="2" xr3:uid="{0E558995-744D-4813-9A4E-F64FFF5047AE}" name="Id"/>
@@ -2640,6 +2649,15 @@
         <v>1</v>
       </c>
       <c r="S8" s="7"/>
+      <c r="U8" t="s">
+        <v>117</v>
+      </c>
+      <c r="V8" t="s">
+        <v>119</v>
+      </c>
+      <c r="W8" t="s">
+        <v>118</v>
+      </c>
       <c r="Z8" t="str">
         <f ca="1"/>
         <v>Sub-Task</v>
@@ -2752,26 +2770,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c471fd26-9765-4fbe-b6fd-c17c1e55c974">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="9df69692-83aa-4c55-88c1-62abad05f4fe" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100FB038601AF41D04A88A4BD446922F1A8" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="e8d32171d27ae41230d53456f24efae5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c471fd26-9765-4fbe-b6fd-c17c1e55c974" xmlns:ns3="9df69692-83aa-4c55-88c1-62abad05f4fe" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1f2fb84de5621acf32f385a2ba90fb29" ns2:_="" ns3:_="">
     <xsd:import namespace="c471fd26-9765-4fbe-b6fd-c17c1e55c974"/>
@@ -3000,26 +2998,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9FFE630F-6530-4863-AB67-8477539A0000}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="c471fd26-9765-4fbe-b6fd-c17c1e55c974"/>
-    <ds:schemaRef ds:uri="9df69692-83aa-4c55-88c1-62abad05f4fe"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{156C3F15-3876-4FBB-8F24-692088DE8D9F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c471fd26-9765-4fbe-b6fd-c17c1e55c974">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="9df69692-83aa-4c55-88c1-62abad05f4fe" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2C983B91-58B3-4C2C-AC55-FFEC9F0DB5F6}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3036,4 +3035,23 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{156C3F15-3876-4FBB-8F24-692088DE8D9F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9FFE630F-6530-4863-AB67-8477539A0000}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="c471fd26-9765-4fbe-b6fd-c17c1e55c974"/>
+    <ds:schemaRef ds:uri="9df69692-83aa-4c55-88c1-62abad05f4fe"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/resources/templates/ImportTemplate.xlsx
+++ b/resources/templates/ImportTemplate.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workdir\DeerHide\sources\jira-toolkit\resources\Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F55D66A0-1E6F-4D7B-9000-CD63805D1508}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09FDBF7F-D200-4D23-A13C-FBD71614ACEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9060" yWindow="7155" windowWidth="33090" windowHeight="19545" xr2:uid="{1FA076D1-0294-4A97-AB8C-3ADE2BC9CEA1}"/>
+    <workbookView xWindow="675" yWindow="4890" windowWidth="25740" windowHeight="15045" activeTab="1" xr2:uid="{1FA076D1-0294-4A97-AB8C-3ADE2BC9CEA1}"/>
   </bookViews>
   <sheets>
     <sheet name="Dataset" sheetId="1" r:id="rId1"/>
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="121">
   <si>
     <t>IssueType</t>
   </si>
@@ -341,9 +341,6 @@
     <t>jira.project.key</t>
   </si>
   <si>
-    <t>validation.skip_rowtype</t>
-  </si>
-  <si>
     <t>validation.skip_issuetypes</t>
   </si>
   <si>
@@ -429,6 +426,12 @@
   </si>
   <si>
     <t>customfield_10128</t>
+  </si>
+  <si>
+    <t>app.import.auto_open_page</t>
+  </si>
+  <si>
+    <t>no</t>
   </si>
 </sst>
 </file>
@@ -1512,8 +1515,8 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{383560BC-B1F2-44B6-B877-188131EFA163}" name="CfgAutofieldValues" displayName="CfgAutofieldValues" ref="Q3:S9" totalsRowShown="0">
-  <autoFilter ref="Q3:S9" xr:uid="{383560BC-B1F2-44B6-B877-188131EFA163}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{383560BC-B1F2-44B6-B877-188131EFA163}" name="CfgAutofieldValues" displayName="CfgAutofieldValues" ref="Q3:S10" totalsRowShown="0">
+  <autoFilter ref="Q3:S10" xr:uid="{383560BC-B1F2-44B6-B877-188131EFA163}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{D4E1611F-A2CF-465D-A219-1759EA66687D}" name="Name"/>
     <tableColumn id="2" xr3:uid="{174D0D86-B1AA-4BF7-AC91-FCACFC898851}" name="Value"/>
@@ -1999,7 +2002,7 @@
     <row r="2" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>35</v>
@@ -2103,7 +2106,7 @@
         <v>84</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>54</v>
@@ -2115,7 +2118,7 @@
         <v>46</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="K3" s="3">
         <v>2</v>
@@ -2376,12 +2379,12 @@
         <v>53</v>
       </c>
       <c r="Q1" s="11" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="R1" s="11"/>
       <c r="S1" s="11"/>
       <c r="U1" s="11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="V1" s="11"/>
       <c r="W1" s="11"/>
@@ -2476,13 +2479,13 @@
         <v>54</v>
       </c>
       <c r="V3" t="s">
+        <v>101</v>
+      </c>
+      <c r="W3" t="s">
         <v>102</v>
       </c>
-      <c r="W3" t="s">
+      <c r="X3" t="s">
         <v>103</v>
-      </c>
-      <c r="X3" t="s">
-        <v>104</v>
       </c>
       <c r="Z3" s="5" t="s">
         <v>63</v>
@@ -2493,7 +2496,7 @@
         <v>54</v>
       </c>
       <c r="B4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D4" t="s">
         <v>46</v>
@@ -2502,7 +2505,7 @@
         <v>1</v>
       </c>
       <c r="G4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I4" t="s">
         <v>86</v>
@@ -2520,19 +2523,19 @@
         <v>51</v>
       </c>
       <c r="R4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="S4" s="7" t="s">
         <v>73</v>
       </c>
       <c r="U4" t="s">
+        <v>104</v>
+      </c>
+      <c r="V4" t="s">
         <v>105</v>
       </c>
-      <c r="V4" t="s">
+      <c r="W4" t="s">
         <v>106</v>
-      </c>
-      <c r="W4" t="s">
-        <v>107</v>
       </c>
       <c r="Z4" t="str" cm="1">
         <f t="array" aca="1" ref="Z4:Z12" ca="1">_xlfn.UNIQUE((_xlfn.VSTACK(INDIRECT("CfgIssueTypes[IssueType.Name]"),INDIRECT("CfgIgnoreList[IgnoreList.Name]"))))</f>
@@ -2559,13 +2562,13 @@
         <v>74</v>
       </c>
       <c r="U5" t="s">
+        <v>107</v>
+      </c>
+      <c r="V5" t="s">
         <v>108</v>
       </c>
-      <c r="V5" t="s">
+      <c r="W5" t="s">
         <v>109</v>
-      </c>
-      <c r="W5" t="s">
-        <v>110</v>
       </c>
       <c r="Z5" t="str">
         <f ca="1"/>
@@ -2580,20 +2583,20 @@
         <v>33</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="Q6" t="s">
         <v>88</v>
       </c>
       <c r="S6" s="7"/>
       <c r="U6" t="s">
+        <v>110</v>
+      </c>
+      <c r="V6" t="s">
         <v>111</v>
       </c>
-      <c r="V6" t="s">
+      <c r="W6" t="s">
         <v>112</v>
-      </c>
-      <c r="W6" t="s">
-        <v>113</v>
       </c>
       <c r="Z6" t="str">
         <f ca="1"/>
@@ -2616,17 +2619,17 @@
         <v>89</v>
       </c>
       <c r="R7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="S7" s="7"/>
       <c r="U7" t="s">
+        <v>113</v>
+      </c>
+      <c r="V7" t="s">
         <v>114</v>
       </c>
-      <c r="V7" t="s">
+      <c r="W7" t="s">
         <v>115</v>
-      </c>
-      <c r="W7" t="s">
-        <v>116</v>
       </c>
       <c r="Z7" t="str">
         <f ca="1"/>
@@ -2637,26 +2640,20 @@
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
       <c r="K8" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="O8" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="Q8" t="s">
-        <v>90</v>
-      </c>
-      <c r="R8" t="b">
-        <v>1</v>
-      </c>
       <c r="S8" s="7"/>
       <c r="U8" t="s">
+        <v>116</v>
+      </c>
+      <c r="V8" t="s">
+        <v>118</v>
+      </c>
+      <c r="W8" t="s">
         <v>117</v>
-      </c>
-      <c r="V8" t="s">
-        <v>119</v>
-      </c>
-      <c r="W8" t="s">
-        <v>118</v>
       </c>
       <c r="Z8" t="str">
         <f ca="1"/>
@@ -2670,10 +2667,10 @@
         <v>50</v>
       </c>
       <c r="Q9" t="s">
+        <v>90</v>
+      </c>
+      <c r="R9" t="s">
         <v>91</v>
-      </c>
-      <c r="R9" t="s">
-        <v>92</v>
       </c>
       <c r="S9" s="7"/>
       <c r="Z9" t="str">
@@ -2684,6 +2681,13 @@
     <row r="10" spans="1:27" x14ac:dyDescent="0.25">
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
+      <c r="Q10" t="s">
+        <v>119</v>
+      </c>
+      <c r="R10" t="s">
+        <v>120</v>
+      </c>
+      <c r="S10" s="7"/>
       <c r="Z10" t="str">
         <f ca="1"/>
         <v>Skip</v>

--- a/resources/templates/ImportTemplate.xlsx
+++ b/resources/templates/ImportTemplate.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workdir\DeerHide\sources\jira-toolkit\resources\Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09FDBF7F-D200-4D23-A13C-FBD71614ACEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E776735C-6F88-4C65-B03D-A4F7E0D12F46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="675" yWindow="4890" windowWidth="25740" windowHeight="15045" activeTab="1" xr2:uid="{1FA076D1-0294-4A97-AB8C-3ADE2BC9CEA1}"/>
+    <workbookView xWindow="4545" yWindow="4545" windowWidth="43200" windowHeight="23445" xr2:uid="{1FA076D1-0294-4A97-AB8C-3ADE2BC9CEA1}"/>
   </bookViews>
   <sheets>
     <sheet name="Dataset" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="120">
   <si>
     <t>IssueType</t>
   </si>
@@ -243,9 +243,6 @@
   </si>
   <si>
     <t>Fix Version</t>
-  </si>
-  <si>
-    <t>Asssignee.Name</t>
   </si>
   <si>
     <t>Assignee.ID</t>
@@ -1496,7 +1493,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{1EF5833D-4918-4C71-A990-1B275126361D}" name="CfgAssignees" displayName="CfgAssignees" ref="A3:B5" totalsRowShown="0">
   <autoFilter ref="A3:B5" xr:uid="{1EF5833D-4918-4C71-A990-1B275126361D}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{7F7B4E10-E51C-443F-875D-3E6A9FD9994C}" name="Asssignee.Name"/>
+    <tableColumn id="1" xr3:uid="{7F7B4E10-E51C-443F-875D-3E6A9FD9994C}" name="Assignee.Name"/>
     <tableColumn id="2" xr3:uid="{3A4C6F03-89A9-4E38-8288-00D055D51CD3}" name="Assignee.ID"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium5" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1924,7 +1921,7 @@
         <v>10</v>
       </c>
       <c r="L1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M1" s="3" t="s">
         <v>11</v>
@@ -2016,7 +2013,7 @@
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K2" s="3">
         <v>1</v>
@@ -2099,26 +2096,26 @@
         <v>41</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>54</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I3" s="3" t="s">
         <v>46</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K3" s="3">
         <v>2</v>
@@ -2287,7 +2284,7 @@
       <formula1>INDIRECT("CfgComponents[Component.Name]")</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" error="must be a valid fixversion" sqref="G2:G3" xr:uid="{44FDC20A-8BF5-49B5-9D2C-3A1FE5A7D835}">
-      <formula1>INDIRECT("CfgAssignees[Asssignee.Name]")</formula1>
+      <formula1>INDIRECT("CfgAssignees[Assignee.Name]")</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="must be a valid component" sqref="I2:I3" xr:uid="{A898E2E7-BC45-4B88-BA1E-4AAA377361D4}">
       <formula1>INDIRECT("CfgSprints[Sprint.Name]")</formula1>
@@ -2356,11 +2353,11 @@
   <sheetData>
     <row r="1" spans="1:27" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="11" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B1" s="11"/>
       <c r="D1" s="11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E1" s="11"/>
       <c r="G1" s="6" t="s">
@@ -2373,55 +2370,55 @@
         <v>52</v>
       </c>
       <c r="M1" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="O1" s="6" t="s">
         <v>53</v>
       </c>
       <c r="Q1" s="11" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="R1" s="11"/>
       <c r="S1" s="11"/>
       <c r="U1" s="11" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="V1" s="11"/>
       <c r="W1" s="11"/>
       <c r="X1" s="11"/>
       <c r="Z1" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B2" s="12"/>
       <c r="C2" s="7"/>
       <c r="D2" s="12" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E2" s="12"/>
       <c r="F2" s="7"/>
       <c r="G2" s="10" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H2" s="10"/>
       <c r="I2" s="10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="J2" s="10"/>
       <c r="K2" s="12" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="L2" s="12"/>
       <c r="M2" s="9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="N2" s="9"/>
       <c r="O2" s="10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="P2" s="10"/>
       <c r="Q2" s="12"/>
@@ -2434,37 +2431,37 @@
       <c r="X2" s="7"/>
       <c r="Y2" s="7"/>
       <c r="Z2" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AA2" s="9"/>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s">
         <v>58</v>
       </c>
-      <c r="B3" t="s">
+      <c r="D3" t="s">
         <v>59</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>60</v>
       </c>
-      <c r="E3" t="s">
+      <c r="G3" t="s">
+        <v>64</v>
+      </c>
+      <c r="I3" t="s">
+        <v>63</v>
+      </c>
+      <c r="K3" t="s">
+        <v>62</v>
+      </c>
+      <c r="M3" t="s">
+        <v>67</v>
+      </c>
+      <c r="O3" t="s">
         <v>61</v>
-      </c>
-      <c r="G3" t="s">
-        <v>65</v>
-      </c>
-      <c r="I3" t="s">
-        <v>64</v>
-      </c>
-      <c r="K3" t="s">
-        <v>63</v>
-      </c>
-      <c r="M3" t="s">
-        <v>68</v>
-      </c>
-      <c r="O3" t="s">
-        <v>62</v>
       </c>
       <c r="Q3" t="s">
         <v>54</v>
@@ -2473,22 +2470,22 @@
         <v>55</v>
       </c>
       <c r="S3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="U3" t="s">
         <v>54</v>
       </c>
       <c r="V3" t="s">
+        <v>100</v>
+      </c>
+      <c r="W3" t="s">
         <v>101</v>
       </c>
-      <c r="W3" t="s">
+      <c r="X3" t="s">
         <v>102</v>
       </c>
-      <c r="X3" t="s">
-        <v>103</v>
-      </c>
       <c r="Z3" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.25">
@@ -2496,7 +2493,7 @@
         <v>54</v>
       </c>
       <c r="B4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D4" t="s">
         <v>46</v>
@@ -2505,10 +2502,10 @@
         <v>1</v>
       </c>
       <c r="G4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K4" t="s">
         <v>39</v>
@@ -2523,19 +2520,19 @@
         <v>51</v>
       </c>
       <c r="R4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="S4" s="7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="U4" t="s">
+        <v>103</v>
+      </c>
+      <c r="V4" t="s">
         <v>104</v>
       </c>
-      <c r="V4" t="s">
+      <c r="W4" t="s">
         <v>105</v>
-      </c>
-      <c r="W4" t="s">
-        <v>106</v>
       </c>
       <c r="Z4" t="str" cm="1">
         <f t="array" aca="1" ref="Z4:Z12" ca="1">_xlfn.UNIQUE((_xlfn.VSTACK(INDIRECT("CfgIssueTypes[IssueType.Name]"),INDIRECT("CfgIgnoreList[IgnoreList.Name]"))))</f>
@@ -2556,19 +2553,19 @@
         <v>47</v>
       </c>
       <c r="R5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="S5" s="7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="U5" t="s">
+        <v>106</v>
+      </c>
+      <c r="V5" t="s">
         <v>107</v>
       </c>
-      <c r="V5" t="s">
+      <c r="W5" t="s">
         <v>108</v>
-      </c>
-      <c r="W5" t="s">
-        <v>109</v>
       </c>
       <c r="Z5" t="str">
         <f ca="1"/>
@@ -2583,20 +2580,20 @@
         <v>33</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="Q6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="S6" s="7"/>
       <c r="U6" t="s">
+        <v>109</v>
+      </c>
+      <c r="V6" t="s">
         <v>110</v>
       </c>
-      <c r="V6" t="s">
+      <c r="W6" t="s">
         <v>111</v>
-      </c>
-      <c r="W6" t="s">
-        <v>112</v>
       </c>
       <c r="Z6" t="str">
         <f ca="1"/>
@@ -2616,20 +2613,20 @@
         <v>42</v>
       </c>
       <c r="Q7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="R7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="S7" s="7"/>
       <c r="U7" t="s">
+        <v>112</v>
+      </c>
+      <c r="V7" t="s">
         <v>113</v>
       </c>
-      <c r="V7" t="s">
+      <c r="W7" t="s">
         <v>114</v>
-      </c>
-      <c r="W7" t="s">
-        <v>115</v>
       </c>
       <c r="Z7" t="str">
         <f ca="1"/>
@@ -2640,20 +2637,20 @@
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
       <c r="K8" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="O8" s="1" t="s">
         <v>49</v>
       </c>
       <c r="S8" s="7"/>
       <c r="U8" t="s">
+        <v>115</v>
+      </c>
+      <c r="V8" t="s">
+        <v>117</v>
+      </c>
+      <c r="W8" t="s">
         <v>116</v>
-      </c>
-      <c r="V8" t="s">
-        <v>118</v>
-      </c>
-      <c r="W8" t="s">
-        <v>117</v>
       </c>
       <c r="Z8" t="str">
         <f ca="1"/>
@@ -2667,10 +2664,10 @@
         <v>50</v>
       </c>
       <c r="Q9" t="s">
+        <v>89</v>
+      </c>
+      <c r="R9" t="s">
         <v>90</v>
-      </c>
-      <c r="R9" t="s">
-        <v>91</v>
       </c>
       <c r="S9" s="7"/>
       <c r="Z9" t="str">
@@ -2682,10 +2679,10 @@
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
       <c r="Q10" t="s">
+        <v>118</v>
+      </c>
+      <c r="R10" t="s">
         <v>119</v>
-      </c>
-      <c r="R10" t="s">
-        <v>120</v>
       </c>
       <c r="S10" s="7"/>
       <c r="Z10" t="str">
@@ -2774,6 +2771,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100FB038601AF41D04A88A4BD446922F1A8" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="e8d32171d27ae41230d53456f24efae5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c471fd26-9765-4fbe-b6fd-c17c1e55c974" xmlns:ns3="9df69692-83aa-4c55-88c1-62abad05f4fe" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1f2fb84de5621acf32f385a2ba90fb29" ns2:_="" ns3:_="">
     <xsd:import namespace="c471fd26-9765-4fbe-b6fd-c17c1e55c974"/>
@@ -3002,15 +3008,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -3023,6 +3020,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{156C3F15-3876-4FBB-8F24-692088DE8D9F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2C983B91-58B3-4C2C-AC55-FFEC9F0DB5F6}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3041,14 +3046,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{156C3F15-3876-4FBB-8F24-692088DE8D9F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9FFE630F-6530-4863-AB67-8477539A0000}">
   <ds:schemaRefs>

--- a/resources/templates/ImportTemplate.xlsx
+++ b/resources/templates/ImportTemplate.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workdir\DeerHide\sources\jira-toolkit\resources\Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E776735C-6F88-4C65-B03D-A4F7E0D12F46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{003E1DC9-7C6D-4031-B67D-8F83CD74C94E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4545" yWindow="4545" windowWidth="43200" windowHeight="23445" xr2:uid="{1FA076D1-0294-4A97-AB8C-3ADE2BC9CEA1}"/>
+    <workbookView xWindow="10215" yWindow="9390" windowWidth="31710" windowHeight="20325" xr2:uid="{1FA076D1-0294-4A97-AB8C-3ADE2BC9CEA1}"/>
   </bookViews>
   <sheets>
     <sheet name="Dataset" sheetId="1" r:id="rId1"/>
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="122">
   <si>
     <t>IssueType</t>
   </si>
@@ -429,6 +429,12 @@
   </si>
   <si>
     <t>no</t>
+  </si>
+  <si>
+    <t>jira.components_source</t>
+  </si>
+  <si>
+    <t>jira</t>
   </si>
 </sst>
 </file>
@@ -1512,8 +1518,8 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{383560BC-B1F2-44B6-B877-188131EFA163}" name="CfgAutofieldValues" displayName="CfgAutofieldValues" ref="Q3:S10" totalsRowShown="0">
-  <autoFilter ref="Q3:S10" xr:uid="{383560BC-B1F2-44B6-B877-188131EFA163}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{383560BC-B1F2-44B6-B877-188131EFA163}" name="CfgAutofieldValues" displayName="CfgAutofieldValues" ref="Q3:S11" totalsRowShown="0">
+  <autoFilter ref="Q3:S11" xr:uid="{383560BC-B1F2-44B6-B877-188131EFA163}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{D4E1611F-A2CF-465D-A219-1759EA66687D}" name="Name"/>
     <tableColumn id="2" xr3:uid="{174D0D86-B1AA-4BF7-AC91-FCACFC898851}" name="Value"/>
@@ -2693,6 +2699,13 @@
     <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
+      <c r="Q11" t="s">
+        <v>120</v>
+      </c>
+      <c r="R11" t="s">
+        <v>121</v>
+      </c>
+      <c r="S11" s="7"/>
       <c r="Z11" t="str">
         <f ca="1"/>
         <v>Note</v>
@@ -2780,6 +2793,17 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c471fd26-9765-4fbe-b6fd-c17c1e55c974">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="9df69692-83aa-4c55-88c1-62abad05f4fe" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100FB038601AF41D04A88A4BD446922F1A8" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="e8d32171d27ae41230d53456f24efae5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c471fd26-9765-4fbe-b6fd-c17c1e55c974" xmlns:ns3="9df69692-83aa-4c55-88c1-62abad05f4fe" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1f2fb84de5621acf32f385a2ba90fb29" ns2:_="" ns3:_="">
     <xsd:import namespace="c471fd26-9765-4fbe-b6fd-c17c1e55c974"/>
@@ -3008,17 +3032,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c471fd26-9765-4fbe-b6fd-c17c1e55c974">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="9df69692-83aa-4c55-88c1-62abad05f4fe" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{156C3F15-3876-4FBB-8F24-692088DE8D9F}">
   <ds:schemaRefs>
@@ -3028,6 +3041,17 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9FFE630F-6530-4863-AB67-8477539A0000}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="c471fd26-9765-4fbe-b6fd-c17c1e55c974"/>
+    <ds:schemaRef ds:uri="9df69692-83aa-4c55-88c1-62abad05f4fe"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2C983B91-58B3-4C2C-AC55-FFEC9F0DB5F6}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3044,15 +3068,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9FFE630F-6530-4863-AB67-8477539A0000}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="c471fd26-9765-4fbe-b6fd-c17c1e55c974"/>
-    <ds:schemaRef ds:uri="9df69692-83aa-4c55-88c1-62abad05f4fe"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/resources/templates/ImportTemplate.xlsx
+++ b/resources/templates/ImportTemplate.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workdir\DeerHide\sources\jira-toolkit\resources\Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{003E1DC9-7C6D-4031-B67D-8F83CD74C94E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19EF8646-AAC6-4786-B8CE-C82C9A8B8D04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10215" yWindow="9390" windowWidth="31710" windowHeight="20325" xr2:uid="{1FA076D1-0294-4A97-AB8C-3ADE2BC9CEA1}"/>
+    <workbookView xWindow="15060" yWindow="5175" windowWidth="43200" windowHeight="23445" activeTab="1" xr2:uid="{1FA076D1-0294-4A97-AB8C-3ADE2BC9CEA1}"/>
   </bookViews>
   <sheets>
     <sheet name="Dataset" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="105">
   <si>
     <t>IssueType</t>
   </si>
@@ -206,9 +206,6 @@
     <t>Skip</t>
   </si>
   <si>
-    <t>WorkItem</t>
-  </si>
-  <si>
     <t>Sprint 1</t>
   </si>
   <si>
@@ -347,9 +344,6 @@
     <t>Version_Tag</t>
   </si>
   <si>
-    <t>PROJECT KEY</t>
-  </si>
-  <si>
     <t>jt-imported</t>
   </si>
   <si>
@@ -380,61 +374,16 @@
     <t>Format</t>
   </si>
   <si>
-    <t>CF Number</t>
-  </si>
-  <si>
-    <t>customfield_10125</t>
-  </si>
-  <si>
-    <t>number</t>
-  </si>
-  <si>
-    <t>CF Plain Text</t>
-  </si>
-  <si>
-    <t>customfield_10124</t>
-  </si>
-  <si>
-    <t>text</t>
-  </si>
-  <si>
-    <t>CF Select</t>
-  </si>
-  <si>
-    <t>customfield_10126</t>
-  </si>
-  <si>
-    <t>select</t>
-  </si>
-  <si>
-    <t>CF Date</t>
-  </si>
-  <si>
-    <t>customfield_10123</t>
-  </si>
-  <si>
-    <t>date</t>
-  </si>
-  <si>
-    <t>CF Field</t>
-  </si>
-  <si>
-    <t>any</t>
-  </si>
-  <si>
-    <t>customfield_10128</t>
-  </si>
-  <si>
-    <t>app.import.auto_open_page</t>
-  </si>
-  <si>
-    <t>no</t>
-  </si>
-  <si>
-    <t>jira.components_source</t>
-  </si>
-  <si>
-    <t>jira</t>
+    <t>Initiative</t>
+  </si>
+  <si>
+    <t>https://your-instance.atlassian.net</t>
+  </si>
+  <si>
+    <t>metadata.version</t>
+  </si>
+  <si>
+    <t>PROJECT-KEY</t>
   </si>
 </sst>
 </file>
@@ -1443,8 +1392,8 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{3EF499BE-ED9A-4C28-BC5A-BCDEF51C613F}" name="CfgCustomFields" displayName="CfgCustomFields" ref="U3:X8" totalsRowShown="0">
-  <autoFilter ref="U3:X8" xr:uid="{3EF499BE-ED9A-4C28-BC5A-BCDEF51C613F}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{3EF499BE-ED9A-4C28-BC5A-BCDEF51C613F}" name="CfgCustomFields" displayName="CfgCustomFields" ref="U3:X4" insertRow="1" totalsRowShown="0">
+  <autoFilter ref="U3:X4" xr:uid="{3EF499BE-ED9A-4C28-BC5A-BCDEF51C613F}"/>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{44010E5A-E449-477A-BFB0-2ECA215E3FEB}" name="Name"/>
     <tableColumn id="2" xr3:uid="{0E558995-744D-4813-9A4E-F64FFF5047AE}" name="Id"/>
@@ -1476,8 +1425,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{6F085B8C-1322-4F43-A516-588923936259}" name="CfgIssueTypes" displayName="CfgIssueTypes" ref="K3:K8" totalsRowShown="0">
-  <autoFilter ref="K3:K8" xr:uid="{6F085B8C-1322-4F43-A516-588923936259}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{6F085B8C-1322-4F43-A516-588923936259}" name="CfgIssueTypes" displayName="CfgIssueTypes" ref="K3:K9" totalsRowShown="0">
+  <autoFilter ref="K3:K9" xr:uid="{6F085B8C-1322-4F43-A516-588923936259}"/>
   <tableColumns count="1">
     <tableColumn id="1" xr3:uid="{A92436BC-3156-493F-B5C6-0BB6B51F89EB}" name="IssueType.Name"/>
   </tableColumns>
@@ -1518,8 +1467,8 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{383560BC-B1F2-44B6-B877-188131EFA163}" name="CfgAutofieldValues" displayName="CfgAutofieldValues" ref="Q3:S11" totalsRowShown="0">
-  <autoFilter ref="Q3:S11" xr:uid="{383560BC-B1F2-44B6-B877-188131EFA163}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{383560BC-B1F2-44B6-B877-188131EFA163}" name="CfgAutofieldValues" displayName="CfgAutofieldValues" ref="Q3:S9" totalsRowShown="0">
+  <autoFilter ref="Q3:S9" xr:uid="{383560BC-B1F2-44B6-B877-188131EFA163}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{D4E1611F-A2CF-465D-A219-1759EA66687D}" name="Name"/>
     <tableColumn id="2" xr3:uid="{174D0D86-B1AA-4BF7-AC91-FCACFC898851}" name="Value"/>
@@ -1530,8 +1479,8 @@
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{0ABE2B38-573A-4A51-8D54-C217B9D7D54F}" name="CfgIgnoreList" displayName="CfgIgnoreList" ref="M3:M7" totalsRowShown="0">
-  <autoFilter ref="M3:M7" xr:uid="{0ABE2B38-573A-4A51-8D54-C217B9D7D54F}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{0ABE2B38-573A-4A51-8D54-C217B9D7D54F}" name="CfgIgnoreList" displayName="CfgIgnoreList" ref="M3:M6" totalsRowShown="0">
+  <autoFilter ref="M3:M6" xr:uid="{0ABE2B38-573A-4A51-8D54-C217B9D7D54F}"/>
   <tableColumns count="1">
     <tableColumn id="1" xr3:uid="{1396737E-05D6-4D62-AF56-4B039C3A3607}" name="IgnoreList.Name"/>
   </tableColumns>
@@ -1927,7 +1876,7 @@
         <v>10</v>
       </c>
       <c r="L1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="M1" s="3" t="s">
         <v>11</v>
@@ -2019,7 +1968,7 @@
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K2" s="3">
         <v>1</v>
@@ -2096,32 +2045,32 @@
     </row>
     <row r="3" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>41</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="K3" s="3">
         <v>2</v>
@@ -2164,7 +2113,7 @@
       </c>
       <c r="AG3" s="3" t="str">
         <f>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",_xlfn.XLOOKUP("jira.project.key", CfgAutofieldValues[Name], CfgAutofieldValues[Value]))</f>
-        <v>PROJECT KEY</v>
+        <v>PROJECT-KEY</v>
       </c>
       <c r="AH3" s="3" cm="1">
         <f t="array" ref="AH3">IF(
@@ -2183,7 +2132,7 @@
 )</f>
         <v>34560000</v>
       </c>
-      <c r="AI3" s="3" t="str" cm="1">
+      <c r="AI3" s="3" cm="1">
         <f t="array" ref="AI3">IFERROR(
     _xlfn.IFS(
         JiraDataset[[#This Row],[IssueType]] = cfg_type_comment,"SKIP",
@@ -2192,7 +2141,7 @@
     ),
     cfg_type_workitem
 )</f>
-        <v>WorkItem</v>
+        <v>0</v>
       </c>
       <c r="AJ3" s="3"/>
     </row>
@@ -2359,72 +2308,72 @@
   <sheetData>
     <row r="1" spans="1:27" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B1" s="11"/>
       <c r="D1" s="11" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E1" s="11"/>
       <c r="G1" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I1" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K1" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="M1" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="O1" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="M1" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="O1" s="6" t="s">
-        <v>53</v>
-      </c>
       <c r="Q1" s="11" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="R1" s="11"/>
       <c r="S1" s="11"/>
       <c r="U1" s="11" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="V1" s="11"/>
       <c r="W1" s="11"/>
       <c r="X1" s="11"/>
       <c r="Z1" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B2" s="12"/>
       <c r="C2" s="7"/>
       <c r="D2" s="12" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E2" s="12"/>
       <c r="F2" s="7"/>
       <c r="G2" s="10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H2" s="10"/>
       <c r="I2" s="10" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J2" s="10"/>
       <c r="K2" s="12" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="L2" s="12"/>
       <c r="M2" s="9" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="N2" s="9"/>
       <c r="O2" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="P2" s="10"/>
       <c r="Q2" s="12"/>
@@ -2437,7 +2386,7 @@
       <c r="X2" s="7"/>
       <c r="Y2" s="7"/>
       <c r="Z2" s="9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AA2" s="9"/>
     </row>
@@ -2446,72 +2395,72 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D3" t="s">
         <v>58</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>59</v>
       </c>
-      <c r="E3" t="s">
+      <c r="G3" t="s">
+        <v>63</v>
+      </c>
+      <c r="I3" t="s">
+        <v>62</v>
+      </c>
+      <c r="K3" t="s">
+        <v>61</v>
+      </c>
+      <c r="M3" t="s">
+        <v>66</v>
+      </c>
+      <c r="O3" t="s">
         <v>60</v>
       </c>
-      <c r="G3" t="s">
+      <c r="Q3" t="s">
+        <v>53</v>
+      </c>
+      <c r="R3" t="s">
+        <v>54</v>
+      </c>
+      <c r="S3" t="s">
         <v>64</v>
       </c>
-      <c r="I3" t="s">
-        <v>63</v>
-      </c>
-      <c r="K3" t="s">
-        <v>62</v>
-      </c>
-      <c r="M3" t="s">
-        <v>67</v>
-      </c>
-      <c r="O3" t="s">
+      <c r="U3" t="s">
+        <v>53</v>
+      </c>
+      <c r="V3" t="s">
+        <v>98</v>
+      </c>
+      <c r="W3" t="s">
+        <v>99</v>
+      </c>
+      <c r="X3" t="s">
+        <v>100</v>
+      </c>
+      <c r="Z3" s="5" t="s">
         <v>61</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>54</v>
-      </c>
-      <c r="R3" t="s">
-        <v>55</v>
-      </c>
-      <c r="S3" t="s">
-        <v>65</v>
-      </c>
-      <c r="U3" t="s">
-        <v>54</v>
-      </c>
-      <c r="V3" t="s">
-        <v>100</v>
-      </c>
-      <c r="W3" t="s">
-        <v>101</v>
-      </c>
-      <c r="X3" t="s">
-        <v>102</v>
-      </c>
-      <c r="Z3" s="5" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E4">
         <v>1</v>
       </c>
       <c r="G4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K4" t="s">
         <v>39</v>
@@ -2523,22 +2472,13 @@
         <v>38</v>
       </c>
       <c r="Q4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="R4" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="S4" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="U4" t="s">
-        <v>103</v>
-      </c>
-      <c r="V4" t="s">
-        <v>104</v>
-      </c>
-      <c r="W4" t="s">
-        <v>105</v>
+        <v>71</v>
       </c>
       <c r="Z4" t="str" cm="1">
         <f t="array" aca="1" ref="Z4:Z12" ca="1">_xlfn.UNIQUE((_xlfn.VSTACK(INDIRECT("CfgIssueTypes[IssueType.Name]"),INDIRECT("CfgIgnoreList[IgnoreList.Name]"))))</f>
@@ -2553,25 +2493,16 @@
         <v>44</v>
       </c>
       <c r="O5" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="Q5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="R5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="S5" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="U5" t="s">
-        <v>106</v>
-      </c>
-      <c r="V5" t="s">
-        <v>107</v>
-      </c>
-      <c r="W5" t="s">
-        <v>108</v>
+        <v>72</v>
       </c>
       <c r="Z5" t="str">
         <f ca="1"/>
@@ -2586,21 +2517,15 @@
         <v>33</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="Q6" t="s">
-        <v>87</v>
+        <v>86</v>
+      </c>
+      <c r="R6" t="s">
+        <v>102</v>
       </c>
       <c r="S6" s="7"/>
-      <c r="U6" t="s">
-        <v>109</v>
-      </c>
-      <c r="V6" t="s">
-        <v>110</v>
-      </c>
-      <c r="W6" t="s">
-        <v>111</v>
-      </c>
       <c r="Z6" t="str">
         <f ca="1"/>
         <v>Bug</v>
@@ -2612,28 +2537,16 @@
       <c r="K7" t="s">
         <v>41</v>
       </c>
-      <c r="M7" t="s">
-        <v>45</v>
-      </c>
       <c r="O7" s="1" t="s">
         <v>42</v>
       </c>
       <c r="Q7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="R7" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="S7" s="7"/>
-      <c r="U7" t="s">
-        <v>112</v>
-      </c>
-      <c r="V7" t="s">
-        <v>113</v>
-      </c>
-      <c r="W7" t="s">
-        <v>114</v>
-      </c>
       <c r="Z7" t="str">
         <f ca="1"/>
         <v>Epic</v>
@@ -2643,21 +2556,18 @@
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
       <c r="K8" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>103</v>
+      </c>
+      <c r="R8">
+        <v>7</v>
       </c>
       <c r="S8" s="7"/>
-      <c r="U8" t="s">
-        <v>115</v>
-      </c>
-      <c r="V8" t="s">
-        <v>117</v>
-      </c>
-      <c r="W8" t="s">
-        <v>116</v>
-      </c>
       <c r="Z8" t="str">
         <f ca="1"/>
         <v>Sub-Task</v>
@@ -2666,49 +2576,40 @@
     <row r="9" spans="1:27" x14ac:dyDescent="0.25">
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
+      <c r="K9" t="s">
+        <v>101</v>
+      </c>
       <c r="O9" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Q9" t="s">
+        <v>88</v>
+      </c>
+      <c r="R9" t="s">
         <v>89</v>
-      </c>
-      <c r="R9" t="s">
-        <v>90</v>
       </c>
       <c r="S9" s="7"/>
       <c r="Z9" t="str">
         <f ca="1"/>
-        <v>Comment</v>
+        <v>Initiative</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.25">
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
-      <c r="Q10" t="s">
-        <v>118</v>
-      </c>
-      <c r="R10" t="s">
-        <v>119</v>
-      </c>
       <c r="S10" s="7"/>
       <c r="Z10" t="str">
         <f ca="1"/>
-        <v>Skip</v>
+        <v>Comment</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
-      <c r="Q11" t="s">
-        <v>120</v>
-      </c>
-      <c r="R11" t="s">
-        <v>121</v>
-      </c>
       <c r="S11" s="7"/>
       <c r="Z11" t="str">
         <f ca="1"/>
-        <v>Note</v>
+        <v>Skip</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.25">
@@ -2716,7 +2617,7 @@
       <c r="E12" s="2"/>
       <c r="Z12" t="str">
         <f ca="1"/>
-        <v>WorkItem</v>
+        <v>Note</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.25">
@@ -2784,26 +2685,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c471fd26-9765-4fbe-b6fd-c17c1e55c974">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="9df69692-83aa-4c55-88c1-62abad05f4fe" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100FB038601AF41D04A88A4BD446922F1A8" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="e8d32171d27ae41230d53456f24efae5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c471fd26-9765-4fbe-b6fd-c17c1e55c974" xmlns:ns3="9df69692-83aa-4c55-88c1-62abad05f4fe" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1f2fb84de5621acf32f385a2ba90fb29" ns2:_="" ns3:_="">
     <xsd:import namespace="c471fd26-9765-4fbe-b6fd-c17c1e55c974"/>
@@ -3032,10 +2913,41 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c471fd26-9765-4fbe-b6fd-c17c1e55c974">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="9df69692-83aa-4c55-88c1-62abad05f4fe" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{156C3F15-3876-4FBB-8F24-692088DE8D9F}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2C983B91-58B3-4C2C-AC55-FFEC9F0DB5F6}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="c471fd26-9765-4fbe-b6fd-c17c1e55c974"/>
+    <ds:schemaRef ds:uri="9df69692-83aa-4c55-88c1-62abad05f4fe"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -3052,20 +2964,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2C983B91-58B3-4C2C-AC55-FFEC9F0DB5F6}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{156C3F15-3876-4FBB-8F24-692088DE8D9F}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="c471fd26-9765-4fbe-b6fd-c17c1e55c974"/>
-    <ds:schemaRef ds:uri="9df69692-83aa-4c55-88c1-62abad05f4fe"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/resources/templates/ImportTemplate.xlsx
+++ b/resources/templates/ImportTemplate.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workdir\DeerHide\sources\jira-toolkit\resources\Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19EF8646-AAC6-4786-B8CE-C82C9A8B8D04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{110EB2ED-6994-4498-ACC7-09390093827A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15060" yWindow="5175" windowWidth="43200" windowHeight="23445" activeTab="1" xr2:uid="{1FA076D1-0294-4A97-AB8C-3ADE2BC9CEA1}"/>
+    <workbookView xWindow="8085" yWindow="4980" windowWidth="43200" windowHeight="23445" activeTab="1" xr2:uid="{1FA076D1-0294-4A97-AB8C-3ADE2BC9CEA1}"/>
   </bookViews>
   <sheets>
     <sheet name="Dataset" sheetId="1" r:id="rId1"/>
@@ -1128,12 +1128,6 @@
       </fill>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="1" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
       <alignment vertical="top"/>
     </dxf>
     <dxf>
@@ -1274,6 +1268,12 @@
     </dxf>
     <dxf>
       <alignment vertical="top"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="1" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1311,55 +1311,55 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{933FCFD5-1AB1-4076-B5DD-E2B69F5EB3F2}" name="JiraDataset" displayName="JiraDataset" ref="A1:AJ3" totalsRowShown="0" headerRowDxfId="55" dataDxfId="54">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{933FCFD5-1AB1-4076-B5DD-E2B69F5EB3F2}" name="JiraDataset" displayName="JiraDataset" ref="A1:AJ3" totalsRowShown="0" headerRowDxfId="53" dataDxfId="52">
   <autoFilter ref="A1:AJ3" xr:uid="{933FCFD5-1AB1-4076-B5DD-E2B69F5EB3F2}"/>
   <tableColumns count="36">
-    <tableColumn id="3" xr3:uid="{AF2EC907-349C-4651-852D-6E39C61E17FF}" name="Priority" dataDxfId="53"/>
-    <tableColumn id="2" xr3:uid="{E90C51F2-4386-421F-A3E4-E2CA9D43D396}" name="IssueType" dataDxfId="52"/>
-    <tableColumn id="1" xr3:uid="{BBAD373B-BA13-47E4-9F74-565F4D9E9680}" name="Summary" dataDxfId="51"/>
-    <tableColumn id="4" xr3:uid="{026E5B97-FAFC-4E46-860E-0B0C976B1148}" name="Issue Key" dataDxfId="50"/>
-    <tableColumn id="5" xr3:uid="{A2C262E8-D544-4669-99F1-151EDE081654}" name="Description" dataDxfId="49"/>
-    <tableColumn id="7" xr3:uid="{0FAD1ACC-432E-462C-8B89-71540710BCB5}" name="FixVersion" dataDxfId="48"/>
-    <tableColumn id="28" xr3:uid="{07F3030C-7187-4B16-BBDB-798304851975}" name="Assignee.Name" dataDxfId="47"/>
-    <tableColumn id="8" xr3:uid="{8C7FB8DB-A85B-4189-93D8-0F0D4EEEF81B}" name="Component" dataDxfId="46"/>
-    <tableColumn id="9" xr3:uid="{DC5101A8-1204-44D2-BC2C-FEE1A4EFE7C1}" name="Sprint Name" dataDxfId="45"/>
-    <tableColumn id="40" xr3:uid="{1F406792-7ED2-4476-8FF4-4C6ABA231C97}" name="Estimate" dataDxfId="44"/>
-    <tableColumn id="10" xr3:uid="{70B7C471-B624-430B-8992-4711F27BB17E}" name="Issue ID" dataDxfId="43"/>
-    <tableColumn id="30" xr3:uid="{938D6CA2-8309-4146-9B62-E8CDFAB7B1C9}" name="Parent" dataDxfId="42"/>
-    <tableColumn id="11" xr3:uid="{594BD56F-7D1D-408F-BEDC-6BB9854C71A1}" name="Epic Link" dataDxfId="41"/>
-    <tableColumn id="33" xr3:uid="{3A94D4B2-1A5B-4BBF-B398-E56D2BB7F948}" name="Epic Name" dataDxfId="40">
+    <tableColumn id="3" xr3:uid="{AF2EC907-349C-4651-852D-6E39C61E17FF}" name="Priority" dataDxfId="51"/>
+    <tableColumn id="2" xr3:uid="{E90C51F2-4386-421F-A3E4-E2CA9D43D396}" name="IssueType" dataDxfId="50"/>
+    <tableColumn id="1" xr3:uid="{BBAD373B-BA13-47E4-9F74-565F4D9E9680}" name="Summary" dataDxfId="49"/>
+    <tableColumn id="4" xr3:uid="{026E5B97-FAFC-4E46-860E-0B0C976B1148}" name="Issue Key" dataDxfId="48"/>
+    <tableColumn id="5" xr3:uid="{A2C262E8-D544-4669-99F1-151EDE081654}" name="Description" dataDxfId="47"/>
+    <tableColumn id="7" xr3:uid="{0FAD1ACC-432E-462C-8B89-71540710BCB5}" name="FixVersion" dataDxfId="46"/>
+    <tableColumn id="28" xr3:uid="{07F3030C-7187-4B16-BBDB-798304851975}" name="Assignee.Name" dataDxfId="45"/>
+    <tableColumn id="8" xr3:uid="{8C7FB8DB-A85B-4189-93D8-0F0D4EEEF81B}" name="Component" dataDxfId="44"/>
+    <tableColumn id="9" xr3:uid="{DC5101A8-1204-44D2-BC2C-FEE1A4EFE7C1}" name="Sprint Name" dataDxfId="43"/>
+    <tableColumn id="40" xr3:uid="{1F406792-7ED2-4476-8FF4-4C6ABA231C97}" name="Estimate" dataDxfId="42"/>
+    <tableColumn id="10" xr3:uid="{70B7C471-B624-430B-8992-4711F27BB17E}" name="Issue ID" dataDxfId="41"/>
+    <tableColumn id="30" xr3:uid="{938D6CA2-8309-4146-9B62-E8CDFAB7B1C9}" name="Parent" dataDxfId="40"/>
+    <tableColumn id="11" xr3:uid="{594BD56F-7D1D-408F-BEDC-6BB9854C71A1}" name="Epic Link" dataDxfId="39"/>
+    <tableColumn id="33" xr3:uid="{3A94D4B2-1A5B-4BBF-B398-E56D2BB7F948}" name="Epic Name" dataDxfId="38">
       <calculatedColumnFormula>IF(JiraDataset[[#This Row],[IssueType]]="Epic",JiraDataset[[#This Row],[Summary]],"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="27" xr3:uid="{911C8FDC-5528-43FC-BDF4-D4761F03C0E5}" name="Child-Issue" dataDxfId="39"/>
-    <tableColumn id="41" xr3:uid="{AB248E07-9BFA-42CC-BC41-B4234F677BFB}" name="Child-Issue1" dataDxfId="38"/>
-    <tableColumn id="29" xr3:uid="{89D12135-F3E3-4253-844F-1B9A54169953}" name="Child-Issue2" dataDxfId="37"/>
-    <tableColumn id="12" xr3:uid="{0699B70E-673B-4238-8A66-12FC943A4812}" name="Labels" dataDxfId="36"/>
-    <tableColumn id="13" xr3:uid="{9840B81F-2CA6-4708-8C93-3E7C8F72A676}" name="Labels1" dataDxfId="35"/>
-    <tableColumn id="14" xr3:uid="{D4A99C0B-46B7-484A-842E-D62E9D5D9341}" name="Labels2" dataDxfId="34"/>
-    <tableColumn id="15" xr3:uid="{1D1C275E-5C65-4393-9663-6C5F617591E1}" name="Labels3" dataDxfId="33"/>
-    <tableColumn id="16" xr3:uid="{D823FA91-7106-42D3-9DBC-B337C509EB09}" name="Labels4" dataDxfId="32"/>
-    <tableColumn id="17" xr3:uid="{05A07F85-1763-4A66-9CBB-4A760BD03D27}" name="Labels5" dataDxfId="31"/>
-    <tableColumn id="18" xr3:uid="{16B98070-7F8A-4FC7-AD99-EA81D0BD26AB}" name="Labels6" dataDxfId="30"/>
-    <tableColumn id="19" xr3:uid="{016EAEF4-8EA9-408B-9F1A-ECFB17E81C77}" name="Labels7" dataDxfId="29"/>
-    <tableColumn id="26" xr3:uid="{8263F9EC-BF0A-46F7-BA83-6083A4262B91}" name="Labels8" dataDxfId="28"/>
-    <tableColumn id="20" xr3:uid="{389B11C5-1B22-48C0-BCA2-72F050425FA1}" name="Labels9" dataDxfId="27"/>
-    <tableColumn id="25" xr3:uid="{AE95F8A2-F7F0-4985-9AE6-4201B9792775}" name="Labels10" dataDxfId="26"/>
-    <tableColumn id="21" xr3:uid="{105F2D0F-70C1-4517-A55F-4C1DDFE85301}" name="Sprint" dataDxfId="25">
+    <tableColumn id="27" xr3:uid="{911C8FDC-5528-43FC-BDF4-D4761F03C0E5}" name="Child-Issue" dataDxfId="37"/>
+    <tableColumn id="41" xr3:uid="{AB248E07-9BFA-42CC-BC41-B4234F677BFB}" name="Child-Issue1" dataDxfId="36"/>
+    <tableColumn id="29" xr3:uid="{89D12135-F3E3-4253-844F-1B9A54169953}" name="Child-Issue2" dataDxfId="35"/>
+    <tableColumn id="12" xr3:uid="{0699B70E-673B-4238-8A66-12FC943A4812}" name="Labels" dataDxfId="34"/>
+    <tableColumn id="13" xr3:uid="{9840B81F-2CA6-4708-8C93-3E7C8F72A676}" name="Labels1" dataDxfId="33"/>
+    <tableColumn id="14" xr3:uid="{D4A99C0B-46B7-484A-842E-D62E9D5D9341}" name="Labels2" dataDxfId="32"/>
+    <tableColumn id="15" xr3:uid="{1D1C275E-5C65-4393-9663-6C5F617591E1}" name="Labels3" dataDxfId="31"/>
+    <tableColumn id="16" xr3:uid="{D823FA91-7106-42D3-9DBC-B337C509EB09}" name="Labels4" dataDxfId="30"/>
+    <tableColumn id="17" xr3:uid="{05A07F85-1763-4A66-9CBB-4A760BD03D27}" name="Labels5" dataDxfId="29"/>
+    <tableColumn id="18" xr3:uid="{16B98070-7F8A-4FC7-AD99-EA81D0BD26AB}" name="Labels6" dataDxfId="28"/>
+    <tableColumn id="19" xr3:uid="{016EAEF4-8EA9-408B-9F1A-ECFB17E81C77}" name="Labels7" dataDxfId="27"/>
+    <tableColumn id="26" xr3:uid="{8263F9EC-BF0A-46F7-BA83-6083A4262B91}" name="Labels8" dataDxfId="26"/>
+    <tableColumn id="20" xr3:uid="{389B11C5-1B22-48C0-BCA2-72F050425FA1}" name="Labels9" dataDxfId="25"/>
+    <tableColumn id="25" xr3:uid="{AE95F8A2-F7F0-4985-9AE6-4201B9792775}" name="Labels10" dataDxfId="24"/>
+    <tableColumn id="21" xr3:uid="{105F2D0F-70C1-4517-A55F-4C1DDFE85301}" name="Sprint" dataDxfId="23">
       <calculatedColumnFormula>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",IFERROR(VLOOKUP(JiraDataset[[#This Row],[Sprint Name]], Config!$D$4:$E$9, 2, FALSE), ""))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{D5984986-D838-4F87-A554-5DC4CA005452}" name="Labels0001" dataDxfId="24">
+    <tableColumn id="22" xr3:uid="{D5984986-D838-4F87-A554-5DC4CA005452}" name="Labels0001" dataDxfId="22">
       <calculatedColumnFormula>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",_xlfn.XLOOKUP("Creation Marker", CfgAutofieldValues[Name], CfgAutofieldValues[Value]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="39" xr3:uid="{C24E9ADD-96A8-4DBB-86A0-08D41975D750}" name="Labels0002" dataDxfId="23">
+    <tableColumn id="39" xr3:uid="{C24E9ADD-96A8-4DBB-86A0-08D41975D750}" name="Labels0002" dataDxfId="21">
       <calculatedColumnFormula>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",_xlfn.XLOOKUP("Feature Pod Label", CfgAutofieldValues[Name], CfgAutofieldValues[Value]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{A6D8D5A6-43EE-415C-80C1-30372C7FE5BF}" name="Assignee" dataDxfId="22">
+    <tableColumn id="6" xr3:uid="{A6D8D5A6-43EE-415C-80C1-30372C7FE5BF}" name="Assignee" dataDxfId="20">
       <calculatedColumnFormula>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",IFERROR(VLOOKUP(JiraDataset[[#This Row],[Assignee.Name]], Config!$A$4:$B$24, 2, FALSE), ""))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="23" xr3:uid="{51D4B5F4-C6D3-4EEC-8B1B-7BEC6E526A64}" name="Project Key" dataDxfId="21">
+    <tableColumn id="23" xr3:uid="{51D4B5F4-C6D3-4EEC-8B1B-7BEC6E526A64}" name="Project Key" dataDxfId="19">
       <calculatedColumnFormula>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",_xlfn.XLOOKUP("jira.project.key", CfgAutofieldValues[Name], CfgAutofieldValues[Value]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="42" xr3:uid="{82B78F0D-CAEF-4615-B12A-B15ACF33913C}" name="OrigEst" dataDxfId="20">
+    <tableColumn id="42" xr3:uid="{82B78F0D-CAEF-4615-B12A-B15ACF33913C}" name="OrigEst" dataDxfId="18">
       <calculatedColumnFormula array="1">IF(
   JiraDataset[[#This Row],[RowType]]=cfg_type_skip,
   "",
@@ -1375,7 +1375,7 @@
   )
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="44" xr3:uid="{C92FD7EC-0EAB-4967-A0E5-D2427E3A55B4}" name="RowType" dataDxfId="19">
+    <tableColumn id="44" xr3:uid="{C92FD7EC-0EAB-4967-A0E5-D2427E3A55B4}" name="RowType" dataDxfId="17">
       <calculatedColumnFormula array="1">IFERROR(
     _xlfn.IFS(
         JiraDataset[[#This Row],[IssueType]] = cfg_type_comment,"SKIP",
@@ -1385,7 +1385,7 @@
     cfg_type_workitem
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="24" xr3:uid="{B63E8FC4-20B3-4755-92F2-EA1F700CA72E}" name="Note" dataDxfId="18"/>
+    <tableColumn id="24" xr3:uid="{B63E8FC4-20B3-4755-92F2-EA1F700CA72E}" name="Note" dataDxfId="16"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1438,7 +1438,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{A6C0EE44-3F60-4588-BF11-75C3DD021846}" name="CfgPriorities" displayName="CfgPriorities" ref="O3:O9" totalsRowShown="0">
   <autoFilter ref="O3:O9" xr:uid="{A6C0EE44-3F60-4588-BF11-75C3DD021846}"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{3B3BE2ED-38C4-410B-B0BF-4A9BD9B4B974}" name="Priority.Name" dataDxfId="17"/>
+    <tableColumn id="1" xr3:uid="{3B3BE2ED-38C4-410B-B0BF-4A9BD9B4B974}" name="Priority.Name" dataDxfId="55"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium5" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1472,7 +1472,7 @@
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{D4E1611F-A2CF-465D-A219-1759EA66687D}" name="Name"/>
     <tableColumn id="2" xr3:uid="{174D0D86-B1AA-4BF7-AC91-FCACFC898851}" name="Value"/>
-    <tableColumn id="3" xr3:uid="{4D0493E3-2ED0-412B-9468-835FC91C2910}" name="Remark" dataDxfId="16"/>
+    <tableColumn id="3" xr3:uid="{4D0493E3-2ED0-412B-9468-835FC91C2910}" name="Remark" dataDxfId="54"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium5" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1809,10 +1809,10 @@
   <sheetFormatPr defaultRowHeight="15" outlineLevelCol="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="31.7109375" customWidth="1"/>
+    <col min="3" max="3" width="41.140625" customWidth="1"/>
     <col min="4" max="4" width="11.85546875" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="33" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="46.28515625" customWidth="1"/>
+    <col min="5" max="5" width="71.28515625" customWidth="1"/>
+    <col min="6" max="6" width="20.85546875" customWidth="1"/>
     <col min="7" max="7" width="17.42578125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="22.5703125" customWidth="1"/>
     <col min="9" max="9" width="14" bestFit="1" customWidth="1"/>
@@ -2685,6 +2685,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c471fd26-9765-4fbe-b6fd-c17c1e55c974">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="9df69692-83aa-4c55-88c1-62abad05f4fe" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100FB038601AF41D04A88A4BD446922F1A8" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="e8d32171d27ae41230d53456f24efae5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c471fd26-9765-4fbe-b6fd-c17c1e55c974" xmlns:ns3="9df69692-83aa-4c55-88c1-62abad05f4fe" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1f2fb84de5621acf32f385a2ba90fb29" ns2:_="" ns3:_="">
     <xsd:import namespace="c471fd26-9765-4fbe-b6fd-c17c1e55c974"/>
@@ -2913,27 +2933,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c471fd26-9765-4fbe-b6fd-c17c1e55c974">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="9df69692-83aa-4c55-88c1-62abad05f4fe" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{156C3F15-3876-4FBB-8F24-692088DE8D9F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9FFE630F-6530-4863-AB67-8477539A0000}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="c471fd26-9765-4fbe-b6fd-c17c1e55c974"/>
+    <ds:schemaRef ds:uri="9df69692-83aa-4c55-88c1-62abad05f4fe"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2C983B91-58B3-4C2C-AC55-FFEC9F0DB5F6}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2950,23 +2969,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9FFE630F-6530-4863-AB67-8477539A0000}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="c471fd26-9765-4fbe-b6fd-c17c1e55c974"/>
-    <ds:schemaRef ds:uri="9df69692-83aa-4c55-88c1-62abad05f4fe"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{156C3F15-3876-4FBB-8F24-692088DE8D9F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/resources/templates/ImportTemplate.xlsx
+++ b/resources/templates/ImportTemplate.xlsx
@@ -8,23 +8,23 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workdir\DeerHide\sources\jira-toolkit\resources\Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{110EB2ED-6994-4498-ACC7-09390093827A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4062769F-6A46-4AC5-A90C-0B6BE8F81ED3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8085" yWindow="4980" windowWidth="43200" windowHeight="23445" activeTab="1" xr2:uid="{1FA076D1-0294-4A97-AB8C-3ADE2BC9CEA1}"/>
+    <workbookView xWindow="3900" yWindow="5655" windowWidth="43200" windowHeight="23445" xr2:uid="{1FA076D1-0294-4A97-AB8C-3ADE2BC9CEA1}"/>
   </bookViews>
   <sheets>
     <sheet name="Dataset" sheetId="1" r:id="rId1"/>
     <sheet name="Config" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="cfg_labels_ft_label">Config!$R$5</definedName>
-    <definedName name="cfg_labels_ft_name">Config!$R$5</definedName>
-    <definedName name="cfg_labels_imported">Config!$R$4</definedName>
-    <definedName name="cfg_projectKey">Config!$R$7</definedName>
-    <definedName name="cfg_type_comment">Config!$M$4</definedName>
-    <definedName name="cfg_type_note">Config!$M$6</definedName>
-    <definedName name="cfg_type_skip">Config!$M$5</definedName>
-    <definedName name="cfg_type_workitem">Config!$M$7</definedName>
+    <definedName name="cfg_labels_ft_label">Config!$U$5</definedName>
+    <definedName name="cfg_labels_ft_name">Config!$U$5</definedName>
+    <definedName name="cfg_labels_imported">Config!$U$4</definedName>
+    <definedName name="cfg_projectKey">Config!$U$7</definedName>
+    <definedName name="cfg_type_comment">Config!$P$4</definedName>
+    <definedName name="cfg_type_note">Config!$P$6</definedName>
+    <definedName name="cfg_type_skip">Config!$P$5</definedName>
+    <definedName name="cfg_type_workitem">Config!$P$7</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="110">
   <si>
     <t>IssueType</t>
   </si>
@@ -384,6 +384,21 @@
   </si>
   <si>
     <t>PROJECT-KEY</t>
+  </si>
+  <si>
+    <t>Team</t>
+  </si>
+  <si>
+    <t>Teams</t>
+  </si>
+  <si>
+    <t>Team.Name</t>
+  </si>
+  <si>
+    <t>Team.ID</t>
+  </si>
+  <si>
+    <t>Team ID</t>
   </si>
 </sst>
 </file>
@@ -984,7 +999,7 @@
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="56">
+  <dxfs count="57">
     <dxf>
       <fill>
         <patternFill patternType="darkUp"/>
@@ -1126,6 +1141,9 @@
           <bgColor rgb="FFFF99CC"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment vertical="top"/>
@@ -1305,61 +1323,62 @@
 <file path=xl/namedSheetViews/namedSheetView1.xml><?xml version="1.0" encoding="utf-8"?>
 <namedSheetViews xmlns="http://schemas.microsoft.com/office/spreadsheetml/2019/namedsheetviews" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <namedSheetView name="View1" id="{77233F75-225A-4D7F-8A86-543E0A8C6E58}">
-    <nsvFilter filterId="{933FCFD5-1AB1-4076-B5DD-E2B69F5EB3F2}" ref="A1:AJ3" tableId="1"/>
+    <nsvFilter filterId="{933FCFD5-1AB1-4076-B5DD-E2B69F5EB3F2}" ref="A1:AK3" tableId="1"/>
   </namedSheetView>
 </namedSheetViews>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{933FCFD5-1AB1-4076-B5DD-E2B69F5EB3F2}" name="JiraDataset" displayName="JiraDataset" ref="A1:AJ3" totalsRowShown="0" headerRowDxfId="53" dataDxfId="52">
-  <autoFilter ref="A1:AJ3" xr:uid="{933FCFD5-1AB1-4076-B5DD-E2B69F5EB3F2}"/>
-  <tableColumns count="36">
-    <tableColumn id="3" xr3:uid="{AF2EC907-349C-4651-852D-6E39C61E17FF}" name="Priority" dataDxfId="51"/>
-    <tableColumn id="2" xr3:uid="{E90C51F2-4386-421F-A3E4-E2CA9D43D396}" name="IssueType" dataDxfId="50"/>
-    <tableColumn id="1" xr3:uid="{BBAD373B-BA13-47E4-9F74-565F4D9E9680}" name="Summary" dataDxfId="49"/>
-    <tableColumn id="4" xr3:uid="{026E5B97-FAFC-4E46-860E-0B0C976B1148}" name="Issue Key" dataDxfId="48"/>
-    <tableColumn id="5" xr3:uid="{A2C262E8-D544-4669-99F1-151EDE081654}" name="Description" dataDxfId="47"/>
-    <tableColumn id="7" xr3:uid="{0FAD1ACC-432E-462C-8B89-71540710BCB5}" name="FixVersion" dataDxfId="46"/>
-    <tableColumn id="28" xr3:uid="{07F3030C-7187-4B16-BBDB-798304851975}" name="Assignee.Name" dataDxfId="45"/>
-    <tableColumn id="8" xr3:uid="{8C7FB8DB-A85B-4189-93D8-0F0D4EEEF81B}" name="Component" dataDxfId="44"/>
-    <tableColumn id="9" xr3:uid="{DC5101A8-1204-44D2-BC2C-FEE1A4EFE7C1}" name="Sprint Name" dataDxfId="43"/>
-    <tableColumn id="40" xr3:uid="{1F406792-7ED2-4476-8FF4-4C6ABA231C97}" name="Estimate" dataDxfId="42"/>
-    <tableColumn id="10" xr3:uid="{70B7C471-B624-430B-8992-4711F27BB17E}" name="Issue ID" dataDxfId="41"/>
-    <tableColumn id="30" xr3:uid="{938D6CA2-8309-4146-9B62-E8CDFAB7B1C9}" name="Parent" dataDxfId="40"/>
-    <tableColumn id="11" xr3:uid="{594BD56F-7D1D-408F-BEDC-6BB9854C71A1}" name="Epic Link" dataDxfId="39"/>
-    <tableColumn id="33" xr3:uid="{3A94D4B2-1A5B-4BBF-B398-E56D2BB7F948}" name="Epic Name" dataDxfId="38">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{933FCFD5-1AB1-4076-B5DD-E2B69F5EB3F2}" name="JiraDataset" displayName="JiraDataset" ref="A1:AK3" totalsRowShown="0" headerRowDxfId="54" dataDxfId="53">
+  <autoFilter ref="A1:AK3" xr:uid="{933FCFD5-1AB1-4076-B5DD-E2B69F5EB3F2}"/>
+  <tableColumns count="37">
+    <tableColumn id="3" xr3:uid="{AF2EC907-349C-4651-852D-6E39C61E17FF}" name="Priority" dataDxfId="52"/>
+    <tableColumn id="2" xr3:uid="{E90C51F2-4386-421F-A3E4-E2CA9D43D396}" name="IssueType" dataDxfId="51"/>
+    <tableColumn id="1" xr3:uid="{BBAD373B-BA13-47E4-9F74-565F4D9E9680}" name="Summary" dataDxfId="50"/>
+    <tableColumn id="4" xr3:uid="{026E5B97-FAFC-4E46-860E-0B0C976B1148}" name="Issue Key" dataDxfId="49"/>
+    <tableColumn id="5" xr3:uid="{A2C262E8-D544-4669-99F1-151EDE081654}" name="Description" dataDxfId="48"/>
+    <tableColumn id="7" xr3:uid="{0FAD1ACC-432E-462C-8B89-71540710BCB5}" name="FixVersion" dataDxfId="47"/>
+    <tableColumn id="28" xr3:uid="{07F3030C-7187-4B16-BBDB-798304851975}" name="Assignee.Name" dataDxfId="46"/>
+    <tableColumn id="8" xr3:uid="{8C7FB8DB-A85B-4189-93D8-0F0D4EEEF81B}" name="Component" dataDxfId="45"/>
+    <tableColumn id="31" xr3:uid="{28FC7838-B632-4214-BEDE-FDACBD086707}" name="Team" dataDxfId="16"/>
+    <tableColumn id="9" xr3:uid="{DC5101A8-1204-44D2-BC2C-FEE1A4EFE7C1}" name="Sprint Name" dataDxfId="44"/>
+    <tableColumn id="40" xr3:uid="{1F406792-7ED2-4476-8FF4-4C6ABA231C97}" name="Estimate" dataDxfId="43"/>
+    <tableColumn id="10" xr3:uid="{70B7C471-B624-430B-8992-4711F27BB17E}" name="Issue ID" dataDxfId="42"/>
+    <tableColumn id="30" xr3:uid="{938D6CA2-8309-4146-9B62-E8CDFAB7B1C9}" name="Parent" dataDxfId="41"/>
+    <tableColumn id="11" xr3:uid="{594BD56F-7D1D-408F-BEDC-6BB9854C71A1}" name="Epic Link" dataDxfId="40"/>
+    <tableColumn id="33" xr3:uid="{3A94D4B2-1A5B-4BBF-B398-E56D2BB7F948}" name="Epic Name" dataDxfId="39">
       <calculatedColumnFormula>IF(JiraDataset[[#This Row],[IssueType]]="Epic",JiraDataset[[#This Row],[Summary]],"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="27" xr3:uid="{911C8FDC-5528-43FC-BDF4-D4761F03C0E5}" name="Child-Issue" dataDxfId="37"/>
-    <tableColumn id="41" xr3:uid="{AB248E07-9BFA-42CC-BC41-B4234F677BFB}" name="Child-Issue1" dataDxfId="36"/>
-    <tableColumn id="29" xr3:uid="{89D12135-F3E3-4253-844F-1B9A54169953}" name="Child-Issue2" dataDxfId="35"/>
-    <tableColumn id="12" xr3:uid="{0699B70E-673B-4238-8A66-12FC943A4812}" name="Labels" dataDxfId="34"/>
-    <tableColumn id="13" xr3:uid="{9840B81F-2CA6-4708-8C93-3E7C8F72A676}" name="Labels1" dataDxfId="33"/>
-    <tableColumn id="14" xr3:uid="{D4A99C0B-46B7-484A-842E-D62E9D5D9341}" name="Labels2" dataDxfId="32"/>
-    <tableColumn id="15" xr3:uid="{1D1C275E-5C65-4393-9663-6C5F617591E1}" name="Labels3" dataDxfId="31"/>
-    <tableColumn id="16" xr3:uid="{D823FA91-7106-42D3-9DBC-B337C509EB09}" name="Labels4" dataDxfId="30"/>
-    <tableColumn id="17" xr3:uid="{05A07F85-1763-4A66-9CBB-4A760BD03D27}" name="Labels5" dataDxfId="29"/>
-    <tableColumn id="18" xr3:uid="{16B98070-7F8A-4FC7-AD99-EA81D0BD26AB}" name="Labels6" dataDxfId="28"/>
-    <tableColumn id="19" xr3:uid="{016EAEF4-8EA9-408B-9F1A-ECFB17E81C77}" name="Labels7" dataDxfId="27"/>
-    <tableColumn id="26" xr3:uid="{8263F9EC-BF0A-46F7-BA83-6083A4262B91}" name="Labels8" dataDxfId="26"/>
-    <tableColumn id="20" xr3:uid="{389B11C5-1B22-48C0-BCA2-72F050425FA1}" name="Labels9" dataDxfId="25"/>
-    <tableColumn id="25" xr3:uid="{AE95F8A2-F7F0-4985-9AE6-4201B9792775}" name="Labels10" dataDxfId="24"/>
-    <tableColumn id="21" xr3:uid="{105F2D0F-70C1-4517-A55F-4C1DDFE85301}" name="Sprint" dataDxfId="23">
-      <calculatedColumnFormula>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",IFERROR(VLOOKUP(JiraDataset[[#This Row],[Sprint Name]], Config!$D$4:$E$9, 2, FALSE), ""))</calculatedColumnFormula>
+    <tableColumn id="27" xr3:uid="{911C8FDC-5528-43FC-BDF4-D4761F03C0E5}" name="Child-Issue" dataDxfId="38"/>
+    <tableColumn id="41" xr3:uid="{AB248E07-9BFA-42CC-BC41-B4234F677BFB}" name="Child-Issue1" dataDxfId="37"/>
+    <tableColumn id="29" xr3:uid="{89D12135-F3E3-4253-844F-1B9A54169953}" name="Child-Issue2" dataDxfId="36"/>
+    <tableColumn id="12" xr3:uid="{0699B70E-673B-4238-8A66-12FC943A4812}" name="Labels" dataDxfId="35"/>
+    <tableColumn id="13" xr3:uid="{9840B81F-2CA6-4708-8C93-3E7C8F72A676}" name="Labels1" dataDxfId="34"/>
+    <tableColumn id="14" xr3:uid="{D4A99C0B-46B7-484A-842E-D62E9D5D9341}" name="Labels2" dataDxfId="33"/>
+    <tableColumn id="15" xr3:uid="{1D1C275E-5C65-4393-9663-6C5F617591E1}" name="Labels3" dataDxfId="32"/>
+    <tableColumn id="16" xr3:uid="{D823FA91-7106-42D3-9DBC-B337C509EB09}" name="Labels4" dataDxfId="31"/>
+    <tableColumn id="17" xr3:uid="{05A07F85-1763-4A66-9CBB-4A760BD03D27}" name="Labels5" dataDxfId="30"/>
+    <tableColumn id="18" xr3:uid="{16B98070-7F8A-4FC7-AD99-EA81D0BD26AB}" name="Labels6" dataDxfId="29"/>
+    <tableColumn id="19" xr3:uid="{016EAEF4-8EA9-408B-9F1A-ECFB17E81C77}" name="Labels7" dataDxfId="28"/>
+    <tableColumn id="26" xr3:uid="{8263F9EC-BF0A-46F7-BA83-6083A4262B91}" name="Labels8" dataDxfId="27"/>
+    <tableColumn id="20" xr3:uid="{389B11C5-1B22-48C0-BCA2-72F050425FA1}" name="Labels9" dataDxfId="26"/>
+    <tableColumn id="25" xr3:uid="{AE95F8A2-F7F0-4985-9AE6-4201B9792775}" name="Labels10" dataDxfId="25"/>
+    <tableColumn id="21" xr3:uid="{105F2D0F-70C1-4517-A55F-4C1DDFE85301}" name="Sprint" dataDxfId="24">
+      <calculatedColumnFormula>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",IFERROR(VLOOKUP(JiraDataset[[#This Row],[Sprint Name]], Config!$G$4:$H$9, 2, FALSE), ""))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{D5984986-D838-4F87-A554-5DC4CA005452}" name="Labels0001" dataDxfId="22">
+    <tableColumn id="22" xr3:uid="{D5984986-D838-4F87-A554-5DC4CA005452}" name="Labels0001" dataDxfId="23">
       <calculatedColumnFormula>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",_xlfn.XLOOKUP("Creation Marker", CfgAutofieldValues[Name], CfgAutofieldValues[Value]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="39" xr3:uid="{C24E9ADD-96A8-4DBB-86A0-08D41975D750}" name="Labels0002" dataDxfId="21">
+    <tableColumn id="39" xr3:uid="{C24E9ADD-96A8-4DBB-86A0-08D41975D750}" name="Labels0002" dataDxfId="22">
       <calculatedColumnFormula>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",_xlfn.XLOOKUP("Feature Pod Label", CfgAutofieldValues[Name], CfgAutofieldValues[Value]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{A6D8D5A6-43EE-415C-80C1-30372C7FE5BF}" name="Assignee" dataDxfId="20">
+    <tableColumn id="6" xr3:uid="{A6D8D5A6-43EE-415C-80C1-30372C7FE5BF}" name="Assignee" dataDxfId="21">
       <calculatedColumnFormula>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",IFERROR(VLOOKUP(JiraDataset[[#This Row],[Assignee.Name]], Config!$A$4:$B$24, 2, FALSE), ""))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="23" xr3:uid="{51D4B5F4-C6D3-4EEC-8B1B-7BEC6E526A64}" name="Project Key" dataDxfId="19">
+    <tableColumn id="23" xr3:uid="{51D4B5F4-C6D3-4EEC-8B1B-7BEC6E526A64}" name="Project Key" dataDxfId="20">
       <calculatedColumnFormula>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",_xlfn.XLOOKUP("jira.project.key", CfgAutofieldValues[Name], CfgAutofieldValues[Value]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="42" xr3:uid="{82B78F0D-CAEF-4615-B12A-B15ACF33913C}" name="OrigEst" dataDxfId="18">
+    <tableColumn id="42" xr3:uid="{82B78F0D-CAEF-4615-B12A-B15ACF33913C}" name="OrigEst" dataDxfId="19">
       <calculatedColumnFormula array="1">IF(
   JiraDataset[[#This Row],[RowType]]=cfg_type_skip,
   "",
@@ -1375,7 +1394,7 @@
   )
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="44" xr3:uid="{C92FD7EC-0EAB-4967-A0E5-D2427E3A55B4}" name="RowType" dataDxfId="17">
+    <tableColumn id="44" xr3:uid="{C92FD7EC-0EAB-4967-A0E5-D2427E3A55B4}" name="RowType" dataDxfId="18">
       <calculatedColumnFormula array="1">IFERROR(
     _xlfn.IFS(
         JiraDataset[[#This Row],[IssueType]] = cfg_type_comment,"SKIP",
@@ -1385,15 +1404,15 @@
     cfg_type_workitem
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="24" xr3:uid="{B63E8FC4-20B3-4755-92F2-EA1F700CA72E}" name="Note" dataDxfId="16"/>
+    <tableColumn id="24" xr3:uid="{B63E8FC4-20B3-4755-92F2-EA1F700CA72E}" name="Note" dataDxfId="17"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{3EF499BE-ED9A-4C28-BC5A-BCDEF51C613F}" name="CfgCustomFields" displayName="CfgCustomFields" ref="U3:X4" insertRow="1" totalsRowShown="0">
-  <autoFilter ref="U3:X4" xr:uid="{3EF499BE-ED9A-4C28-BC5A-BCDEF51C613F}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{3EF499BE-ED9A-4C28-BC5A-BCDEF51C613F}" name="CfgCustomFields" displayName="CfgCustomFields" ref="X3:AA4" insertRow="1" totalsRowShown="0">
+  <autoFilter ref="X3:AA4" xr:uid="{3EF499BE-ED9A-4C28-BC5A-BCDEF51C613F}"/>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{44010E5A-E449-477A-BFB0-2ECA215E3FEB}" name="Name"/>
     <tableColumn id="2" xr3:uid="{0E558995-744D-4813-9A4E-F64FFF5047AE}" name="Id"/>
@@ -1404,9 +1423,20 @@
 </table>
 </file>
 
+<file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{9BDE4941-2A84-46A5-8151-88377A8724D2}" name="CfgTeams" displayName="CfgTeams" ref="D3:E4" totalsRowShown="0">
+  <autoFilter ref="D3:E4" xr:uid="{9BDE4941-2A84-46A5-8151-88377A8724D2}"/>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{00649780-E35F-4B89-8C72-05E0797C267E}" name="Team.Name"/>
+    <tableColumn id="2" xr3:uid="{AE7CB114-5EE3-4BFF-9E4E-5034242719C9}" name="Team.ID"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium5" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{93F2D14D-2ABD-4171-895D-1041B0893491}" name="CfgComponents" displayName="CfgComponents" ref="I3:I5" totalsRowShown="0">
-  <autoFilter ref="I3:I5" xr:uid="{93F2D14D-2ABD-4171-895D-1041B0893491}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{93F2D14D-2ABD-4171-895D-1041B0893491}" name="CfgComponents" displayName="CfgComponents" ref="L3:L5" totalsRowShown="0">
+  <autoFilter ref="L3:L5" xr:uid="{93F2D14D-2ABD-4171-895D-1041B0893491}"/>
   <tableColumns count="1">
     <tableColumn id="1" xr3:uid="{10F6CCA4-1068-4FC8-AB82-E48B87DB0F71}" name="Component.Name"/>
   </tableColumns>
@@ -1415,8 +1445,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{7007FF9D-9384-422B-8DB3-300D782E5FE6}" name="CfgFixVersions" displayName="CfgFixVersions" ref="G3:G5" totalsRowShown="0">
-  <autoFilter ref="G3:G5" xr:uid="{7007FF9D-9384-422B-8DB3-300D782E5FE6}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{7007FF9D-9384-422B-8DB3-300D782E5FE6}" name="CfgFixVersions" displayName="CfgFixVersions" ref="J3:J5" totalsRowShown="0">
+  <autoFilter ref="J3:J5" xr:uid="{7007FF9D-9384-422B-8DB3-300D782E5FE6}"/>
   <tableColumns count="1">
     <tableColumn id="1" xr3:uid="{E20FAA91-E54E-42EA-9BFF-2FDA27CD5D33}" name="FixVersion.Name"/>
   </tableColumns>
@@ -1425,8 +1455,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{6F085B8C-1322-4F43-A516-588923936259}" name="CfgIssueTypes" displayName="CfgIssueTypes" ref="K3:K9" totalsRowShown="0">
-  <autoFilter ref="K3:K9" xr:uid="{6F085B8C-1322-4F43-A516-588923936259}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{6F085B8C-1322-4F43-A516-588923936259}" name="CfgIssueTypes" displayName="CfgIssueTypes" ref="N3:N9" totalsRowShown="0">
+  <autoFilter ref="N3:N9" xr:uid="{6F085B8C-1322-4F43-A516-588923936259}"/>
   <tableColumns count="1">
     <tableColumn id="1" xr3:uid="{A92436BC-3156-493F-B5C6-0BB6B51F89EB}" name="IssueType.Name"/>
   </tableColumns>
@@ -1435,10 +1465,10 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{A6C0EE44-3F60-4588-BF11-75C3DD021846}" name="CfgPriorities" displayName="CfgPriorities" ref="O3:O9" totalsRowShown="0">
-  <autoFilter ref="O3:O9" xr:uid="{A6C0EE44-3F60-4588-BF11-75C3DD021846}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{A6C0EE44-3F60-4588-BF11-75C3DD021846}" name="CfgPriorities" displayName="CfgPriorities" ref="R3:R9" totalsRowShown="0">
+  <autoFilter ref="R3:R9" xr:uid="{A6C0EE44-3F60-4588-BF11-75C3DD021846}"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{3B3BE2ED-38C4-410B-B0BF-4A9BD9B4B974}" name="Priority.Name" dataDxfId="55"/>
+    <tableColumn id="1" xr3:uid="{3B3BE2ED-38C4-410B-B0BF-4A9BD9B4B974}" name="Priority.Name" dataDxfId="56"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium5" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1456,8 +1486,8 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{72674B63-54C8-47AC-9FF0-4034C2D499BA}" name="CfgSprints" displayName="CfgSprints" ref="D3:E5" totalsRowShown="0">
-  <autoFilter ref="D3:E5" xr:uid="{72674B63-54C8-47AC-9FF0-4034C2D499BA}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{72674B63-54C8-47AC-9FF0-4034C2D499BA}" name="CfgSprints" displayName="CfgSprints" ref="G3:H5" totalsRowShown="0">
+  <autoFilter ref="G3:H5" xr:uid="{72674B63-54C8-47AC-9FF0-4034C2D499BA}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{397B719B-4CC6-4F47-8F3C-168F13ED56DA}" name="Sprint.Name"/>
     <tableColumn id="2" xr3:uid="{2FD208E7-540E-4D07-9144-6E9F3065D9DE}" name="Sprint.ID"/>
@@ -1467,20 +1497,20 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{383560BC-B1F2-44B6-B877-188131EFA163}" name="CfgAutofieldValues" displayName="CfgAutofieldValues" ref="Q3:S9" totalsRowShown="0">
-  <autoFilter ref="Q3:S9" xr:uid="{383560BC-B1F2-44B6-B877-188131EFA163}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{383560BC-B1F2-44B6-B877-188131EFA163}" name="CfgAutofieldValues" displayName="CfgAutofieldValues" ref="T3:V9" totalsRowShown="0">
+  <autoFilter ref="T3:V9" xr:uid="{383560BC-B1F2-44B6-B877-188131EFA163}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{D4E1611F-A2CF-465D-A219-1759EA66687D}" name="Name"/>
     <tableColumn id="2" xr3:uid="{174D0D86-B1AA-4BF7-AC91-FCACFC898851}" name="Value"/>
-    <tableColumn id="3" xr3:uid="{4D0493E3-2ED0-412B-9468-835FC91C2910}" name="Remark" dataDxfId="54"/>
+    <tableColumn id="3" xr3:uid="{4D0493E3-2ED0-412B-9468-835FC91C2910}" name="Remark" dataDxfId="55"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium5" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{0ABE2B38-573A-4A51-8D54-C217B9D7D54F}" name="CfgIgnoreList" displayName="CfgIgnoreList" ref="M3:M6" totalsRowShown="0">
-  <autoFilter ref="M3:M6" xr:uid="{0ABE2B38-573A-4A51-8D54-C217B9D7D54F}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{0ABE2B38-573A-4A51-8D54-C217B9D7D54F}" name="CfgIgnoreList" displayName="CfgIgnoreList" ref="P3:P6" totalsRowShown="0">
+  <autoFilter ref="P3:P6" xr:uid="{0ABE2B38-573A-4A51-8D54-C217B9D7D54F}"/>
   <tableColumns count="1">
     <tableColumn id="1" xr3:uid="{1396737E-05D6-4D62-AF56-4B039C3A3607}" name="IgnoreList.Name"/>
   </tableColumns>
@@ -1805,43 +1835,37 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F73058B-F76D-4AAE-8108-6C4469E9D8B5}">
-  <dimension ref="A1:AK3"/>
+  <dimension ref="A1:AL3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelCol="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.140625" customWidth="1"/>
-    <col min="4" max="4" width="11.85546875" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="71.28515625" customWidth="1"/>
+    <col min="3" max="3" width="50" customWidth="1"/>
+    <col min="4" max="4" width="50" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="50" customWidth="1"/>
     <col min="6" max="6" width="20.85546875" customWidth="1"/>
-    <col min="7" max="7" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="22.5703125" customWidth="1"/>
-    <col min="9" max="9" width="14" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.28515625" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" customWidth="1"/>
-    <col min="14" max="14" width="14.28515625" customWidth="1"/>
-    <col min="15" max="15" width="0" hidden="1" customWidth="1"/>
-    <col min="16" max="16" width="22.28515625" hidden="1" customWidth="1"/>
-    <col min="17" max="17" width="12.85546875" hidden="1" customWidth="1"/>
-    <col min="18" max="18" width="12.42578125" customWidth="1"/>
-    <col min="19" max="19" width="15.5703125" customWidth="1"/>
-    <col min="20" max="20" width="12.85546875" customWidth="1"/>
-    <col min="21" max="21" width="10" customWidth="1"/>
-    <col min="22" max="22" width="10" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="10" customWidth="1"/>
-    <col min="24" max="24" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="25" max="30" width="10" customWidth="1" outlineLevel="1"/>
-    <col min="31" max="31" width="10" customWidth="1"/>
-    <col min="32" max="32" width="8.7109375" customWidth="1" outlineLevel="1"/>
-    <col min="33" max="34" width="13.140625" customWidth="1" outlineLevel="1"/>
-    <col min="35" max="35" width="11.42578125" customWidth="1" outlineLevel="1"/>
-    <col min="36" max="37" width="13.7109375" customWidth="1" outlineLevel="1"/>
-    <col min="38" max="38" width="36.5703125" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="18.7109375" customWidth="1"/>
-    <col min="41" max="41" width="87.28515625" customWidth="1"/>
+    <col min="7" max="10" width="14.28515625" customWidth="1"/>
+    <col min="11" max="11" width="11.42578125" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.28515625" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" customWidth="1"/>
+    <col min="15" max="15" width="14.28515625" customWidth="1"/>
+    <col min="16" max="16" width="0" hidden="1" customWidth="1"/>
+    <col min="17" max="17" width="22.28515625" hidden="1" customWidth="1"/>
+    <col min="18" max="18" width="9.85546875" hidden="1" customWidth="1"/>
+    <col min="19" max="25" width="11.42578125" customWidth="1"/>
+    <col min="26" max="29" width="11.42578125" customWidth="1" outlineLevel="1"/>
+    <col min="30" max="31" width="10" customWidth="1" outlineLevel="1"/>
+    <col min="32" max="32" width="10" customWidth="1"/>
+    <col min="33" max="33" width="8.7109375" customWidth="1" outlineLevel="1"/>
+    <col min="34" max="35" width="13.140625" customWidth="1" outlineLevel="1"/>
+    <col min="36" max="36" width="11.42578125" customWidth="1" outlineLevel="1"/>
+    <col min="37" max="38" width="13.7109375" customWidth="1" outlineLevel="1"/>
+    <col min="39" max="39" width="36.5703125" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="18.7109375" customWidth="1"/>
+    <col min="42" max="42" width="87.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>1</v>
       </c>
@@ -1867,91 +1891,94 @@
         <v>7</v>
       </c>
       <c r="I1" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="J1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>83</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="N1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="P1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="Q1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="R1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="S1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="S1" s="3" t="s">
+      <c r="T1" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="T1" s="3" t="s">
+      <c r="U1" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="U1" s="3" t="s">
+      <c r="V1" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="V1" s="3" t="s">
+      <c r="W1" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="W1" s="3" t="s">
+      <c r="X1" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="X1" s="3" t="s">
+      <c r="Y1" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="Y1" s="3" t="s">
+      <c r="Z1" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="Z1" s="3" t="s">
+      <c r="AA1" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AA1" s="3" t="s">
+      <c r="AB1" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="AB1" s="3" t="s">
+      <c r="AC1" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="AC1" s="3" t="s">
+      <c r="AD1" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="AD1" s="3" t="s">
+      <c r="AE1" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="AE1" s="3" t="s">
+      <c r="AF1" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="AF1" s="3" t="s">
+      <c r="AG1" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="AG1" s="3" t="s">
+      <c r="AH1" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AH1" s="4" t="s">
+      <c r="AI1" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="AI1" s="4" t="s">
+      <c r="AJ1" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="AJ1" s="3" t="s">
+      <c r="AK1" s="3" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="3" t="s">
         <v>34</v>
@@ -1967,19 +1994,19 @@
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
-      <c r="J2" s="3" t="s">
+      <c r="J2" s="3"/>
+      <c r="K2" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="K2" s="3">
+      <c r="L2" s="3">
         <v>1</v>
       </c>
-      <c r="L2" s="3"/>
       <c r="M2" s="3"/>
-      <c r="N2" s="3" t="str">
+      <c r="N2" s="3"/>
+      <c r="O2" s="3" t="str">
         <f>IF(JiraDataset[[#This Row],[IssueType]]="Epic",JiraDataset[[#This Row],[Summary]],"")</f>
         <v/>
       </c>
-      <c r="O2" s="3"/>
       <c r="P2" s="3"/>
       <c r="Q2" s="3"/>
       <c r="R2" s="3"/>
@@ -1993,28 +2020,29 @@
       <c r="Z2" s="3"/>
       <c r="AA2" s="3"/>
       <c r="AB2" s="3"/>
-      <c r="AC2" s="3" t="str">
-        <f>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",IFERROR(VLOOKUP(JiraDataset[[#This Row],[Sprint Name]], Config!$D$4:$E$9, 2, FALSE), ""))</f>
+      <c r="AC2" s="3"/>
+      <c r="AD2" s="3" t="str">
+        <f>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",IFERROR(VLOOKUP(JiraDataset[[#This Row],[Sprint Name]], Config!$G$4:$H$9, 2, FALSE), ""))</f>
         <v/>
       </c>
-      <c r="AD2" s="3" t="str">
+      <c r="AE2" s="3" t="str">
         <f>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",_xlfn.XLOOKUP("Creation Marker", CfgAutofieldValues[Name], CfgAutofieldValues[Value]))</f>
         <v/>
       </c>
-      <c r="AE2" s="8" t="str">
+      <c r="AF2" s="8" t="str">
         <f>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",_xlfn.XLOOKUP("Feature Pod Label", CfgAutofieldValues[Name], CfgAutofieldValues[Value]))</f>
         <v/>
       </c>
-      <c r="AF2" s="3" t="str">
+      <c r="AG2" s="3" t="str">
         <f>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",IFERROR(VLOOKUP(JiraDataset[[#This Row],[Assignee.Name]], Config!$A$4:$B$24, 2, FALSE), ""))</f>
         <v/>
       </c>
-      <c r="AG2" s="3" t="str">
+      <c r="AH2" s="3" t="str">
         <f>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",_xlfn.XLOOKUP("jira.project.key", CfgAutofieldValues[Name], CfgAutofieldValues[Value]))</f>
         <v/>
       </c>
-      <c r="AH2" s="3" t="str" cm="1">
-        <f t="array" ref="AH2">IF(
+      <c r="AI2" s="3" t="str" cm="1">
+        <f t="array" ref="AI2">IF(
   JiraDataset[[#This Row],[RowType]]=cfg_type_skip,
   "",
   _xlfn.LET(
@@ -2030,8 +2058,8 @@
 )</f>
         <v/>
       </c>
-      <c r="AI2" s="3" t="str" cm="1">
-        <f t="array" ref="AI2">IFERROR(
+      <c r="AJ2" s="3" t="str" cm="1">
+        <f t="array" ref="AJ2">IFERROR(
     _xlfn.IFS(
         JiraDataset[[#This Row],[IssueType]] = cfg_type_comment,"SKIP",
         JiraDataset[[#This Row],[IssueType]] = cfg_type_skip,"SKIP",
@@ -2041,9 +2069,9 @@
 )</f>
         <v>SKIP</v>
       </c>
-      <c r="AJ2" s="3"/>
+      <c r="AK2" s="3"/>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>47</v>
       </c>
@@ -2066,22 +2094,22 @@
       <c r="H3" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="3"/>
+      <c r="J3" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="K3" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="K3" s="3">
+      <c r="L3" s="3">
         <v>2</v>
       </c>
-      <c r="L3" s="3"/>
       <c r="M3" s="3"/>
-      <c r="N3" s="3" t="str">
+      <c r="N3" s="3"/>
+      <c r="O3" s="3" t="str">
         <f>IF(JiraDataset[[#This Row],[IssueType]]="Epic",JiraDataset[[#This Row],[Summary]],"")</f>
         <v>Test, Epic</v>
       </c>
-      <c r="O3" s="3"/>
       <c r="P3" s="3"/>
       <c r="Q3" s="3"/>
       <c r="R3" s="3"/>
@@ -2095,28 +2123,29 @@
       <c r="Z3" s="3"/>
       <c r="AA3" s="3"/>
       <c r="AB3" s="3"/>
-      <c r="AC3" s="3">
-        <f>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",IFERROR(VLOOKUP(JiraDataset[[#This Row],[Sprint Name]], Config!$D$4:$E$9, 2, FALSE), ""))</f>
+      <c r="AC3" s="3"/>
+      <c r="AD3" s="3">
+        <f>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",IFERROR(VLOOKUP(JiraDataset[[#This Row],[Sprint Name]], Config!$G$4:$H$9, 2, FALSE), ""))</f>
         <v>1</v>
       </c>
-      <c r="AD3" s="3" t="str">
+      <c r="AE3" s="3" t="str">
         <f>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",_xlfn.XLOOKUP("Creation Marker", CfgAutofieldValues[Name], CfgAutofieldValues[Value]))</f>
         <v>jt-imported</v>
       </c>
-      <c r="AE3" s="8" t="str">
+      <c r="AF3" s="8" t="str">
         <f>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",_xlfn.XLOOKUP("Feature Pod Label", CfgAutofieldValues[Name], CfgAutofieldValues[Value]))</f>
         <v>pod_test</v>
       </c>
-      <c r="AF3" s="3" t="str">
+      <c r="AG3" s="3" t="str">
         <f>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",IFERROR(VLOOKUP(JiraDataset[[#This Row],[Assignee.Name]], Config!$A$4:$B$24, 2, FALSE), ""))</f>
         <v>AtlassianID (cloud) or Email (DC)</v>
       </c>
-      <c r="AG3" s="3" t="str">
+      <c r="AH3" s="3" t="str">
         <f>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",_xlfn.XLOOKUP("jira.project.key", CfgAutofieldValues[Name], CfgAutofieldValues[Value]))</f>
         <v>PROJECT-KEY</v>
       </c>
-      <c r="AH3" s="3" cm="1">
-        <f t="array" ref="AH3">IF(
+      <c r="AI3" s="3" cm="1">
+        <f t="array" ref="AI3">IF(
   JiraDataset[[#This Row],[RowType]]=cfg_type_skip,
   "",
   _xlfn.LET(
@@ -2132,8 +2161,8 @@
 )</f>
         <v>34560000</v>
       </c>
-      <c r="AI3" s="3" cm="1">
-        <f t="array" ref="AI3">IFERROR(
+      <c r="AJ3" s="3" cm="1">
+        <f t="array" ref="AJ3">IFERROR(
     _xlfn.IFS(
         JiraDataset[[#This Row],[IssueType]] = cfg_type_comment,"SKIP",
         JiraDataset[[#This Row],[IssueType]] = cfg_type_skip,"SKIP",
@@ -2143,12 +2172,12 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="AJ3" s="3"/>
+      <c r="AK3" s="3"/>
     </row>
   </sheetData>
   <protectedRanges>
-    <protectedRange sqref="D4:N1048576 P4:AD1048576 C1:AB3 A1:A1048576" name="User Input"/>
-    <protectedRange algorithmName="SHA-512" hashValue="tpheD+JLADkhiyalt6vInlMwkILPZx4PVQN/k2vmwjOBdYUuHaXCrwtObHeFz5dJh9f853O84pZ1Rn9Ujz33+A==" saltValue="9ir5NB4CJc/69S/Eh84/mA==" spinCount="100000" sqref="AC1:AI3 AE4:AK1048576" name="Computed values"/>
+    <protectedRange sqref="D4:O1048576 Q4:AE1048576 C1:AC3 A1:A1048576" name="User Input"/>
+    <protectedRange algorithmName="SHA-512" hashValue="tpheD+JLADkhiyalt6vInlMwkILPZx4PVQN/k2vmwjOBdYUuHaXCrwtObHeFz5dJh9f853O84pZ1Rn9Ujz33+A==" saltValue="9ir5NB4CJc/69S/Eh84/mA==" spinCount="100000" sqref="AD1:AJ3 AF4:AL1048576" name="Computed values"/>
   </protectedRanges>
   <phoneticPr fontId="18" type="noConversion"/>
   <conditionalFormatting sqref="A2:A3 C2:C3">
@@ -2172,7 +2201,7 @@
       <formula>NOT(ISERROR(SEARCH("blocker",A2)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:AJ3">
+  <conditionalFormatting sqref="A2:AK3">
     <cfRule type="expression" dxfId="10" priority="409" stopIfTrue="1">
       <formula>$B2=cfg_type_comment</formula>
     </cfRule>
@@ -2197,7 +2226,7 @@
       <formula>LEN(TRIM(B2))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:AJ3">
+  <conditionalFormatting sqref="B2:AK3">
     <cfRule type="expression" dxfId="3" priority="1">
       <formula>$B2="Epic"</formula>
     </cfRule>
@@ -2210,49 +2239,52 @@
       <formula>LEN(TRIM(C2))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:L3">
+  <conditionalFormatting sqref="L2:M3">
     <cfRule type="containsBlanks" dxfId="0" priority="412">
-      <formula>LEN(TRIM(K2))=0</formula>
+      <formula>LEN(TRIM(L2))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations xWindow="1573" yWindow="665" count="21">
-    <dataValidation type="whole" allowBlank="1" showErrorMessage="1" prompt="It must be a number (integer). This reference is only used during the import process." sqref="K2:L3" xr:uid="{005E18F2-4447-4781-8F18-5A58920A4F75}">
+  <dataValidations xWindow="1573" yWindow="665" count="22">
+    <dataValidation type="whole" allowBlank="1" showErrorMessage="1" prompt="It must be a number (integer). This reference is only used during the import process." sqref="L2:M3" xr:uid="{005E18F2-4447-4781-8F18-5A58920A4F75}">
       <formula1>1</formula1>
       <formula2>1000</formula2>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" error="must be a valid component" sqref="J2:J3" xr:uid="{386E3B68-2486-4DDE-BEB1-45F897521149}"/>
-    <dataValidation type="whole" allowBlank="1" showErrorMessage="1" promptTitle="Warning" prompt="This field should be the Issue ID or Issue Key of the child tasks. (upstream linkage is not possible)._x000a__x000a__x000a_To link Epics and Stories, use the Epic Link from the Story Issue." sqref="O2:Q3" xr:uid="{D7BD960D-9CEA-4120-B2E3-2AE0D4661093}">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" error="must be a valid component" sqref="K2:K3" xr:uid="{386E3B68-2486-4DDE-BEB1-45F897521149}"/>
+    <dataValidation type="whole" allowBlank="1" showErrorMessage="1" promptTitle="Warning" prompt="This field should be the Issue ID or Issue Key of the child tasks. (upstream linkage is not possible)._x000a__x000a__x000a_To link Epics and Stories, use the Epic Link from the Story Issue." sqref="P2:R3" xr:uid="{D7BD960D-9CEA-4120-B2E3-2AE0D4661093}">
       <formula1>1</formula1>
       <formula2>1000</formula2>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Note" prompt="The content of this column will be ignored during the Jira import." sqref="AJ2:AJ3" xr:uid="{2DA3EDB6-7635-4349-8860-B614B5B71275}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Note" prompt="The content of this column will be ignored during the Jira import." sqref="AK2:AK3" xr:uid="{2DA3EDB6-7635-4349-8860-B614B5B71275}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Permissions" prompt="Updating Existing Issues requires global admin permissions" sqref="D2:D3" xr:uid="{D5E4A4BB-53C8-42DF-9B52-F5E00AC6407B}"/>
-    <dataValidation type="whole" allowBlank="1" showErrorMessage="1" promptTitle="Warning" prompt="Use the Issue ID value to link this work item to an Epic_x000a__x000a_Story Issues are not Child-Issues and should have Epic Link instead. " sqref="M2:M3" xr:uid="{16C14239-D6AA-4935-8809-57760481D8F1}">
+    <dataValidation type="whole" allowBlank="1" showErrorMessage="1" promptTitle="Warning" prompt="Use the Issue ID value to link this work item to an Epic_x000a__x000a_Story Issues are not Child-Issues and should have Epic Link instead. " sqref="N2:N3" xr:uid="{16C14239-D6AA-4935-8809-57760481D8F1}">
       <formula1>1</formula1>
       <formula2>1000</formula2>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="It must be a number (integer). This reference is only used during the import process." sqref="K1" xr:uid="{9C637146-F2E3-4D08-87A8-F70FD358E47E}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Use the Issue ID value to link this work item to an Epic_x000a__x000a_Story Issues are not Child-Issues and should have Epic Link instead. " sqref="M1" xr:uid="{A61138FD-C2B2-49D2-810B-69EAE2230B73}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="This field should be the Issue ID or Issue Key of the child tasks. (upstream linkage is not possible)._x000a__x000a__x000a_To link Epics and Stories, use the Epic Link from the Story Issue." sqref="O1:Q1" xr:uid="{BE6B7503-A11A-4130-9D63-988F0CFED80E}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" error="must be a valid fixversion" promptTitle="AUTOMATIC FIELD" prompt="Do not manually edit these!" sqref="AC2:AC3 AF1:AH3" xr:uid="{893DA5FE-9FD0-4D28-BBD0-3D7AEDECEACB}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="It must be a number (integer). This reference is only used during the import process." sqref="L1" xr:uid="{9C637146-F2E3-4D08-87A8-F70FD358E47E}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Use the Issue ID value to link this work item to an Epic_x000a__x000a_Story Issues are not Child-Issues and should have Epic Link instead. " sqref="N1" xr:uid="{A61138FD-C2B2-49D2-810B-69EAE2230B73}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="This field should be the Issue ID or Issue Key of the child tasks. (upstream linkage is not possible)._x000a__x000a__x000a_To link Epics and Stories, use the Epic Link from the Story Issue." sqref="P1:R1" xr:uid="{BE6B7503-A11A-4130-9D63-988F0CFED80E}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" error="must be a valid fixversion" promptTitle="AUTOMATIC FIELD" prompt="Do not manually edit these!" sqref="AD2:AD3 AG1:AI3" xr:uid="{893DA5FE-9FD0-4D28-BBD0-3D7AEDECEACB}"/>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="must be a valid component" sqref="H2:H3" xr:uid="{65EDED96-6789-400B-B504-6BC3F5A79E70}">
       <formula1>INDIRECT("CfgComponents[Component.Name]")</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" error="must be a valid fixversion" sqref="G2:G3" xr:uid="{44FDC20A-8BF5-49B5-9D2C-3A1FE5A7D835}">
       <formula1>INDIRECT("CfgAssignees[Assignee.Name]")</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="must be a valid component" sqref="I2:I3" xr:uid="{A898E2E7-BC45-4B88-BA1E-4AAA377361D4}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="must be a valid component" sqref="J2:J3" xr:uid="{A898E2E7-BC45-4B88-BA1E-4AAA377361D4}">
       <formula1>INDIRECT("CfgSprints[Sprint.Name]")</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showErrorMessage="1" promptTitle="Warning" prompt="Field only used for Epic Issues, so they can be referenced in Story Issues via the Epic Link field.," sqref="N2:N3 L2:L3" xr:uid="{541AD292-0123-4B65-9663-081991FDF0C1}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Field only used for Epic Issues, so they can be referenced in Story Issues via the Epic Link field.," sqref="L1" xr:uid="{64C73155-DEE7-497D-8A98-01E54655ACA8}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="It must be a number (integer) or the Work Item key. This reference is only used during the import process to set the parent." sqref="L1" xr:uid="{8A2BE248-5762-43AD-9C47-C5A92A2E2357}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Field only used for Epic work item, so they can be referenced in Story work items via the Epic Link field. _x000a_DC Only" sqref="N1" xr:uid="{E8F6E005-1F9B-40F3-B24C-E2A3D286C532}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" error="must be a valid fixversion" promptTitle="Creation Marker (Config Sheet)" prompt="Do not manually edit these!" sqref="AD1:AD3" xr:uid="{412C516D-E091-4DDD-9C14-C33AC653C143}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" error="must be a valid fixversion" promptTitle="Feature Pod Label (Config Sheet)" prompt="Do not manually edit these!" sqref="AE1:AE3" xr:uid="{D2234141-379F-4413-AB08-6835BD9FF967}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" error="must be a valid fixversion" promptTitle="AUTOMATIC FIELD" prompt="Do not manually edit these! SKIP types won't be imported into Jira" sqref="AI1:AI3" xr:uid="{5A336857-7D14-4900-8734-BED680BE5154}"/>
+    <dataValidation allowBlank="1" showErrorMessage="1" promptTitle="Warning" prompt="Field only used for Epic Issues, so they can be referenced in Story Issues via the Epic Link field.," sqref="O2:O3 M2:M3" xr:uid="{541AD292-0123-4B65-9663-081991FDF0C1}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Field only used for Epic Issues, so they can be referenced in Story Issues via the Epic Link field.," sqref="M1" xr:uid="{64C73155-DEE7-497D-8A98-01E54655ACA8}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="It must be a number (integer) or the Work Item key. This reference is only used during the import process to set the parent." sqref="M1" xr:uid="{8A2BE248-5762-43AD-9C47-C5A92A2E2357}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Field only used for Epic work item, so they can be referenced in Story work items via the Epic Link field. _x000a_DC Only" sqref="O1" xr:uid="{E8F6E005-1F9B-40F3-B24C-E2A3D286C532}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" error="must be a valid fixversion" promptTitle="Creation Marker (Config Sheet)" prompt="Do not manually edit these!" sqref="AE1:AE3" xr:uid="{412C516D-E091-4DDD-9C14-C33AC653C143}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" error="must be a valid fixversion" promptTitle="Feature Pod Label (Config Sheet)" prompt="Do not manually edit these!" sqref="AF1:AF3" xr:uid="{D2234141-379F-4413-AB08-6835BD9FF967}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" error="must be a valid fixversion" promptTitle="AUTOMATIC FIELD" prompt="Do not manually edit these! SKIP types won't be imported into Jira" sqref="AJ1:AJ3" xr:uid="{5A336857-7D14-4900-8734-BED680BE5154}"/>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="must be a valid fixversion" sqref="F2:F3" xr:uid="{7708D6E2-1D6B-41D8-A9EE-0E87219BA8EA}">
       <formula1>INDIRECT("CfgFixVersions[FixVersion.Name]")</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="must be a valid component" sqref="I2:I3" xr:uid="{ED307577-9088-47BA-9824-74F4BBFC13C9}">
+      <formula1>INDIRECT("CfgTeams[Team.Name]")</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2265,13 +2297,13 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xWindow="1573" yWindow="665" count="2">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{5EEBB8D5-878D-4D0E-9267-0919B5A1B925}">
           <x14:formula1>
-            <xm:f>Config!$O$4:$O$10</xm:f>
+            <xm:f>Config!$R$4:$R$10</xm:f>
           </x14:formula1>
           <xm:sqref>A2:A3</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Issue Type" xr:uid="{28BF52BF-C0B0-4D22-B02F-F1408D5A055B}">
           <x14:formula1>
-            <xm:f>Config!$Z$4:$Z$33</xm:f>
+            <xm:f>Config!$AC$4:$AC$33</xm:f>
           </x14:formula1>
           <xm:sqref>B2:B3</xm:sqref>
         </x14:dataValidation>
@@ -2283,114 +2315,123 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2D54512-1380-4F02-BB23-352387C91232}">
-  <dimension ref="A1:AA21"/>
+  <dimension ref="A1:AD21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29.7109375" customWidth="1"/>
     <col min="2" max="2" width="49" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="4.28515625" customWidth="1"/>
-    <col min="4" max="5" width="18.7109375" customWidth="1"/>
+    <col min="4" max="5" width="49" customWidth="1"/>
     <col min="6" max="6" width="4.28515625" customWidth="1"/>
-    <col min="7" max="7" width="18.5703125" customWidth="1"/>
-    <col min="8" max="8" width="4.28515625" customWidth="1"/>
-    <col min="9" max="9" width="19.140625" customWidth="1"/>
-    <col min="10" max="10" width="4.28515625" customWidth="1"/>
-    <col min="11" max="11" width="18.5703125" customWidth="1"/>
-    <col min="12" max="12" width="4.28515625" customWidth="1"/>
-    <col min="13" max="13" width="17.5703125" customWidth="1"/>
-    <col min="14" max="14" width="4.28515625" customWidth="1"/>
-    <col min="15" max="15" width="18.7109375" customWidth="1"/>
-    <col min="16" max="16" width="4.28515625" customWidth="1"/>
-    <col min="17" max="18" width="18.7109375" customWidth="1"/>
-    <col min="19" max="19" width="35" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="18.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.28515625" customWidth="1"/>
+    <col min="10" max="10" width="18.5703125" customWidth="1"/>
+    <col min="11" max="11" width="4.28515625" customWidth="1"/>
+    <col min="12" max="12" width="19.140625" customWidth="1"/>
+    <col min="13" max="13" width="4.28515625" customWidth="1"/>
+    <col min="14" max="14" width="18.5703125" customWidth="1"/>
+    <col min="15" max="15" width="4.28515625" customWidth="1"/>
+    <col min="16" max="16" width="17.5703125" customWidth="1"/>
+    <col min="17" max="17" width="4.28515625" customWidth="1"/>
+    <col min="18" max="18" width="18.7109375" customWidth="1"/>
+    <col min="19" max="19" width="4.28515625" customWidth="1"/>
+    <col min="20" max="21" width="18.7109375" customWidth="1"/>
+    <col min="22" max="22" width="35" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="22.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="21" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:30" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="11" t="s">
         <v>67</v>
       </c>
       <c r="B1" s="11"/>
       <c r="D1" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="E1" s="11"/>
+      <c r="G1" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="E1" s="11"/>
-      <c r="G1" s="6" t="s">
+      <c r="H1" s="11"/>
+      <c r="J1" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="L1" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="N1" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="P1" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="O1" s="6" t="s">
+      <c r="R1" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="Q1" s="11" t="s">
+      <c r="T1" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="R1" s="11"/>
-      <c r="S1" s="11"/>
-      <c r="U1" s="11" t="s">
+      <c r="U1" s="11"/>
+      <c r="V1" s="11"/>
+      <c r="X1" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="V1" s="11"/>
-      <c r="W1" s="11"/>
-      <c r="X1" s="11"/>
-      <c r="Z1" s="6" t="s">
+      <c r="Y1" s="11"/>
+      <c r="Z1" s="11"/>
+      <c r="AA1" s="11"/>
+      <c r="AC1" s="6" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
         <v>73</v>
       </c>
       <c r="B2" s="12"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="12" t="s">
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="E2" s="12"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="10" t="s">
+      <c r="H2" s="12"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="H2" s="10"/>
-      <c r="I2" s="10" t="s">
+      <c r="K2" s="10"/>
+      <c r="L2" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="J2" s="10"/>
-      <c r="K2" s="12" t="s">
+      <c r="M2" s="10"/>
+      <c r="N2" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="L2" s="12"/>
-      <c r="M2" s="9" t="s">
+      <c r="O2" s="12"/>
+      <c r="P2" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="N2" s="9"/>
-      <c r="O2" s="10" t="s">
+      <c r="Q2" s="9"/>
+      <c r="R2" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="P2" s="10"/>
-      <c r="Q2" s="12"/>
-      <c r="R2" s="12"/>
-      <c r="S2" s="9"/>
-      <c r="T2" s="7"/>
-      <c r="U2" s="7"/>
-      <c r="V2" s="7"/>
+      <c r="S2" s="10"/>
+      <c r="T2" s="12"/>
+      <c r="U2" s="12"/>
+      <c r="V2" s="9"/>
       <c r="W2" s="7"/>
       <c r="X2" s="7"/>
       <c r="Y2" s="7"/>
-      <c r="Z2" s="9" t="s">
+      <c r="Z2" s="7"/>
+      <c r="AA2" s="7"/>
+      <c r="AB2" s="7"/>
+      <c r="AC2" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="AA2" s="9"/>
+      <c r="AD2" s="9"/>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -2398,52 +2439,58 @@
         <v>57</v>
       </c>
       <c r="D3" t="s">
+        <v>107</v>
+      </c>
+      <c r="E3" t="s">
+        <v>108</v>
+      </c>
+      <c r="G3" t="s">
         <v>58</v>
       </c>
-      <c r="E3" t="s">
+      <c r="H3" t="s">
         <v>59</v>
       </c>
-      <c r="G3" t="s">
+      <c r="J3" t="s">
         <v>63</v>
       </c>
-      <c r="I3" t="s">
+      <c r="L3" t="s">
         <v>62</v>
       </c>
-      <c r="K3" t="s">
+      <c r="N3" t="s">
         <v>61</v>
       </c>
-      <c r="M3" t="s">
+      <c r="P3" t="s">
         <v>66</v>
       </c>
-      <c r="O3" t="s">
+      <c r="R3" t="s">
         <v>60</v>
       </c>
-      <c r="Q3" t="s">
+      <c r="T3" t="s">
         <v>53</v>
       </c>
-      <c r="R3" t="s">
+      <c r="U3" t="s">
         <v>54</v>
       </c>
-      <c r="S3" t="s">
+      <c r="V3" t="s">
         <v>64</v>
       </c>
-      <c r="U3" t="s">
+      <c r="X3" t="s">
         <v>53</v>
       </c>
-      <c r="V3" t="s">
+      <c r="Y3" t="s">
         <v>98</v>
       </c>
-      <c r="W3" t="s">
+      <c r="Z3" t="s">
         <v>99</v>
       </c>
-      <c r="X3" t="s">
+      <c r="AA3" t="s">
         <v>100</v>
       </c>
-      <c r="Z3" s="5" t="s">
+      <c r="AC3" s="5" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>53</v>
       </c>
@@ -2451,226 +2498,233 @@
         <v>94</v>
       </c>
       <c r="D4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E4" t="s">
+        <v>109</v>
+      </c>
+      <c r="G4" t="s">
         <v>45</v>
       </c>
-      <c r="E4">
+      <c r="H4">
         <v>1</v>
       </c>
-      <c r="G4" t="s">
+      <c r="J4" t="s">
         <v>90</v>
       </c>
-      <c r="I4" t="s">
+      <c r="L4" t="s">
         <v>84</v>
       </c>
-      <c r="K4" t="s">
+      <c r="N4" t="s">
         <v>39</v>
       </c>
-      <c r="M4" t="s">
+      <c r="P4" t="s">
         <v>34</v>
       </c>
-      <c r="O4" s="1" t="s">
+      <c r="R4" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="Q4" t="s">
+      <c r="T4" t="s">
         <v>50</v>
       </c>
-      <c r="R4" t="s">
+      <c r="U4" t="s">
         <v>91</v>
       </c>
-      <c r="S4" s="7" t="s">
+      <c r="V4" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="Z4" t="str" cm="1">
-        <f t="array" aca="1" ref="Z4:Z12" ca="1">_xlfn.UNIQUE((_xlfn.VSTACK(INDIRECT("CfgIssueTypes[IssueType.Name]"),INDIRECT("CfgIgnoreList[IgnoreList.Name]"))))</f>
+      <c r="AC4" t="str" cm="1">
+        <f t="array" aca="1" ref="AC4:AC12" ca="1">_xlfn.UNIQUE((_xlfn.VSTACK(INDIRECT("CfgIssueTypes[IssueType.Name]"),INDIRECT("CfgIgnoreList[IgnoreList.Name]"))))</f>
         <v>Story</v>
       </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="K5" t="s">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="N5" t="s">
         <v>37</v>
       </c>
-      <c r="M5" t="s">
+      <c r="P5" t="s">
         <v>44</v>
       </c>
-      <c r="O5" s="1" t="s">
+      <c r="R5" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="Q5" t="s">
+      <c r="T5" t="s">
         <v>46</v>
       </c>
-      <c r="R5" t="s">
+      <c r="U5" t="s">
         <v>85</v>
       </c>
-      <c r="S5" s="7" t="s">
+      <c r="V5" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="Z5" t="str">
+      <c r="AC5" t="str">
         <f ca="1"/>
         <v>Task</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="K6" t="s">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="N6" t="s">
         <v>40</v>
       </c>
-      <c r="M6" t="s">
+      <c r="P6" t="s">
         <v>33</v>
       </c>
-      <c r="O6" s="1" t="s">
+      <c r="R6" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="Q6" t="s">
+      <c r="T6" t="s">
         <v>86</v>
       </c>
-      <c r="R6" t="s">
+      <c r="U6" t="s">
         <v>102</v>
       </c>
-      <c r="S6" s="7"/>
-      <c r="Z6" t="str">
+      <c r="V6" s="7"/>
+      <c r="AC6" t="str">
         <f ca="1"/>
         <v>Bug</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="K7" t="s">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+      <c r="N7" t="s">
         <v>41</v>
       </c>
-      <c r="O7" s="1" t="s">
+      <c r="R7" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="Q7" t="s">
+      <c r="T7" t="s">
         <v>87</v>
       </c>
-      <c r="R7" t="s">
+      <c r="U7" t="s">
         <v>104</v>
       </c>
-      <c r="S7" s="7"/>
-      <c r="Z7" t="str">
+      <c r="V7" s="7"/>
+      <c r="AC7" t="str">
         <f ca="1"/>
         <v>Epic</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="K8" t="s">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="N8" t="s">
         <v>93</v>
       </c>
-      <c r="O8" s="1" t="s">
+      <c r="R8" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="Q8" t="s">
+      <c r="T8" t="s">
         <v>103</v>
       </c>
-      <c r="R8">
+      <c r="U8">
         <v>7</v>
       </c>
-      <c r="S8" s="7"/>
-      <c r="Z8" t="str">
+      <c r="V8" s="7"/>
+      <c r="AC8" t="str">
         <f ca="1"/>
         <v>Sub-Task</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="K9" t="s">
+    <row r="9" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="N9" t="s">
         <v>101</v>
       </c>
-      <c r="O9" s="1" t="s">
+      <c r="R9" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="Q9" t="s">
+      <c r="T9" t="s">
         <v>88</v>
       </c>
-      <c r="R9" t="s">
+      <c r="U9" t="s">
         <v>89</v>
       </c>
-      <c r="S9" s="7"/>
-      <c r="Z9" t="str">
+      <c r="V9" s="7"/>
+      <c r="AC9" t="str">
         <f ca="1"/>
         <v>Initiative</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="S10" s="7"/>
-      <c r="Z10" t="str">
+    <row r="10" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="V10" s="7"/>
+      <c r="AC10" t="str">
         <f ca="1"/>
         <v>Comment</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="S11" s="7"/>
-      <c r="Z11" t="str">
+    <row r="11" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="V11" s="7"/>
+      <c r="AC11" t="str">
         <f ca="1"/>
         <v>Skip</v>
       </c>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="Z12" t="str">
+    <row r="12" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="AC12" t="str">
         <f ca="1"/>
         <v>Note</v>
       </c>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
     </row>
-    <row r="17" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
+    <row r="17" spans="7:8" x14ac:dyDescent="0.25">
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
     </row>
-    <row r="18" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
+    <row r="18" spans="7:8" x14ac:dyDescent="0.25">
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
     </row>
-    <row r="19" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
+    <row r="19" spans="7:8" x14ac:dyDescent="0.25">
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
     </row>
-    <row r="20" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
+    <row r="20" spans="7:8" x14ac:dyDescent="0.25">
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
     </row>
-    <row r="21" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
+    <row r="21" spans="7:8" x14ac:dyDescent="0.25">
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="U1:X1"/>
-    <mergeCell ref="Q1:S1"/>
-    <mergeCell ref="D1:E1"/>
+  <mergeCells count="9">
+    <mergeCell ref="X1:AA1"/>
+    <mergeCell ref="T1:V1"/>
+    <mergeCell ref="G1:H1"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="Q2:R2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="T2:U2"/>
+    <mergeCell ref="D1:E1"/>
   </mergeCells>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
-  <tableParts count="9">
+  <tableParts count="10">
     <tablePart r:id="rId2"/>
     <tablePart r:id="rId3"/>
     <tablePart r:id="rId4"/>
@@ -2680,31 +2734,12 @@
     <tablePart r:id="rId8"/>
     <tablePart r:id="rId9"/>
     <tablePart r:id="rId10"/>
+    <tablePart r:id="rId11"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c471fd26-9765-4fbe-b6fd-c17c1e55c974">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="9df69692-83aa-4c55-88c1-62abad05f4fe" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100FB038601AF41D04A88A4BD446922F1A8" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="e8d32171d27ae41230d53456f24efae5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c471fd26-9765-4fbe-b6fd-c17c1e55c974" xmlns:ns3="9df69692-83aa-4c55-88c1-62abad05f4fe" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1f2fb84de5621acf32f385a2ba90fb29" ns2:_="" ns3:_="">
     <xsd:import namespace="c471fd26-9765-4fbe-b6fd-c17c1e55c974"/>
@@ -2933,10 +2968,41 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c471fd26-9765-4fbe-b6fd-c17c1e55c974">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="9df69692-83aa-4c55-88c1-62abad05f4fe" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{156C3F15-3876-4FBB-8F24-692088DE8D9F}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2C983B91-58B3-4C2C-AC55-FFEC9F0DB5F6}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="c471fd26-9765-4fbe-b6fd-c17c1e55c974"/>
+    <ds:schemaRef ds:uri="9df69692-83aa-4c55-88c1-62abad05f4fe"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -2953,20 +3019,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2C983B91-58B3-4C2C-AC55-FFEC9F0DB5F6}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{156C3F15-3876-4FBB-8F24-692088DE8D9F}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="c471fd26-9765-4fbe-b6fd-c17c1e55c974"/>
-    <ds:schemaRef ds:uri="9df69692-83aa-4c55-88c1-62abad05f4fe"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/resources/templates/ImportTemplate.xlsx
+++ b/resources/templates/ImportTemplate.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workdir\DeerHide\sources\jira-toolkit\resources\Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4BC4158-D472-4903-A82C-8B483D399CF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5D59A5B-E3CC-4BE2-8CC3-FDE61B5D10DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1485" yWindow="6135" windowWidth="29685" windowHeight="23445" xr2:uid="{1FA076D1-0294-4A97-AB8C-3ADE2BC9CEA1}"/>
+    <workbookView xWindow="735" yWindow="735" windowWidth="29685" windowHeight="23445" activeTab="4" xr2:uid="{1FA076D1-0294-4A97-AB8C-3ADE2BC9CEA1}"/>
   </bookViews>
   <sheets>
     <sheet name="Dataset" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="7" r:id="rId10"/>
+    <pivotCache cacheId="9" r:id="rId10"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -83,7 +83,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Issue type (Epic, Story, Task…). Skip types like comment/note are ignored.</t>
         </r>
@@ -819,7 +819,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="24" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -982,12 +982,6 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
     </font>
     <font>
       <sz val="9"/>
@@ -1357,7 +1351,7 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1407,7 +1401,6 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="16" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1598,35 +1591,35 @@
       </fill>
     </dxf>
     <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="1" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="1" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="1" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
       <alignment vertical="top"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
       <alignment vertical="top"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="1" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="1" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="1" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -2006,7 +1999,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9326BD75-A09D-4578-BB55-882D1F75C66E}" name="PT_Issues" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9326BD75-A09D-4578-BB55-882D1F75C66E}" name="PT_Issues" cacheId="9" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A5:B12" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="36">
     <pivotField showAll="0"/>
@@ -2114,7 +2107,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A931C4D6-0F40-4FC0-8FE0-7829E37288EB}" name="PT_Assignees" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A931C4D6-0F40-4FC0-8FE0-7829E37288EB}" name="PT_Assignees" cacheId="9" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
   <location ref="D5:E10" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="36">
     <pivotField showAll="0"/>
@@ -2297,19 +2290,19 @@
     <tableColumn id="21" xr3:uid="{105F2D0F-70C1-4517-A55F-4C1DDFE85301}" name="Sprint" dataDxfId="27">
       <calculatedColumnFormula>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",IFERROR(VLOOKUP(JiraDataset[[#This Row],[Sprint Name]], 'Config - Mappings'!$G$4:$H$8, 2, FALSE), ""))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{D5984986-D838-4F87-A554-5DC4CA005452}" name="Labels0001" dataDxfId="16">
+    <tableColumn id="22" xr3:uid="{D5984986-D838-4F87-A554-5DC4CA005452}" name="Labels0001" dataDxfId="26">
       <calculatedColumnFormula>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",_xlfn.XLOOKUP("Creation Marker", CfgMisc[Name], CfgMisc[Value],"",1))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="39" xr3:uid="{C24E9ADD-96A8-4DBB-86A0-08D41975D750}" name="Labels0002" dataDxfId="17">
+    <tableColumn id="39" xr3:uid="{C24E9ADD-96A8-4DBB-86A0-08D41975D750}" name="Labels0002" dataDxfId="25">
       <calculatedColumnFormula>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",_xlfn.XLOOKUP("Work Group", CfgMisc[Name], CfgMisc[Value],"",1))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{A6D8D5A6-43EE-415C-80C1-30372C7FE5BF}" name="Assignee" dataDxfId="26">
+    <tableColumn id="6" xr3:uid="{A6D8D5A6-43EE-415C-80C1-30372C7FE5BF}" name="Assignee" dataDxfId="24">
       <calculatedColumnFormula>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",IFERROR(VLOOKUP(JiraDataset[[#This Row],[Assignee.Name]], 'Config - Mappings'!$A$4:$B$26, 2, FALSE), ""))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="23" xr3:uid="{51D4B5F4-C6D3-4EEC-8B1B-7BEC6E526A64}" name="Project Key" dataDxfId="25">
+    <tableColumn id="23" xr3:uid="{51D4B5F4-C6D3-4EEC-8B1B-7BEC6E526A64}" name="Project Key" dataDxfId="23">
       <calculatedColumnFormula>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",_xlfn.XLOOKUP("jira.project.key", CfgBasic[Name], CfgBasic[Value]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="42" xr3:uid="{82B78F0D-CAEF-4615-B12A-B15ACF33913C}" name="OrigEst" dataDxfId="24">
+    <tableColumn id="42" xr3:uid="{82B78F0D-CAEF-4615-B12A-B15ACF33913C}" name="OrigEst" dataDxfId="22">
       <calculatedColumnFormula array="1">IF(
   JiraDataset[[#This Row],[RowType]]=cfg_type_skip,
   "",
@@ -2325,7 +2318,7 @@
   )
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="44" xr3:uid="{C92FD7EC-0EAB-4967-A0E5-D2427E3A55B4}" name="RowType" dataDxfId="23">
+    <tableColumn id="44" xr3:uid="{C92FD7EC-0EAB-4967-A0E5-D2427E3A55B4}" name="RowType" dataDxfId="21">
       <calculatedColumnFormula array="1">IFERROR(
     _xlfn.IFS(
         JiraDataset[[#This Row],[IssueType]] = cfg_type_comment,"SKIP",
@@ -2335,7 +2328,7 @@
     cfg_type_workitem
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="24" xr3:uid="{B63E8FC4-20B3-4755-92F2-EA1F700CA72E}" name="Note" dataDxfId="22"/>
+    <tableColumn id="24" xr3:uid="{B63E8FC4-20B3-4755-92F2-EA1F700CA72E}" name="Note" dataDxfId="20"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2345,7 +2338,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{A6C0EE44-3F60-4588-BF11-75C3DD021846}" name="CfgPriorities" displayName="CfgPriorities" ref="L22:L28" totalsRowShown="0">
   <autoFilter ref="L22:L28" xr:uid="{A6C0EE44-3F60-4588-BF11-75C3DD021846}"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{3B3BE2ED-38C4-410B-B0BF-4A9BD9B4B974}" name="Priority.Name" dataDxfId="19"/>
+    <tableColumn id="1" xr3:uid="{3B3BE2ED-38C4-410B-B0BF-4A9BD9B4B974}" name="Priority.Name" dataDxfId="17"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium5" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2381,7 +2374,7 @@
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{724752C0-2EB0-4307-9766-E95D142383BC}" name="Name"/>
     <tableColumn id="2" xr3:uid="{1B4D7FE1-60C9-4319-8B9F-E66C19764AEE}" name="Value"/>
-    <tableColumn id="3" xr3:uid="{F0634D25-384E-480B-B675-9F8463C0D844}" name="Note" dataDxfId="20"/>
+    <tableColumn id="3" xr3:uid="{F0634D25-384E-480B-B675-9F8463C0D844}" name="Note" dataDxfId="16"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium5" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2437,7 +2430,7 @@
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{D4E1611F-A2CF-465D-A219-1759EA66687D}" name="Name"/>
     <tableColumn id="2" xr3:uid="{174D0D86-B1AA-4BF7-AC91-FCACFC898851}" name="Value"/>
-    <tableColumn id="3" xr3:uid="{4D0493E3-2ED0-412B-9468-835FC91C2910}" name="Note" dataDxfId="21"/>
+    <tableColumn id="3" xr3:uid="{4D0493E3-2ED0-412B-9468-835FC91C2910}" name="Note" dataDxfId="19"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium5" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3340,13 +3333,13 @@
       <c r="A6" s="14" t="s">
         <v>149</v>
       </c>
-      <c r="B6" s="21">
+      <c r="B6">
         <v>1</v>
       </c>
       <c r="D6" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="E6" s="21">
+      <c r="E6">
         <v>1</v>
       </c>
     </row>
@@ -3354,13 +3347,13 @@
       <c r="A7" s="15" t="s">
         <v>149</v>
       </c>
-      <c r="B7" s="21">
+      <c r="B7">
         <v>1</v>
       </c>
       <c r="D7" s="15" t="s">
         <v>155</v>
       </c>
-      <c r="E7" s="21">
+      <c r="E7">
         <v>1</v>
       </c>
     </row>
@@ -3368,13 +3361,13 @@
       <c r="A8" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="B8" s="21">
+      <c r="B8">
         <v>1</v>
       </c>
       <c r="D8" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="E8" s="21">
+      <c r="E8">
         <v>1</v>
       </c>
     </row>
@@ -3382,13 +3375,13 @@
       <c r="A9" s="14" t="s">
         <v>165</v>
       </c>
-      <c r="B9" s="21">
+      <c r="B9">
         <v>1</v>
       </c>
       <c r="D9" s="15" t="s">
         <v>149</v>
       </c>
-      <c r="E9" s="21">
+      <c r="E9">
         <v>1</v>
       </c>
     </row>
@@ -3396,13 +3389,13 @@
       <c r="A10" s="15" t="s">
         <v>166</v>
       </c>
-      <c r="B10" s="21">
+      <c r="B10">
         <v>1</v>
       </c>
       <c r="D10" s="14" t="s">
         <v>148</v>
       </c>
-      <c r="E10" s="21">
+      <c r="E10">
         <v>2</v>
       </c>
     </row>
@@ -3410,7 +3403,7 @@
       <c r="A11" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="21">
+      <c r="B11">
         <v>1</v>
       </c>
     </row>
@@ -3418,7 +3411,7 @@
       <c r="A12" s="14" t="s">
         <v>148</v>
       </c>
-      <c r="B12" s="21">
+      <c r="B12">
         <v>2</v>
       </c>
     </row>
@@ -4042,7 +4035,7 @@
         <v>38</v>
       </c>
       <c r="M4">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
@@ -4062,7 +4055,7 @@
         <v>36</v>
       </c>
       <c r="M5">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
@@ -4084,7 +4077,7 @@
         <v>40</v>
       </c>
       <c r="M6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
@@ -4106,7 +4099,7 @@
         <v>41</v>
       </c>
       <c r="M7">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
@@ -4128,7 +4121,7 @@
         <v>89</v>
       </c>
       <c r="M8">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
@@ -4674,6 +4667,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100FB038601AF41D04A88A4BD446922F1A8" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="e8d32171d27ae41230d53456f24efae5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c471fd26-9765-4fbe-b6fd-c17c1e55c974" xmlns:ns3="9df69692-83aa-4c55-88c1-62abad05f4fe" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1f2fb84de5621acf32f385a2ba90fb29" ns2:_="" ns3:_="">
     <xsd:import namespace="c471fd26-9765-4fbe-b6fd-c17c1e55c974"/>
@@ -4902,15 +4904,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -4923,6 +4916,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{156C3F15-3876-4FBB-8F24-692088DE8D9F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2C983B91-58B3-4C2C-AC55-FFEC9F0DB5F6}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4941,14 +4942,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{156C3F15-3876-4FBB-8F24-692088DE8D9F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9FFE630F-6530-4863-AB67-8477539A0000}">
   <ds:schemaRefs>

--- a/resources/templates/ImportTemplate.xlsx
+++ b/resources/templates/ImportTemplate.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workdir\DeerHide\sources\jira-toolkit\resources\Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5D59A5B-E3CC-4BE2-8CC3-FDE61B5D10DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12369D8C-D85F-47D4-A1D7-BC151129C134}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="735" yWindow="735" windowWidth="29685" windowHeight="23445" activeTab="4" xr2:uid="{1FA076D1-0294-4A97-AB8C-3ADE2BC9CEA1}"/>
+    <workbookView xWindow="1845" yWindow="4695" windowWidth="33615" windowHeight="23445" xr2:uid="{1FA076D1-0294-4A97-AB8C-3ADE2BC9CEA1}"/>
   </bookViews>
   <sheets>
     <sheet name="Dataset" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="9" r:id="rId10"/>
+    <pivotCache cacheId="0" r:id="rId10"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -115,7 +115,59 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{9C29F0D9-EEC2-4CD5-94B3-E79BFBEEBA7A}">
+    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{D37165B4-6A0B-4DE1-BBC9-E2B87095C67A}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Assignee name from CfgAssignees (mapped to account ID).</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{BF9D9590-454C-4556-A96A-8432D26EB0AA}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Component name from CfgComponents. One per cell.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{098743DC-80FD-4D99-8C10-F8768C499BB1}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Effort estimate. Blank if unknown. Format 1w 2d 4h (week=5days, day=8h)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J1" authorId="0" shapeId="0" xr:uid="{E0BF772F-400D-4779-B463-DF3B16DC24EF}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Sprint name from CfgSprints. Blank if unplanned.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K1" authorId="0" shapeId="0" xr:uid="{9C29F0D9-EEC2-4CD5-94B3-E79BFBEEBA7A}">
       <text>
         <r>
           <rPr>
@@ -128,7 +180,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{D37165B4-6A0B-4DE1-BBC9-E2B87095C67A}">
+    <comment ref="L1" authorId="0" shapeId="0" xr:uid="{E6A239CC-FBE8-42B6-BE3E-9D37323CB14A}">
       <text>
         <r>
           <rPr>
@@ -137,63 +189,12 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>Assignee name from CfgAssignees (mapped to account ID).</t>
+          <t>Unique local ID in this file (not a Jira key). Used for links.
+Empty row can be generated using -af/--auto-fix</t>
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{BF9D9590-454C-4556-A96A-8432D26EB0AA}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Component name from CfgComponents. One per cell.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{E0BF772F-400D-4779-B463-DF3B16DC24EF}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Sprint name from CfgSprints. Blank if unplanned.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="J1" authorId="0" shapeId="0" xr:uid="{098743DC-80FD-4D99-8C10-F8768C499BB1}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Effort estimate. Blank if unknown. Format 1w 2d 4h (week=5days, day=8h)</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="K1" authorId="0" shapeId="0" xr:uid="{E6A239CC-FBE8-42B6-BE3E-9D37323CB14A}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Unique local ID in this file (not a Jira key). Used for links.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="L1" authorId="0" shapeId="0" xr:uid="{B1D0971D-6639-458E-AEB8-E00BC927C14D}">
+    <comment ref="M1" authorId="0" shapeId="0" xr:uid="{B1D0971D-6639-458E-AEB8-E00BC927C14D}">
       <text>
         <r>
           <rPr>
@@ -206,7 +207,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R1" authorId="0" shapeId="0" xr:uid="{FD454FB1-970A-43A3-8724-BF23CA54530B}">
+    <comment ref="P1" authorId="0" shapeId="0" xr:uid="{FD454FB1-970A-43A3-8724-BF23CA54530B}">
       <text>
         <r>
           <rPr>
@@ -246,7 +247,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="200">
   <si>
     <t>IssueType</t>
   </si>
@@ -287,15 +288,6 @@
     <t>Epic Name</t>
   </si>
   <si>
-    <t>Child-Issue</t>
-  </si>
-  <si>
-    <t>Child-Issue1</t>
-  </si>
-  <si>
-    <t>Child-Issue2</t>
-  </si>
-  <si>
     <t>Labels</t>
   </si>
   <si>
@@ -314,21 +306,6 @@
     <t>Labels5</t>
   </si>
   <si>
-    <t>Labels6</t>
-  </si>
-  <si>
-    <t>Labels7</t>
-  </si>
-  <si>
-    <t>Labels8</t>
-  </si>
-  <si>
-    <t>Labels9</t>
-  </si>
-  <si>
-    <t>Labels10</t>
-  </si>
-  <si>
     <t>Sprint</t>
   </si>
   <si>
@@ -473,9 +450,6 @@
     <t>List of Components</t>
   </si>
   <si>
-    <t>Accepted User Types</t>
-  </si>
-  <si>
     <t>Issue Types that won't be imported</t>
   </si>
   <si>
@@ -813,6 +787,66 @@
   </si>
   <si>
     <t>This sheet is ignored by the importer, it can contain anything</t>
+  </si>
+  <si>
+    <t>Team</t>
+  </si>
+  <si>
+    <t>QA Team</t>
+  </si>
+  <si>
+    <t>PM Team</t>
+  </si>
+  <si>
+    <t>Design Team</t>
+  </si>
+  <si>
+    <t>Dev Team</t>
+  </si>
+  <si>
+    <t>Accepted IssueType and Levels</t>
+  </si>
+  <si>
+    <t>CF Number01</t>
+  </si>
+  <si>
+    <t>customfield_10125</t>
+  </si>
+  <si>
+    <t>number</t>
+  </si>
+  <si>
+    <t>CF Plain Text</t>
+  </si>
+  <si>
+    <t>customfield_10124</t>
+  </si>
+  <si>
+    <t>text</t>
+  </si>
+  <si>
+    <t>CF Date</t>
+  </si>
+  <si>
+    <t>customfield_10123</t>
+  </si>
+  <si>
+    <t>date</t>
+  </si>
+  <si>
+    <t>CF List</t>
+  </si>
+  <si>
+    <t>customfield_10126</t>
+  </si>
+  <si>
+    <t>any</t>
+  </si>
+  <si>
+    <t>The names need to match a column in the dataset (first sheet)</t>
+  </si>
+  <si>
+    <t>This is the description of the work item</t>
   </si>
 </sst>
 </file>
@@ -1351,7 +1385,7 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1401,6 +1435,9 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="16" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" shrinkToFit="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1447,7 +1484,7 @@
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="58">
+  <dxfs count="52">
     <dxf>
       <fill>
         <patternFill patternType="darkUp"/>
@@ -1591,121 +1628,101 @@
       </fill>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="1" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="1" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="1" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment vertical="top"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment vertical="top"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment vertical="top"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment vertical="top"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment vertical="top"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment vertical="top"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top"/>
-    </dxf>
-    <dxf>
       <font>
         <b val="0"/>
       </font>
       <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment vertical="top"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment vertical="top"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="1" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="1" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="1" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment vertical="top"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment vertical="top"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment vertical="top"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment vertical="top"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top"/>
+    </dxf>
+    <dxf>
       <alignment vertical="top"/>
     </dxf>
     <dxf>
@@ -1743,6 +1760,9 @@
     </dxf>
     <dxf>
       <alignment vertical="top"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1774,7 +1794,7 @@
 <file path=xl/namedSheetViews/namedSheetView1.xml><?xml version="1.0" encoding="utf-8"?>
 <namedSheetViews xmlns="http://schemas.microsoft.com/office/spreadsheetml/2019/namedsheetviews" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <namedSheetView name="View1" id="{77233F75-225A-4D7F-8A86-543E0A8C6E58}">
-    <nsvFilter filterId="{933FCFD5-1AB1-4076-B5DD-E2B69F5EB3F2}" ref="A1:AJ3" tableId="1"/>
+    <nsvFilter filterId="{933FCFD5-1AB1-4076-B5DD-E2B69F5EB3F2}" ref="A1:AD3" tableId="1"/>
   </namedSheetView>
 </namedSheetViews>
 </file>
@@ -1999,7 +2019,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9326BD75-A09D-4578-BB55-882D1F75C66E}" name="PT_Issues" cacheId="9" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9326BD75-A09D-4578-BB55-882D1F75C66E}" name="PT_Issues" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A5:B12" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="36">
     <pivotField showAll="0"/>
@@ -2107,7 +2127,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A931C4D6-0F40-4FC0-8FE0-7829E37288EB}" name="PT_Assignees" cacheId="9" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A931C4D6-0F40-4FC0-8FE0-7829E37288EB}" name="PT_Assignees" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
   <location ref="D5:E10" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="36">
     <pivotField showAll="0"/>
@@ -2252,57 +2272,53 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{933FCFD5-1AB1-4076-B5DD-E2B69F5EB3F2}" name="JiraDataset" displayName="JiraDataset" ref="A1:AJ3" totalsRowShown="0" headerRowDxfId="57" dataDxfId="56">
-  <autoFilter ref="A1:AJ3" xr:uid="{933FCFD5-1AB1-4076-B5DD-E2B69F5EB3F2}"/>
-  <tableColumns count="36">
-    <tableColumn id="3" xr3:uid="{AF2EC907-349C-4651-852D-6E39C61E17FF}" name="Priority" dataDxfId="55"/>
-    <tableColumn id="2" xr3:uid="{E90C51F2-4386-421F-A3E4-E2CA9D43D396}" name="IssueType" dataDxfId="54"/>
-    <tableColumn id="1" xr3:uid="{BBAD373B-BA13-47E4-9F74-565F4D9E9680}" name="Summary" dataDxfId="53"/>
-    <tableColumn id="4" xr3:uid="{026E5B97-FAFC-4E46-860E-0B0C976B1148}" name="Issue Key" dataDxfId="52"/>
-    <tableColumn id="5" xr3:uid="{A2C262E8-D544-4669-99F1-151EDE081654}" name="Description" dataDxfId="51"/>
-    <tableColumn id="7" xr3:uid="{0FAD1ACC-432E-462C-8B89-71540710BCB5}" name="FixVersion" dataDxfId="50">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{933FCFD5-1AB1-4076-B5DD-E2B69F5EB3F2}" name="JiraDataset" displayName="JiraDataset" ref="A1:AD3" totalsRowShown="0" headerRowDxfId="50" dataDxfId="49">
+  <autoFilter ref="A1:AD3" xr:uid="{933FCFD5-1AB1-4076-B5DD-E2B69F5EB3F2}"/>
+  <tableColumns count="30">
+    <tableColumn id="3" xr3:uid="{AF2EC907-349C-4651-852D-6E39C61E17FF}" name="Priority" dataDxfId="48"/>
+    <tableColumn id="2" xr3:uid="{E90C51F2-4386-421F-A3E4-E2CA9D43D396}" name="IssueType" dataDxfId="47"/>
+    <tableColumn id="1" xr3:uid="{BBAD373B-BA13-47E4-9F74-565F4D9E9680}" name="Summary" dataDxfId="46"/>
+    <tableColumn id="4" xr3:uid="{026E5B97-FAFC-4E46-860E-0B0C976B1148}" name="Issue Key" dataDxfId="45"/>
+    <tableColumn id="5" xr3:uid="{A2C262E8-D544-4669-99F1-151EDE081654}" name="Description" dataDxfId="44"/>
+    <tableColumn id="28" xr3:uid="{07F3030C-7187-4B16-BBDB-798304851975}" name="Assignee.Name" dataDxfId="43"/>
+    <tableColumn id="8" xr3:uid="{8C7FB8DB-A85B-4189-93D8-0F0D4EEEF81B}" name="Component" dataDxfId="42"/>
+    <tableColumn id="31" xr3:uid="{BB70BDE8-70CB-404D-896E-075FB6ED93B1}" name="Team.Name" dataDxfId="20"/>
+    <tableColumn id="40" xr3:uid="{1F406792-7ED2-4476-8FF4-4C6ABA231C97}" name="Estimate" dataDxfId="17"/>
+    <tableColumn id="9" xr3:uid="{DC5101A8-1204-44D2-BC2C-FEE1A4EFE7C1}" name="Sprint Name" dataDxfId="18"/>
+    <tableColumn id="7" xr3:uid="{0FAD1ACC-432E-462C-8B89-71540710BCB5}" name="FixVersion" dataDxfId="16">
       <calculatedColumnFormula>'Config - Mappings'!$J$4</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="28" xr3:uid="{07F3030C-7187-4B16-BBDB-798304851975}" name="Assignee.Name" dataDxfId="49"/>
-    <tableColumn id="8" xr3:uid="{8C7FB8DB-A85B-4189-93D8-0F0D4EEEF81B}" name="Component" dataDxfId="48"/>
-    <tableColumn id="9" xr3:uid="{DC5101A8-1204-44D2-BC2C-FEE1A4EFE7C1}" name="Sprint Name" dataDxfId="47"/>
-    <tableColumn id="40" xr3:uid="{1F406792-7ED2-4476-8FF4-4C6ABA231C97}" name="Estimate" dataDxfId="46"/>
-    <tableColumn id="10" xr3:uid="{70B7C471-B624-430B-8992-4711F27BB17E}" name="Issue ID" dataDxfId="45"/>
-    <tableColumn id="30" xr3:uid="{938D6CA2-8309-4146-9B62-E8CDFAB7B1C9}" name="Parent" dataDxfId="44"/>
-    <tableColumn id="11" xr3:uid="{594BD56F-7D1D-408F-BEDC-6BB9854C71A1}" name="Epic Link" dataDxfId="43"/>
-    <tableColumn id="33" xr3:uid="{3A94D4B2-1A5B-4BBF-B398-E56D2BB7F948}" name="Epic Name" dataDxfId="42">
+    <tableColumn id="10" xr3:uid="{70B7C471-B624-430B-8992-4711F27BB17E}" name="Issue ID" dataDxfId="41"/>
+    <tableColumn id="30" xr3:uid="{938D6CA2-8309-4146-9B62-E8CDFAB7B1C9}" name="Parent" dataDxfId="40"/>
+    <tableColumn id="11" xr3:uid="{594BD56F-7D1D-408F-BEDC-6BB9854C71A1}" name="Epic Link" dataDxfId="39"/>
+    <tableColumn id="33" xr3:uid="{3A94D4B2-1A5B-4BBF-B398-E56D2BB7F948}" name="Epic Name" dataDxfId="38">
       <calculatedColumnFormula>IF(JiraDataset[[#This Row],[IssueType]]="Epic",JiraDataset[[#This Row],[Summary]],"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="27" xr3:uid="{911C8FDC-5528-43FC-BDF4-D4761F03C0E5}" name="Child-Issue" dataDxfId="41"/>
-    <tableColumn id="41" xr3:uid="{AB248E07-9BFA-42CC-BC41-B4234F677BFB}" name="Child-Issue1" dataDxfId="40"/>
-    <tableColumn id="29" xr3:uid="{89D12135-F3E3-4253-844F-1B9A54169953}" name="Child-Issue2" dataDxfId="39"/>
-    <tableColumn id="12" xr3:uid="{0699B70E-673B-4238-8A66-12FC943A4812}" name="Labels" dataDxfId="38"/>
-    <tableColumn id="13" xr3:uid="{9840B81F-2CA6-4708-8C93-3E7C8F72A676}" name="Labels1" dataDxfId="37"/>
-    <tableColumn id="14" xr3:uid="{D4A99C0B-46B7-484A-842E-D62E9D5D9341}" name="Labels2" dataDxfId="36"/>
-    <tableColumn id="15" xr3:uid="{1D1C275E-5C65-4393-9663-6C5F617591E1}" name="Labels3" dataDxfId="35"/>
-    <tableColumn id="16" xr3:uid="{D823FA91-7106-42D3-9DBC-B337C509EB09}" name="Labels4" dataDxfId="34"/>
-    <tableColumn id="17" xr3:uid="{05A07F85-1763-4A66-9CBB-4A760BD03D27}" name="Labels5" dataDxfId="33"/>
-    <tableColumn id="18" xr3:uid="{16B98070-7F8A-4FC7-AD99-EA81D0BD26AB}" name="Labels6" dataDxfId="32"/>
-    <tableColumn id="19" xr3:uid="{016EAEF4-8EA9-408B-9F1A-ECFB17E81C77}" name="Labels7" dataDxfId="31"/>
-    <tableColumn id="26" xr3:uid="{8263F9EC-BF0A-46F7-BA83-6083A4262B91}" name="Labels8" dataDxfId="30"/>
-    <tableColumn id="20" xr3:uid="{389B11C5-1B22-48C0-BCA2-72F050425FA1}" name="Labels9" dataDxfId="29"/>
-    <tableColumn id="25" xr3:uid="{AE95F8A2-F7F0-4985-9AE6-4201B9792775}" name="Labels10" dataDxfId="28"/>
-    <tableColumn id="21" xr3:uid="{105F2D0F-70C1-4517-A55F-4C1DDFE85301}" name="Sprint" dataDxfId="27">
-      <calculatedColumnFormula>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",IFERROR(VLOOKUP(JiraDataset[[#This Row],[Sprint Name]], 'Config - Mappings'!$G$4:$H$8, 2, FALSE), ""))</calculatedColumnFormula>
+    <tableColumn id="12" xr3:uid="{0699B70E-673B-4238-8A66-12FC943A4812}" name="Labels" dataDxfId="37"/>
+    <tableColumn id="13" xr3:uid="{9840B81F-2CA6-4708-8C93-3E7C8F72A676}" name="Labels1" dataDxfId="36"/>
+    <tableColumn id="14" xr3:uid="{D4A99C0B-46B7-484A-842E-D62E9D5D9341}" name="Labels2" dataDxfId="35"/>
+    <tableColumn id="15" xr3:uid="{1D1C275E-5C65-4393-9663-6C5F617591E1}" name="Labels3" dataDxfId="34"/>
+    <tableColumn id="16" xr3:uid="{D823FA91-7106-42D3-9DBC-B337C509EB09}" name="Labels4" dataDxfId="33"/>
+    <tableColumn id="17" xr3:uid="{05A07F85-1763-4A66-9CBB-4A760BD03D27}" name="Labels5" dataDxfId="32"/>
+    <tableColumn id="21" xr3:uid="{105F2D0F-70C1-4517-A55F-4C1DDFE85301}" name="Sprint" dataDxfId="22">
+      <calculatedColumnFormula>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",IFERROR(VLOOKUP(JiraDataset[[#This Row],[Sprint Name]], CfgSprints[], 2, FALSE), ""))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{D5984986-D838-4F87-A554-5DC4CA005452}" name="Labels0001" dataDxfId="26">
+    <tableColumn id="22" xr3:uid="{D5984986-D838-4F87-A554-5DC4CA005452}" name="Labels0001" dataDxfId="31">
       <calculatedColumnFormula>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",_xlfn.XLOOKUP("Creation Marker", CfgMisc[Name], CfgMisc[Value],"",1))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="39" xr3:uid="{C24E9ADD-96A8-4DBB-86A0-08D41975D750}" name="Labels0002" dataDxfId="25">
+    <tableColumn id="39" xr3:uid="{C24E9ADD-96A8-4DBB-86A0-08D41975D750}" name="Labels0002" dataDxfId="30">
       <calculatedColumnFormula>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",_xlfn.XLOOKUP("Work Group", CfgMisc[Name], CfgMisc[Value],"",1))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{A6D8D5A6-43EE-415C-80C1-30372C7FE5BF}" name="Assignee" dataDxfId="24">
-      <calculatedColumnFormula>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",IFERROR(VLOOKUP(JiraDataset[[#This Row],[Assignee.Name]], 'Config - Mappings'!$A$4:$B$26, 2, FALSE), ""))</calculatedColumnFormula>
+    <tableColumn id="6" xr3:uid="{A6D8D5A6-43EE-415C-80C1-30372C7FE5BF}" name="Assignee" dataDxfId="21">
+      <calculatedColumnFormula>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",IFERROR(VLOOKUP(JiraDataset[[#This Row],[Assignee.Name]], CfgAssignees[], 2, FALSE), ""))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="23" xr3:uid="{51D4B5F4-C6D3-4EEC-8B1B-7BEC6E526A64}" name="Project Key" dataDxfId="23">
+    <tableColumn id="32" xr3:uid="{B9236297-6F08-4471-BC00-A337F6321979}" name="Team" dataDxfId="19">
+      <calculatedColumnFormula>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",IFERROR(VLOOKUP(JiraDataset[[#This Row],[Team.Name]], CfgTeams[], 2, FALSE), ""))</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="23" xr3:uid="{51D4B5F4-C6D3-4EEC-8B1B-7BEC6E526A64}" name="Project Key" dataDxfId="29">
       <calculatedColumnFormula>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",_xlfn.XLOOKUP("jira.project.key", CfgBasic[Name], CfgBasic[Value]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="42" xr3:uid="{82B78F0D-CAEF-4615-B12A-B15ACF33913C}" name="OrigEst" dataDxfId="22">
+    <tableColumn id="42" xr3:uid="{82B78F0D-CAEF-4615-B12A-B15ACF33913C}" name="OrigEst" dataDxfId="28">
       <calculatedColumnFormula array="1">IF(
   JiraDataset[[#This Row],[RowType]]=cfg_type_skip,
   "",
@@ -2318,7 +2334,7 @@
   )
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="44" xr3:uid="{C92FD7EC-0EAB-4967-A0E5-D2427E3A55B4}" name="RowType" dataDxfId="21">
+    <tableColumn id="44" xr3:uid="{C92FD7EC-0EAB-4967-A0E5-D2427E3A55B4}" name="RowType" dataDxfId="27">
       <calculatedColumnFormula array="1">IFERROR(
     _xlfn.IFS(
         JiraDataset[[#This Row],[IssueType]] = cfg_type_comment,"SKIP",
@@ -2328,7 +2344,7 @@
     cfg_type_workitem
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="24" xr3:uid="{B63E8FC4-20B3-4755-92F2-EA1F700CA72E}" name="Note" dataDxfId="20"/>
+    <tableColumn id="24" xr3:uid="{B63E8FC4-20B3-4755-92F2-EA1F700CA72E}" name="Note" dataDxfId="26"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2338,15 +2354,15 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{A6C0EE44-3F60-4588-BF11-75C3DD021846}" name="CfgPriorities" displayName="CfgPriorities" ref="L22:L28" totalsRowShown="0">
   <autoFilter ref="L22:L28" xr:uid="{A6C0EE44-3F60-4588-BF11-75C3DD021846}"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{3B3BE2ED-38C4-410B-B0BF-4A9BD9B4B974}" name="Priority.Name" dataDxfId="17"/>
+    <tableColumn id="1" xr3:uid="{3B3BE2ED-38C4-410B-B0BF-4A9BD9B4B974}" name="Priority.Name" dataDxfId="51"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium5" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{DE352608-207B-4EFC-9BD3-2BD6976D373F}" name="CfgTeams" displayName="CfgTeams" ref="D3:E9" totalsRowShown="0">
-  <autoFilter ref="D3:E9" xr:uid="{DE352608-207B-4EFC-9BD3-2BD6976D373F}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{DE352608-207B-4EFC-9BD3-2BD6976D373F}" name="CfgTeams" displayName="CfgTeams" ref="D3:E8" totalsRowShown="0">
+  <autoFilter ref="D3:E8" xr:uid="{DE352608-207B-4EFC-9BD3-2BD6976D373F}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{59E7B951-2640-4BEF-926D-11574E54F447}" name="Team.Name"/>
     <tableColumn id="2" xr3:uid="{1C40E406-7D3C-45A3-AAA3-B5BBB7E9C3AA}" name="Team.ID"/>
@@ -2356,8 +2372,8 @@
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{71F57F46-4709-4A78-8D88-CD75C743FE14}" name="CfgCustomFields" displayName="CfgCustomFields" ref="E3:H4" insertRow="1" totalsRowShown="0">
-  <autoFilter ref="E3:H4" xr:uid="{71F57F46-4709-4A78-8D88-CD75C743FE14}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{71F57F46-4709-4A78-8D88-CD75C743FE14}" name="CfgCustomFields" displayName="CfgCustomFields" ref="E3:H7" totalsRowShown="0">
+  <autoFilter ref="E3:H7" xr:uid="{71F57F46-4709-4A78-8D88-CD75C743FE14}"/>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{4E62A8D1-901A-4C3B-920B-726A6F2C172C}" name="Name"/>
     <tableColumn id="2" xr3:uid="{F3AA6FE2-2D0B-4D90-9B62-6DA6E107F572}" name="Id"/>
@@ -2374,7 +2390,7 @@
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{724752C0-2EB0-4307-9766-E95D142383BC}" name="Name"/>
     <tableColumn id="2" xr3:uid="{1B4D7FE1-60C9-4319-8B9F-E66C19764AEE}" name="Value"/>
-    <tableColumn id="3" xr3:uid="{F0634D25-384E-480B-B675-9F8463C0D844}" name="Note" dataDxfId="16"/>
+    <tableColumn id="3" xr3:uid="{F0634D25-384E-480B-B675-9F8463C0D844}" name="Note" dataDxfId="23"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium5" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2430,7 +2446,7 @@
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{D4E1611F-A2CF-465D-A219-1759EA66687D}" name="Name"/>
     <tableColumn id="2" xr3:uid="{174D0D86-B1AA-4BF7-AC91-FCACFC898851}" name="Value"/>
-    <tableColumn id="3" xr3:uid="{4D0493E3-2ED0-412B-9468-835FC91C2910}" name="Note" dataDxfId="19"/>
+    <tableColumn id="3" xr3:uid="{4D0493E3-2ED0-412B-9468-835FC91C2910}" name="Note" dataDxfId="25"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium5" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2442,7 +2458,7 @@
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{19232286-858A-4316-B524-2259E904D535}" name="Name"/>
     <tableColumn id="2" xr3:uid="{E6137B31-22A5-4579-8A81-0FBB4015A668}" name="Value"/>
-    <tableColumn id="3" xr3:uid="{03DA91C8-48E1-4BFC-B993-8C1071BAA534}" name="Note" dataDxfId="18"/>
+    <tableColumn id="3" xr3:uid="{03DA91C8-48E1-4BFC-B993-8C1071BAA534}" name="Note" dataDxfId="24"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium5" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2821,39 +2837,38 @@
   <sheetPr>
     <tabColor theme="4"/>
   </sheetPr>
-  <dimension ref="A1:AL3"/>
+  <dimension ref="A1:AP3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelCol="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="12.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="31.7109375" customWidth="1"/>
     <col min="4" max="4" width="26.42578125" hidden="1" customWidth="1"/>
     <col min="5" max="5" width="39.42578125" customWidth="1"/>
-    <col min="6" max="6" width="14.28515625" customWidth="1"/>
-    <col min="7" max="7" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="22.5703125" customWidth="1"/>
-    <col min="9" max="9" width="16.42578125" customWidth="1"/>
-    <col min="10" max="11" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="8" width="20" customWidth="1"/>
+    <col min="9" max="9" width="22.5703125" customWidth="1"/>
+    <col min="10" max="10" width="16.42578125" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="14.28515625" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" customWidth="1"/>
-    <col min="14" max="14" width="14.28515625" customWidth="1"/>
-    <col min="15" max="15" width="0" hidden="1" customWidth="1"/>
-    <col min="16" max="16" width="22.28515625" hidden="1" customWidth="1"/>
-    <col min="17" max="17" width="12.85546875" hidden="1" customWidth="1"/>
-    <col min="18" max="24" width="14.28515625" customWidth="1"/>
-    <col min="25" max="28" width="14.28515625" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="29" max="30" width="10" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="31" max="31" width="10" customWidth="1" collapsed="1"/>
-    <col min="32" max="32" width="28.140625" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="33" max="33" width="15.85546875" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="34" max="34" width="14" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="35" max="35" width="12.5703125" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="36" max="37" width="13.7109375" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="38" max="38" width="36.5703125" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="40" max="40" width="18.7109375" customWidth="1"/>
-    <col min="41" max="41" width="87.28515625" customWidth="1"/>
+    <col min="13" max="13" width="13.140625" customWidth="1"/>
+    <col min="14" max="14" width="13.140625" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="15" max="15" width="14.42578125" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="16" max="16" width="14.28515625" customWidth="1" collapsed="1"/>
+    <col min="17" max="21" width="14.28515625" customWidth="1"/>
+    <col min="22" max="22" width="14.28515625" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="23" max="24" width="13.140625" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="25" max="26" width="28.140625" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="27" max="27" width="13.42578125" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="28" max="29" width="28.140625" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="30" max="30" width="21.140625" customWidth="1" collapsed="1"/>
+    <col min="31" max="31" width="14" customWidth="1"/>
+    <col min="32" max="32" width="12.5703125" customWidth="1"/>
+    <col min="33" max="34" width="13.7109375" customWidth="1"/>
+    <col min="35" max="35" width="36.5703125" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="18.7109375" customWidth="1"/>
+    <col min="38" max="38" width="87.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>1</v>
       </c>
@@ -2870,110 +2885,92 @@
         <v>4</v>
       </c>
       <c r="F1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
-        <v>80</v>
-      </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" t="s">
+        <v>71</v>
+      </c>
+      <c r="N1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="P1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="Q1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="R1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="S1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="S1" s="3" t="s">
+      <c r="T1" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="T1" s="3" t="s">
+      <c r="U1" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="U1" s="3" t="s">
+      <c r="V1" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="V1" s="3" t="s">
+      <c r="W1" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="W1" s="3" t="s">
+      <c r="X1" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="X1" s="3" t="s">
+      <c r="Y1" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="Y1" s="3" t="s">
+      <c r="Z1" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="AA1" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="Z1" s="3" t="s">
+      <c r="AB1" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="AA1" s="3" t="s">
+      <c r="AC1" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="AD1" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="AB1" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="AC1" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="AD1" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="AE1" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="AF1" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="AG1" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="AH1" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="AI1" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="AJ1" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="3" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="F2" s="3"/>
       <c r="G2" s="3"/>
@@ -2983,46 +2980,43 @@
       <c r="K2" s="3"/>
       <c r="L2" s="3"/>
       <c r="M2" s="3"/>
-      <c r="N2" s="3" t="str">
+      <c r="N2" s="3"/>
+      <c r="O2" s="3" t="str">
         <f>IF(JiraDataset[[#This Row],[IssueType]]="Epic",JiraDataset[[#This Row],[Summary]],"")</f>
         <v/>
       </c>
-      <c r="O2" s="3"/>
       <c r="P2" s="3"/>
       <c r="Q2" s="3"/>
       <c r="R2" s="3"/>
       <c r="S2" s="3"/>
       <c r="T2" s="3"/>
       <c r="U2" s="3"/>
-      <c r="V2" s="3"/>
-      <c r="W2" s="3"/>
-      <c r="X2" s="3"/>
-      <c r="Y2" s="3"/>
-      <c r="Z2" s="3"/>
-      <c r="AA2" s="3"/>
-      <c r="AB2" s="3"/>
-      <c r="AC2" s="3" t="str">
-        <f>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",IFERROR(VLOOKUP(JiraDataset[[#This Row],[Sprint Name]], 'Config - Mappings'!$G$4:$H$8, 2, FALSE), ""))</f>
+      <c r="V2" s="3" t="str">
+        <f>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",IFERROR(VLOOKUP(JiraDataset[[#This Row],[Sprint Name]], CfgSprints[], 2, FALSE), ""))</f>
         <v/>
       </c>
-      <c r="AD2" s="3" t="str">
+      <c r="W2" s="3" t="str">
         <f>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",_xlfn.XLOOKUP("Creation Marker", CfgMisc[Name], CfgMisc[Value],"",1))</f>
         <v/>
       </c>
-      <c r="AE2" s="3" t="str">
+      <c r="X2" s="3" t="str">
         <f>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",_xlfn.XLOOKUP("Work Group", CfgMisc[Name], CfgMisc[Value],"",1))</f>
         <v/>
       </c>
-      <c r="AF2" s="3" t="str">
-        <f>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",IFERROR(VLOOKUP(JiraDataset[[#This Row],[Assignee.Name]], 'Config - Mappings'!$A$4:$B$26, 2, FALSE), ""))</f>
+      <c r="Y2" s="3" t="str">
+        <f>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",IFERROR(VLOOKUP(JiraDataset[[#This Row],[Assignee.Name]], CfgAssignees[], 2, FALSE), ""))</f>
         <v/>
       </c>
-      <c r="AG2" s="3" t="str">
+      <c r="Z2" s="3" t="str">
+        <f>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",IFERROR(VLOOKUP(JiraDataset[[#This Row],[Team.Name]], CfgTeams[], 2, FALSE), ""))</f>
+        <v/>
+      </c>
+      <c r="AA2" s="3" t="str">
         <f>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",_xlfn.XLOOKUP("jira.project.key", CfgBasic[Name], CfgBasic[Value]))</f>
         <v/>
       </c>
-      <c r="AH2" s="3" t="str" cm="1">
-        <f t="array" ref="AH2">IF(
+      <c r="AB2" s="3" t="str" cm="1">
+        <f t="array" ref="AB2">IF(
   JiraDataset[[#This Row],[RowType]]=cfg_type_skip,
   "",
   _xlfn.LET(
@@ -3038,8 +3032,8 @@
 )</f>
         <v/>
       </c>
-      <c r="AI2" s="3" t="str" cm="1">
-        <f t="array" ref="AI2">IFERROR(
+      <c r="AC2" s="3" t="str" cm="1">
+        <f t="array" ref="AC2">IFERROR(
     _xlfn.IFS(
         JiraDataset[[#This Row],[IssueType]] = cfg_type_comment,"SKIP",
         JiraDataset[[#This Row],[IssueType]] = cfg_type_skip,"SKIP",
@@ -3049,85 +3043,86 @@
 )</f>
         <v>SKIP</v>
       </c>
-      <c r="AJ2" s="3"/>
-    </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AD2" s="3"/>
+    </row>
+    <row r="3" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3" t="str">
+      <c r="E3" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="K3" s="3" t="str">
         <f>'Config - Mappings'!$J$4</f>
         <v>JITTP Version 1</v>
       </c>
-      <c r="G3" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="K3" s="3"/>
       <c r="L3" s="3"/>
       <c r="M3" s="3"/>
-      <c r="N3" s="3" t="str">
+      <c r="N3" s="3"/>
+      <c r="O3" s="3" t="str">
         <f>IF(JiraDataset[[#This Row],[IssueType]]="Epic",JiraDataset[[#This Row],[Summary]],"")</f>
         <v>First Work Item</v>
       </c>
-      <c r="O3" s="3"/>
-      <c r="P3" s="3"/>
-      <c r="Q3" s="3"/>
+      <c r="P3" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="Q3" s="3" t="s">
+        <v>161</v>
+      </c>
       <c r="R3" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="S3" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="T3" s="3" t="s">
-        <v>171</v>
-      </c>
+        <v>162</v>
+      </c>
+      <c r="S3" s="3"/>
+      <c r="T3" s="3"/>
       <c r="U3" s="3"/>
-      <c r="V3" s="3"/>
-      <c r="W3" s="3"/>
-      <c r="X3" s="3"/>
-      <c r="Y3" s="3"/>
-      <c r="Z3" s="3"/>
-      <c r="AA3" s="3"/>
-      <c r="AB3" s="3"/>
-      <c r="AC3" s="3">
-        <f>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",IFERROR(VLOOKUP(JiraDataset[[#This Row],[Sprint Name]], 'Config - Mappings'!$G$4:$H$8, 2, FALSE), ""))</f>
+      <c r="V3" s="3">
+        <f>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",IFERROR(VLOOKUP(JiraDataset[[#This Row],[Sprint Name]], CfgSprints[], 2, FALSE), ""))</f>
         <v>97</v>
       </c>
-      <c r="AD3" s="3" t="str">
+      <c r="W3" s="3" t="str">
         <f>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",_xlfn.XLOOKUP("Creation Marker", CfgMisc[Name], CfgMisc[Value],"",1))</f>
         <v>imported</v>
       </c>
-      <c r="AE3" s="3" t="str">
+      <c r="X3" s="3" t="str">
         <f>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",_xlfn.XLOOKUP("Work Group", CfgMisc[Name], CfgMisc[Value],"",1))</f>
         <v>pod_test</v>
       </c>
-      <c r="AF3" s="3" t="str">
-        <f>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",IFERROR(VLOOKUP(JiraDataset[[#This Row],[Assignee.Name]], 'Config - Mappings'!$A$4:$B$26, 2, FALSE), ""))</f>
+      <c r="Y3" s="3" t="str">
+        <f>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",IFERROR(VLOOKUP(JiraDataset[[#This Row],[Assignee.Name]], CfgAssignees[], 2, FALSE), ""))</f>
         <v>712020:09876543212345678901</v>
       </c>
-      <c r="AG3" s="3" t="str">
+      <c r="Z3" s="3" t="str">
+        <f>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",IFERROR(VLOOKUP(JiraDataset[[#This Row],[Team.Name]], CfgTeams[], 2, FALSE), ""))</f>
+        <v>712020:09876543212345678902</v>
+      </c>
+      <c r="AA3" s="3" t="str">
         <f>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",_xlfn.XLOOKUP("jira.project.key", CfgBasic[Name], CfgBasic[Value]))</f>
         <v>JITTP2</v>
       </c>
-      <c r="AH3" s="3" cm="1">
-        <f t="array" ref="AH3">IF(
+      <c r="AB3" s="3" cm="1">
+        <f t="array" ref="AB3">IF(
   JiraDataset[[#This Row],[RowType]]=cfg_type_skip,
   "",
   _xlfn.LET(
@@ -3143,8 +3138,8 @@
 )</f>
         <v>12744000</v>
       </c>
-      <c r="AI3" s="3" t="str" cm="1">
-        <f t="array" ref="AI3">IFERROR(
+      <c r="AC3" s="3" t="str" cm="1">
+        <f t="array" ref="AC3">IFERROR(
     _xlfn.IFS(
         JiraDataset[[#This Row],[IssueType]] = cfg_type_comment,"SKIP",
         JiraDataset[[#This Row],[IssueType]] = cfg_type_skip,"SKIP",
@@ -3154,12 +3149,12 @@
 )</f>
         <v>WorkItem</v>
       </c>
-      <c r="AJ3" s="3"/>
+      <c r="AD3" s="3"/>
     </row>
   </sheetData>
   <protectedRanges>
-    <protectedRange sqref="C1:AB2 A1:A1048576 P3:AD1048576 D3:N1048576" name="User Input"/>
-    <protectedRange algorithmName="SHA-512" hashValue="tpheD+JLADkhiyalt6vInlMwkILPZx4PVQN/k2vmwjOBdYUuHaXCrwtObHeFz5dJh9f853O84pZ1Rn9Ujz33+A==" saltValue="9ir5NB4CJc/69S/Eh84/mA==" spinCount="100000" sqref="AC1:AI2 AE3:AK1048576" name="Computed values"/>
+    <protectedRange sqref="A1:A1048576 L4:L1048576 C1:E2 D3:E1048576 F1:J3 G4:J1048576 K1:U2 Q4:Z1048576 K3:W3 N4:O1048576" name="User Input"/>
+    <protectedRange algorithmName="SHA-512" hashValue="tpheD+JLADkhiyalt6vInlMwkILPZx4PVQN/k2vmwjOBdYUuHaXCrwtObHeFz5dJh9f853O84pZ1Rn9Ujz33+A==" saltValue="9ir5NB4CJc/69S/Eh84/mA==" spinCount="100000" sqref="V1:AC2 X3:AE3 AA4:AH1048576" name="Computed values"/>
   </protectedRanges>
   <phoneticPr fontId="18" type="noConversion"/>
   <conditionalFormatting sqref="A2:A3 C2:C3">
@@ -3181,7 +3176,7 @@
       <formula>LEN(TRIM(A2))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:AJ3">
+  <conditionalFormatting sqref="A2:AD3">
     <cfRule type="expression" dxfId="10" priority="409" stopIfTrue="1">
       <formula>$B2=cfg_type_comment</formula>
     </cfRule>
@@ -3206,7 +3201,7 @@
       <formula>LEN(TRIM(B2))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:AJ3">
+  <conditionalFormatting sqref="B2:AD3">
     <cfRule type="expression" dxfId="3" priority="1">
       <formula>$B2="Epic"</formula>
     </cfRule>
@@ -3219,61 +3214,59 @@
       <formula>LEN(TRIM(C2))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:L3">
+  <conditionalFormatting sqref="L2:M3">
     <cfRule type="containsBlanks" dxfId="0" priority="412">
-      <formula>LEN(TRIM(K2))=0</formula>
+      <formula>LEN(TRIM(L2))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations xWindow="1573" yWindow="665" count="23">
-    <dataValidation type="whole" allowBlank="1" showErrorMessage="1" prompt="It must be a number (integer). This reference is only used during the import process." sqref="K2:L2" xr:uid="{005E18F2-4447-4781-8F18-5A58920A4F75}">
+  <dataValidations xWindow="1573" yWindow="665" count="22">
+    <dataValidation type="whole" allowBlank="1" showErrorMessage="1" prompt="It must be a number (integer). This reference is only used during the import process." sqref="L2:M2" xr:uid="{005E18F2-4447-4781-8F18-5A58920A4F75}">
       <formula1>1</formula1>
       <formula2>1000</formula2>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="It must be a number (integer). This reference is only used during the import process." sqref="K1" xr:uid="{9C637146-F2E3-4D08-87A8-F70FD358E47E}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Use the Issue ID value to link this work item to an Epic_x000a__x000a_Story Issues are not Child-Issues and should have Epic Link instead. " sqref="M1" xr:uid="{A61138FD-C2B2-49D2-810B-69EAE2230B73}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="This field should be the Issue ID or Issue Key of the child tasks. (upstream linkage is not possible)._x000a__x000a__x000a_To link Epics and Stories, use the Epic Link from the Story Issue." sqref="O1:Q1" xr:uid="{BE6B7503-A11A-4130-9D63-988F0CFED80E}"/>
-    <dataValidation allowBlank="1" showErrorMessage="1" promptTitle="Warning" prompt="Field only used for Epic Issues, so they can be referenced in Story Issues via the Epic Link field.," sqref="L2 N2" xr:uid="{541AD292-0123-4B65-9663-081991FDF0C1}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Field only used for Epic Issues, so they can be referenced in Story Issues via the Epic Link field.," sqref="L1" xr:uid="{64C73155-DEE7-497D-8A98-01E54655ACA8}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="It must be a number (integer) or the Work Item key. This reference is only used during the import process to set the parent." sqref="L1" xr:uid="{8A2BE248-5762-43AD-9C47-C5A92A2E2357}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Field only used for Epic work item, so they can be referenced in Story work items via the Epic Link field. _x000a_DC Only" sqref="N1" xr:uid="{E8F6E005-1F9B-40F3-B24C-E2A3D286C532}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" error="must be a valid component" sqref="J2:J3" xr:uid="{386E3B68-2486-4DDE-BEB1-45F897521149}"/>
-    <dataValidation type="whole" allowBlank="1" showErrorMessage="1" promptTitle="Warning" prompt="This field should be the Issue ID or Issue Key of the child tasks. (upstream linkage is not possible)._x000a__x000a__x000a_To link Epics and Stories, use the Epic Link from the Story Issue." sqref="O2:Q3" xr:uid="{D7BD960D-9CEA-4120-B2E3-2AE0D4661093}">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="It must be a number (integer). This reference is only used during the import process." sqref="L1" xr:uid="{9C637146-F2E3-4D08-87A8-F70FD358E47E}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Use the Issue ID value to link this work item to an Epic_x000a__x000a_Story Issues are not Child-Issues and should have Epic Link instead. " sqref="N1" xr:uid="{A61138FD-C2B2-49D2-810B-69EAE2230B73}"/>
+    <dataValidation allowBlank="1" showErrorMessage="1" promptTitle="Warning" prompt="Field only used for Epic Issues, so they can be referenced in Story Issues via the Epic Link field.," sqref="M2 O2" xr:uid="{541AD292-0123-4B65-9663-081991FDF0C1}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Field only used for Epic Issues, so they can be referenced in Story Issues via the Epic Link field.," sqref="M1" xr:uid="{64C73155-DEE7-497D-8A98-01E54655ACA8}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="It must be a number (integer) or the Work Item key. This reference is only used during the import process to set the parent." sqref="M1" xr:uid="{8A2BE248-5762-43AD-9C47-C5A92A2E2357}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Field only used for Epic work item, so they can be referenced in Story work items via the Epic Link field. _x000a_DC Only, this field is ignored when importing in Jira Cloud" sqref="O1" xr:uid="{E8F6E005-1F9B-40F3-B24C-E2A3D286C532}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" error="must be a valid component" sqref="I2:I3" xr:uid="{386E3B68-2486-4DDE-BEB1-45F897521149}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Note" prompt="The content of this column will be ignored during the Jira import." sqref="AD2:AD3" xr:uid="{2DA3EDB6-7635-4349-8860-B614B5B71275}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Permissions" prompt="Updating Existing Issues requires global admin permissions" sqref="D2:D3" xr:uid="{D5E4A4BB-53C8-42DF-9B52-F5E00AC6407B}"/>
+    <dataValidation type="whole" allowBlank="1" showErrorMessage="1" promptTitle="Warning" prompt="Use the Issue ID value to link this work item to an Epic_x000a__x000a_Story Issues are not Child-Issues and should have Epic Link instead. " sqref="N2:N3" xr:uid="{16C14239-D6AA-4935-8809-57760481D8F1}">
       <formula1>1</formula1>
       <formula2>1000</formula2>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Note" prompt="The content of this column will be ignored during the Jira import." sqref="AJ2:AJ3" xr:uid="{2DA3EDB6-7635-4349-8860-B614B5B71275}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Permissions" prompt="Updating Existing Issues requires global admin permissions" sqref="D2:D3" xr:uid="{D5E4A4BB-53C8-42DF-9B52-F5E00AC6407B}"/>
-    <dataValidation type="whole" allowBlank="1" showErrorMessage="1" promptTitle="Warning" prompt="Use the Issue ID value to link this work item to an Epic_x000a__x000a_Story Issues are not Child-Issues and should have Epic Link instead. " sqref="M2:M3" xr:uid="{16C14239-D6AA-4935-8809-57760481D8F1}">
-      <formula1>1</formula1>
-      <formula2>1000</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" error="must be a valid fixversion" promptTitle="AUTOMATIC FIELD" prompt="Do not manually edit these!" sqref="AC2:AC3 AF1:AH3" xr:uid="{893DA5FE-9FD0-4D28-BBD0-3D7AEDECEACB}"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="must be a valid component" sqref="H2:H3" xr:uid="{65EDED96-6789-400B-B504-6BC3F5A79E70}">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" error="must be a valid fixversion" promptTitle="AUTOMATIC FIELD" prompt="Do not manually edit these!" sqref="V2:V3 Y1:AB3" xr:uid="{893DA5FE-9FD0-4D28-BBD0-3D7AEDECEACB}"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="must be a valid component" sqref="G2:G3" xr:uid="{65EDED96-6789-400B-B504-6BC3F5A79E70}">
       <formula1>INDIRECT("CfgComponents[Component.Name]")</formula1>
     </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" error="must be a valid fixversion" sqref="G2:G3" xr:uid="{44FDC20A-8BF5-49B5-9D2C-3A1FE5A7D835}">
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" error="must be a valid fixversion" sqref="F2:F3" xr:uid="{44FDC20A-8BF5-49B5-9D2C-3A1FE5A7D835}">
       <formula1>INDIRECT("CfgAssignees[Assignee.Name]")</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="must be a valid component" sqref="I2:I3" xr:uid="{A898E2E7-BC45-4B88-BA1E-4AAA377361D4}">
-      <formula1>INDIRECT("CfgSprints[Sprint.Name]")</formula1>
-    </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" error="must be a valid fixversion" promptTitle="Creation Marker (Config Sheet)" prompt="Do not manually edit these!" sqref="AD1:AD3 AE2:AE3" xr:uid="{412C516D-E091-4DDD-9C14-C33AC653C143}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" error="must be a valid fixversion" promptTitle="Feature Pod Label (Config Sheet)" prompt="Do not manually edit these!" sqref="AE1" xr:uid="{D2234141-379F-4413-AB08-6835BD9FF967}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" error="must be a valid fixversion" promptTitle="AUTOMATIC FIELD" prompt="Do not manually edit these! SKIP types won't be imported into Jira" sqref="AI1:AI3" xr:uid="{5A336857-7D14-4900-8734-BED680BE5154}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" error="must be a valid fixversion" promptTitle="Creation Marker (Config Sheet)" prompt="Do not manually edit these!" sqref="W1:W3 X2:X3" xr:uid="{412C516D-E091-4DDD-9C14-C33AC653C143}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" error="must be a valid fixversion" promptTitle="Feature Pod Label (Config Sheet)" prompt="Do not manually edit these!" sqref="X1" xr:uid="{D2234141-379F-4413-AB08-6835BD9FF967}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" error="must be a valid fixversion" promptTitle="AUTOMATIC FIELD" prompt="Do not manually edit these! SKIP types won't be imported into Jira" sqref="AC1:AC3" xr:uid="{5A336857-7D14-4900-8734-BED680BE5154}"/>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Issue Type" sqref="B2:B3" xr:uid="{28BF52BF-C0B0-4D22-B02F-F1408D5A055B}">
       <formula1>INDIRECT("CfgIssueTypeList")</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="must be a valid fixversion" sqref="F2:F3" xr:uid="{7708D6E2-1D6B-41D8-A9EE-0E87219BA8EA}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="must be a valid fixversion" sqref="K2:K3" xr:uid="{7708D6E2-1D6B-41D8-A9EE-0E87219BA8EA}">
       <formula1>INDIRECT("CfgFixVersions[FixVersion.Name]")</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A3" xr:uid="{5EEBB8D5-878D-4D0E-9267-0919B5A1B925}">
       <formula1>INDIRECT("CfgPriorities[Priority.Name]")</formula1>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="must be a valid component" sqref="H2:I3" xr:uid="{A5F34B19-946D-4921-8173-A4364233D328}">
+      <formula1>INDIRECT("CfgTeams[Team.Name]")</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="must be a valid component" sqref="J2:K3" xr:uid="{A898E2E7-BC45-4B88-BA1E-4AAA377361D4}">
+      <formula1>INDIRECT("CfgSprints[Sprint.Name]")</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="F2" calculatedColumn="1"/>
+    <ignoredError sqref="K2" calculatedColumn="1"/>
   </ignoredErrors>
   <legacyDrawing r:id="rId2"/>
   <tableParts count="1">
@@ -3296,7 +3289,7 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -3304,40 +3297,40 @@
         <v>5</v>
       </c>
       <c r="E3" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="D4" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="B5" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="E5" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="B6">
         <v>1</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -3345,13 +3338,13 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="15" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="B7">
         <v>1</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -3359,13 +3352,13 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="16" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="B8">
         <v>1</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -3373,13 +3366,13 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="B9">
         <v>1</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -3387,13 +3380,13 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="15" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="B10">
         <v>1</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="E10">
         <v>2</v>
@@ -3401,7 +3394,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="16" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="B11">
         <v>1</v>
@@ -3409,7 +3402,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="14" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="B12">
         <v>2</v>
@@ -3435,14 +3428,14 @@
   <sheetData>
     <row r="1" spans="1:3" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="18" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="B2" s="17"/>
       <c r="C2" t="str">
@@ -3452,47 +3445,47 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="B3" s="17"/>
       <c r="C3" s="12" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="B4" s="17"/>
       <c r="C4" s="12" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="B5" s="17"/>
       <c r="C5" s="12" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="B6" s="17"/>
       <c r="C6" s="12" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="B7" s="17"/>
       <c r="C7" s="12" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -3501,19 +3494,19 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="B9" s="17">
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B10" s="17"/>
       <c r="C10" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -3521,13 +3514,13 @@
         <v>2</v>
       </c>
       <c r="C11" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B12" s="17"/>
       <c r="C12" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -3547,17 +3540,17 @@
     </row>
     <row r="19" spans="1:3" ht="21" x14ac:dyDescent="0.35">
       <c r="A19" s="18" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="B19" s="18"/>
       <c r="C19" s="18"/>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="B21" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="C21" t="s">
         <v>4</v>
@@ -3565,13 +3558,13 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -3580,21 +3573,21 @@
         <v>CfgBasic</v>
       </c>
       <c r="B23" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="C23" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -3603,10 +3596,10 @@
         <v>CfgAssignees</v>
       </c>
       <c r="B25" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="C25" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -3615,10 +3608,10 @@
         <v>CfgSprints</v>
       </c>
       <c r="B26" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="C26" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -3627,10 +3620,10 @@
         <v>CfgFixVersions</v>
       </c>
       <c r="B27" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="C27" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -3639,10 +3632,10 @@
         <v>CfgIssueTypes</v>
       </c>
       <c r="B28" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="C28" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -3651,10 +3644,10 @@
         <v>CfgComponents</v>
       </c>
       <c r="B29" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="C29" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
@@ -3663,21 +3656,21 @@
         <v>CfgPriorities</v>
       </c>
       <c r="B30" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="C30" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="11" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
@@ -3686,10 +3679,10 @@
         <v>CfgAdvanced</v>
       </c>
       <c r="B32" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="C32" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
@@ -3698,21 +3691,21 @@
         <v>CfgCustomFields</v>
       </c>
       <c r="B33" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="C33" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="11" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
@@ -3721,10 +3714,10 @@
         <v>CfgSettings</v>
       </c>
       <c r="B35" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="C35" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
@@ -3733,21 +3726,21 @@
         <v>CfgAutofieldValues</v>
       </c>
       <c r="B36" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="C36" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="B37" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="C37" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
@@ -3756,15 +3749,15 @@
         <v>cfg_type_note</v>
       </c>
       <c r="B38" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="C38" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C45" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
     </row>
   </sheetData>
@@ -3804,105 +3797,105 @@
   <sheetData>
     <row r="1" spans="1:7" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="18" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
       <c r="E1" s="18" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="F1" s="18"/>
       <c r="G1" s="18"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="19" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="B2" s="19"/>
       <c r="C2" s="8"/>
       <c r="E2" s="19" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="F2" s="19"/>
       <c r="G2" s="19"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="B3" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="C3" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="E3" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="F3" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="G3" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="B4" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="E4" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="F4" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B5" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="E5" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="F5" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="B6" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="B7" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="C7" s="7"/>
     </row>
@@ -3942,97 +3935,99 @@
   <sheetData>
     <row r="1" spans="1:13" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="18" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="B1" s="18"/>
       <c r="D1" s="18" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="E1" s="18"/>
       <c r="G1" s="18" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="H1" s="18"/>
       <c r="J1" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="L1" s="6" t="s">
-        <v>49</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="L1" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="M1" s="18"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="19" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="B2" s="19"/>
       <c r="D2" s="19" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="E2" s="19"/>
       <c r="G2" s="19" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="H2" s="19"/>
       <c r="J2" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="L2" s="9" t="s">
-        <v>75</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="L2" s="19" t="s">
+        <v>185</v>
+      </c>
+      <c r="M2" s="19"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="D3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="E3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="G3" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="H3" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="J3" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="L3" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="M3" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="B4" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="D4" t="s">
-        <v>155</v>
+        <v>184</v>
       </c>
       <c r="E4" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="G4" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="H4">
         <v>97</v>
       </c>
       <c r="J4" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="L4" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="M4">
         <v>3</v>
@@ -4040,19 +4035,19 @@
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="B5" t="s">
-        <v>161</v>
+        <v>152</v>
       </c>
       <c r="D5" t="s">
-        <v>156</v>
+        <v>181</v>
       </c>
       <c r="E5" t="s">
-        <v>161</v>
+        <v>152</v>
       </c>
       <c r="L5" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="M5">
         <v>3</v>
@@ -4060,21 +4055,21 @@
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="B6" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="D6" t="s">
-        <v>157</v>
+        <v>182</v>
       </c>
       <c r="E6" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
       <c r="L6" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="M6">
         <v>3</v>
@@ -4082,21 +4077,21 @@
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="B7" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="D7" t="s">
-        <v>158</v>
+        <v>183</v>
       </c>
       <c r="E7" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
       <c r="L7" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="M7">
         <v>2</v>
@@ -4104,21 +4099,15 @@
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="B8" t="s">
-        <v>164</v>
-      </c>
-      <c r="D8" t="s">
-        <v>159</v>
-      </c>
-      <c r="E8" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
       <c r="L8" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="M8">
         <v>4</v>
@@ -4172,83 +4161,85 @@
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
       <c r="J20" s="6" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="L20" s="6" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
     </row>
     <row r="21" spans="7:12" x14ac:dyDescent="0.25">
       <c r="J21" s="9" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="L21" s="9" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
     </row>
     <row r="22" spans="7:12" x14ac:dyDescent="0.25">
       <c r="J22" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="L22" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
     </row>
     <row r="23" spans="7:12" x14ac:dyDescent="0.25">
       <c r="J23" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
     </row>
     <row r="24" spans="7:12" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
     </row>
     <row r="25" spans="7:12" x14ac:dyDescent="0.25">
       <c r="J25" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
     </row>
     <row r="26" spans="7:12" x14ac:dyDescent="0.25">
       <c r="J26" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
     </row>
     <row r="27" spans="7:12" x14ac:dyDescent="0.25">
       <c r="J27" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
     </row>
     <row r="28" spans="7:12" x14ac:dyDescent="0.25">
       <c r="J28" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
     </row>
     <row r="29" spans="7:12" x14ac:dyDescent="0.25">
       <c r="J29" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="8">
+    <mergeCell ref="L1:M1"/>
+    <mergeCell ref="L2:M2"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="G1:H1"/>
@@ -4274,7 +4265,7 @@
   <sheetPr>
     <tabColor theme="5" tint="0.39997558519241921"/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="44.7109375" customWidth="1"/>
@@ -4285,12 +4276,12 @@
   <sheetData>
     <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="18" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
       <c r="E1" s="18" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="F1" s="18"/>
       <c r="G1" s="18"/>
@@ -4300,61 +4291,104 @@
       <c r="A2" s="19"/>
       <c r="B2" s="19"/>
       <c r="C2" s="8"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
+      <c r="E2" s="21" t="s">
+        <v>198</v>
+      </c>
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
+      <c r="H2" s="21"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="B3" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="C3" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="E3" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="F3" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="G3" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="H3" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="B4" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>98</v>
+        <v>89</v>
+      </c>
+      <c r="E4" t="s">
+        <v>186</v>
+      </c>
+      <c r="F4" t="s">
+        <v>187</v>
+      </c>
+      <c r="G4" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="B5" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>146</v>
+        <v>137</v>
+      </c>
+      <c r="E5" t="s">
+        <v>189</v>
+      </c>
+      <c r="F5" t="s">
+        <v>190</v>
+      </c>
+      <c r="G5" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E6" t="s">
+        <v>192</v>
+      </c>
+      <c r="F6" t="s">
+        <v>193</v>
+      </c>
+      <c r="G6" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E7" t="s">
+        <v>195</v>
+      </c>
+      <c r="F7" t="s">
+        <v>196</v>
+      </c>
+      <c r="G7" t="s">
+        <v>197</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="E1:H1"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A2:B2"/>
+    <mergeCell ref="E2:H2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="2">
@@ -4381,46 +4415,46 @@
   <sheetData>
     <row r="1" spans="1:9" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="C1" s="18" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="D1" s="18"/>
       <c r="F1" s="18" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="G1" s="18"/>
       <c r="I1" s="6" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="I2" s="8" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="C3" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="D3" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="F3" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="G3" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="I3" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -4429,13 +4463,13 @@
         <v>Story</v>
       </c>
       <c r="C4" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="D4">
         <v>8</v>
       </c>
       <c r="I4" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -4444,14 +4478,14 @@
         <v>Task</v>
       </c>
       <c r="C5" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="D5" t="str" cm="1">
         <f t="array" aca="1" ref="D5" ca="1">"[" &amp; _xlfn.TEXTJOIN(",",TRUE,_xlfn.MAP(_xlfn._xlws.FILTER(INDIRECT("CfgIgnoreList[IgnoreList.Name]"),INDIRECT("CfgIgnoreList[IgnoreList.Name]")&lt;&gt;""),_xlfn.LAMBDA(_xlpm.x,"""" &amp; SUBSTITUTE(_xlpm.x,"""","""""") &amp; """"))) &amp; "]"</f>
         <v>["Comment","Skip","Note","WorkItem"]</v>
       </c>
       <c r="I5" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
@@ -4460,7 +4494,7 @@
         <v>Bug</v>
       </c>
       <c r="I6" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
@@ -4469,7 +4503,7 @@
         <v>Epic</v>
       </c>
       <c r="I7" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
@@ -4504,7 +4538,7 @@
     </row>
     <row r="13" spans="1:9" ht="21" x14ac:dyDescent="0.35">
       <c r="C13" s="18" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="D13" s="18"/>
       <c r="E13" s="18"/>
@@ -4513,7 +4547,7 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C14" s="20" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="D14" s="20"/>
       <c r="E14" s="20"/>
@@ -4667,12 +4701,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c471fd26-9765-4fbe-b6fd-c17c1e55c974">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="9df69692-83aa-4c55-88c1-62abad05f4fe" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4905,20 +4941,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c471fd26-9765-4fbe-b6fd-c17c1e55c974">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="9df69692-83aa-4c55-88c1-62abad05f4fe" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{156C3F15-3876-4FBB-8F24-692088DE8D9F}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9FFE630F-6530-4863-AB67-8477539A0000}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="c471fd26-9765-4fbe-b6fd-c17c1e55c974"/>
+    <ds:schemaRef ds:uri="9df69692-83aa-4c55-88c1-62abad05f4fe"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -4943,12 +4980,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9FFE630F-6530-4863-AB67-8477539A0000}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{156C3F15-3876-4FBB-8F24-692088DE8D9F}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="c471fd26-9765-4fbe-b6fd-c17c1e55c974"/>
-    <ds:schemaRef ds:uri="9df69692-83aa-4c55-88c1-62abad05f4fe"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/resources/templates/ImportTemplate.xlsx
+++ b/resources/templates/ImportTemplate.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workdir\DeerHide\sources\jira-toolkit\resources\Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12369D8C-D85F-47D4-A1D7-BC151129C134}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16B68D21-5867-4D97-B166-F646694B05B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1845" yWindow="4695" windowWidth="33615" windowHeight="23445" xr2:uid="{1FA076D1-0294-4A97-AB8C-3ADE2BC9CEA1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="31920" xr2:uid="{1FA076D1-0294-4A97-AB8C-3ADE2BC9CEA1}"/>
   </bookViews>
   <sheets>
     <sheet name="Dataset" sheetId="1" r:id="rId1"/>
@@ -247,7 +247,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="200">
   <si>
     <t>IssueType</t>
   </si>
@@ -1432,11 +1432,11 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="16" applyAlignment="1">
       <alignment horizontal="left" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="16" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" shrinkToFit="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="43">
@@ -1484,7 +1484,7 @@
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="52">
+  <dxfs count="148">
     <dxf>
       <fill>
         <patternFill patternType="darkUp"/>
@@ -1628,6 +1628,925 @@
       </fill>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill patternType="darkUp"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor auto="1"/>
+          <bgColor rgb="FFFF5050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDAF2D0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF2CEEF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor auto="1"/>
+          <bgColor rgb="FFFF5050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.89996032593768116"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.34998626667073579"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor auto="1"/>
+          <bgColor rgb="FFF9B1AB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFCC99"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF99CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF6699"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="darkUp"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor auto="1"/>
+          <bgColor rgb="FFFF5050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDAF2D0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF2CEEF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor auto="1"/>
+          <bgColor rgb="FFFF5050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.89996032593768116"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.34998626667073579"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor auto="1"/>
+          <bgColor rgb="FFF9B1AB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFCC99"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF99CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF6699"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="darkUp"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor auto="1"/>
+          <bgColor rgb="FFFF5050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDAF2D0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF2CEEF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor auto="1"/>
+          <bgColor rgb="FFFF5050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.89996032593768116"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.34998626667073579"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor auto="1"/>
+          <bgColor rgb="FFF9B1AB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFCC99"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF99CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF6699"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="darkUp"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor auto="1"/>
+          <bgColor rgb="FFFF5050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDAF2D0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF2CEEF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor auto="1"/>
+          <bgColor rgb="FFFF5050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.89996032593768116"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.34998626667073579"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor auto="1"/>
+          <bgColor rgb="FFF9B1AB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFCC99"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF99CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF6699"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="darkUp"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor auto="1"/>
+          <bgColor rgb="FFFF5050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDAF2D0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF2CEEF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor auto="1"/>
+          <bgColor rgb="FFFF5050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.89996032593768116"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.34998626667073579"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor auto="1"/>
+          <bgColor rgb="FFF9B1AB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFCC99"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF99CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF6699"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="darkUp"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor auto="1"/>
+          <bgColor rgb="FFFF5050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDAF2D0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF2CEEF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor auto="1"/>
+          <bgColor rgb="FFFF5050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.89996032593768116"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.34998626667073579"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor auto="1"/>
+          <bgColor rgb="FFF9B1AB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFCC99"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF99CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF6699"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <alignment vertical="top"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment vertical="top"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment vertical="top"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment vertical="top"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment vertical="top"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment vertical="top"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment vertical="top"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top"/>
+    </dxf>
+    <dxf>
       <font>
         <b val="0"/>
       </font>
@@ -1641,83 +2560,7 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment vertical="top"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment vertical="top"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="1" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="1" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="1" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment vertical="top"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment vertical="top"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment vertical="top"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment vertical="top"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top"/>
     </dxf>
     <dxf>
       <alignment vertical="top"/>
@@ -1762,7 +2605,16 @@
       <alignment vertical="top"/>
     </dxf>
     <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="1" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="1" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="1" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2272,53 +3124,51 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{933FCFD5-1AB1-4076-B5DD-E2B69F5EB3F2}" name="JiraDataset" displayName="JiraDataset" ref="A1:AD3" totalsRowShown="0" headerRowDxfId="50" dataDxfId="49">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{933FCFD5-1AB1-4076-B5DD-E2B69F5EB3F2}" name="JiraDataset" displayName="JiraDataset" ref="A1:AD3" totalsRowShown="0" headerRowDxfId="143" dataDxfId="142">
   <autoFilter ref="A1:AD3" xr:uid="{933FCFD5-1AB1-4076-B5DD-E2B69F5EB3F2}"/>
   <tableColumns count="30">
-    <tableColumn id="3" xr3:uid="{AF2EC907-349C-4651-852D-6E39C61E17FF}" name="Priority" dataDxfId="48"/>
-    <tableColumn id="2" xr3:uid="{E90C51F2-4386-421F-A3E4-E2CA9D43D396}" name="IssueType" dataDxfId="47"/>
-    <tableColumn id="1" xr3:uid="{BBAD373B-BA13-47E4-9F74-565F4D9E9680}" name="Summary" dataDxfId="46"/>
-    <tableColumn id="4" xr3:uid="{026E5B97-FAFC-4E46-860E-0B0C976B1148}" name="Issue Key" dataDxfId="45"/>
-    <tableColumn id="5" xr3:uid="{A2C262E8-D544-4669-99F1-151EDE081654}" name="Description" dataDxfId="44"/>
-    <tableColumn id="28" xr3:uid="{07F3030C-7187-4B16-BBDB-798304851975}" name="Assignee.Name" dataDxfId="43"/>
-    <tableColumn id="8" xr3:uid="{8C7FB8DB-A85B-4189-93D8-0F0D4EEEF81B}" name="Component" dataDxfId="42"/>
-    <tableColumn id="31" xr3:uid="{BB70BDE8-70CB-404D-896E-075FB6ED93B1}" name="Team.Name" dataDxfId="20"/>
-    <tableColumn id="40" xr3:uid="{1F406792-7ED2-4476-8FF4-4C6ABA231C97}" name="Estimate" dataDxfId="17"/>
-    <tableColumn id="9" xr3:uid="{DC5101A8-1204-44D2-BC2C-FEE1A4EFE7C1}" name="Sprint Name" dataDxfId="18"/>
-    <tableColumn id="7" xr3:uid="{0FAD1ACC-432E-462C-8B89-71540710BCB5}" name="FixVersion" dataDxfId="16">
-      <calculatedColumnFormula>'Config - Mappings'!$J$4</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="10" xr3:uid="{70B7C471-B624-430B-8992-4711F27BB17E}" name="Issue ID" dataDxfId="41"/>
-    <tableColumn id="30" xr3:uid="{938D6CA2-8309-4146-9B62-E8CDFAB7B1C9}" name="Parent" dataDxfId="40"/>
-    <tableColumn id="11" xr3:uid="{594BD56F-7D1D-408F-BEDC-6BB9854C71A1}" name="Epic Link" dataDxfId="39"/>
-    <tableColumn id="33" xr3:uid="{3A94D4B2-1A5B-4BBF-B398-E56D2BB7F948}" name="Epic Name" dataDxfId="38">
+    <tableColumn id="3" xr3:uid="{AF2EC907-349C-4651-852D-6E39C61E17FF}" name="Priority" dataDxfId="141"/>
+    <tableColumn id="2" xr3:uid="{E90C51F2-4386-421F-A3E4-E2CA9D43D396}" name="IssueType" dataDxfId="140"/>
+    <tableColumn id="1" xr3:uid="{BBAD373B-BA13-47E4-9F74-565F4D9E9680}" name="Summary" dataDxfId="139"/>
+    <tableColumn id="4" xr3:uid="{026E5B97-FAFC-4E46-860E-0B0C976B1148}" name="Issue Key" dataDxfId="138"/>
+    <tableColumn id="5" xr3:uid="{A2C262E8-D544-4669-99F1-151EDE081654}" name="Description" dataDxfId="137"/>
+    <tableColumn id="28" xr3:uid="{07F3030C-7187-4B16-BBDB-798304851975}" name="Assignee.Name" dataDxfId="136"/>
+    <tableColumn id="8" xr3:uid="{8C7FB8DB-A85B-4189-93D8-0F0D4EEEF81B}" name="Component" dataDxfId="135"/>
+    <tableColumn id="31" xr3:uid="{BB70BDE8-70CB-404D-896E-075FB6ED93B1}" name="Team.Name" dataDxfId="134"/>
+    <tableColumn id="40" xr3:uid="{1F406792-7ED2-4476-8FF4-4C6ABA231C97}" name="Estimate" dataDxfId="133"/>
+    <tableColumn id="9" xr3:uid="{DC5101A8-1204-44D2-BC2C-FEE1A4EFE7C1}" name="Sprint Name" dataDxfId="132"/>
+    <tableColumn id="7" xr3:uid="{0FAD1ACC-432E-462C-8B89-71540710BCB5}" name="FixVersion" dataDxfId="131"/>
+    <tableColumn id="10" xr3:uid="{70B7C471-B624-430B-8992-4711F27BB17E}" name="Issue ID" dataDxfId="130"/>
+    <tableColumn id="30" xr3:uid="{938D6CA2-8309-4146-9B62-E8CDFAB7B1C9}" name="Parent" dataDxfId="129"/>
+    <tableColumn id="11" xr3:uid="{594BD56F-7D1D-408F-BEDC-6BB9854C71A1}" name="Epic Link" dataDxfId="128"/>
+    <tableColumn id="33" xr3:uid="{3A94D4B2-1A5B-4BBF-B398-E56D2BB7F948}" name="Epic Name" dataDxfId="127">
       <calculatedColumnFormula>IF(JiraDataset[[#This Row],[IssueType]]="Epic",JiraDataset[[#This Row],[Summary]],"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{0699B70E-673B-4238-8A66-12FC943A4812}" name="Labels" dataDxfId="37"/>
-    <tableColumn id="13" xr3:uid="{9840B81F-2CA6-4708-8C93-3E7C8F72A676}" name="Labels1" dataDxfId="36"/>
-    <tableColumn id="14" xr3:uid="{D4A99C0B-46B7-484A-842E-D62E9D5D9341}" name="Labels2" dataDxfId="35"/>
-    <tableColumn id="15" xr3:uid="{1D1C275E-5C65-4393-9663-6C5F617591E1}" name="Labels3" dataDxfId="34"/>
-    <tableColumn id="16" xr3:uid="{D823FA91-7106-42D3-9DBC-B337C509EB09}" name="Labels4" dataDxfId="33"/>
-    <tableColumn id="17" xr3:uid="{05A07F85-1763-4A66-9CBB-4A760BD03D27}" name="Labels5" dataDxfId="32"/>
-    <tableColumn id="21" xr3:uid="{105F2D0F-70C1-4517-A55F-4C1DDFE85301}" name="Sprint" dataDxfId="22">
+    <tableColumn id="12" xr3:uid="{0699B70E-673B-4238-8A66-12FC943A4812}" name="Labels" dataDxfId="126"/>
+    <tableColumn id="13" xr3:uid="{9840B81F-2CA6-4708-8C93-3E7C8F72A676}" name="Labels1" dataDxfId="125"/>
+    <tableColumn id="14" xr3:uid="{D4A99C0B-46B7-484A-842E-D62E9D5D9341}" name="Labels2" dataDxfId="124"/>
+    <tableColumn id="15" xr3:uid="{1D1C275E-5C65-4393-9663-6C5F617591E1}" name="Labels3" dataDxfId="123"/>
+    <tableColumn id="16" xr3:uid="{D823FA91-7106-42D3-9DBC-B337C509EB09}" name="Labels4" dataDxfId="122"/>
+    <tableColumn id="17" xr3:uid="{05A07F85-1763-4A66-9CBB-4A760BD03D27}" name="Labels5" dataDxfId="121"/>
+    <tableColumn id="21" xr3:uid="{105F2D0F-70C1-4517-A55F-4C1DDFE85301}" name="Sprint" dataDxfId="120">
       <calculatedColumnFormula>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",IFERROR(VLOOKUP(JiraDataset[[#This Row],[Sprint Name]], CfgSprints[], 2, FALSE), ""))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{D5984986-D838-4F87-A554-5DC4CA005452}" name="Labels0001" dataDxfId="31">
+    <tableColumn id="22" xr3:uid="{D5984986-D838-4F87-A554-5DC4CA005452}" name="Labels0001" dataDxfId="119">
       <calculatedColumnFormula>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",_xlfn.XLOOKUP("Creation Marker", CfgMisc[Name], CfgMisc[Value],"",1))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="39" xr3:uid="{C24E9ADD-96A8-4DBB-86A0-08D41975D750}" name="Labels0002" dataDxfId="30">
+    <tableColumn id="39" xr3:uid="{C24E9ADD-96A8-4DBB-86A0-08D41975D750}" name="Labels0002" dataDxfId="118">
       <calculatedColumnFormula>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",_xlfn.XLOOKUP("Work Group", CfgMisc[Name], CfgMisc[Value],"",1))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{A6D8D5A6-43EE-415C-80C1-30372C7FE5BF}" name="Assignee" dataDxfId="21">
+    <tableColumn id="6" xr3:uid="{A6D8D5A6-43EE-415C-80C1-30372C7FE5BF}" name="Assignee" dataDxfId="117">
       <calculatedColumnFormula>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",IFERROR(VLOOKUP(JiraDataset[[#This Row],[Assignee.Name]], CfgAssignees[], 2, FALSE), ""))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="32" xr3:uid="{B9236297-6F08-4471-BC00-A337F6321979}" name="Team" dataDxfId="19">
+    <tableColumn id="32" xr3:uid="{B9236297-6F08-4471-BC00-A337F6321979}" name="Team" dataDxfId="116">
       <calculatedColumnFormula>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",IFERROR(VLOOKUP(JiraDataset[[#This Row],[Team.Name]], CfgTeams[], 2, FALSE), ""))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="23" xr3:uid="{51D4B5F4-C6D3-4EEC-8B1B-7BEC6E526A64}" name="Project Key" dataDxfId="29">
+    <tableColumn id="23" xr3:uid="{51D4B5F4-C6D3-4EEC-8B1B-7BEC6E526A64}" name="Project Key" dataDxfId="115">
       <calculatedColumnFormula>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",_xlfn.XLOOKUP("jira.project.key", CfgBasic[Name], CfgBasic[Value]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="42" xr3:uid="{82B78F0D-CAEF-4615-B12A-B15ACF33913C}" name="OrigEst" dataDxfId="28">
+    <tableColumn id="42" xr3:uid="{82B78F0D-CAEF-4615-B12A-B15ACF33913C}" name="OrigEst" dataDxfId="114">
       <calculatedColumnFormula array="1">IF(
   JiraDataset[[#This Row],[RowType]]=cfg_type_skip,
   "",
@@ -2334,7 +3184,7 @@
   )
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="44" xr3:uid="{C92FD7EC-0EAB-4967-A0E5-D2427E3A55B4}" name="RowType" dataDxfId="27">
+    <tableColumn id="44" xr3:uid="{C92FD7EC-0EAB-4967-A0E5-D2427E3A55B4}" name="RowType" dataDxfId="113">
       <calculatedColumnFormula array="1">IFERROR(
     _xlfn.IFS(
         JiraDataset[[#This Row],[IssueType]] = cfg_type_comment,"SKIP",
@@ -2344,7 +3194,7 @@
     cfg_type_workitem
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="24" xr3:uid="{B63E8FC4-20B3-4755-92F2-EA1F700CA72E}" name="Note" dataDxfId="26"/>
+    <tableColumn id="24" xr3:uid="{B63E8FC4-20B3-4755-92F2-EA1F700CA72E}" name="Note" dataDxfId="112"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2354,7 +3204,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{A6C0EE44-3F60-4588-BF11-75C3DD021846}" name="CfgPriorities" displayName="CfgPriorities" ref="L22:L28" totalsRowShown="0">
   <autoFilter ref="L22:L28" xr:uid="{A6C0EE44-3F60-4588-BF11-75C3DD021846}"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{3B3BE2ED-38C4-410B-B0BF-4A9BD9B4B974}" name="Priority.Name" dataDxfId="51"/>
+    <tableColumn id="1" xr3:uid="{3B3BE2ED-38C4-410B-B0BF-4A9BD9B4B974}" name="Priority.Name" dataDxfId="145"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium5" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2390,7 +3240,7 @@
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{724752C0-2EB0-4307-9766-E95D142383BC}" name="Name"/>
     <tableColumn id="2" xr3:uid="{1B4D7FE1-60C9-4319-8B9F-E66C19764AEE}" name="Value"/>
-    <tableColumn id="3" xr3:uid="{F0634D25-384E-480B-B675-9F8463C0D844}" name="Note" dataDxfId="23"/>
+    <tableColumn id="3" xr3:uid="{F0634D25-384E-480B-B675-9F8463C0D844}" name="Note" dataDxfId="144"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium5" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2446,7 +3296,7 @@
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{D4E1611F-A2CF-465D-A219-1759EA66687D}" name="Name"/>
     <tableColumn id="2" xr3:uid="{174D0D86-B1AA-4BF7-AC91-FCACFC898851}" name="Value"/>
-    <tableColumn id="3" xr3:uid="{4D0493E3-2ED0-412B-9468-835FC91C2910}" name="Note" dataDxfId="25"/>
+    <tableColumn id="3" xr3:uid="{4D0493E3-2ED0-412B-9468-835FC91C2910}" name="Note" dataDxfId="147"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium5" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2458,7 +3308,7 @@
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{19232286-858A-4316-B524-2259E904D535}" name="Name"/>
     <tableColumn id="2" xr3:uid="{E6137B31-22A5-4579-8A81-0FBB4015A668}" name="Value"/>
-    <tableColumn id="3" xr3:uid="{03DA91C8-48E1-4BFC-B993-8C1071BAA534}" name="Note" dataDxfId="24"/>
+    <tableColumn id="3" xr3:uid="{03DA91C8-48E1-4BFC-B993-8C1071BAA534}" name="Note" dataDxfId="146"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium5" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2837,7 +3687,7 @@
   <sheetPr>
     <tabColor theme="4"/>
   </sheetPr>
-  <dimension ref="A1:AP3"/>
+  <dimension ref="A1:AD3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelCol="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="12.42578125" bestFit="1" customWidth="1"/>
@@ -2854,12 +3704,12 @@
     <col min="15" max="15" width="14.42578125" hidden="1" customWidth="1" outlineLevel="1"/>
     <col min="16" max="16" width="14.28515625" customWidth="1" collapsed="1"/>
     <col min="17" max="21" width="14.28515625" customWidth="1"/>
-    <col min="22" max="22" width="14.28515625" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="23" max="24" width="13.140625" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="25" max="26" width="28.140625" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="27" max="27" width="13.42578125" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="28" max="29" width="28.140625" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="30" max="30" width="21.140625" customWidth="1" collapsed="1"/>
+    <col min="22" max="22" width="14.28515625" customWidth="1" outlineLevel="1"/>
+    <col min="23" max="24" width="13.140625" customWidth="1" outlineLevel="1"/>
+    <col min="25" max="26" width="28.140625" customWidth="1" outlineLevel="1"/>
+    <col min="27" max="27" width="13.42578125" customWidth="1" outlineLevel="1"/>
+    <col min="28" max="29" width="28.140625" customWidth="1" outlineLevel="1"/>
+    <col min="30" max="30" width="21.140625" customWidth="1"/>
     <col min="31" max="31" width="14" customWidth="1"/>
     <col min="32" max="32" width="12.5703125" customWidth="1"/>
     <col min="33" max="34" width="13.7109375" customWidth="1"/>
@@ -3065,19 +3915,12 @@
       <c r="G3" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="H3" s="3" t="s">
-        <v>181</v>
-      </c>
+      <c r="H3" s="3"/>
       <c r="I3" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="J3" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="K3" s="3" t="str">
-        <f>'Config - Mappings'!$J$4</f>
-        <v>JITTP Version 1</v>
-      </c>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
       <c r="L3" s="3"/>
       <c r="M3" s="3"/>
       <c r="N3" s="3"/>
@@ -3097,9 +3940,9 @@
       <c r="S3" s="3"/>
       <c r="T3" s="3"/>
       <c r="U3" s="3"/>
-      <c r="V3" s="3">
+      <c r="V3" s="3" t="str">
         <f>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",IFERROR(VLOOKUP(JiraDataset[[#This Row],[Sprint Name]], CfgSprints[], 2, FALSE), ""))</f>
-        <v>97</v>
+        <v/>
       </c>
       <c r="W3" s="3" t="str">
         <f>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",_xlfn.XLOOKUP("Creation Marker", CfgMisc[Name], CfgMisc[Value],"",1))</f>
@@ -3115,7 +3958,7 @@
       </c>
       <c r="Z3" s="3" t="str">
         <f>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",IFERROR(VLOOKUP(JiraDataset[[#This Row],[Team.Name]], CfgTeams[], 2, FALSE), ""))</f>
-        <v>712020:09876543212345678902</v>
+        <v/>
       </c>
       <c r="AA3" s="3" t="str">
         <f>IF(JiraDataset[[#This Row],[RowType]]=cfg_type_skip,"",_xlfn.XLOOKUP("jira.project.key", CfgBasic[Name], CfgBasic[Value]))</f>
@@ -3153,7 +3996,7 @@
     </row>
   </sheetData>
   <protectedRanges>
-    <protectedRange sqref="A1:A1048576 L4:L1048576 C1:E2 D3:E1048576 F1:J3 G4:J1048576 K1:U2 Q4:Z1048576 K3:W3 N4:O1048576" name="User Input"/>
+    <protectedRange sqref="L4:L1048576 C1:E2 F1:J3 G4:J1048576 K1:U2 Q4:Z1048576 K3:W3 N4:O1048576 A1:A1048576 D3:E1048576" name="User Input"/>
     <protectedRange algorithmName="SHA-512" hashValue="tpheD+JLADkhiyalt6vInlMwkILPZx4PVQN/k2vmwjOBdYUuHaXCrwtObHeFz5dJh9f853O84pZ1Rn9Ujz33+A==" saltValue="9ir5NB4CJc/69S/Eh84/mA==" spinCount="100000" sqref="V1:AC2 X3:AE3 AA4:AH1048576" name="Computed values"/>
   </protectedRanges>
   <phoneticPr fontId="18" type="noConversion"/>
@@ -3219,7 +4062,7 @@
       <formula>LEN(TRIM(L2))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations xWindow="1573" yWindow="665" count="22">
+  <dataValidations xWindow="1573" yWindow="665" count="23">
     <dataValidation type="whole" allowBlank="1" showErrorMessage="1" prompt="It must be a number (integer). This reference is only used during the import process." sqref="L2:M2" xr:uid="{005E18F2-4447-4781-8F18-5A58920A4F75}">
       <formula1>1</formula1>
       <formula2>1000</formula2>
@@ -3250,24 +4093,24 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Issue Type" sqref="B2:B3" xr:uid="{28BF52BF-C0B0-4D22-B02F-F1408D5A055B}">
       <formula1>INDIRECT("CfgIssueTypeList")</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="must be a valid fixversion" sqref="K2:K3" xr:uid="{7708D6E2-1D6B-41D8-A9EE-0E87219BA8EA}">
-      <formula1>INDIRECT("CfgFixVersions[FixVersion.Name]")</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A3" xr:uid="{5EEBB8D5-878D-4D0E-9267-0919B5A1B925}">
       <formula1>INDIRECT("CfgPriorities[Priority.Name]")</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="must be a valid component" sqref="H2:I3" xr:uid="{A5F34B19-946D-4921-8173-A4364233D328}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="must be a valid component" sqref="I2:I3" xr:uid="{A5F34B19-946D-4921-8173-A4364233D328}">
       <formula1>INDIRECT("CfgTeams[Team.Name]")</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="must be a valid component" sqref="J2:K3" xr:uid="{A898E2E7-BC45-4B88-BA1E-4AAA377361D4}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="must be a valid component" sqref="J2:J3" xr:uid="{A898E2E7-BC45-4B88-BA1E-4AAA377361D4}">
       <formula1>INDIRECT("CfgSprints[Sprint.Name]")</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" error="must be a valid component" sqref="H2:H3" xr:uid="{7B68C246-CBB3-46A9-A050-68D1E898B8E3}">
+      <formula1>INDIRECT("CfgTeams[Team.Name]")</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K3" xr:uid="{C49FC18E-7E95-4F52-B450-E61F830A5C7D}">
+      <formula1>INDIRECT("CfgFixVersions[FixVersion.Name]")</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
-  <ignoredErrors>
-    <ignoredError sqref="K2" calculatedColumn="1"/>
-  </ignoredErrors>
   <legacyDrawing r:id="rId2"/>
   <tableParts count="1">
     <tablePart r:id="rId3"/>
@@ -4291,12 +5134,12 @@
       <c r="A2" s="19"/>
       <c r="B2" s="19"/>
       <c r="C2" s="8"/>
-      <c r="E2" s="21" t="s">
+      <c r="E2" s="20" t="s">
         <v>198</v>
       </c>
-      <c r="F2" s="21"/>
-      <c r="G2" s="21"/>
-      <c r="H2" s="21"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
@@ -4546,13 +5389,13 @@
       <c r="G13" s="18"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C14" s="20" t="s">
+      <c r="C14" s="21" t="s">
         <v>164</v>
       </c>
-      <c r="D14" s="20"/>
-      <c r="E14" s="20"/>
-      <c r="F14" s="20"/>
-      <c r="G14" s="20"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="21"/>
+      <c r="F14" s="21"/>
+      <c r="G14" s="21"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C15" t="str" cm="1">
